--- a/ข้อมูลครุภัณฑ์/Template_Items_and_Assets_v3.xlsx
+++ b/ข้อมูลครุภัณฑ์/Template_Items_and_Assets_v3.xlsx
@@ -4689,19 +4689,19 @@
         <v>1</v>
       </c>
       <c r="G123">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="H123" t="str">
-        <v>2025-08-19</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I123" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J123" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR (CPR-B)</v>
+        <v>กระดานรองสำหรับช่วยฟื้นคืนชีพ</v>
       </c>
       <c r="K123" t="str">
-        <v>1-B9701-FN17-65450010002/001-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (42-1/1)</v>
       </c>
     </row>
     <row r="124">
@@ -4736,7 +4736,7 @@
         <v>กระดานรองหลังผู้ป่วยสำหรับ CPR (CPR-B)</v>
       </c>
       <c r="K124" t="str">
-        <v>1-B9701-FN17-65450010002/002-68</v>
+        <v>1-B9701-FN17-65450010002/001-68</v>
       </c>
     </row>
     <row r="125">
@@ -4771,21 +4771,21 @@
         <v>กระดานรองหลังผู้ป่วยสำหรับ CPR (CPR-B)</v>
       </c>
       <c r="K125" t="str">
-        <v>1-B9701-FN17-65450010002/003-68</v>
+        <v>1-B9701-FN17-65450010002/002-68</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="B126" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-TRS-0004</v>
       </c>
       <c r="C126" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D126" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="E126" t="str">
         <v>แผ่น</v>
@@ -4794,7 +4794,7 @@
         <v>1</v>
       </c>
       <c r="G126">
-        <v>4700</v>
+        <v>1000</v>
       </c>
       <c r="H126" t="str">
         <v>2025-08-19</v>
@@ -4803,10 +4803,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J126" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR (CPR-B)</v>
       </c>
       <c r="K126" t="str">
-        <v>1-B9701-FN17-65450010002/004-68</v>
+        <v>1-B9701-FN17-65450010002/003-68</v>
       </c>
     </row>
     <row r="127">
@@ -4814,7 +4814,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B127" t="str">
-        <v>EQ-STI-0025</v>
+        <v>EQ-STI-0024</v>
       </c>
       <c r="C127" t="str">
         <v>EQUIPMENT</v>
@@ -4841,7 +4841,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K127" t="str">
-        <v>1-B9701-FN17-65450010002/005-68</v>
+        <v>1-B9701-FN17-65450010002/004-68</v>
       </c>
     </row>
     <row r="128">
@@ -4849,7 +4849,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B128" t="str">
-        <v>EQ-STI-0026</v>
+        <v>EQ-STI-0025</v>
       </c>
       <c r="C128" t="str">
         <v>EQUIPMENT</v>
@@ -4876,7 +4876,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K128" t="str">
-        <v>1-B9701-FN17-65450010002/006-68</v>
+        <v>1-B9701-FN17-65450010002/005-68</v>
       </c>
     </row>
     <row r="129">
@@ -4884,7 +4884,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B129" t="str">
-        <v>EQ-STI-0027</v>
+        <v>EQ-STI-0026</v>
       </c>
       <c r="C129" t="str">
         <v>EQUIPMENT</v>
@@ -4911,7 +4911,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K129" t="str">
-        <v>1-B9701-FN17-65450010002/007-68</v>
+        <v>1-B9701-FN17-65450010002/006-68</v>
       </c>
     </row>
     <row r="130">
@@ -4919,7 +4919,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B130" t="str">
-        <v>EQ-STI-0028</v>
+        <v>EQ-STI-0027</v>
       </c>
       <c r="C130" t="str">
         <v>EQUIPMENT</v>
@@ -4946,7 +4946,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K130" t="str">
-        <v>1-B9701-FN17-65450010002/008-68</v>
+        <v>1-B9701-FN17-65450010002/007-68</v>
       </c>
     </row>
     <row r="131">
@@ -4954,7 +4954,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B131" t="str">
-        <v>EQ-STI-0029</v>
+        <v>EQ-STI-0028</v>
       </c>
       <c r="C131" t="str">
         <v>EQUIPMENT</v>
@@ -4981,7 +4981,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K131" t="str">
-        <v>1-B9701-FN17-65450010002/009-68</v>
+        <v>1-B9701-FN17-65450010002/008-68</v>
       </c>
     </row>
     <row r="132">
@@ -4989,7 +4989,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B132" t="str">
-        <v>EQ-STI-0030</v>
+        <v>EQ-STI-0029</v>
       </c>
       <c r="C132" t="str">
         <v>EQUIPMENT</v>
@@ -5016,7 +5016,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K132" t="str">
-        <v>1-B9701-FN17-65450010002/010-68</v>
+        <v>1-B9701-FN17-65450010002/009-68</v>
       </c>
     </row>
     <row r="133">
@@ -5024,7 +5024,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B133" t="str">
-        <v>EQ-STI-0031</v>
+        <v>EQ-STI-0030</v>
       </c>
       <c r="C133" t="str">
         <v>EQUIPMENT</v>
@@ -5051,7 +5051,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K133" t="str">
-        <v>1-B9701-FN17-65450010002/011-68</v>
+        <v>1-B9701-FN17-65450010002/010-68</v>
       </c>
     </row>
     <row r="134">
@@ -5059,7 +5059,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B134" t="str">
-        <v>EQ-STI-0032</v>
+        <v>EQ-STI-0031</v>
       </c>
       <c r="C134" t="str">
         <v>EQUIPMENT</v>
@@ -5086,7 +5086,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K134" t="str">
-        <v>1-B9701-FN17-65450010002/012-68</v>
+        <v>1-B9701-FN17-65450010002/011-68</v>
       </c>
     </row>
     <row r="135">
@@ -5094,7 +5094,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B135" t="str">
-        <v>EQ-STI-0033</v>
+        <v>EQ-STI-0032</v>
       </c>
       <c r="C135" t="str">
         <v>EQUIPMENT</v>
@@ -5121,7 +5121,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K135" t="str">
-        <v>1-B9701-FN17-65450010002/013-68</v>
+        <v>1-B9701-FN17-65450010002/012-68</v>
       </c>
     </row>
     <row r="136">
@@ -5129,7 +5129,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B136" t="str">
-        <v>EQ-STI-0034</v>
+        <v>EQ-STI-0033</v>
       </c>
       <c r="C136" t="str">
         <v>EQUIPMENT</v>
@@ -5156,7 +5156,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K136" t="str">
-        <v>1-B9701-FN17-65450010002/014-68</v>
+        <v>1-B9701-FN17-65450010002/013-68</v>
       </c>
     </row>
     <row r="137">
@@ -5164,7 +5164,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B137" t="str">
-        <v>EQ-STI-0035</v>
+        <v>EQ-STI-0034</v>
       </c>
       <c r="C137" t="str">
         <v>EQUIPMENT</v>
@@ -5191,7 +5191,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K137" t="str">
-        <v>1-B9701-FN17-65450010002/015-68</v>
+        <v>1-B9701-FN17-65450010002/014-68</v>
       </c>
     </row>
     <row r="138">
@@ -5199,7 +5199,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B138" t="str">
-        <v>EQ-STI-0036</v>
+        <v>EQ-STI-0035</v>
       </c>
       <c r="C138" t="str">
         <v>EQUIPMENT</v>
@@ -5226,7 +5226,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K138" t="str">
-        <v>1-B9701-FN17-65450010002/016-68</v>
+        <v>1-B9701-FN17-65450010002/015-68</v>
       </c>
     </row>
     <row r="139">
@@ -5234,7 +5234,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B139" t="str">
-        <v>EQ-STI-0037</v>
+        <v>EQ-STI-0036</v>
       </c>
       <c r="C139" t="str">
         <v>EQUIPMENT</v>
@@ -5261,7 +5261,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K139" t="str">
-        <v>1-B9701-FN17-65450010002/017-68</v>
+        <v>1-B9701-FN17-65450010002/016-68</v>
       </c>
     </row>
     <row r="140">
@@ -5269,7 +5269,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B140" t="str">
-        <v>EQ-STI-0038</v>
+        <v>EQ-STI-0037</v>
       </c>
       <c r="C140" t="str">
         <v>EQUIPMENT</v>
@@ -5296,7 +5296,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K140" t="str">
-        <v>1-B9701-FN17-65450010002/018-68</v>
+        <v>1-B9701-FN17-65450010002/017-68</v>
       </c>
     </row>
     <row r="141">
@@ -5304,7 +5304,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B141" t="str">
-        <v>EQ-STI-0039</v>
+        <v>EQ-STI-0038</v>
       </c>
       <c r="C141" t="str">
         <v>EQUIPMENT</v>
@@ -5331,7 +5331,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K141" t="str">
-        <v>1-B9701-FN17-65450010002/019-68</v>
+        <v>1-B9701-FN17-65450010002/018-68</v>
       </c>
     </row>
     <row r="142">
@@ -5339,7 +5339,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B142" t="str">
-        <v>EQ-STI-0040</v>
+        <v>EQ-STI-0039</v>
       </c>
       <c r="C142" t="str">
         <v>EQUIPMENT</v>
@@ -5366,7 +5366,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K142" t="str">
-        <v>1-B9701-FN17-65450010002/020-68</v>
+        <v>1-B9701-FN17-65450010002/019-68</v>
       </c>
     </row>
     <row r="143">
@@ -5374,7 +5374,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B143" t="str">
-        <v>EQ-STI-0041</v>
+        <v>EQ-STI-0040</v>
       </c>
       <c r="C143" t="str">
         <v>EQUIPMENT</v>
@@ -5401,7 +5401,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K143" t="str">
-        <v>1-B9701-FN17-65450010002/021-68</v>
+        <v>1-B9701-FN17-65450010002/020-68</v>
       </c>
     </row>
     <row r="144">
@@ -5409,7 +5409,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B144" t="str">
-        <v>EQ-STI-0042</v>
+        <v>EQ-STI-0041</v>
       </c>
       <c r="C144" t="str">
         <v>EQUIPMENT</v>
@@ -5436,7 +5436,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K144" t="str">
-        <v>1-B9701-FN17-65450010002/022-68</v>
+        <v>1-B9701-FN17-65450010002/021-68</v>
       </c>
     </row>
     <row r="145">
@@ -5444,7 +5444,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B145" t="str">
-        <v>EQ-STI-0043</v>
+        <v>EQ-STI-0042</v>
       </c>
       <c r="C145" t="str">
         <v>EQUIPMENT</v>
@@ -5471,30 +5471,30 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K145" t="str">
-        <v>1-B9701-FN17-65450010002/023-68</v>
+        <v>1-B9701-FN17-65450010002/022-68</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>แทบเล็ตสำหรับหุ่น AI</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B146" t="str">
-        <v>EQ-AI-0003</v>
+        <v>EQ-STI-0043</v>
       </c>
       <c r="C146" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D146" t="str">
-        <v>(หุ่น AI) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E146" t="str">
-        <v>ชุด</v>
+        <v>แผ่น</v>
       </c>
       <c r="F146">
         <v>1</v>
       </c>
       <c r="G146">
-        <v>5000</v>
+        <v>4700</v>
       </c>
       <c r="H146" t="str">
         <v>2025-08-19</v>
@@ -5503,10 +5503,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J146" t="str">
-        <v>แทบเล็ตสำหรับหุ่น AI (i-pad-alex)</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K146" t="str">
-        <v>1-B9701-FN18-74400010005/001-68</v>
+        <v>1-B9701-FN17-65450010002/023-68</v>
       </c>
     </row>
     <row r="147">
@@ -5514,7 +5514,7 @@
         <v>แทบเล็ตสำหรับหุ่น AI</v>
       </c>
       <c r="B147" t="str">
-        <v>EQ-AI-0004</v>
+        <v>EQ-AI-0003</v>
       </c>
       <c r="C147" t="str">
         <v>EQUIPMENT</v>
@@ -5541,30 +5541,30 @@
         <v>แทบเล็ตสำหรับหุ่น AI (i-pad-alex)</v>
       </c>
       <c r="K147" t="str">
-        <v>1-B9701-FN18-74400010005/002-68</v>
+        <v>1-B9701-FN18-74400010005/001-68</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Android tablet</v>
+        <v>แทบเล็ตสำหรับหุ่น AI</v>
       </c>
       <c r="B148" t="str">
-        <v>EQ-IT-0005</v>
+        <v>EQ-AI-0004</v>
       </c>
       <c r="C148" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D148" t="str">
-        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
+        <v>(หุ่น AI) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E148" t="str">
-        <v>เครื่อง</v>
+        <v>ชุด</v>
       </c>
       <c r="F148">
         <v>1</v>
       </c>
       <c r="G148">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="H148" t="str">
         <v>2025-08-19</v>
@@ -5573,10 +5573,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J148" t="str">
-        <v>Android tablet (AD-Tablet)</v>
+        <v>แทบเล็ตสำหรับหุ่น AI (i-pad-alex)</v>
       </c>
       <c r="K148" t="str">
-        <v>1-B9701-FN18-74400010005/003-68</v>
+        <v>1-B9701-FN18-74400010005/002-68</v>
       </c>
     </row>
     <row r="149">
@@ -5584,7 +5584,7 @@
         <v>Android tablet</v>
       </c>
       <c r="B149" t="str">
-        <v>EQ-IT-0006</v>
+        <v>EQ-IT-0005</v>
       </c>
       <c r="C149" t="str">
         <v>EQUIPMENT</v>
@@ -5611,7 +5611,7 @@
         <v>Android tablet (AD-Tablet)</v>
       </c>
       <c r="K149" t="str">
-        <v>1-B9701-FN18-74400010005/004-68</v>
+        <v>1-B9701-FN18-74400010005/003-68</v>
       </c>
     </row>
     <row r="150">
@@ -5619,7 +5619,7 @@
         <v>Android tablet</v>
       </c>
       <c r="B150" t="str">
-        <v>EQ-IT-0007</v>
+        <v>EQ-IT-0006</v>
       </c>
       <c r="C150" t="str">
         <v>EQUIPMENT</v>
@@ -5646,21 +5646,21 @@
         <v>Android tablet (AD-Tablet)</v>
       </c>
       <c r="K150" t="str">
-        <v>1-B9701-FN18-74400010005/005-68</v>
+        <v>1-B9701-FN18-74400010005/004-68</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>เครื่องสำรองไฟ (BI)</v>
+        <v>Android tablet</v>
       </c>
       <c r="B151" t="str">
-        <v>EQ-BI-0002</v>
+        <v>EQ-IT-0007</v>
       </c>
       <c r="C151" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D151" t="str">
-        <v>เครื่องจำลองสถานการณ์ (BI)</v>
+        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
       </c>
       <c r="E151" t="str">
         <v>เครื่อง</v>
@@ -5669,7 +5669,7 @@
         <v>1</v>
       </c>
       <c r="G151">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="H151" t="str">
         <v>2025-08-19</v>
@@ -5678,10 +5678,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J151" t="str">
-        <v>เครื่องสำรองไฟที่สามารถรองรับการไฟดับได้อย่างน้อย 15 นาที (UPS 1200W)</v>
+        <v>Android tablet (AD-Tablet)</v>
       </c>
       <c r="K151" t="str">
-        <v>1-B9701-FN18-74400090003/001-68</v>
+        <v>1-B9701-FN18-74400010005/005-68</v>
       </c>
     </row>
     <row r="152">
@@ -5689,7 +5689,7 @@
         <v>เครื่องสำรองไฟ (BI)</v>
       </c>
       <c r="B152" t="str">
-        <v>EQ-BI-0003</v>
+        <v>EQ-BI-0002</v>
       </c>
       <c r="C152" t="str">
         <v>EQUIPMENT</v>
@@ -5716,21 +5716,21 @@
         <v>เครื่องสำรองไฟที่สามารถรองรับการไฟดับได้อย่างน้อย 15 นาที (UPS 1200W)</v>
       </c>
       <c r="K152" t="str">
-        <v>1-B9701-FN18-74400090003/002-68</v>
+        <v>1-B9701-FN18-74400090003/001-68</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>เครื่องพิมพ์</v>
+        <v>เครื่องสำรองไฟ (BI)</v>
       </c>
       <c r="B153" t="str">
-        <v>EQ-IT-0008</v>
+        <v>EQ-BI-0003</v>
       </c>
       <c r="C153" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D153" t="str">
-        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
+        <v>เครื่องจำลองสถานการณ์ (BI)</v>
       </c>
       <c r="E153" t="str">
         <v>เครื่อง</v>
@@ -5739,7 +5739,7 @@
         <v>1</v>
       </c>
       <c r="G153">
-        <v>1500</v>
+        <v>4000</v>
       </c>
       <c r="H153" t="str">
         <v>2025-08-19</v>
@@ -5748,10 +5748,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J153" t="str">
-        <v>เครื่องพิมพ์ (IM-PT-PERI)</v>
+        <v>เครื่องสำรองไฟที่สามารถรองรับการไฟดับได้อย่างน้อย 15 นาที (UPS 1200W)</v>
       </c>
       <c r="K153" t="str">
-        <v>1-B9701-FN18-74400120002/001-68</v>
+        <v>1-B9701-FN18-74400090003/002-68</v>
       </c>
     </row>
     <row r="154">
@@ -5759,7 +5759,7 @@
         <v>เครื่องพิมพ์</v>
       </c>
       <c r="B154" t="str">
-        <v>EQ-IT-0009</v>
+        <v>EQ-IT-0008</v>
       </c>
       <c r="C154" t="str">
         <v>EQUIPMENT</v>
@@ -5786,7 +5786,7 @@
         <v>เครื่องพิมพ์ (IM-PT-PERI)</v>
       </c>
       <c r="K154" t="str">
-        <v>1-B9701-FN18-74400120002/002-68</v>
+        <v>1-B9701-FN18-74400120002/001-68</v>
       </c>
     </row>
     <row r="155">
@@ -5794,7 +5794,7 @@
         <v>เครื่องพิมพ์</v>
       </c>
       <c r="B155" t="str">
-        <v>EQ-IT-0010</v>
+        <v>EQ-IT-0009</v>
       </c>
       <c r="C155" t="str">
         <v>EQUIPMENT</v>
@@ -5821,42 +5821,42 @@
         <v>เครื่องพิมพ์ (IM-PT-PERI)</v>
       </c>
       <c r="K155" t="str">
-        <v>1-B9701-FN18-74400120002/003-68</v>
+        <v>1-B9701-FN18-74400120002/002-68</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>เครื่องพิมพ์</v>
       </c>
       <c r="B156" t="str">
-        <v>EQ-FN-0001</v>
+        <v>EQ-IT-0010</v>
       </c>
       <c r="C156" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D156" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
       </c>
       <c r="E156" t="str">
-        <v>ตู้</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F156">
         <v>1</v>
       </c>
       <c r="G156">
-        <v>4500</v>
+        <v>1500</v>
       </c>
       <c r="H156" t="str">
-        <v>2024-08-01</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I156" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J156" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>เครื่องพิมพ์ (IM-PT-PERI)</v>
       </c>
       <c r="K156" t="str">
-        <v>2-B9701-FP05-71100150007/001-67</v>
+        <v>1-B9701-FN18-74400120002/003-68</v>
       </c>
     </row>
     <row r="157">
@@ -5864,7 +5864,7 @@
         <v>ตู้เก็บของ</v>
       </c>
       <c r="B157" t="str">
-        <v>EQ-FN-0002</v>
+        <v>EQ-FN-0001</v>
       </c>
       <c r="C157" t="str">
         <v>EQUIPMENT</v>
@@ -5891,7 +5891,7 @@
         <v>ตู้เก็บของ</v>
       </c>
       <c r="K157" t="str">
-        <v>2-B9701-FP05-71100150007/002-67</v>
+        <v>2-B9701-FP05-71100150007/001-67</v>
       </c>
     </row>
     <row r="158">
@@ -5899,7 +5899,7 @@
         <v>ตู้เก็บของ</v>
       </c>
       <c r="B158" t="str">
-        <v>EQ-FN-0003</v>
+        <v>EQ-FN-0002</v>
       </c>
       <c r="C158" t="str">
         <v>EQUIPMENT</v>
@@ -5926,7 +5926,7 @@
         <v>ตู้เก็บของ</v>
       </c>
       <c r="K158" t="str">
-        <v>2-B9701-FP05-71100150007/003-67</v>
+        <v>2-B9701-FP05-71100150007/002-67</v>
       </c>
     </row>
     <row r="159">
@@ -5934,7 +5934,7 @@
         <v>ตู้เก็บของ</v>
       </c>
       <c r="B159" t="str">
-        <v>EQ-FN-0004</v>
+        <v>EQ-FN-0003</v>
       </c>
       <c r="C159" t="str">
         <v>EQUIPMENT</v>
@@ -5961,7 +5961,7 @@
         <v>ตู้เก็บของ</v>
       </c>
       <c r="K159" t="str">
-        <v>2-B9701-FP05-71100150007/004-67</v>
+        <v>2-B9701-FP05-71100150007/003-67</v>
       </c>
     </row>
     <row r="160">
@@ -5969,7 +5969,7 @@
         <v>ตู้เก็บของ</v>
       </c>
       <c r="B160" t="str">
-        <v>EQ-FN-0005</v>
+        <v>EQ-FN-0004</v>
       </c>
       <c r="C160" t="str">
         <v>EQUIPMENT</v>
@@ -5990,13 +5990,13 @@
         <v>2024-08-01</v>
       </c>
       <c r="I160" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 2</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
       </c>
       <c r="J160" t="str">
         <v>ตู้เก็บของ</v>
       </c>
       <c r="K160" t="str">
-        <v>2-B9701-FP05-71100150007/005-67</v>
+        <v>2-B9701-FP05-71100150007/004-67</v>
       </c>
     </row>
     <row r="161">
@@ -6004,7 +6004,7 @@
         <v>ตู้เก็บของ</v>
       </c>
       <c r="B161" t="str">
-        <v>EQ-FN-0006</v>
+        <v>EQ-FN-0005</v>
       </c>
       <c r="C161" t="str">
         <v>EQUIPMENT</v>
@@ -6025,13 +6025,13 @@
         <v>2024-08-01</v>
       </c>
       <c r="I161" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 2</v>
       </c>
       <c r="J161" t="str">
         <v>ตู้เก็บของ</v>
       </c>
       <c r="K161" t="str">
-        <v>2-B9701-FP05-71100150007/006-67</v>
+        <v>2-B9701-FP05-71100150007/005-67</v>
       </c>
     </row>
     <row r="162">
@@ -6039,7 +6039,7 @@
         <v>ตู้เก็บของ</v>
       </c>
       <c r="B162" t="str">
-        <v>EQ-FN-0007</v>
+        <v>EQ-FN-0006</v>
       </c>
       <c r="C162" t="str">
         <v>EQUIPMENT</v>
@@ -6066,42 +6066,42 @@
         <v>ตู้เก็บของ</v>
       </c>
       <c r="K162" t="str">
-        <v>2-B9701-FP05-71100150007/007-67</v>
+        <v>2-B9701-FP05-71100150007/006-67</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>ชั้นวางของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="B163" t="str">
-        <v>EQ-FN-0008</v>
+        <v>EQ-FN-0007</v>
       </c>
       <c r="C163" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D163" t="str">
-        <v>ชั้นเก็บของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="E163" t="str">
-        <v>ชั้น</v>
+        <v>ตู้</v>
       </c>
       <c r="F163">
         <v>1</v>
       </c>
       <c r="G163">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="H163" t="str">
         <v>2024-08-01</v>
       </c>
       <c r="I163" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
       </c>
       <c r="J163" t="str">
-        <v>ชั้นวางของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="K163" t="str">
-        <v>2-B9701-FP05-73300160001/001-67</v>
+        <v>2-B9701-FP05-71100150007/007-67</v>
       </c>
     </row>
     <row r="164">
@@ -6109,7 +6109,7 @@
         <v>ชั้นวางของ</v>
       </c>
       <c r="B164" t="str">
-        <v>EQ-FN-0009</v>
+        <v>EQ-FN-0008</v>
       </c>
       <c r="C164" t="str">
         <v>EQUIPMENT</v>
@@ -6136,7 +6136,7 @@
         <v>ชั้นวางของ</v>
       </c>
       <c r="K164" t="str">
-        <v>2-B9701-FP05-73300160001/002-67</v>
+        <v>2-B9701-FP05-73300160001/001-67</v>
       </c>
     </row>
     <row r="165">
@@ -6144,7 +6144,7 @@
         <v>ชั้นวางของ</v>
       </c>
       <c r="B165" t="str">
-        <v>EQ-FN-0010</v>
+        <v>EQ-FN-0009</v>
       </c>
       <c r="C165" t="str">
         <v>EQUIPMENT</v>
@@ -6171,7 +6171,7 @@
         <v>ชั้นวางของ</v>
       </c>
       <c r="K165" t="str">
-        <v>2-B9701-FP05-73300160001/003-67</v>
+        <v>2-B9701-FP05-73300160001/002-67</v>
       </c>
     </row>
     <row r="166">
@@ -6179,7 +6179,7 @@
         <v>ชั้นวางของ</v>
       </c>
       <c r="B166" t="str">
-        <v>EQ-FN-0011</v>
+        <v>EQ-FN-0010</v>
       </c>
       <c r="C166" t="str">
         <v>EQUIPMENT</v>
@@ -6200,13 +6200,13 @@
         <v>2024-08-01</v>
       </c>
       <c r="I166" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 2</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
       </c>
       <c r="J166" t="str">
         <v>ชั้นวางของ</v>
       </c>
       <c r="K166" t="str">
-        <v>2-B9701-FP05-73300160001/004-67</v>
+        <v>2-B9701-FP05-73300160001/003-67</v>
       </c>
     </row>
     <row r="167">
@@ -6214,7 +6214,7 @@
         <v>ชั้นวางของ</v>
       </c>
       <c r="B167" t="str">
-        <v>EQ-FN-0012</v>
+        <v>EQ-FN-0011</v>
       </c>
       <c r="C167" t="str">
         <v>EQUIPMENT</v>
@@ -6235,13 +6235,13 @@
         <v>2024-08-01</v>
       </c>
       <c r="I167" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 2</v>
       </c>
       <c r="J167" t="str">
         <v>ชั้นวางของ</v>
       </c>
       <c r="K167" t="str">
-        <v>2-B9701-FP05-73300160001/005-67</v>
+        <v>2-B9701-FP05-73300160001/004-67</v>
       </c>
     </row>
     <row r="168">
@@ -6249,7 +6249,7 @@
         <v>ชั้นวางของ</v>
       </c>
       <c r="B168" t="str">
-        <v>EQ-FN-0013</v>
+        <v>EQ-FN-0012</v>
       </c>
       <c r="C168" t="str">
         <v>EQUIPMENT</v>
@@ -6276,7 +6276,7 @@
         <v>ชั้นวางของ</v>
       </c>
       <c r="K168" t="str">
-        <v>2-B9701-FP05-73300160001/006-67</v>
+        <v>2-B9701-FP05-73300160001/005-67</v>
       </c>
     </row>
     <row r="169">
@@ -6284,7 +6284,7 @@
         <v>ชั้นวางของ</v>
       </c>
       <c r="B169" t="str">
-        <v>EQ-FN-0014</v>
+        <v>EQ-FN-0013</v>
       </c>
       <c r="C169" t="str">
         <v>EQUIPMENT</v>
@@ -6305,48 +6305,48 @@
         <v>2024-08-01</v>
       </c>
       <c r="I169" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 5</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
       </c>
       <c r="J169" t="str">
         <v>ชั้นวางของ</v>
       </c>
       <c r="K169" t="str">
-        <v>2-B9701-FP05-73300160001/007-67</v>
+        <v>2-B9701-FP05-73300160001/006-67</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="B170" t="str">
-        <v>EQ-BED-0004</v>
+        <v>EQ-FN-0014</v>
       </c>
       <c r="C170" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D170" t="str">
-        <v>เตียงและตู้ข้างเตียง</v>
+        <v>ชั้นเก็บของ</v>
       </c>
       <c r="E170" t="str">
-        <v>หลัง</v>
+        <v>ชั้น</v>
       </c>
       <c r="F170">
         <v>1</v>
       </c>
       <c r="G170">
-        <v>70645</v>
+        <v>2500</v>
       </c>
       <c r="H170" t="str">
-        <v>2025-05-01</v>
+        <v>2024-08-01</v>
       </c>
       <c r="I170" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 5</v>
       </c>
       <c r="J170" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="K170" t="str">
-        <v>1-B9701-FT17-65300010001/001-68</v>
+        <v>2-B9701-FP05-73300160001/007-67</v>
       </c>
     </row>
     <row r="171">
@@ -6354,7 +6354,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B171" t="str">
-        <v>EQ-BED-0005</v>
+        <v>EQ-BED-0004</v>
       </c>
       <c r="C171" t="str">
         <v>EQUIPMENT</v>
@@ -6381,7 +6381,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K171" t="str">
-        <v>1-B9701-FT17-65300010001/002-68</v>
+        <v>1-B9701-FT17-65300010001/001-68</v>
       </c>
     </row>
     <row r="172">
@@ -6389,7 +6389,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B172" t="str">
-        <v>EQ-BED-0006</v>
+        <v>EQ-BED-0005</v>
       </c>
       <c r="C172" t="str">
         <v>EQUIPMENT</v>
@@ -6416,7 +6416,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K172" t="str">
-        <v>1-B9701-FT17-65300010001/003-68</v>
+        <v>1-B9701-FT17-65300010001/002-68</v>
       </c>
     </row>
     <row r="173">
@@ -6424,7 +6424,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B173" t="str">
-        <v>EQ-BED-0007</v>
+        <v>EQ-BED-0006</v>
       </c>
       <c r="C173" t="str">
         <v>EQUIPMENT</v>
@@ -6451,7 +6451,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K173" t="str">
-        <v>1-B9701-FT17-65300010001/004-68</v>
+        <v>1-B9701-FT17-65300010001/003-68</v>
       </c>
     </row>
     <row r="174">
@@ -6459,7 +6459,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B174" t="str">
-        <v>EQ-BED-0008</v>
+        <v>EQ-BED-0007</v>
       </c>
       <c r="C174" t="str">
         <v>EQUIPMENT</v>
@@ -6486,7 +6486,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K174" t="str">
-        <v>1-B9701-FT17-65300010001/005-68</v>
+        <v>1-B9701-FT17-65300010001/004-68</v>
       </c>
     </row>
     <row r="175">
@@ -6494,7 +6494,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B175" t="str">
-        <v>EQ-BED-0009</v>
+        <v>EQ-BED-0008</v>
       </c>
       <c r="C175" t="str">
         <v>EQUIPMENT</v>
@@ -6521,7 +6521,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K175" t="str">
-        <v>1-B9701-FT17-65300010001/006-68</v>
+        <v>1-B9701-FT17-65300010001/005-68</v>
       </c>
     </row>
     <row r="176">
@@ -6529,7 +6529,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B176" t="str">
-        <v>EQ-BED-0010</v>
+        <v>EQ-BED-0009</v>
       </c>
       <c r="C176" t="str">
         <v>EQUIPMENT</v>
@@ -6556,7 +6556,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K176" t="str">
-        <v>1-B9701-FT17-65300010001/007-68</v>
+        <v>1-B9701-FT17-65300010001/006-68</v>
       </c>
     </row>
     <row r="177">
@@ -6564,7 +6564,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B177" t="str">
-        <v>EQ-BED-0011</v>
+        <v>EQ-BED-0010</v>
       </c>
       <c r="C177" t="str">
         <v>EQUIPMENT</v>
@@ -6591,7 +6591,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K177" t="str">
-        <v>1-B9701-FT17-65300010001/008-68</v>
+        <v>1-B9701-FT17-65300010001/007-68</v>
       </c>
     </row>
     <row r="178">
@@ -6599,7 +6599,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B178" t="str">
-        <v>EQ-BED-0012</v>
+        <v>EQ-BED-0011</v>
       </c>
       <c r="C178" t="str">
         <v>EQUIPMENT</v>
@@ -6626,7 +6626,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K178" t="str">
-        <v>1-B9701-FT17-65300010001/009-68</v>
+        <v>1-B9701-FT17-65300010001/008-68</v>
       </c>
     </row>
     <row r="179">
@@ -6634,7 +6634,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B179" t="str">
-        <v>EQ-BED-0013</v>
+        <v>EQ-BED-0012</v>
       </c>
       <c r="C179" t="str">
         <v>EQUIPMENT</v>
@@ -6661,7 +6661,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K179" t="str">
-        <v>1-B9701-FT17-65300010001/010-68</v>
+        <v>1-B9701-FT17-65300010001/009-68</v>
       </c>
     </row>
     <row r="180">
@@ -6669,7 +6669,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B180" t="str">
-        <v>EQ-BED-0014</v>
+        <v>EQ-BED-0013</v>
       </c>
       <c r="C180" t="str">
         <v>EQUIPMENT</v>
@@ -6696,7 +6696,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K180" t="str">
-        <v>1-B9701-FT17-65300010001/011-68</v>
+        <v>1-B9701-FT17-65300010001/010-68</v>
       </c>
     </row>
     <row r="181">
@@ -6704,7 +6704,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B181" t="str">
-        <v>EQ-BED-0015</v>
+        <v>EQ-BED-0014</v>
       </c>
       <c r="C181" t="str">
         <v>EQUIPMENT</v>
@@ -6731,7 +6731,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K181" t="str">
-        <v>1-B9701-FT17-65300010001/012-68</v>
+        <v>1-B9701-FT17-65300010001/011-68</v>
       </c>
     </row>
     <row r="182">
@@ -6739,7 +6739,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B182" t="str">
-        <v>EQ-BED-0016</v>
+        <v>EQ-BED-0015</v>
       </c>
       <c r="C182" t="str">
         <v>EQUIPMENT</v>
@@ -6766,7 +6766,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K182" t="str">
-        <v>1-B9701-FT17-65300010001/013-68</v>
+        <v>1-B9701-FT17-65300010001/012-68</v>
       </c>
     </row>
     <row r="183">
@@ -6774,7 +6774,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B183" t="str">
-        <v>EQ-BED-0017</v>
+        <v>EQ-BED-0016</v>
       </c>
       <c r="C183" t="str">
         <v>EQUIPMENT</v>
@@ -6801,7 +6801,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K183" t="str">
-        <v>1-B9701-FT17-65300010001/014-68</v>
+        <v>1-B9701-FT17-65300010001/013-68</v>
       </c>
     </row>
     <row r="184">
@@ -6809,7 +6809,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B184" t="str">
-        <v>EQ-BED-0018</v>
+        <v>EQ-BED-0017</v>
       </c>
       <c r="C184" t="str">
         <v>EQUIPMENT</v>
@@ -6836,7 +6836,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K184" t="str">
-        <v>1-B9701-FT17-65300010001/015-68</v>
+        <v>1-B9701-FT17-65300010001/014-68</v>
       </c>
     </row>
     <row r="185">
@@ -6844,7 +6844,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B185" t="str">
-        <v>EQ-BED-0019</v>
+        <v>EQ-BED-0018</v>
       </c>
       <c r="C185" t="str">
         <v>EQUIPMENT</v>
@@ -6871,7 +6871,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K185" t="str">
-        <v>1-B9701-FT17-65300010001/016-68</v>
+        <v>1-B9701-FT17-65300010001/015-68</v>
       </c>
     </row>
     <row r="186">
@@ -6879,7 +6879,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B186" t="str">
-        <v>EQ-BED-0020</v>
+        <v>EQ-BED-0019</v>
       </c>
       <c r="C186" t="str">
         <v>EQUIPMENT</v>
@@ -6906,7 +6906,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K186" t="str">
-        <v>1-B9701-FT17-65300010001/017-68</v>
+        <v>1-B9701-FT17-65300010001/016-68</v>
       </c>
     </row>
     <row r="187">
@@ -6914,7 +6914,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B187" t="str">
-        <v>EQ-BED-0021</v>
+        <v>EQ-BED-0020</v>
       </c>
       <c r="C187" t="str">
         <v>EQUIPMENT</v>
@@ -6941,7 +6941,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K187" t="str">
-        <v>1-B9701-FT17-65300010001/018-68</v>
+        <v>1-B9701-FT17-65300010001/017-68</v>
       </c>
     </row>
     <row r="188">
@@ -6949,7 +6949,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B188" t="str">
-        <v>EQ-BED-0022</v>
+        <v>EQ-BED-0021</v>
       </c>
       <c r="C188" t="str">
         <v>EQUIPMENT</v>
@@ -6976,7 +6976,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K188" t="str">
-        <v>1-B9701-FT17-65300010001/019-68</v>
+        <v>1-B9701-FT17-65300010001/018-68</v>
       </c>
     </row>
     <row r="189">
@@ -6984,7 +6984,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B189" t="str">
-        <v>EQ-BED-0023</v>
+        <v>EQ-BED-0022</v>
       </c>
       <c r="C189" t="str">
         <v>EQUIPMENT</v>
@@ -7011,15 +7011,15 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K189" t="str">
-        <v>1-B9701-FT17-65300010001/020-68</v>
+        <v>1-B9701-FT17-65300010001/019-68</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 2 ไกร์ราวสไลด์ (เตียงใหญ่)</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B190" t="str">
-        <v>EQ-BED-0024</v>
+        <v>EQ-BED-0023</v>
       </c>
       <c r="C190" t="str">
         <v>EQUIPMENT</v>
@@ -7034,7 +7034,7 @@
         <v>1</v>
       </c>
       <c r="G190">
-        <v>64900</v>
+        <v>70645</v>
       </c>
       <c r="H190" t="str">
         <v>2025-05-01</v>
@@ -7043,33 +7043,33 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J190" t="str">
-        <v>เตียงเฟาว์เลอร์ 2 ไกร์ แบบดิจิตอล พร้อมที่นอน หมอน</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K190" t="str">
-        <v>1-B9701-FT17-65300010001/021-68</v>
+        <v>1-B9701-FT17-65300010001/020-68</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>เครื่องแสดงสัญญาณชีพ</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 2 ไกร์ราวสไลด์ (เตียงใหญ่)</v>
       </c>
       <c r="B191" t="str">
-        <v>EQ-SIM2-0001</v>
+        <v>EQ-BED-0024</v>
       </c>
       <c r="C191" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D191" t="str">
-        <v>(SIM MAN 2)ครุภัณฑ์การแพทย์และการพยาบาล</v>
+        <v>เตียงและตู้ข้างเตียง</v>
       </c>
       <c r="E191" t="str">
-        <v>เครื่อง</v>
+        <v>หลัง</v>
       </c>
       <c r="F191">
         <v>1</v>
       </c>
       <c r="G191">
-        <v>280000</v>
+        <v>64900</v>
       </c>
       <c r="H191" t="str">
         <v>2025-05-01</v>
@@ -7078,18 +7078,18 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J191" t="str">
-        <v>เครื่องแสดงสัญญาณชีพ</v>
+        <v>เตียงเฟาว์เลอร์ 2 ไกร์ แบบดิจิตอล พร้อมที่นอน หมอน</v>
       </c>
       <c r="K191" t="str">
-        <v>1-B9701-FT17-65450010002/001-68</v>
+        <v>1-B9701-FT17-65300010001/021-68</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>ชุดระบบบันทึกสถานการณ์การฝึกแบบเคลื่อนที่</v>
+        <v>เครื่องแสดงสัญญาณชีพ</v>
       </c>
       <c r="B192" t="str">
-        <v>EQ-SIM2-0002</v>
+        <v>EQ-SIM2-0001</v>
       </c>
       <c r="C192" t="str">
         <v>EQUIPMENT</v>
@@ -7098,13 +7098,13 @@
         <v>(SIM MAN 2)ครุภัณฑ์การแพทย์และการพยาบาล</v>
       </c>
       <c r="E192" t="str">
-        <v>ชุด</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F192">
         <v>1</v>
       </c>
       <c r="G192">
-        <v>1200000</v>
+        <v>280000</v>
       </c>
       <c r="H192" t="str">
         <v>2025-05-01</v>
@@ -7113,24 +7113,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J192" t="str">
-        <v>ชุดระบบบันทึกสถานการณ์การฝึกแบบเคลื่อนที่</v>
+        <v>เครื่องแสดงสัญญาณชีพ</v>
       </c>
       <c r="K192" t="str">
-        <v>1-B9701-FT17-65450010002/002-68</v>
+        <v>1-B9701-FT17-65450010002/001-68</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>ชุดระบบบันทึกสถานการณ์การฝึกแบบเคลื่อนที่</v>
       </c>
       <c r="B193" t="str">
-        <v>EQ-CPR-0004</v>
+        <v>EQ-SIM2-0002</v>
       </c>
       <c r="C193" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D193" t="str">
-        <v>หุ่นฝึก CPR</v>
+        <v>(SIM MAN 2)ครุภัณฑ์การแพทย์และการพยาบาล</v>
       </c>
       <c r="E193" t="str">
         <v>ชุด</v>
@@ -7139,7 +7139,7 @@
         <v>1</v>
       </c>
       <c r="G193">
-        <v>12500</v>
+        <v>1200000</v>
       </c>
       <c r="H193" t="str">
         <v>2025-05-01</v>
@@ -7148,10 +7148,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J193" t="str">
-        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>ชุดระบบบันทึกสถานการณ์การฝึกแบบเคลื่อนที่</v>
       </c>
       <c r="K193" t="str">
-        <v>1-B9701-FT17-65450010003/001-68</v>
+        <v>1-B9701-FT17-65450010002/002-68</v>
       </c>
     </row>
     <row r="194">
@@ -7159,7 +7159,7 @@
         <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B194" t="str">
-        <v>EQ-CPR-0005</v>
+        <v>EQ-CPR-0004</v>
       </c>
       <c r="C194" t="str">
         <v>EQUIPMENT</v>
@@ -7186,7 +7186,7 @@
         <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="K194" t="str">
-        <v>1-B9701-FT17-65450010003/002-68</v>
+        <v>1-B9701-FT17-65450010003/001-68</v>
       </c>
     </row>
     <row r="195">
@@ -7194,7 +7194,7 @@
         <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B195" t="str">
-        <v>EQ-CPR-0006</v>
+        <v>EQ-CPR-0005</v>
       </c>
       <c r="C195" t="str">
         <v>EQUIPMENT</v>
@@ -7221,7 +7221,7 @@
         <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="K195" t="str">
-        <v>1-B9701-FT17-65450010003/003-68</v>
+        <v>1-B9701-FT17-65450010003/002-68</v>
       </c>
     </row>
     <row r="196">
@@ -7229,7 +7229,7 @@
         <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B196" t="str">
-        <v>EQ-CPR-0007</v>
+        <v>EQ-CPR-0006</v>
       </c>
       <c r="C196" t="str">
         <v>EQUIPMENT</v>
@@ -7256,7 +7256,7 @@
         <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="K196" t="str">
-        <v>1-B9701-FT17-65450010003/004-68</v>
+        <v>1-B9701-FT17-65450010003/003-68</v>
       </c>
     </row>
     <row r="197">
@@ -7264,7 +7264,7 @@
         <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B197" t="str">
-        <v>EQ-CPR-0008</v>
+        <v>EQ-CPR-0007</v>
       </c>
       <c r="C197" t="str">
         <v>EQUIPMENT</v>
@@ -7291,21 +7291,21 @@
         <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="K197" t="str">
-        <v>1-B9701-FT17-65450010003/005-68</v>
+        <v>1-B9701-FT17-65450010003/004-68</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
+        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B198" t="str">
-        <v>EQ-URC-0011</v>
+        <v>EQ-CPR-0008</v>
       </c>
       <c r="C198" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D198" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>หุ่นฝึก CPR</v>
       </c>
       <c r="E198" t="str">
         <v>ชุด</v>
@@ -7314,7 +7314,7 @@
         <v>1</v>
       </c>
       <c r="G198">
-        <v>111100</v>
+        <v>12500</v>
       </c>
       <c r="H198" t="str">
         <v>2025-05-01</v>
@@ -7323,10 +7323,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J198" t="str">
-        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
+        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="K198" t="str">
-        <v>1-B9701-FT17-65450010004/001-68</v>
+        <v>1-B9701-FT17-65450010003/005-68</v>
       </c>
     </row>
     <row r="199">
@@ -7334,7 +7334,7 @@
         <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
       </c>
       <c r="B199" t="str">
-        <v>EQ-URC-0012</v>
+        <v>EQ-URC-0011</v>
       </c>
       <c r="C199" t="str">
         <v>EQUIPMENT</v>
@@ -7361,7 +7361,7 @@
         <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
       </c>
       <c r="K199" t="str">
-        <v>1-B9701-FT17-65450010004/002-68</v>
+        <v>1-B9701-FT17-65450010004/001-68</v>
       </c>
     </row>
     <row r="200">
@@ -7369,7 +7369,7 @@
         <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
       </c>
       <c r="B200" t="str">
-        <v>EQ-URC-0013</v>
+        <v>EQ-URC-0012</v>
       </c>
       <c r="C200" t="str">
         <v>EQUIPMENT</v>
@@ -7396,7 +7396,7 @@
         <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
       </c>
       <c r="K200" t="str">
-        <v>1-B9701-FT17-65450010004/003-68</v>
+        <v>1-B9701-FT17-65450010004/002-68</v>
       </c>
     </row>
     <row r="201">
@@ -7404,7 +7404,7 @@
         <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
       </c>
       <c r="B201" t="str">
-        <v>EQ-URC-0014</v>
+        <v>EQ-URC-0013</v>
       </c>
       <c r="C201" t="str">
         <v>EQUIPMENT</v>
@@ -7431,7 +7431,7 @@
         <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
       </c>
       <c r="K201" t="str">
-        <v>1-B9701-FT17-65450010004/004-68</v>
+        <v>1-B9701-FT17-65450010004/003-68</v>
       </c>
     </row>
     <row r="202">
@@ -7439,7 +7439,7 @@
         <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
       </c>
       <c r="B202" t="str">
-        <v>EQ-URC-0015</v>
+        <v>EQ-URC-0014</v>
       </c>
       <c r="C202" t="str">
         <v>EQUIPMENT</v>
@@ -7466,15 +7466,15 @@
         <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
       </c>
       <c r="K202" t="str">
-        <v>1-B9701-FT17-65450010004/005-68</v>
+        <v>1-B9701-FT17-65450010004/004-68</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
+        <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
       </c>
       <c r="B203" t="str">
-        <v>EQ-URC-0016</v>
+        <v>EQ-URC-0015</v>
       </c>
       <c r="C203" t="str">
         <v>EQUIPMENT</v>
@@ -7498,10 +7498,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J203" t="str">
-        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
+        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
       </c>
       <c r="K203" t="str">
-        <v>1-B9701-FT17-65450010004/006-68</v>
+        <v>1-B9701-FT17-65450010004/005-68</v>
       </c>
     </row>
     <row r="204">
@@ -7509,7 +7509,7 @@
         <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
       </c>
       <c r="B204" t="str">
-        <v>EQ-URC-0017</v>
+        <v>EQ-URC-0016</v>
       </c>
       <c r="C204" t="str">
         <v>EQUIPMENT</v>
@@ -7536,7 +7536,7 @@
         <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
       </c>
       <c r="K204" t="str">
-        <v>1-B9701-FT17-65450010004/007-68</v>
+        <v>1-B9701-FT17-65450010004/006-68</v>
       </c>
     </row>
     <row r="205">
@@ -7544,7 +7544,7 @@
         <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
       </c>
       <c r="B205" t="str">
-        <v>EQ-URC-0018</v>
+        <v>EQ-URC-0017</v>
       </c>
       <c r="C205" t="str">
         <v>EQUIPMENT</v>
@@ -7571,7 +7571,7 @@
         <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
       </c>
       <c r="K205" t="str">
-        <v>1-B9701-FT17-65450010004/008-68</v>
+        <v>1-B9701-FT17-65450010004/007-68</v>
       </c>
     </row>
     <row r="206">
@@ -7579,7 +7579,7 @@
         <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
       </c>
       <c r="B206" t="str">
-        <v>EQ-URC-0019</v>
+        <v>EQ-URC-0018</v>
       </c>
       <c r="C206" t="str">
         <v>EQUIPMENT</v>
@@ -7606,7 +7606,7 @@
         <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
       </c>
       <c r="K206" t="str">
-        <v>1-B9701-FT17-65450010004/009-68</v>
+        <v>1-B9701-FT17-65450010004/008-68</v>
       </c>
     </row>
     <row r="207">
@@ -7614,7 +7614,7 @@
         <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
       </c>
       <c r="B207" t="str">
-        <v>EQ-URC-0020</v>
+        <v>EQ-URC-0019</v>
       </c>
       <c r="C207" t="str">
         <v>EQUIPMENT</v>
@@ -7641,21 +7641,21 @@
         <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
       </c>
       <c r="K207" t="str">
-        <v>1-B9701-FT17-65450010004/010-68</v>
+        <v>1-B9701-FT17-65450010004/009-68</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
       </c>
       <c r="B208" t="str">
-        <v>EQ-NG-0006</v>
+        <v>EQ-URC-0020</v>
       </c>
       <c r="C208" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D208" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E208" t="str">
         <v>ชุด</v>
@@ -7664,7 +7664,7 @@
         <v>1</v>
       </c>
       <c r="G208">
-        <v>121330</v>
+        <v>111100</v>
       </c>
       <c r="H208" t="str">
         <v>2025-05-01</v>
@@ -7673,10 +7673,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J208" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
       </c>
       <c r="K208" t="str">
-        <v>1-B9701-FT17-65450010004/011-68</v>
+        <v>1-B9701-FT17-65450010004/010-68</v>
       </c>
     </row>
     <row r="209">
@@ -7684,7 +7684,7 @@
         <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="B209" t="str">
-        <v>EQ-NG-0007</v>
+        <v>EQ-NG-0006</v>
       </c>
       <c r="C209" t="str">
         <v>EQUIPMENT</v>
@@ -7711,7 +7711,7 @@
         <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="K209" t="str">
-        <v>1-B9701-FT17-65450010004/012-68</v>
+        <v>1-B9701-FT17-65450010004/011-68</v>
       </c>
     </row>
     <row r="210">
@@ -7719,7 +7719,7 @@
         <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="B210" t="str">
-        <v>EQ-NG-0008</v>
+        <v>EQ-NG-0007</v>
       </c>
       <c r="C210" t="str">
         <v>EQUIPMENT</v>
@@ -7746,7 +7746,7 @@
         <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="K210" t="str">
-        <v>1-B9701-FT17-65450010004/013-68</v>
+        <v>1-B9701-FT17-65450010004/012-68</v>
       </c>
     </row>
     <row r="211">
@@ -7754,7 +7754,7 @@
         <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="B211" t="str">
-        <v>EQ-NG-0009</v>
+        <v>EQ-NG-0008</v>
       </c>
       <c r="C211" t="str">
         <v>EQUIPMENT</v>
@@ -7781,7 +7781,7 @@
         <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="K211" t="str">
-        <v>1-B9701-FT17-65450010004/014-68</v>
+        <v>1-B9701-FT17-65450010004/013-68</v>
       </c>
     </row>
     <row r="212">
@@ -7789,7 +7789,7 @@
         <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="B212" t="str">
-        <v>EQ-NG-0010</v>
+        <v>EQ-NG-0009</v>
       </c>
       <c r="C212" t="str">
         <v>EQUIPMENT</v>
@@ -7816,21 +7816,21 @@
         <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="K212" t="str">
-        <v>1-B9701-FT17-65450010004/015-68</v>
+        <v>1-B9701-FT17-65450010004/014-68</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>หุ่นจำลองผู้ใหญ่</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="B213" t="str">
-        <v>EQ-FMS-0003</v>
+        <v>EQ-NG-0010</v>
       </c>
       <c r="C213" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D213" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="E213" t="str">
         <v>ชุด</v>
@@ -7839,7 +7839,7 @@
         <v>1</v>
       </c>
       <c r="G213">
-        <v>3920000</v>
+        <v>121330</v>
       </c>
       <c r="H213" t="str">
         <v>2025-05-01</v>
@@ -7848,24 +7848,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J213" t="str">
-        <v>หุ่นจำลองผู้ใหญ่</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="K213" t="str">
-        <v>1-B9701-FT17-65450010004/016-68</v>
+        <v>1-B9701-FT17-65450010004/015-68</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
+        <v>หุ่นจำลองผู้ใหญ่</v>
       </c>
       <c r="B214" t="str">
-        <v>EQ-IV-0001</v>
+        <v>EQ-FMS-0003</v>
       </c>
       <c r="C214" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D214" t="str">
-        <v>หุ่นฝึกฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E214" t="str">
         <v>ชุด</v>
@@ -7874,19 +7874,19 @@
         <v>1</v>
       </c>
       <c r="G214">
-        <v>40000</v>
+        <v>3920000</v>
       </c>
       <c r="H214" t="str">
-        <v>2024-06-28</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I214" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J214" t="str">
-        <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
+        <v>หุ่นจำลองผู้ใหญ่</v>
       </c>
       <c r="K214" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (11-1/4)</v>
+        <v>1-B9701-FT17-65450010004/016-68</v>
       </c>
     </row>
     <row r="215">
@@ -7894,7 +7894,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B215" t="str">
-        <v>EQ-IV-0002</v>
+        <v>EQ-IV-0001</v>
       </c>
       <c r="C215" t="str">
         <v>EQUIPMENT</v>
@@ -7921,7 +7921,7 @@
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K215" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (11-2/4)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (11-1/4)</v>
       </c>
     </row>
     <row r="216">
@@ -7929,7 +7929,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B216" t="str">
-        <v>EQ-IV-0003</v>
+        <v>EQ-IV-0002</v>
       </c>
       <c r="C216" t="str">
         <v>EQUIPMENT</v>
@@ -7956,7 +7956,7 @@
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K216" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (11-3/4)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (11-2/4)</v>
       </c>
     </row>
     <row r="217">
@@ -7964,7 +7964,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B217" t="str">
-        <v>EQ-IV-0004</v>
+        <v>EQ-IV-0003</v>
       </c>
       <c r="C217" t="str">
         <v>EQUIPMENT</v>
@@ -7991,7 +7991,7 @@
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K217" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (11-4/4)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (11-3/4)</v>
       </c>
     </row>
     <row r="218">
@@ -7999,7 +7999,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B218" t="str">
-        <v>EQ-IV-0005</v>
+        <v>EQ-IV-0004</v>
       </c>
       <c r="C218" t="str">
         <v>EQUIPMENT</v>
@@ -8014,19 +8014,19 @@
         <v>1</v>
       </c>
       <c r="G218">
-        <v>60100</v>
+        <v>40000</v>
       </c>
       <c r="H218" t="str">
-        <v>2025-05-01</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I218" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J218" t="str">
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K218" t="str">
-        <v>1-B9701-FT17-65450010004/017-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (11-4/4)</v>
       </c>
     </row>
     <row r="219">
@@ -8034,7 +8034,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B219" t="str">
-        <v>EQ-IV-0006</v>
+        <v>EQ-IV-0005</v>
       </c>
       <c r="C219" t="str">
         <v>EQUIPMENT</v>
@@ -8061,7 +8061,7 @@
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K219" t="str">
-        <v>1-B9701-FT17-65450010004/018-68</v>
+        <v>1-B9701-FT17-65450010004/017-68</v>
       </c>
     </row>
     <row r="220">
@@ -8069,7 +8069,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B220" t="str">
-        <v>EQ-IV-0007</v>
+        <v>EQ-IV-0006</v>
       </c>
       <c r="C220" t="str">
         <v>EQUIPMENT</v>
@@ -8096,7 +8096,7 @@
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K220" t="str">
-        <v>1-B9701-FT17-65450010004/019-68</v>
+        <v>1-B9701-FT17-65450010004/018-68</v>
       </c>
     </row>
     <row r="221">
@@ -8104,7 +8104,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B221" t="str">
-        <v>EQ-IV-0008</v>
+        <v>EQ-IV-0007</v>
       </c>
       <c r="C221" t="str">
         <v>EQUIPMENT</v>
@@ -8131,7 +8131,7 @@
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K221" t="str">
-        <v>1-B9701-FT17-65450010004/020-68</v>
+        <v>1-B9701-FT17-65450010004/019-68</v>
       </c>
     </row>
     <row r="222">
@@ -8139,7 +8139,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B222" t="str">
-        <v>EQ-IV-0009</v>
+        <v>EQ-IV-0008</v>
       </c>
       <c r="C222" t="str">
         <v>EQUIPMENT</v>
@@ -8166,7 +8166,7 @@
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K222" t="str">
-        <v>1-B9701-FT17-65450010004/021-68</v>
+        <v>1-B9701-FT17-65450010004/020-68</v>
       </c>
     </row>
     <row r="223">
@@ -8174,7 +8174,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B223" t="str">
-        <v>EQ-IV-0010</v>
+        <v>EQ-IV-0009</v>
       </c>
       <c r="C223" t="str">
         <v>EQUIPMENT</v>
@@ -8201,7 +8201,7 @@
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K223" t="str">
-        <v>1-B9701-FT17-65450010004/022-68</v>
+        <v>1-B9701-FT17-65450010004/021-68</v>
       </c>
     </row>
     <row r="224">
@@ -8209,7 +8209,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B224" t="str">
-        <v>EQ-IV-0011</v>
+        <v>EQ-IV-0010</v>
       </c>
       <c r="C224" t="str">
         <v>EQUIPMENT</v>
@@ -8236,21 +8236,21 @@
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K224" t="str">
-        <v>1-B9701-FT17-65450010004/023-68</v>
+        <v>1-B9701-FT17-65450010004/022-68</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
+        <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B225" t="str">
-        <v>EQ-STI-0044</v>
+        <v>EQ-IV-0011</v>
       </c>
       <c r="C225" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D225" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="E225" t="str">
         <v>ชุด</v>
@@ -8259,7 +8259,7 @@
         <v>1</v>
       </c>
       <c r="G225">
-        <v>54800</v>
+        <v>60100</v>
       </c>
       <c r="H225" t="str">
         <v>2025-05-01</v>
@@ -8268,10 +8268,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J225" t="str">
-        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
+        <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K225" t="str">
-        <v>1-B9701-FT17-65450010004/024-68</v>
+        <v>1-B9701-FT17-65450010004/023-68</v>
       </c>
     </row>
     <row r="226">
@@ -8279,7 +8279,7 @@
         <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="B226" t="str">
-        <v>EQ-STI-0045</v>
+        <v>EQ-STI-0044</v>
       </c>
       <c r="C226" t="str">
         <v>EQUIPMENT</v>
@@ -8306,7 +8306,7 @@
         <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="K226" t="str">
-        <v>1-B9701-FT17-65450010004/025-68</v>
+        <v>1-B9701-FT17-65450010004/024-68</v>
       </c>
     </row>
     <row r="227">
@@ -8314,7 +8314,7 @@
         <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="B227" t="str">
-        <v>EQ-STI-0046</v>
+        <v>EQ-STI-0045</v>
       </c>
       <c r="C227" t="str">
         <v>EQUIPMENT</v>
@@ -8341,7 +8341,7 @@
         <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="K227" t="str">
-        <v>1-B9701-FT17-65450010004/026-68</v>
+        <v>1-B9701-FT17-65450010004/025-68</v>
       </c>
     </row>
     <row r="228">
@@ -8349,7 +8349,7 @@
         <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="B228" t="str">
-        <v>EQ-STI-0047</v>
+        <v>EQ-STI-0046</v>
       </c>
       <c r="C228" t="str">
         <v>EQUIPMENT</v>
@@ -8376,7 +8376,7 @@
         <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="K228" t="str">
-        <v>1-B9701-FT17-65450010004/027-68</v>
+        <v>1-B9701-FT17-65450010004/026-68</v>
       </c>
     </row>
     <row r="229">
@@ -8384,7 +8384,7 @@
         <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="B229" t="str">
-        <v>EQ-STI-0048</v>
+        <v>EQ-STI-0047</v>
       </c>
       <c r="C229" t="str">
         <v>EQUIPMENT</v>
@@ -8411,21 +8411,21 @@
         <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="K229" t="str">
-        <v>1-B9701-FT17-65450010004/028-68</v>
+        <v>1-B9701-FT17-65450010004/027-68</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
+        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="B230" t="str">
-        <v>EQ-IM-0010</v>
+        <v>EQ-STI-0048</v>
       </c>
       <c r="C230" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D230" t="str">
-        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E230" t="str">
         <v>ชุด</v>
@@ -8434,7 +8434,7 @@
         <v>1</v>
       </c>
       <c r="G230">
-        <v>17900</v>
+        <v>54800</v>
       </c>
       <c r="H230" t="str">
         <v>2025-05-01</v>
@@ -8443,10 +8443,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J230" t="str">
-        <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
+        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="K230" t="str">
-        <v>1-B9701-FT17-65450010004/029-68</v>
+        <v>1-B9701-FT17-65450010004/028-68</v>
       </c>
     </row>
     <row r="231">
@@ -8454,7 +8454,7 @@
         <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
       </c>
       <c r="B231" t="str">
-        <v>EQ-IM-0011</v>
+        <v>EQ-IM-0010</v>
       </c>
       <c r="C231" t="str">
         <v>EQUIPMENT</v>
@@ -8481,7 +8481,7 @@
         <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
       </c>
       <c r="K231" t="str">
-        <v>1-B9701-FT17-65450010004/030-68</v>
+        <v>1-B9701-FT17-65450010004/029-68</v>
       </c>
     </row>
     <row r="232">
@@ -8489,7 +8489,7 @@
         <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
       </c>
       <c r="B232" t="str">
-        <v>EQ-IM-0012</v>
+        <v>EQ-IM-0011</v>
       </c>
       <c r="C232" t="str">
         <v>EQUIPMENT</v>
@@ -8516,7 +8516,7 @@
         <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
       </c>
       <c r="K232" t="str">
-        <v>1-B9701-FT17-65450010004/031-68</v>
+        <v>1-B9701-FT17-65450010004/030-68</v>
       </c>
     </row>
     <row r="233">
@@ -8524,7 +8524,7 @@
         <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
       </c>
       <c r="B233" t="str">
-        <v>EQ-IM-0013</v>
+        <v>EQ-IM-0012</v>
       </c>
       <c r="C233" t="str">
         <v>EQUIPMENT</v>
@@ -8551,7 +8551,7 @@
         <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
       </c>
       <c r="K233" t="str">
-        <v>1-B9701-FT17-65450010004/032-68</v>
+        <v>1-B9701-FT17-65450010004/031-68</v>
       </c>
     </row>
     <row r="234">
@@ -8559,7 +8559,7 @@
         <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
       </c>
       <c r="B234" t="str">
-        <v>EQ-IM-0014</v>
+        <v>EQ-IM-0013</v>
       </c>
       <c r="C234" t="str">
         <v>EQUIPMENT</v>
@@ -8586,21 +8586,21 @@
         <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
       </c>
       <c r="K234" t="str">
-        <v>1-B9701-FT17-65450010004/033-68</v>
+        <v>1-B9701-FT17-65450010004/032-68</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
+        <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
       </c>
       <c r="B235" t="str">
-        <v>EQ-FMS-0004</v>
+        <v>EQ-IM-0014</v>
       </c>
       <c r="C235" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D235" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
       </c>
       <c r="E235" t="str">
         <v>ชุด</v>
@@ -8609,7 +8609,7 @@
         <v>1</v>
       </c>
       <c r="G235">
-        <v>246500</v>
+        <v>17900</v>
       </c>
       <c r="H235" t="str">
         <v>2025-05-01</v>
@@ -8618,10 +8618,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J235" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
+        <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
       </c>
       <c r="K235" t="str">
-        <v>1-B9701-FT17-65450010004/034-68</v>
+        <v>1-B9701-FT17-65450010004/033-68</v>
       </c>
     </row>
     <row r="236">
@@ -8629,7 +8629,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
       </c>
       <c r="B236" t="str">
-        <v>EQ-FMS-0005</v>
+        <v>EQ-FMS-0004</v>
       </c>
       <c r="C236" t="str">
         <v>EQUIPMENT</v>
@@ -8656,7 +8656,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
       </c>
       <c r="K236" t="str">
-        <v>1-B9701-FT17-65450010004/035-68</v>
+        <v>1-B9701-FT17-65450010004/034-68</v>
       </c>
     </row>
     <row r="237">
@@ -8664,7 +8664,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
       </c>
       <c r="B237" t="str">
-        <v>EQ-FMS-0006</v>
+        <v>EQ-FMS-0005</v>
       </c>
       <c r="C237" t="str">
         <v>EQUIPMENT</v>
@@ -8691,7 +8691,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
       </c>
       <c r="K237" t="str">
-        <v>1-B9701-FT17-65450010004/036-68</v>
+        <v>1-B9701-FT17-65450010004/035-68</v>
       </c>
     </row>
     <row r="238">
@@ -8699,7 +8699,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
       </c>
       <c r="B238" t="str">
-        <v>EQ-FMS-0007</v>
+        <v>EQ-FMS-0006</v>
       </c>
       <c r="C238" t="str">
         <v>EQUIPMENT</v>
@@ -8726,7 +8726,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
       </c>
       <c r="K238" t="str">
-        <v>1-B9701-FT17-65450010004/037-68</v>
+        <v>1-B9701-FT17-65450010004/036-68</v>
       </c>
     </row>
     <row r="239">
@@ -8734,7 +8734,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
       </c>
       <c r="B239" t="str">
-        <v>EQ-FMS-0008</v>
+        <v>EQ-FMS-0007</v>
       </c>
       <c r="C239" t="str">
         <v>EQUIPMENT</v>
@@ -8761,15 +8761,15 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
       </c>
       <c r="K239" t="str">
-        <v>1-B9701-FT17-65450010004/038-68</v>
+        <v>1-B9701-FT17-65450010004/037-68</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
       </c>
       <c r="B240" t="str">
-        <v>EQ-FMS-0009</v>
+        <v>EQ-FMS-0008</v>
       </c>
       <c r="C240" t="str">
         <v>EQUIPMENT</v>
@@ -8793,10 +8793,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J240" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
       </c>
       <c r="K240" t="str">
-        <v>1-B9701-FT17-65450010004/039-68</v>
+        <v>1-B9701-FT17-65450010004/038-68</v>
       </c>
     </row>
     <row r="241">
@@ -8804,7 +8804,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
       </c>
       <c r="B241" t="str">
-        <v>EQ-FMS-0010</v>
+        <v>EQ-FMS-0009</v>
       </c>
       <c r="C241" t="str">
         <v>EQUIPMENT</v>
@@ -8831,7 +8831,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
       </c>
       <c r="K241" t="str">
-        <v>1-B9701-FT17-65450010004/040-68</v>
+        <v>1-B9701-FT17-65450010004/039-68</v>
       </c>
     </row>
     <row r="242">
@@ -8839,7 +8839,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
       </c>
       <c r="B242" t="str">
-        <v>EQ-FMS-0011</v>
+        <v>EQ-FMS-0010</v>
       </c>
       <c r="C242" t="str">
         <v>EQUIPMENT</v>
@@ -8866,7 +8866,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
       </c>
       <c r="K242" t="str">
-        <v>1-B9701-FT17-65450010004/041-68</v>
+        <v>1-B9701-FT17-65450010004/040-68</v>
       </c>
     </row>
     <row r="243">
@@ -8874,7 +8874,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
       </c>
       <c r="B243" t="str">
-        <v>EQ-FMS-0012</v>
+        <v>EQ-FMS-0011</v>
       </c>
       <c r="C243" t="str">
         <v>EQUIPMENT</v>
@@ -8901,7 +8901,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
       </c>
       <c r="K243" t="str">
-        <v>1-B9701-FT17-65450010004/042-68</v>
+        <v>1-B9701-FT17-65450010004/041-68</v>
       </c>
     </row>
     <row r="244">
@@ -8909,7 +8909,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
       </c>
       <c r="B244" t="str">
-        <v>EQ-FMS-0013</v>
+        <v>EQ-FMS-0012</v>
       </c>
       <c r="C244" t="str">
         <v>EQUIPMENT</v>
@@ -8936,21 +8936,21 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
       </c>
       <c r="K244" t="str">
-        <v>1-B9701-FT17-65450010004/043-68</v>
+        <v>1-B9701-FT17-65450010004/042-68</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>หุ่นจำลองกะโหลกศีรษะ</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
       </c>
       <c r="B245" t="str">
-        <v>EQ-ANA-0001</v>
+        <v>EQ-FMS-0013</v>
       </c>
       <c r="C245" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D245" t="str">
-        <v>หุ่นจำลองกายวิภาคศาสตร์</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E245" t="str">
         <v>ชุด</v>
@@ -8959,27 +8959,27 @@
         <v>1</v>
       </c>
       <c r="G245">
-        <v>7600</v>
+        <v>246500</v>
       </c>
       <c r="H245" t="str">
-        <v>2024-06-28</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I245" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J245" t="str">
-        <v>หุ่นจำลองกะโหลกศีรษะ แยกชิ้นส่วนได้</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
       </c>
       <c r="K245" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (1-1/1)</v>
+        <v>1-B9701-FT17-65450010004/043-68</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>หุ่นจำลองสมองและเส้นเลือดแดง</v>
+        <v>หุ่นจำลองกะโหลกศีรษะ</v>
       </c>
       <c r="B246" t="str">
-        <v>EQ-ANA-0002</v>
+        <v>EQ-ANA-0001</v>
       </c>
       <c r="C246" t="str">
         <v>EQUIPMENT</v>
@@ -8994,7 +8994,7 @@
         <v>1</v>
       </c>
       <c r="G246">
-        <v>18000</v>
+        <v>7600</v>
       </c>
       <c r="H246" t="str">
         <v>2024-06-28</v>
@@ -9003,18 +9003,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J246" t="str">
-        <v>หุ่นจำลองสมองและเส้นเลือดแดง</v>
+        <v>หุ่นจำลองกะโหลกศีรษะ แยกชิ้นส่วนได้</v>
       </c>
       <c r="K246" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (2-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (1-1/1)</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>หุ่นจำลองโครงกระดูกเต็มตัวขนาดเท่าจริง</v>
+        <v>หุ่นจำลองสมองและเส้นเลือดแดง</v>
       </c>
       <c r="B247" t="str">
-        <v>EQ-ANA-0003</v>
+        <v>EQ-ANA-0002</v>
       </c>
       <c r="C247" t="str">
         <v>EQUIPMENT</v>
@@ -9038,18 +9038,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J247" t="str">
-        <v>หุ่นจำลองโครงกระดูกเต็มตัวขนาดเท่าจริง</v>
+        <v>หุ่นจำลองสมองและเส้นเลือดแดง</v>
       </c>
       <c r="K247" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (3-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (2-1/1)</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>โมเดลหัวใจ</v>
+        <v>หุ่นจำลองโครงกระดูกเต็มตัวขนาดเท่าจริง</v>
       </c>
       <c r="B248" t="str">
-        <v>EQ-ANA-0004</v>
+        <v>EQ-ANA-0003</v>
       </c>
       <c r="C248" t="str">
         <v>EQUIPMENT</v>
@@ -9064,7 +9064,7 @@
         <v>1</v>
       </c>
       <c r="G248">
-        <v>4100</v>
+        <v>18000</v>
       </c>
       <c r="H248" t="str">
         <v>2024-06-28</v>
@@ -9073,24 +9073,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J248" t="str">
-        <v>โมเดลหัวใจ</v>
+        <v>หุ่นจำลองโครงกระดูกเต็มตัวขนาดเท่าจริง</v>
       </c>
       <c r="K248" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (4-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (3-1/1)</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
+        <v>โมเดลหัวใจ</v>
       </c>
       <c r="B249" t="str">
-        <v>EQ-FMS-0014</v>
+        <v>EQ-ANA-0004</v>
       </c>
       <c r="C249" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D249" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นจำลองกายวิภาคศาสตร์</v>
       </c>
       <c r="E249" t="str">
         <v>ชุด</v>
@@ -9099,7 +9099,7 @@
         <v>1</v>
       </c>
       <c r="G249">
-        <v>140000</v>
+        <v>4100</v>
       </c>
       <c r="H249" t="str">
         <v>2024-06-28</v>
@@ -9108,10 +9108,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J249" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
+        <v>โมเดลหัวใจ</v>
       </c>
       <c r="K249" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (5-1/6)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (4-1/1)</v>
       </c>
     </row>
     <row r="250">
@@ -9119,7 +9119,7 @@
         <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="B250" t="str">
-        <v>EQ-FMS-0015</v>
+        <v>EQ-FMS-0014</v>
       </c>
       <c r="C250" t="str">
         <v>EQUIPMENT</v>
@@ -9146,7 +9146,7 @@
         <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="K250" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (5-2/6)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (5-1/6)</v>
       </c>
     </row>
     <row r="251">
@@ -9154,7 +9154,7 @@
         <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="B251" t="str">
-        <v>EQ-FMS-0016</v>
+        <v>EQ-FMS-0015</v>
       </c>
       <c r="C251" t="str">
         <v>EQUIPMENT</v>
@@ -9181,7 +9181,7 @@
         <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="K251" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (5-3/6)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (5-2/6)</v>
       </c>
     </row>
     <row r="252">
@@ -9189,7 +9189,7 @@
         <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="B252" t="str">
-        <v>EQ-FMS-0017</v>
+        <v>EQ-FMS-0016</v>
       </c>
       <c r="C252" t="str">
         <v>EQUIPMENT</v>
@@ -9216,7 +9216,7 @@
         <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="K252" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (5-4/6)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (5-3/6)</v>
       </c>
     </row>
     <row r="253">
@@ -9224,7 +9224,7 @@
         <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="B253" t="str">
-        <v>EQ-FMS-0018</v>
+        <v>EQ-FMS-0017</v>
       </c>
       <c r="C253" t="str">
         <v>EQUIPMENT</v>
@@ -9251,7 +9251,7 @@
         <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="K253" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (5-5/6)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (5-4/6)</v>
       </c>
     </row>
     <row r="254">
@@ -9259,7 +9259,7 @@
         <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="B254" t="str">
-        <v>EQ-FMS-0019</v>
+        <v>EQ-FMS-0018</v>
       </c>
       <c r="C254" t="str">
         <v>EQUIPMENT</v>
@@ -9286,21 +9286,21 @@
         <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="K254" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (5-6/6)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (5-5/6)</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>หุ่นฝึก CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="B255" t="str">
-        <v>EQ-CPR-0009</v>
+        <v>EQ-FMS-0019</v>
       </c>
       <c r="C255" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D255" t="str">
-        <v>หุ่นฝึก CPR</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E255" t="str">
         <v>ชุด</v>
@@ -9309,7 +9309,7 @@
         <v>1</v>
       </c>
       <c r="G255">
-        <v>20000</v>
+        <v>140000</v>
       </c>
       <c r="H255" t="str">
         <v>2024-06-28</v>
@@ -9318,10 +9318,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J255" t="str">
-        <v>หุ่นฝึกช่วยพื้นคืนชีพผู้ใหญ่ขั้นพื้นฐานแบบครึ่งตัว</v>
+        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="K255" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (6-1/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (5-6/6)</v>
       </c>
     </row>
     <row r="256">
@@ -9329,7 +9329,7 @@
         <v>หุ่นฝึก CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B256" t="str">
-        <v>EQ-CPR-0010</v>
+        <v>EQ-CPR-0009</v>
       </c>
       <c r="C256" t="str">
         <v>EQUIPMENT</v>
@@ -9356,21 +9356,21 @@
         <v>หุ่นฝึกช่วยพื้นคืนชีพผู้ใหญ่ขั้นพื้นฐานแบบครึ่งตัว</v>
       </c>
       <c r="K256" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (6-2/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (6-1/2)</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหารทางจมูก</v>
+        <v>หุ่นฝึก CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B257" t="str">
-        <v>EQ-NG-0011</v>
+        <v>EQ-CPR-0010</v>
       </c>
       <c r="C257" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D257" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นฝึก CPR</v>
       </c>
       <c r="E257" t="str">
         <v>ชุด</v>
@@ -9379,7 +9379,7 @@
         <v>1</v>
       </c>
       <c r="G257">
-        <v>60000</v>
+        <v>20000</v>
       </c>
       <c r="H257" t="str">
         <v>2024-06-28</v>
@@ -9388,24 +9388,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J257" t="str">
-        <v>หุ่นฝึกการใส่สายให้อาหารทางจมูก</v>
+        <v>หุ่นฝึกช่วยพื้นคืนชีพผู้ใหญ่ขั้นพื้นฐานแบบครึ่งตัว</v>
       </c>
       <c r="K257" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (8-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (6-2/2)</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
+        <v>หุ่นฝึกใส่สายให้อาหารทางจมูก</v>
       </c>
       <c r="B258" t="str">
-        <v>EQ-URC-0021</v>
+        <v>EQ-NG-0011</v>
       </c>
       <c r="C258" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D258" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="E258" t="str">
         <v>ชุด</v>
@@ -9414,7 +9414,7 @@
         <v>1</v>
       </c>
       <c r="G258">
-        <v>65000</v>
+        <v>60000</v>
       </c>
       <c r="H258" t="str">
         <v>2024-06-28</v>
@@ -9423,10 +9423,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J258" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
+        <v>หุ่นฝึกการใส่สายให้อาหารทางจมูก</v>
       </c>
       <c r="K258" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (9-1/3)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (8-1/1)</v>
       </c>
     </row>
     <row r="259">
@@ -9434,7 +9434,7 @@
         <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
       </c>
       <c r="B259" t="str">
-        <v>EQ-URC-0022</v>
+        <v>EQ-URC-0021</v>
       </c>
       <c r="C259" t="str">
         <v>EQUIPMENT</v>
@@ -9461,7 +9461,7 @@
         <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
       </c>
       <c r="K259" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (9-2/3)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (9-1/3)</v>
       </c>
     </row>
     <row r="260">
@@ -9469,7 +9469,7 @@
         <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
       </c>
       <c r="B260" t="str">
-        <v>EQ-URC-0023</v>
+        <v>EQ-URC-0022</v>
       </c>
       <c r="C260" t="str">
         <v>EQUIPMENT</v>
@@ -9496,21 +9496,21 @@
         <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
       </c>
       <c r="K260" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (9-3/3)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (9-2/3)</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
       </c>
       <c r="B261" t="str">
-        <v>EQ-STI-0049</v>
+        <v>EQ-URC-0023</v>
       </c>
       <c r="C261" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D261" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E261" t="str">
         <v>ชุด</v>
@@ -9519,7 +9519,7 @@
         <v>1</v>
       </c>
       <c r="G261">
-        <v>40000</v>
+        <v>65000</v>
       </c>
       <c r="H261" t="str">
         <v>2024-06-28</v>
@@ -9528,10 +9528,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J261" t="str">
-        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
       </c>
       <c r="K261" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (12-1/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (9-3/3)</v>
       </c>
     </row>
     <row r="262">
@@ -9539,7 +9539,7 @@
         <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล</v>
       </c>
       <c r="B262" t="str">
-        <v>EQ-STI-0050</v>
+        <v>EQ-STI-0049</v>
       </c>
       <c r="C262" t="str">
         <v>EQUIPMENT</v>
@@ -9566,21 +9566,21 @@
         <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล</v>
       </c>
       <c r="K262" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (12-2/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (12-1/2)</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
+        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล</v>
       </c>
       <c r="B263" t="str">
-        <v>EQ-OB-0001</v>
+        <v>EQ-STI-0050</v>
       </c>
       <c r="C263" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D263" t="str">
-        <v>หุ่นฝึกสูติศาสตร์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E263" t="str">
         <v>ชุด</v>
@@ -9589,7 +9589,7 @@
         <v>1</v>
       </c>
       <c r="G263">
-        <v>300000</v>
+        <v>40000</v>
       </c>
       <c r="H263" t="str">
         <v>2024-06-28</v>
@@ -9598,10 +9598,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J263" t="str">
-        <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
+        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล</v>
       </c>
       <c r="K263" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (14-1/5)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (12-2/2)</v>
       </c>
     </row>
     <row r="264">
@@ -9609,7 +9609,7 @@
         <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
       </c>
       <c r="B264" t="str">
-        <v>EQ-OB-0002</v>
+        <v>EQ-OB-0001</v>
       </c>
       <c r="C264" t="str">
         <v>EQUIPMENT</v>
@@ -9636,7 +9636,7 @@
         <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
       </c>
       <c r="K264" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (14-2/5)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (14-1/5)</v>
       </c>
     </row>
     <row r="265">
@@ -9644,7 +9644,7 @@
         <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
       </c>
       <c r="B265" t="str">
-        <v>EQ-OB-0003</v>
+        <v>EQ-OB-0002</v>
       </c>
       <c r="C265" t="str">
         <v>EQUIPMENT</v>
@@ -9671,7 +9671,7 @@
         <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
       </c>
       <c r="K265" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (14-3/5)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (14-2/5)</v>
       </c>
     </row>
     <row r="266">
@@ -9679,7 +9679,7 @@
         <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
       </c>
       <c r="B266" t="str">
-        <v>EQ-OB-0004</v>
+        <v>EQ-OB-0003</v>
       </c>
       <c r="C266" t="str">
         <v>EQUIPMENT</v>
@@ -9706,7 +9706,7 @@
         <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
       </c>
       <c r="K266" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (14-4/5)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (14-3/5)</v>
       </c>
     </row>
     <row r="267">
@@ -9714,7 +9714,7 @@
         <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
       </c>
       <c r="B267" t="str">
-        <v>EQ-OB-0005</v>
+        <v>EQ-OB-0004</v>
       </c>
       <c r="C267" t="str">
         <v>EQUIPMENT</v>
@@ -9741,15 +9741,15 @@
         <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
       </c>
       <c r="K267" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (14-5/5)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (14-4/5)</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>ชุดฝึกการตรวจความกว้างและความบางของปากมดลูกก่อนคลอด</v>
+        <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
       </c>
       <c r="B268" t="str">
-        <v>EQ-OB-0006</v>
+        <v>EQ-OB-0005</v>
       </c>
       <c r="C268" t="str">
         <v>EQUIPMENT</v>
@@ -9764,7 +9764,7 @@
         <v>1</v>
       </c>
       <c r="G268">
-        <v>50000</v>
+        <v>300000</v>
       </c>
       <c r="H268" t="str">
         <v>2024-06-28</v>
@@ -9773,18 +9773,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J268" t="str">
-        <v>ชุดฝึกการตรวจความกว้างและความบางของปากมดลูกก่อนคลอด</v>
+        <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
       </c>
       <c r="K268" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (15-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (14-5/5)</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>หุ่นฝึกตรวจครรภ์</v>
+        <v>ชุดฝึกการตรวจความกว้างและความบางของปากมดลูกก่อนคลอด</v>
       </c>
       <c r="B269" t="str">
-        <v>EQ-OB-0007</v>
+        <v>EQ-OB-0006</v>
       </c>
       <c r="C269" t="str">
         <v>EQUIPMENT</v>
@@ -9799,7 +9799,7 @@
         <v>1</v>
       </c>
       <c r="G269">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="H269" t="str">
         <v>2024-06-28</v>
@@ -9808,18 +9808,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J269" t="str">
-        <v>หุ่นฝึกตรวจครรภ์</v>
+        <v>ชุดฝึกการตรวจความกว้างและความบางของปากมดลูกก่อนคลอด</v>
       </c>
       <c r="K269" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (16-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (15-1/1)</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>หุ่นฝึกอาบน้ำทารก เพศชาย</v>
+        <v>หุ่นฝึกตรวจครรภ์</v>
       </c>
       <c r="B270" t="str">
-        <v>EQ-OB-0008</v>
+        <v>EQ-OB-0007</v>
       </c>
       <c r="C270" t="str">
         <v>EQUIPMENT</v>
@@ -9834,7 +9834,7 @@
         <v>1</v>
       </c>
       <c r="G270">
-        <v>40000</v>
+        <v>45000</v>
       </c>
       <c r="H270" t="str">
         <v>2024-06-28</v>
@@ -9843,10 +9843,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J270" t="str">
-        <v>หุ่นฝึกอาบน้ำทารก เพศชาย</v>
+        <v>หุ่นฝึกตรวจครรภ์</v>
       </c>
       <c r="K270" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (17-1/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (16-1/1)</v>
       </c>
     </row>
     <row r="271">
@@ -9854,7 +9854,7 @@
         <v>หุ่นฝึกอาบน้ำทารก เพศชาย</v>
       </c>
       <c r="B271" t="str">
-        <v>EQ-OB-0009</v>
+        <v>EQ-OB-0008</v>
       </c>
       <c r="C271" t="str">
         <v>EQUIPMENT</v>
@@ -9881,15 +9881,15 @@
         <v>หุ่นฝึกอาบน้ำทารก เพศชาย</v>
       </c>
       <c r="K271" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (17-2/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (17-1/2)</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>หุ่นฝึกอาบน้ำทารก เพศหญิง</v>
+        <v>หุ่นฝึกอาบน้ำทารก เพศชาย</v>
       </c>
       <c r="B272" t="str">
-        <v>EQ-OB-0010</v>
+        <v>EQ-OB-0009</v>
       </c>
       <c r="C272" t="str">
         <v>EQUIPMENT</v>
@@ -9913,10 +9913,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J272" t="str">
-        <v>หุ่นฝึกอาบน้ำทารก เพศหญิง</v>
+        <v>หุ่นฝึกอาบน้ำทารก เพศชาย</v>
       </c>
       <c r="K272" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (18-1/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (17-2/2)</v>
       </c>
     </row>
     <row r="273">
@@ -9924,7 +9924,7 @@
         <v>หุ่นฝึกอาบน้ำทารก เพศหญิง</v>
       </c>
       <c r="B273" t="str">
-        <v>EQ-OB-0011</v>
+        <v>EQ-OB-0010</v>
       </c>
       <c r="C273" t="str">
         <v>EQUIPMENT</v>
@@ -9951,15 +9951,15 @@
         <v>หุ่นฝึกอาบน้ำทารก เพศหญิง</v>
       </c>
       <c r="K273" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (18-2/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (18-1/2)</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>หุ่นจำลองฝึกตรวจสัญญาณชีพทารก</v>
+        <v>หุ่นฝึกอาบน้ำทารก เพศหญิง</v>
       </c>
       <c r="B274" t="str">
-        <v>EQ-OB-0012</v>
+        <v>EQ-OB-0011</v>
       </c>
       <c r="C274" t="str">
         <v>EQUIPMENT</v>
@@ -9974,7 +9974,7 @@
         <v>1</v>
       </c>
       <c r="G274">
-        <v>170000</v>
+        <v>40000</v>
       </c>
       <c r="H274" t="str">
         <v>2024-06-28</v>
@@ -9983,18 +9983,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J274" t="str">
-        <v>หุ่นจำลองฝึกตรวจสัญญาณชีพทารก</v>
+        <v>หุ่นฝึกอาบน้ำทารก เพศหญิง</v>
       </c>
       <c r="K274" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (19-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (18-2/2)</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>หุ่นจำลองช่วยฟื้นคืนชีพ ทารก แบบมีสัญญาณไฟ</v>
+        <v>หุ่นจำลองฝึกตรวจสัญญาณชีพทารก</v>
       </c>
       <c r="B275" t="str">
-        <v>EQ-OB-0013</v>
+        <v>EQ-OB-0012</v>
       </c>
       <c r="C275" t="str">
         <v>EQUIPMENT</v>
@@ -10009,7 +10009,7 @@
         <v>1</v>
       </c>
       <c r="G275">
-        <v>10000</v>
+        <v>170000</v>
       </c>
       <c r="H275" t="str">
         <v>2024-06-28</v>
@@ -10018,10 +10018,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J275" t="str">
-        <v>หุ่นจำลองช่วยฟื้นคืนชีพ ทารก แบบมีสัญญาณไฟ</v>
+        <v>หุ่นจำลองฝึกตรวจสัญญาณชีพทารก</v>
       </c>
       <c r="K275" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (20-1/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (19-1/1)</v>
       </c>
     </row>
     <row r="276">
@@ -10029,7 +10029,7 @@
         <v>หุ่นจำลองช่วยฟื้นคืนชีพ ทารก แบบมีสัญญาณไฟ</v>
       </c>
       <c r="B276" t="str">
-        <v>EQ-OB-0014</v>
+        <v>EQ-OB-0013</v>
       </c>
       <c r="C276" t="str">
         <v>EQUIPMENT</v>
@@ -10056,21 +10056,21 @@
         <v>หุ่นจำลองช่วยฟื้นคืนชีพ ทารก แบบมีสัญญาณไฟ</v>
       </c>
       <c r="K276" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (20-2/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (20-1/2)</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกายผู้ใหญ่</v>
+        <v>หุ่นจำลองช่วยฟื้นคืนชีพ ทารก แบบมีสัญญาณไฟ</v>
       </c>
       <c r="B277" t="str">
-        <v>EQ-SAM-0021</v>
+        <v>EQ-OB-0014</v>
       </c>
       <c r="C277" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D277" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>หุ่นฝึกสูติศาสตร์</v>
       </c>
       <c r="E277" t="str">
         <v>ชุด</v>
@@ -10079,7 +10079,7 @@
         <v>1</v>
       </c>
       <c r="G277">
-        <v>200000</v>
+        <v>10000</v>
       </c>
       <c r="H277" t="str">
         <v>2024-06-28</v>
@@ -10088,24 +10088,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J277" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกายผู้ใหญ่</v>
+        <v>หุ่นจำลองช่วยฟื้นคืนชีพ ทารก แบบมีสัญญาณไฟ</v>
       </c>
       <c r="K277" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (21-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (20-2/2)</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>กระเป๋าเยี่ยมบ้านพร้อมอุปกรณ์</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกายผู้ใหญ่</v>
       </c>
       <c r="B278" t="str">
-        <v>EQ-HB-0001</v>
+        <v>EQ-SAM-0021</v>
       </c>
       <c r="C278" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D278" t="str">
-        <v>กระเป๋าเยี่ยมบ้าน</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E278" t="str">
         <v>ชุด</v>
@@ -10114,7 +10114,7 @@
         <v>1</v>
       </c>
       <c r="G278">
-        <v>10000</v>
+        <v>200000</v>
       </c>
       <c r="H278" t="str">
         <v>2024-06-28</v>
@@ -10123,10 +10123,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J278" t="str">
-        <v>กระเป๋าเยี่ยมบ้านพร้อมอุปกรณ์</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกายผู้ใหญ่</v>
       </c>
       <c r="K278" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (22-1/3)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (21-1/1)</v>
       </c>
     </row>
     <row r="279">
@@ -10134,7 +10134,7 @@
         <v>กระเป๋าเยี่ยมบ้านพร้อมอุปกรณ์</v>
       </c>
       <c r="B279" t="str">
-        <v>EQ-HB-0002</v>
+        <v>EQ-HB-0001</v>
       </c>
       <c r="C279" t="str">
         <v>EQUIPMENT</v>
@@ -10161,7 +10161,7 @@
         <v>กระเป๋าเยี่ยมบ้านพร้อมอุปกรณ์</v>
       </c>
       <c r="K279" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (22-2/3)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (22-1/3)</v>
       </c>
     </row>
     <row r="280">
@@ -10169,7 +10169,7 @@
         <v>กระเป๋าเยี่ยมบ้านพร้อมอุปกรณ์</v>
       </c>
       <c r="B280" t="str">
-        <v>EQ-HB-0003</v>
+        <v>EQ-HB-0002</v>
       </c>
       <c r="C280" t="str">
         <v>EQUIPMENT</v>
@@ -10196,30 +10196,30 @@
         <v>กระเป๋าเยี่ยมบ้านพร้อมอุปกรณ์</v>
       </c>
       <c r="K280" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (22-3/3)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (22-2/3)</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>เตียงคนไข้ไฟฟ้า 3 ไกร์</v>
+        <v>กระเป๋าเยี่ยมบ้านพร้อมอุปกรณ์</v>
       </c>
       <c r="B281" t="str">
-        <v>EQ-BED-0025</v>
+        <v>EQ-HB-0003</v>
       </c>
       <c r="C281" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D281" t="str">
-        <v>เตียงและตู้ข้างเตียง</v>
+        <v>กระเป๋าเยี่ยมบ้าน</v>
       </c>
       <c r="E281" t="str">
-        <v>หลัง</v>
+        <v>ชุด</v>
       </c>
       <c r="F281">
         <v>1</v>
       </c>
       <c r="G281">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="H281" t="str">
         <v>2024-06-28</v>
@@ -10228,18 +10228,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J281" t="str">
-        <v>เตียงไฟฟ้า 3 ฟังก์ชั่น 3 ไกร์</v>
+        <v>กระเป๋าเยี่ยมบ้านพร้อมอุปกรณ์</v>
       </c>
       <c r="K281" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (23-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (22-3/3)</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>เตียงคนไข้ 3 ไกร์ (มือหมุน)</v>
+        <v>เตียงคนไข้ไฟฟ้า 3 ไกร์</v>
       </c>
       <c r="B282" t="str">
-        <v>EQ-BED-0026</v>
+        <v>EQ-BED-0025</v>
       </c>
       <c r="C282" t="str">
         <v>EQUIPMENT</v>
@@ -10254,7 +10254,7 @@
         <v>1</v>
       </c>
       <c r="G282">
-        <v>25000</v>
+        <v>40000</v>
       </c>
       <c r="H282" t="str">
         <v>2024-06-28</v>
@@ -10263,10 +10263,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J282" t="str">
-        <v>เตียง 3 ไกร์ แบบมือหมุน</v>
+        <v>เตียงไฟฟ้า 3 ฟังก์ชั่น 3 ไกร์</v>
       </c>
       <c r="K282" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (24-1/9)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (23-1/1)</v>
       </c>
     </row>
     <row r="283">
@@ -10274,7 +10274,7 @@
         <v>เตียงคนไข้ 3 ไกร์ (มือหมุน)</v>
       </c>
       <c r="B283" t="str">
-        <v>EQ-BED-0027</v>
+        <v>EQ-BED-0026</v>
       </c>
       <c r="C283" t="str">
         <v>EQUIPMENT</v>
@@ -10301,7 +10301,7 @@
         <v>เตียง 3 ไกร์ แบบมือหมุน</v>
       </c>
       <c r="K283" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (24-2/9)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (24-1/9)</v>
       </c>
     </row>
     <row r="284">
@@ -10309,7 +10309,7 @@
         <v>เตียงคนไข้ 3 ไกร์ (มือหมุน)</v>
       </c>
       <c r="B284" t="str">
-        <v>EQ-BED-0028</v>
+        <v>EQ-BED-0027</v>
       </c>
       <c r="C284" t="str">
         <v>EQUIPMENT</v>
@@ -10336,7 +10336,7 @@
         <v>เตียง 3 ไกร์ แบบมือหมุน</v>
       </c>
       <c r="K284" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (24-3/9)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (24-2/9)</v>
       </c>
     </row>
     <row r="285">
@@ -10344,7 +10344,7 @@
         <v>เตียงคนไข้ 3 ไกร์ (มือหมุน)</v>
       </c>
       <c r="B285" t="str">
-        <v>EQ-BED-0029</v>
+        <v>EQ-BED-0028</v>
       </c>
       <c r="C285" t="str">
         <v>EQUIPMENT</v>
@@ -10371,7 +10371,7 @@
         <v>เตียง 3 ไกร์ แบบมือหมุน</v>
       </c>
       <c r="K285" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (24-4/9)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (24-3/9)</v>
       </c>
     </row>
     <row r="286">
@@ -10379,7 +10379,7 @@
         <v>เตียงคนไข้ 3 ไกร์ (มือหมุน)</v>
       </c>
       <c r="B286" t="str">
-        <v>EQ-BED-0030</v>
+        <v>EQ-BED-0029</v>
       </c>
       <c r="C286" t="str">
         <v>EQUIPMENT</v>
@@ -10406,7 +10406,7 @@
         <v>เตียง 3 ไกร์ แบบมือหมุน</v>
       </c>
       <c r="K286" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (24-5/9)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (24-4/9)</v>
       </c>
     </row>
     <row r="287">
@@ -10414,7 +10414,7 @@
         <v>เตียงคนไข้ 3 ไกร์ (มือหมุน)</v>
       </c>
       <c r="B287" t="str">
-        <v>EQ-BED-0031</v>
+        <v>EQ-BED-0030</v>
       </c>
       <c r="C287" t="str">
         <v>EQUIPMENT</v>
@@ -10441,7 +10441,7 @@
         <v>เตียง 3 ไกร์ แบบมือหมุน</v>
       </c>
       <c r="K287" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (24-6/9)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (24-5/9)</v>
       </c>
     </row>
     <row r="288">
@@ -10449,7 +10449,7 @@
         <v>เตียงคนไข้ 3 ไกร์ (มือหมุน)</v>
       </c>
       <c r="B288" t="str">
-        <v>EQ-BED-0032</v>
+        <v>EQ-BED-0031</v>
       </c>
       <c r="C288" t="str">
         <v>EQUIPMENT</v>
@@ -10476,7 +10476,7 @@
         <v>เตียง 3 ไกร์ แบบมือหมุน</v>
       </c>
       <c r="K288" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (24-7/9)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (24-6/9)</v>
       </c>
     </row>
     <row r="289">
@@ -10484,7 +10484,7 @@
         <v>เตียงคนไข้ 3 ไกร์ (มือหมุน)</v>
       </c>
       <c r="B289" t="str">
-        <v>EQ-BED-0033</v>
+        <v>EQ-BED-0032</v>
       </c>
       <c r="C289" t="str">
         <v>EQUIPMENT</v>
@@ -10511,7 +10511,7 @@
         <v>เตียง 3 ไกร์ แบบมือหมุน</v>
       </c>
       <c r="K289" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (24-8/9)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (24-7/9)</v>
       </c>
     </row>
     <row r="290">
@@ -10519,7 +10519,7 @@
         <v>เตียงคนไข้ 3 ไกร์ (มือหมุน)</v>
       </c>
       <c r="B290" t="str">
-        <v>EQ-BED-0034</v>
+        <v>EQ-BED-0033</v>
       </c>
       <c r="C290" t="str">
         <v>EQUIPMENT</v>
@@ -10546,15 +10546,15 @@
         <v>เตียง 3 ไกร์ แบบมือหมุน</v>
       </c>
       <c r="K290" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (24-9/9)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (24-8/9)</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>เตียงทำคลอด 2 ตอนปรับระดับได้</v>
+        <v>เตียงคนไข้ 3 ไกร์ (มือหมุน)</v>
       </c>
       <c r="B291" t="str">
-        <v>EQ-BED-0035</v>
+        <v>EQ-BED-0034</v>
       </c>
       <c r="C291" t="str">
         <v>EQUIPMENT</v>
@@ -10569,7 +10569,7 @@
         <v>1</v>
       </c>
       <c r="G291">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="H291" t="str">
         <v>2024-06-28</v>
@@ -10578,18 +10578,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J291" t="str">
-        <v>เตียงทำคลอดแบบ 2 ตอนแบบปรับระดับได้</v>
+        <v>เตียง 3 ไกร์ แบบมือหมุน</v>
       </c>
       <c r="K291" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (25-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (24-9/9)</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>เตียงเด็กอ่อนพร้อมเบาะ</v>
+        <v>เตียงทำคลอด 2 ตอนปรับระดับได้</v>
       </c>
       <c r="B292" t="str">
-        <v>EQ-BED-0036</v>
+        <v>EQ-BED-0035</v>
       </c>
       <c r="C292" t="str">
         <v>EQUIPMENT</v>
@@ -10598,13 +10598,13 @@
         <v>เตียงและตู้ข้างเตียง</v>
       </c>
       <c r="E292" t="str">
-        <v>ชุด</v>
+        <v>หลัง</v>
       </c>
       <c r="F292">
         <v>1</v>
       </c>
       <c r="G292">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="H292" t="str">
         <v>2024-06-28</v>
@@ -10613,10 +10613,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J292" t="str">
-        <v>คลิปเด็กอ่อนพร้อมเบาะ</v>
+        <v>เตียงทำคลอดแบบ 2 ตอนแบบปรับระดับได้</v>
       </c>
       <c r="K292" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (26-1/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (25-1/1)</v>
       </c>
     </row>
     <row r="293">
@@ -10624,7 +10624,7 @@
         <v>เตียงเด็กอ่อนพร้อมเบาะ</v>
       </c>
       <c r="B293" t="str">
-        <v>EQ-BED-0037</v>
+        <v>EQ-BED-0036</v>
       </c>
       <c r="C293" t="str">
         <v>EQUIPMENT</v>
@@ -10651,15 +10651,15 @@
         <v>คลิปเด็กอ่อนพร้อมเบาะ</v>
       </c>
       <c r="K293" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (26-2/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (26-1/2)</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>ตู้ข้างเตียง</v>
+        <v>เตียงเด็กอ่อนพร้อมเบาะ</v>
       </c>
       <c r="B294" t="str">
-        <v>EQ-BED-0038</v>
+        <v>EQ-BED-0037</v>
       </c>
       <c r="C294" t="str">
         <v>EQUIPMENT</v>
@@ -10668,13 +10668,13 @@
         <v>เตียงและตู้ข้างเตียง</v>
       </c>
       <c r="E294" t="str">
-        <v>หลัง</v>
+        <v>ชุด</v>
       </c>
       <c r="F294">
         <v>1</v>
       </c>
       <c r="G294">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="H294" t="str">
         <v>2024-06-28</v>
@@ -10683,10 +10683,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J294" t="str">
-        <v>ตู้ข้างเตียง</v>
+        <v>คลิปเด็กอ่อนพร้อมเบาะ</v>
       </c>
       <c r="K294" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (27-1/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (26-2/2)</v>
       </c>
     </row>
     <row r="295">
@@ -10694,7 +10694,7 @@
         <v>ตู้ข้างเตียง</v>
       </c>
       <c r="B295" t="str">
-        <v>EQ-BED-0039</v>
+        <v>EQ-BED-0038</v>
       </c>
       <c r="C295" t="str">
         <v>EQUIPMENT</v>
@@ -10721,7 +10721,7 @@
         <v>ตู้ข้างเตียง</v>
       </c>
       <c r="K295" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (27-2/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (27-1/8)</v>
       </c>
     </row>
     <row r="296">
@@ -10729,7 +10729,7 @@
         <v>ตู้ข้างเตียง</v>
       </c>
       <c r="B296" t="str">
-        <v>EQ-BED-0040</v>
+        <v>EQ-BED-0039</v>
       </c>
       <c r="C296" t="str">
         <v>EQUIPMENT</v>
@@ -10756,7 +10756,7 @@
         <v>ตู้ข้างเตียง</v>
       </c>
       <c r="K296" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (27-3/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (27-2/8)</v>
       </c>
     </row>
     <row r="297">
@@ -10764,7 +10764,7 @@
         <v>ตู้ข้างเตียง</v>
       </c>
       <c r="B297" t="str">
-        <v>EQ-BED-0041</v>
+        <v>EQ-BED-0040</v>
       </c>
       <c r="C297" t="str">
         <v>EQUIPMENT</v>
@@ -10791,7 +10791,7 @@
         <v>ตู้ข้างเตียง</v>
       </c>
       <c r="K297" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (27-4/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (27-3/8)</v>
       </c>
     </row>
     <row r="298">
@@ -10799,7 +10799,7 @@
         <v>ตู้ข้างเตียง</v>
       </c>
       <c r="B298" t="str">
-        <v>EQ-BED-0042</v>
+        <v>EQ-BED-0041</v>
       </c>
       <c r="C298" t="str">
         <v>EQUIPMENT</v>
@@ -10834,7 +10834,7 @@
         <v>ตู้ข้างเตียง</v>
       </c>
       <c r="B299" t="str">
-        <v>EQ-BED-0043</v>
+        <v>EQ-BED-0042</v>
       </c>
       <c r="C299" t="str">
         <v>EQUIPMENT</v>
@@ -10861,7 +10861,7 @@
         <v>ตู้ข้างเตียง</v>
       </c>
       <c r="K299" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (27-6/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (27-4/8)</v>
       </c>
     </row>
     <row r="300">
@@ -10869,7 +10869,7 @@
         <v>ตู้ข้างเตียง</v>
       </c>
       <c r="B300" t="str">
-        <v>EQ-BED-0044</v>
+        <v>EQ-BED-0043</v>
       </c>
       <c r="C300" t="str">
         <v>EQUIPMENT</v>
@@ -10896,7 +10896,7 @@
         <v>ตู้ข้างเตียง</v>
       </c>
       <c r="K300" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (27-7/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (27-6/8)</v>
       </c>
     </row>
     <row r="301">
@@ -10904,7 +10904,7 @@
         <v>ตู้ข้างเตียง</v>
       </c>
       <c r="B301" t="str">
-        <v>EQ-BED-0045</v>
+        <v>EQ-BED-0044</v>
       </c>
       <c r="C301" t="str">
         <v>EQUIPMENT</v>
@@ -10931,15 +10931,15 @@
         <v>ตู้ข้างเตียง</v>
       </c>
       <c r="K301" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (27-8/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (27-7/8)</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>โต๊ะคร่อมเตียง</v>
+        <v>ตู้ข้างเตียง</v>
       </c>
       <c r="B302" t="str">
-        <v>EQ-BED-0046</v>
+        <v>EQ-BED-0045</v>
       </c>
       <c r="C302" t="str">
         <v>EQUIPMENT</v>
@@ -10954,7 +10954,7 @@
         <v>1</v>
       </c>
       <c r="G302">
-        <v>7000</v>
+        <v>7500</v>
       </c>
       <c r="H302" t="str">
         <v>2024-06-28</v>
@@ -10963,10 +10963,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J302" t="str">
-        <v>โต๊ะคร่อมเตียง</v>
+        <v>ตู้ข้างเตียง</v>
       </c>
       <c r="K302" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (28-1/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (27-8/8)</v>
       </c>
     </row>
     <row r="303">
@@ -10974,7 +10974,7 @@
         <v>โต๊ะคร่อมเตียง</v>
       </c>
       <c r="B303" t="str">
-        <v>EQ-BED-0047</v>
+        <v>EQ-BED-0046</v>
       </c>
       <c r="C303" t="str">
         <v>EQUIPMENT</v>
@@ -11001,7 +11001,7 @@
         <v>โต๊ะคร่อมเตียง</v>
       </c>
       <c r="K303" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (28-2/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (28-1/8)</v>
       </c>
     </row>
     <row r="304">
@@ -11009,7 +11009,7 @@
         <v>โต๊ะคร่อมเตียง</v>
       </c>
       <c r="B304" t="str">
-        <v>EQ-BED-0048</v>
+        <v>EQ-BED-0047</v>
       </c>
       <c r="C304" t="str">
         <v>EQUIPMENT</v>
@@ -11036,7 +11036,7 @@
         <v>โต๊ะคร่อมเตียง</v>
       </c>
       <c r="K304" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (28-3/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (28-2/8)</v>
       </c>
     </row>
     <row r="305">
@@ -11044,7 +11044,7 @@
         <v>โต๊ะคร่อมเตียง</v>
       </c>
       <c r="B305" t="str">
-        <v>EQ-BED-0049</v>
+        <v>EQ-BED-0048</v>
       </c>
       <c r="C305" t="str">
         <v>EQUIPMENT</v>
@@ -11071,7 +11071,7 @@
         <v>โต๊ะคร่อมเตียง</v>
       </c>
       <c r="K305" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (28-4/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (28-3/8)</v>
       </c>
     </row>
     <row r="306">
@@ -11079,7 +11079,7 @@
         <v>โต๊ะคร่อมเตียง</v>
       </c>
       <c r="B306" t="str">
-        <v>EQ-BED-0050</v>
+        <v>EQ-BED-0049</v>
       </c>
       <c r="C306" t="str">
         <v>EQUIPMENT</v>
@@ -11106,7 +11106,7 @@
         <v>โต๊ะคร่อมเตียง</v>
       </c>
       <c r="K306" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (28-5/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (28-4/8)</v>
       </c>
     </row>
     <row r="307">
@@ -11114,7 +11114,7 @@
         <v>โต๊ะคร่อมเตียง</v>
       </c>
       <c r="B307" t="str">
-        <v>EQ-BED-0051</v>
+        <v>EQ-BED-0050</v>
       </c>
       <c r="C307" t="str">
         <v>EQUIPMENT</v>
@@ -11141,7 +11141,7 @@
         <v>โต๊ะคร่อมเตียง</v>
       </c>
       <c r="K307" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (28-6/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (28-5/8)</v>
       </c>
     </row>
     <row r="308">
@@ -11149,7 +11149,7 @@
         <v>โต๊ะคร่อมเตียง</v>
       </c>
       <c r="B308" t="str">
-        <v>EQ-BED-0052</v>
+        <v>EQ-BED-0051</v>
       </c>
       <c r="C308" t="str">
         <v>EQUIPMENT</v>
@@ -11176,7 +11176,7 @@
         <v>โต๊ะคร่อมเตียง</v>
       </c>
       <c r="K308" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (28-7/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (28-6/8)</v>
       </c>
     </row>
     <row r="309">
@@ -11184,7 +11184,7 @@
         <v>โต๊ะคร่อมเตียง</v>
       </c>
       <c r="B309" t="str">
-        <v>EQ-BED-0053</v>
+        <v>EQ-BED-0052</v>
       </c>
       <c r="C309" t="str">
         <v>EQUIPMENT</v>
@@ -11211,30 +11211,30 @@
         <v>โต๊ะคร่อมเตียง</v>
       </c>
       <c r="K309" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (28-8/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (28-7/8)</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>รถเข็นทำแผลพร้อมอุปกรณ์</v>
+        <v>โต๊ะคร่อมเตียง</v>
       </c>
       <c r="B310" t="str">
-        <v>EQ-CRT-0001</v>
+        <v>EQ-BED-0053</v>
       </c>
       <c r="C310" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D310" t="str">
-        <v>รถเข็นทางการแพทย์</v>
+        <v>เตียงและตู้ข้างเตียง</v>
       </c>
       <c r="E310" t="str">
-        <v>คัน</v>
+        <v>หลัง</v>
       </c>
       <c r="F310">
         <v>1</v>
       </c>
       <c r="G310">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="H310" t="str">
         <v>2024-06-28</v>
@@ -11243,10 +11243,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J310" t="str">
-        <v>รถเข็นทำแผลพร้อมอุปกรณ์</v>
+        <v>โต๊ะคร่อมเตียง</v>
       </c>
       <c r="K310" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (29-1/3)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (28-8/8)</v>
       </c>
     </row>
     <row r="311">
@@ -11254,7 +11254,7 @@
         <v>รถเข็นทำแผลพร้อมอุปกรณ์</v>
       </c>
       <c r="B311" t="str">
-        <v>EQ-CRT-0002</v>
+        <v>EQ-CRT-0001</v>
       </c>
       <c r="C311" t="str">
         <v>EQUIPMENT</v>
@@ -11281,7 +11281,7 @@
         <v>รถเข็นทำแผลพร้อมอุปกรณ์</v>
       </c>
       <c r="K311" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (29-2/3)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (29-1/3)</v>
       </c>
     </row>
     <row r="312">
@@ -11289,7 +11289,7 @@
         <v>รถเข็นทำแผลพร้อมอุปกรณ์</v>
       </c>
       <c r="B312" t="str">
-        <v>EQ-CRT-0003</v>
+        <v>EQ-CRT-0002</v>
       </c>
       <c r="C312" t="str">
         <v>EQUIPMENT</v>
@@ -11316,15 +11316,15 @@
         <v>รถเข็นทำแผลพร้อมอุปกรณ์</v>
       </c>
       <c r="K312" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (29-3/3)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (29-2/3)</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>รถเข็นฉีดยาและให้สารน้ำ</v>
+        <v>รถเข็นทำแผลพร้อมอุปกรณ์</v>
       </c>
       <c r="B313" t="str">
-        <v>EQ-CRT-0004</v>
+        <v>EQ-CRT-0003</v>
       </c>
       <c r="C313" t="str">
         <v>EQUIPMENT</v>
@@ -11348,10 +11348,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J313" t="str">
-        <v>รถเข็นฉีดยาและให้สารน้ำ</v>
+        <v>รถเข็นทำแผลพร้อมอุปกรณ์</v>
       </c>
       <c r="K313" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (30-1/3)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (29-3/3)</v>
       </c>
     </row>
     <row r="314">
@@ -11359,7 +11359,7 @@
         <v>รถเข็นฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B314" t="str">
-        <v>EQ-CRT-0005</v>
+        <v>EQ-CRT-0004</v>
       </c>
       <c r="C314" t="str">
         <v>EQUIPMENT</v>
@@ -11386,7 +11386,7 @@
         <v>รถเข็นฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="K314" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (30-2/3)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (30-1/3)</v>
       </c>
     </row>
     <row r="315">
@@ -11394,7 +11394,7 @@
         <v>รถเข็นฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B315" t="str">
-        <v>EQ-CRT-0006</v>
+        <v>EQ-CRT-0005</v>
       </c>
       <c r="C315" t="str">
         <v>EQUIPMENT</v>
@@ -11421,15 +11421,15 @@
         <v>รถเข็นฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="K315" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (30-3/3)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (30-2/3)</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>รถเข็นผู้ป่วย (Wheelchair)</v>
+        <v>รถเข็นฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B316" t="str">
-        <v>EQ-CRT-0007</v>
+        <v>EQ-CRT-0006</v>
       </c>
       <c r="C316" t="str">
         <v>EQUIPMENT</v>
@@ -11444,7 +11444,7 @@
         <v>1</v>
       </c>
       <c r="G316">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="H316" t="str">
         <v>2024-06-28</v>
@@ -11453,10 +11453,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J316" t="str">
-        <v>รถเข็นผู้ป่วย</v>
+        <v>รถเข็นฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="K316" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (31-1/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (30-3/3)</v>
       </c>
     </row>
     <row r="317">
@@ -11464,7 +11464,7 @@
         <v>รถเข็นผู้ป่วย (Wheelchair)</v>
       </c>
       <c r="B317" t="str">
-        <v>EQ-CRT-0008</v>
+        <v>EQ-CRT-0007</v>
       </c>
       <c r="C317" t="str">
         <v>EQUIPMENT</v>
@@ -11491,30 +11491,30 @@
         <v>รถเข็นผู้ป่วย</v>
       </c>
       <c r="K317" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (31-2/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (31-1/2)</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>ชุดถังออกซิเจน 0.5Q พร้อมอุปกรณ์</v>
+        <v>รถเข็นผู้ป่วย (Wheelchair)</v>
       </c>
       <c r="B318" t="str">
-        <v>EQ-MED-0001</v>
+        <v>EQ-CRT-0008</v>
       </c>
       <c r="C318" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D318" t="str">
-        <v>เครื่องมือและอุปกรณ์การแพทย์ตรวจรักษา</v>
+        <v>รถเข็นทางการแพทย์</v>
       </c>
       <c r="E318" t="str">
-        <v>ชุด</v>
+        <v>คัน</v>
       </c>
       <c r="F318">
         <v>1</v>
       </c>
       <c r="G318">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="H318" t="str">
         <v>2024-06-28</v>
@@ -11523,33 +11523,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J318" t="str">
-        <v>ชุดถังอ๊อกซิเจ 0.5Q พร้อมอุปกรณ์ครบชุด</v>
+        <v>รถเข็นผู้ป่วย</v>
       </c>
       <c r="K318" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (32-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (31-2/2)</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>ถังขยะกลมสแตนเลส</v>
+        <v>ชุดถังออกซิเจน 0.5Q พร้อมอุปกรณ์</v>
       </c>
       <c r="B319" t="str">
-        <v>EQ-FN-0015</v>
+        <v>EQ-MED-0001</v>
       </c>
       <c r="C319" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D319" t="str">
-        <v>ครุภัณฑ์สำนักงานและเฟอร์นิเจอร์</v>
+        <v>เครื่องมือและอุปกรณ์การแพทย์ตรวจรักษา</v>
       </c>
       <c r="E319" t="str">
-        <v>ใบ</v>
+        <v>ชุด</v>
       </c>
       <c r="F319">
         <v>1</v>
       </c>
       <c r="G319">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="H319" t="str">
         <v>2024-06-28</v>
@@ -11558,10 +11558,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J319" t="str">
-        <v>ถังขยะกลม ไม่มีวงล้อ</v>
+        <v>ชุดถังอ๊อกซิเจ 0.5Q พร้อมอุปกรณ์ครบชุด</v>
       </c>
       <c r="K319" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (33-1/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (32-1/1)</v>
       </c>
     </row>
     <row r="320">
@@ -11569,7 +11569,7 @@
         <v>ถังขยะกลมสแตนเลส</v>
       </c>
       <c r="B320" t="str">
-        <v>EQ-FN-0016</v>
+        <v>EQ-FN-0015</v>
       </c>
       <c r="C320" t="str">
         <v>EQUIPMENT</v>
@@ -11596,7 +11596,7 @@
         <v>ถังขยะกลม ไม่มีวงล้อ</v>
       </c>
       <c r="K320" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (33-2/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (33-1/8)</v>
       </c>
     </row>
     <row r="321">
@@ -11604,7 +11604,7 @@
         <v>ถังขยะกลมสแตนเลส</v>
       </c>
       <c r="B321" t="str">
-        <v>EQ-FN-0017</v>
+        <v>EQ-FN-0016</v>
       </c>
       <c r="C321" t="str">
         <v>EQUIPMENT</v>
@@ -11631,7 +11631,7 @@
         <v>ถังขยะกลม ไม่มีวงล้อ</v>
       </c>
       <c r="K321" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (33-3/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (33-2/8)</v>
       </c>
     </row>
     <row r="322">
@@ -11639,7 +11639,7 @@
         <v>ถังขยะกลมสแตนเลส</v>
       </c>
       <c r="B322" t="str">
-        <v>EQ-FN-0018</v>
+        <v>EQ-FN-0017</v>
       </c>
       <c r="C322" t="str">
         <v>EQUIPMENT</v>
@@ -11666,7 +11666,7 @@
         <v>ถังขยะกลม ไม่มีวงล้อ</v>
       </c>
       <c r="K322" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (33-4/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (33-3/8)</v>
       </c>
     </row>
     <row r="323">
@@ -11674,7 +11674,7 @@
         <v>ถังขยะกลมสแตนเลส</v>
       </c>
       <c r="B323" t="str">
-        <v>EQ-FN-0019</v>
+        <v>EQ-FN-0018</v>
       </c>
       <c r="C323" t="str">
         <v>EQUIPMENT</v>
@@ -11701,7 +11701,7 @@
         <v>ถังขยะกลม ไม่มีวงล้อ</v>
       </c>
       <c r="K323" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (33-5/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (33-4/8)</v>
       </c>
     </row>
     <row r="324">
@@ -11709,7 +11709,7 @@
         <v>ถังขยะกลมสแตนเลส</v>
       </c>
       <c r="B324" t="str">
-        <v>EQ-FN-0020</v>
+        <v>EQ-FN-0019</v>
       </c>
       <c r="C324" t="str">
         <v>EQUIPMENT</v>
@@ -11736,7 +11736,7 @@
         <v>ถังขยะกลม ไม่มีวงล้อ</v>
       </c>
       <c r="K324" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (33-6/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (33-5/8)</v>
       </c>
     </row>
     <row r="325">
@@ -11744,7 +11744,7 @@
         <v>ถังขยะกลมสแตนเลส</v>
       </c>
       <c r="B325" t="str">
-        <v>EQ-FN-0021</v>
+        <v>EQ-FN-0020</v>
       </c>
       <c r="C325" t="str">
         <v>EQUIPMENT</v>
@@ -11771,7 +11771,7 @@
         <v>ถังขยะกลม ไม่มีวงล้อ</v>
       </c>
       <c r="K325" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (33-7/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (33-6/8)</v>
       </c>
     </row>
     <row r="326">
@@ -11779,7 +11779,7 @@
         <v>ถังขยะกลมสแตนเลส</v>
       </c>
       <c r="B326" t="str">
-        <v>EQ-FN-0022</v>
+        <v>EQ-FN-0021</v>
       </c>
       <c r="C326" t="str">
         <v>EQUIPMENT</v>
@@ -11806,30 +11806,30 @@
         <v>ถังขยะกลม ไม่มีวงล้อ</v>
       </c>
       <c r="K326" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (33-8/8)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (33-7/8)</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>เครื่องดูดเสมหะชนิดหิ้ว</v>
+        <v>ถังขยะกลมสแตนเลส</v>
       </c>
       <c r="B327" t="str">
-        <v>EQ-MED-0002</v>
+        <v>EQ-FN-0022</v>
       </c>
       <c r="C327" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D327" t="str">
-        <v>เครื่องมือและอุปกรณ์การแพทย์ตรวจรักษา</v>
+        <v>ครุภัณฑ์สำนักงานและเฟอร์นิเจอร์</v>
       </c>
       <c r="E327" t="str">
-        <v>เครื่อง</v>
+        <v>ใบ</v>
       </c>
       <c r="F327">
         <v>1</v>
       </c>
       <c r="G327">
-        <v>8000</v>
+        <v>3500</v>
       </c>
       <c r="H327" t="str">
         <v>2024-06-28</v>
@@ -11838,10 +11838,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J327" t="str">
-        <v>เครื่องดูดเสมหะชนิดหิ้ว</v>
+        <v>ถังขยะกลม ไม่มีวงล้อ</v>
       </c>
       <c r="K327" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (34-1/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (33-8/8)</v>
       </c>
     </row>
     <row r="328">
@@ -11849,7 +11849,7 @@
         <v>เครื่องดูดเสมหะชนิดหิ้ว</v>
       </c>
       <c r="B328" t="str">
-        <v>EQ-MED-0003</v>
+        <v>EQ-MED-0002</v>
       </c>
       <c r="C328" t="str">
         <v>EQUIPMENT</v>
@@ -11876,21 +11876,21 @@
         <v>เครื่องดูดเสมหะชนิดหิ้ว</v>
       </c>
       <c r="K328" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (34-2/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (34-1/2)</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>เครื่องวัดความดันแบบปรอท</v>
+        <v>เครื่องดูดเสมหะชนิดหิ้ว</v>
       </c>
       <c r="B329" t="str">
-        <v>EQ-BP-0001</v>
+        <v>EQ-MED-0003</v>
       </c>
       <c r="C329" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D329" t="str">
-        <v>เครื่องวัดความดันโลหิต</v>
+        <v>เครื่องมือและอุปกรณ์การแพทย์ตรวจรักษา</v>
       </c>
       <c r="E329" t="str">
         <v>เครื่อง</v>
@@ -11899,7 +11899,7 @@
         <v>1</v>
       </c>
       <c r="G329">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="H329" t="str">
         <v>2024-06-28</v>
@@ -11908,10 +11908,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J329" t="str">
-        <v>เครื่องวัดความดันแบบปรอท</v>
+        <v>เครื่องดูดเสมหะชนิดหิ้ว</v>
       </c>
       <c r="K329" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (35-1/5)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (34-2/2)</v>
       </c>
     </row>
     <row r="330">
@@ -11919,7 +11919,7 @@
         <v>เครื่องวัดความดันแบบปรอท</v>
       </c>
       <c r="B330" t="str">
-        <v>EQ-BP-0002</v>
+        <v>EQ-BP-0001</v>
       </c>
       <c r="C330" t="str">
         <v>EQUIPMENT</v>
@@ -11946,7 +11946,7 @@
         <v>เครื่องวัดความดันแบบปรอท</v>
       </c>
       <c r="K330" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (35-2/5)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (35-1/5)</v>
       </c>
     </row>
     <row r="331">
@@ -11954,7 +11954,7 @@
         <v>เครื่องวัดความดันแบบปรอท</v>
       </c>
       <c r="B331" t="str">
-        <v>EQ-BP-0003</v>
+        <v>EQ-BP-0002</v>
       </c>
       <c r="C331" t="str">
         <v>EQUIPMENT</v>
@@ -11981,7 +11981,7 @@
         <v>เครื่องวัดความดันแบบปรอท</v>
       </c>
       <c r="K331" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (35-3/5)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (35-2/5)</v>
       </c>
     </row>
     <row r="332">
@@ -11989,7 +11989,7 @@
         <v>เครื่องวัดความดันแบบปรอท</v>
       </c>
       <c r="B332" t="str">
-        <v>EQ-BP-0004</v>
+        <v>EQ-BP-0003</v>
       </c>
       <c r="C332" t="str">
         <v>EQUIPMENT</v>
@@ -12016,7 +12016,7 @@
         <v>เครื่องวัดความดันแบบปรอท</v>
       </c>
       <c r="K332" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (35-4/5)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (35-3/5)</v>
       </c>
     </row>
     <row r="333">
@@ -12024,7 +12024,7 @@
         <v>เครื่องวัดความดันแบบปรอท</v>
       </c>
       <c r="B333" t="str">
-        <v>EQ-BP-0005</v>
+        <v>EQ-BP-0004</v>
       </c>
       <c r="C333" t="str">
         <v>EQUIPMENT</v>
@@ -12051,15 +12051,15 @@
         <v>เครื่องวัดความดันแบบปรอท</v>
       </c>
       <c r="K333" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (35-5/5)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (35-4/5)</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>เครื่องวัดความดันโลหิตอัตโนมัติ</v>
+        <v>เครื่องวัดความดันแบบปรอท</v>
       </c>
       <c r="B334" t="str">
-        <v>EQ-BP-0006</v>
+        <v>EQ-BP-0005</v>
       </c>
       <c r="C334" t="str">
         <v>EQUIPMENT</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="G334">
-        <v>2900</v>
+        <v>2000</v>
       </c>
       <c r="H334" t="str">
         <v>2024-06-28</v>
@@ -12083,10 +12083,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J334" t="str">
-        <v>เครื่องวัตความดันโลหิตอัตโนมัติ</v>
+        <v>เครื่องวัดความดันแบบปรอท</v>
       </c>
       <c r="K334" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (36-1/10)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (35-5/5)</v>
       </c>
     </row>
     <row r="335">
@@ -12094,7 +12094,7 @@
         <v>เครื่องวัดความดันโลหิตอัตโนมัติ</v>
       </c>
       <c r="B335" t="str">
-        <v>EQ-BP-0007</v>
+        <v>EQ-BP-0006</v>
       </c>
       <c r="C335" t="str">
         <v>EQUIPMENT</v>
@@ -12121,7 +12121,7 @@
         <v>เครื่องวัตความดันโลหิตอัตโนมัติ</v>
       </c>
       <c r="K335" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (36-2/10)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (36-1/10)</v>
       </c>
     </row>
     <row r="336">
@@ -12129,7 +12129,7 @@
         <v>เครื่องวัดความดันโลหิตอัตโนมัติ</v>
       </c>
       <c r="B336" t="str">
-        <v>EQ-BP-0008</v>
+        <v>EQ-BP-0007</v>
       </c>
       <c r="C336" t="str">
         <v>EQUIPMENT</v>
@@ -12156,7 +12156,7 @@
         <v>เครื่องวัตความดันโลหิตอัตโนมัติ</v>
       </c>
       <c r="K336" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (36-3/10)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (36-2/10)</v>
       </c>
     </row>
     <row r="337">
@@ -12164,7 +12164,7 @@
         <v>เครื่องวัดความดันโลหิตอัตโนมัติ</v>
       </c>
       <c r="B337" t="str">
-        <v>EQ-BP-0009</v>
+        <v>EQ-BP-0008</v>
       </c>
       <c r="C337" t="str">
         <v>EQUIPMENT</v>
@@ -12191,7 +12191,7 @@
         <v>เครื่องวัตความดันโลหิตอัตโนมัติ</v>
       </c>
       <c r="K337" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (36-4/10)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (36-3/10)</v>
       </c>
     </row>
     <row r="338">
@@ -12199,7 +12199,7 @@
         <v>เครื่องวัดความดันโลหิตอัตโนมัติ</v>
       </c>
       <c r="B338" t="str">
-        <v>EQ-BP-0010</v>
+        <v>EQ-BP-0009</v>
       </c>
       <c r="C338" t="str">
         <v>EQUIPMENT</v>
@@ -12226,7 +12226,7 @@
         <v>เครื่องวัตความดันโลหิตอัตโนมัติ</v>
       </c>
       <c r="K338" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (36-5/10)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (36-4/10)</v>
       </c>
     </row>
     <row r="339">
@@ -12234,7 +12234,7 @@
         <v>เครื่องวัดความดันโลหิตอัตโนมัติ</v>
       </c>
       <c r="B339" t="str">
-        <v>EQ-BP-0011</v>
+        <v>EQ-BP-0010</v>
       </c>
       <c r="C339" t="str">
         <v>EQUIPMENT</v>
@@ -12261,7 +12261,7 @@
         <v>เครื่องวัตความดันโลหิตอัตโนมัติ</v>
       </c>
       <c r="K339" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (36-6/10)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (36-5/10)</v>
       </c>
     </row>
     <row r="340">
@@ -12269,7 +12269,7 @@
         <v>เครื่องวัดความดันโลหิตอัตโนมัติ</v>
       </c>
       <c r="B340" t="str">
-        <v>EQ-BP-0012</v>
+        <v>EQ-BP-0011</v>
       </c>
       <c r="C340" t="str">
         <v>EQUIPMENT</v>
@@ -12296,7 +12296,7 @@
         <v>เครื่องวัตความดันโลหิตอัตโนมัติ</v>
       </c>
       <c r="K340" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (36-7/10)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (36-6/10)</v>
       </c>
     </row>
     <row r="341">
@@ -12304,7 +12304,7 @@
         <v>เครื่องวัดความดันโลหิตอัตโนมัติ</v>
       </c>
       <c r="B341" t="str">
-        <v>EQ-BP-0013</v>
+        <v>EQ-BP-0012</v>
       </c>
       <c r="C341" t="str">
         <v>EQUIPMENT</v>
@@ -12331,7 +12331,7 @@
         <v>เครื่องวัตความดันโลหิตอัตโนมัติ</v>
       </c>
       <c r="K341" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (36-8/10)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (36-7/10)</v>
       </c>
     </row>
     <row r="342">
@@ -12339,7 +12339,7 @@
         <v>เครื่องวัดความดันโลหิตอัตโนมัติ</v>
       </c>
       <c r="B342" t="str">
-        <v>EQ-BP-0014</v>
+        <v>EQ-BP-0013</v>
       </c>
       <c r="C342" t="str">
         <v>EQUIPMENT</v>
@@ -12366,7 +12366,7 @@
         <v>เครื่องวัตความดันโลหิตอัตโนมัติ</v>
       </c>
       <c r="K342" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (36-9/10)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (36-8/10)</v>
       </c>
     </row>
     <row r="343">
@@ -12374,7 +12374,7 @@
         <v>เครื่องวัดความดันโลหิตอัตโนมัติ</v>
       </c>
       <c r="B343" t="str">
-        <v>EQ-BP-0015</v>
+        <v>EQ-BP-0014</v>
       </c>
       <c r="C343" t="str">
         <v>EQUIPMENT</v>
@@ -12401,21 +12401,21 @@
         <v>เครื่องวัตความดันโลหิตอัตโนมัติ</v>
       </c>
       <c r="K343" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (36-10/10)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (36-9/10)</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>เครื่องชั่งน้ำหนักพร้อมเครื่องวัดส่วนสูง</v>
+        <v>เครื่องวัดความดันโลหิตอัตโนมัติ</v>
       </c>
       <c r="B344" t="str">
-        <v>EQ-MED-0004</v>
+        <v>EQ-BP-0015</v>
       </c>
       <c r="C344" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D344" t="str">
-        <v>เครื่องมือและอุปกรณ์การแพทย์ตรวจรักษา</v>
+        <v>เครื่องวัดความดันโลหิต</v>
       </c>
       <c r="E344" t="str">
         <v>เครื่อง</v>
@@ -12424,7 +12424,7 @@
         <v>1</v>
       </c>
       <c r="G344">
-        <v>8000</v>
+        <v>2900</v>
       </c>
       <c r="H344" t="str">
         <v>2024-06-28</v>
@@ -12433,18 +12433,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J344" t="str">
-        <v>เครื่องชั่งน้ำหนักพร้อมเครื่องวัดส่วนสูง</v>
+        <v>เครื่องวัตความดันโลหิตอัตโนมัติ</v>
       </c>
       <c r="K344" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (37-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (36-10/10)</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>เครื่องตรวจน้ำตาลในเลือด</v>
+        <v>เครื่องชั่งน้ำหนักพร้อมเครื่องวัดส่วนสูง</v>
       </c>
       <c r="B345" t="str">
-        <v>EQ-MED-0005</v>
+        <v>EQ-MED-0004</v>
       </c>
       <c r="C345" t="str">
         <v>EQUIPMENT</v>
@@ -12459,7 +12459,7 @@
         <v>1</v>
       </c>
       <c r="G345">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="H345" t="str">
         <v>2024-06-28</v>
@@ -12468,10 +12468,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J345" t="str">
-        <v>เครื่องตรวจน้ำตาลในเลือด</v>
+        <v>เครื่องชั่งน้ำหนักพร้อมเครื่องวัดส่วนสูง</v>
       </c>
       <c r="K345" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (38-1/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (37-1/1)</v>
       </c>
     </row>
     <row r="346">
@@ -12479,7 +12479,7 @@
         <v>เครื่องตรวจน้ำตาลในเลือด</v>
       </c>
       <c r="B346" t="str">
-        <v>EQ-MED-0006</v>
+        <v>EQ-MED-0005</v>
       </c>
       <c r="C346" t="str">
         <v>EQUIPMENT</v>
@@ -12506,30 +12506,30 @@
         <v>เครื่องตรวจน้ำตาลในเลือด</v>
       </c>
       <c r="K346" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (38-2/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (38-1/2)</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>ชุดตรวจหู</v>
+        <v>เครื่องตรวจน้ำตาลในเลือด</v>
       </c>
       <c r="B347" t="str">
-        <v>EQ-DIA-0011</v>
+        <v>EQ-MED-0006</v>
       </c>
       <c r="C347" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D347" t="str">
-        <v>ชุดตรวจหูตรวจตา</v>
+        <v>เครื่องมือและอุปกรณ์การแพทย์ตรวจรักษา</v>
       </c>
       <c r="E347" t="str">
-        <v>ชุด</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F347">
         <v>1</v>
       </c>
       <c r="G347">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="H347" t="str">
         <v>2024-06-28</v>
@@ -12538,18 +12538,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J347" t="str">
-        <v>ชุดตรวจหู</v>
+        <v>เครื่องตรวจน้ำตาลในเลือด</v>
       </c>
       <c r="K347" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (39-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (38-2/2)</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>ชุดตรวจตา</v>
+        <v>ชุดตรวจหู</v>
       </c>
       <c r="B348" t="str">
-        <v>EQ-DIA-0012</v>
+        <v>EQ-DIA-0011</v>
       </c>
       <c r="C348" t="str">
         <v>EQUIPMENT</v>
@@ -12564,7 +12564,7 @@
         <v>1</v>
       </c>
       <c r="G348">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="H348" t="str">
         <v>2024-06-28</v>
@@ -12573,24 +12573,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J348" t="str">
-        <v>ชุดตรวจตา</v>
+        <v>ชุดตรวจหู</v>
       </c>
       <c r="K348" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (40-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (39-1/1)</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>ชุดใส่ท่อช่วยหายใจ Laryngoscope</v>
+        <v>ชุดตรวจตา</v>
       </c>
       <c r="B349" t="str">
-        <v>EQ-LAR-0006</v>
+        <v>EQ-DIA-0012</v>
       </c>
       <c r="C349" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D349" t="str">
-        <v>ชุดใส่ท่อช่วยหายใจ</v>
+        <v>ชุดตรวจหูตรวจตา</v>
       </c>
       <c r="E349" t="str">
         <v>ชุด</v>
@@ -12599,7 +12599,7 @@
         <v>1</v>
       </c>
       <c r="G349">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="H349" t="str">
         <v>2024-06-28</v>
@@ -12608,33 +12608,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J349" t="str">
-        <v>Laryngoscope with blades สำหรับผู้ใหญ่</v>
+        <v>ชุดตรวจตา</v>
       </c>
       <c r="K349" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (41-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (40-1/1)</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>กระดานรองหลัง CPR</v>
+        <v>ชุดใส่ท่อช่วยหายใจ Laryngoscope</v>
       </c>
       <c r="B350" t="str">
-        <v>EQ-TRS-0004</v>
+        <v>EQ-LAR-0006</v>
       </c>
       <c r="C350" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D350" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
+        <v>ชุดใส่ท่อช่วยหายใจ</v>
       </c>
       <c r="E350" t="str">
-        <v>แผ่น</v>
+        <v>ชุด</v>
       </c>
       <c r="F350">
         <v>1</v>
       </c>
       <c r="G350">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="H350" t="str">
         <v>2024-06-28</v>
@@ -12643,10 +12643,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J350" t="str">
-        <v>กระดานรองสำหรับช่วยฟื้นคืนชีพ</v>
+        <v>Laryngoscope with blades สำหรับผู้ใหญ่</v>
       </c>
       <c r="K350" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (42-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (41-1/1)</v>
       </c>
     </row>
     <row r="351">

--- a/ข้อมูลครุภัณฑ์/Template_Items_and_Assets_v3.xlsx
+++ b/ข้อมูลครุภัณฑ์/Template_Items_and_Assets_v3.xlsx
@@ -2449,19 +2449,19 @@
         <v>1</v>
       </c>
       <c r="G59">
-        <v>79200</v>
+        <v>65000</v>
       </c>
       <c r="H59" t="str">
-        <v>2025-08-19</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I59" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J59" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
       </c>
       <c r="K59" t="str">
-        <v>1-B9701-FA17-65450010004/017-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (9-1/3)</v>
       </c>
     </row>
     <row r="60">
@@ -2484,19 +2484,19 @@
         <v>1</v>
       </c>
       <c r="G60">
-        <v>79200</v>
+        <v>65000</v>
       </c>
       <c r="H60" t="str">
-        <v>2025-08-19</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I60" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J60" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
       </c>
       <c r="K60" t="str">
-        <v>1-B9701-FA17-65450010004/018-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (9-2/3)</v>
       </c>
     </row>
     <row r="61">
@@ -2519,19 +2519,19 @@
         <v>1</v>
       </c>
       <c r="G61">
-        <v>79200</v>
+        <v>65000</v>
       </c>
       <c r="H61" t="str">
-        <v>2025-08-19</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I61" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J61" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
       </c>
       <c r="K61" t="str">
-        <v>1-B9701-FA17-65450010004/019-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (9-3/3)</v>
       </c>
     </row>
     <row r="62">
@@ -2566,7 +2566,7 @@
         <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
       </c>
       <c r="K62" t="str">
-        <v>1-B9701-FA17-65450010004/020-68</v>
+        <v>1-B9701-FA17-65450010004/017-68</v>
       </c>
     </row>
     <row r="63">
@@ -2601,7 +2601,7 @@
         <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
       </c>
       <c r="K63" t="str">
-        <v>1-B9701-FA17-65450010004/021-68</v>
+        <v>1-B9701-FA17-65450010004/018-68</v>
       </c>
     </row>
     <row r="64">
@@ -2636,7 +2636,7 @@
         <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
       </c>
       <c r="K64" t="str">
-        <v>1-B9701-FA17-65450010004/022-68</v>
+        <v>1-B9701-FA17-65450010004/019-68</v>
       </c>
     </row>
     <row r="65">
@@ -2671,7 +2671,7 @@
         <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
       </c>
       <c r="K65" t="str">
-        <v>1-B9701-FA17-65450010004/023-68</v>
+        <v>1-B9701-FA17-65450010004/020-68</v>
       </c>
     </row>
     <row r="66">
@@ -2706,7 +2706,7 @@
         <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
       </c>
       <c r="K66" t="str">
-        <v>1-B9701-FA17-65450010004/024-68</v>
+        <v>1-B9701-FA17-65450010004/021-68</v>
       </c>
     </row>
     <row r="67">
@@ -2741,7 +2741,7 @@
         <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
       </c>
       <c r="K67" t="str">
-        <v>1-B9701-FA17-65450010004/025-68</v>
+        <v>1-B9701-FA17-65450010004/022-68</v>
       </c>
     </row>
     <row r="68">
@@ -2776,56 +2776,56 @@
         <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
       </c>
       <c r="K68" t="str">
-        <v>1-B9701-FA17-65450010004/026-68</v>
+        <v>1-B9701-FA17-65450010004/023-68</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
       </c>
       <c r="B69" t="str">
-        <v>EQ-BRE-0001</v>
+        <v>EQ-URC-0021</v>
       </c>
       <c r="C69" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D69" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E69" t="str">
-        <v>ชุด</v>
+        <v>ตัว</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69">
-        <v>60000</v>
+        <v>79200</v>
       </c>
       <c r="H69" t="str">
-        <v>2024-06-28</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I69" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J69" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
       </c>
       <c r="K69" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (10-1/1)</v>
+        <v>1-B9701-FA17-65450010004/024-68</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
       </c>
       <c r="B70" t="str">
-        <v>EQ-BRE-0002</v>
+        <v>EQ-URC-0022</v>
       </c>
       <c r="C70" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D70" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E70" t="str">
         <v>ตัว</v>
@@ -2834,7 +2834,7 @@
         <v>1</v>
       </c>
       <c r="G70">
-        <v>64000</v>
+        <v>79200</v>
       </c>
       <c r="H70" t="str">
         <v>2025-08-19</v>
@@ -2843,24 +2843,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J70" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม (40201)</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
       </c>
       <c r="K70" t="str">
-        <v>1-B9701-FA17-65450010004/027-68</v>
+        <v>1-B9701-FA17-65450010004/025-68</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
       </c>
       <c r="B71" t="str">
-        <v>EQ-BRE-0003</v>
+        <v>EQ-URC-0023</v>
       </c>
       <c r="C71" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D71" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E71" t="str">
         <v>ตัว</v>
@@ -2869,7 +2869,7 @@
         <v>1</v>
       </c>
       <c r="G71">
-        <v>64000</v>
+        <v>79200</v>
       </c>
       <c r="H71" t="str">
         <v>2025-08-19</v>
@@ -2878,10 +2878,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J71" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม (40201)</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
       </c>
       <c r="K71" t="str">
-        <v>1-B9701-FA17-65450010004/028-68</v>
+        <v>1-B9701-FA17-65450010004/026-68</v>
       </c>
     </row>
     <row r="72">
@@ -2889,7 +2889,7 @@
         <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="B72" t="str">
-        <v>EQ-BRE-0004</v>
+        <v>EQ-BRE-0001</v>
       </c>
       <c r="C72" t="str">
         <v>EQUIPMENT</v>
@@ -2898,25 +2898,25 @@
         <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="E72" t="str">
-        <v>ตัว</v>
+        <v>ชุด</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
       <c r="G72">
-        <v>64000</v>
+        <v>60000</v>
       </c>
       <c r="H72" t="str">
-        <v>2025-08-19</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I72" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J72" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม (40201)</v>
+        <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="K72" t="str">
-        <v>1-B9701-FA17-65450010004/029-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (10-1/1)</v>
       </c>
     </row>
     <row r="73">
@@ -2924,7 +2924,7 @@
         <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="B73" t="str">
-        <v>EQ-BRE-0005</v>
+        <v>EQ-BRE-0002</v>
       </c>
       <c r="C73" t="str">
         <v>EQUIPMENT</v>
@@ -2951,7 +2951,7 @@
         <v>หุ่นฝึกการตรวจเต้านม (40201)</v>
       </c>
       <c r="K73" t="str">
-        <v>1-B9701-FA17-65450010004/030-68</v>
+        <v>1-B9701-FA17-65450010004/027-68</v>
       </c>
     </row>
     <row r="74">
@@ -2959,7 +2959,7 @@
         <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="B74" t="str">
-        <v>EQ-BRE-0006</v>
+        <v>EQ-BRE-0003</v>
       </c>
       <c r="C74" t="str">
         <v>EQUIPMENT</v>
@@ -2986,30 +2986,30 @@
         <v>หุ่นฝึกการตรวจเต้านม (40201)</v>
       </c>
       <c r="K74" t="str">
-        <v>1-B9701-FA17-65450010004/031-68</v>
+        <v>1-B9701-FA17-65450010004/028-68</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>หุ่นฝึกทำแผลและการดูแลแผล</v>
+        <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="B75" t="str">
-        <v>EQ-STI-0001</v>
+        <v>EQ-BRE-0004</v>
       </c>
       <c r="C75" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D75" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="E75" t="str">
-        <v>ชุด</v>
+        <v>ตัว</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="G75">
-        <v>60000</v>
+        <v>64000</v>
       </c>
       <c r="H75" t="str">
         <v>2025-08-19</v>
@@ -3018,33 +3018,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J75" t="str">
-        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล (P100)</v>
+        <v>หุ่นฝึกการตรวจเต้านม (40201)</v>
       </c>
       <c r="K75" t="str">
-        <v>1-B9701-FA17-65450010004/032-68</v>
+        <v>1-B9701-FA17-65450010004/029-68</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>หุ่นฝึกทำแผลและการดูแลแผล</v>
+        <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="B76" t="str">
-        <v>EQ-STI-0002</v>
+        <v>EQ-BRE-0005</v>
       </c>
       <c r="C76" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D76" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="E76" t="str">
-        <v>ชุด</v>
+        <v>ตัว</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76">
-        <v>60000</v>
+        <v>64000</v>
       </c>
       <c r="H76" t="str">
         <v>2025-08-19</v>
@@ -3053,33 +3053,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J76" t="str">
-        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล (P100)</v>
+        <v>หุ่นฝึกการตรวจเต้านม (40201)</v>
       </c>
       <c r="K76" t="str">
-        <v>1-B9701-FA17-65450010004/033-68</v>
+        <v>1-B9701-FA17-65450010004/030-68</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>หุ่นฝึกทำแผลและการดูแลแผล</v>
+        <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="B77" t="str">
-        <v>EQ-STI-0003</v>
+        <v>EQ-BRE-0006</v>
       </c>
       <c r="C77" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D77" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="E77" t="str">
-        <v>ชุด</v>
+        <v>ตัว</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77">
-        <v>60000</v>
+        <v>64000</v>
       </c>
       <c r="H77" t="str">
         <v>2025-08-19</v>
@@ -3088,10 +3088,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J77" t="str">
-        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล (P100)</v>
+        <v>หุ่นฝึกการตรวจเต้านม (40201)</v>
       </c>
       <c r="K77" t="str">
-        <v>1-B9701-FA17-65450010004/034-68</v>
+        <v>1-B9701-FA17-65450010004/031-68</v>
       </c>
     </row>
     <row r="78">
@@ -3099,7 +3099,7 @@
         <v>หุ่นฝึกทำแผลและการดูแลแผล</v>
       </c>
       <c r="B78" t="str">
-        <v>EQ-STI-0004</v>
+        <v>EQ-STI-0001</v>
       </c>
       <c r="C78" t="str">
         <v>EQUIPMENT</v>
@@ -3126,7 +3126,7 @@
         <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล (P100)</v>
       </c>
       <c r="K78" t="str">
-        <v>1-B9701-FA17-65450010004/035-68</v>
+        <v>1-B9701-FA17-65450010004/032-68</v>
       </c>
     </row>
     <row r="79">
@@ -3134,7 +3134,7 @@
         <v>หุ่นฝึกทำแผลและการดูแลแผล</v>
       </c>
       <c r="B79" t="str">
-        <v>EQ-STI-0005</v>
+        <v>EQ-STI-0002</v>
       </c>
       <c r="C79" t="str">
         <v>EQUIPMENT</v>
@@ -3161,15 +3161,15 @@
         <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล (P100)</v>
       </c>
       <c r="K79" t="str">
-        <v>1-B9701-FA17-65450010004/036-68</v>
+        <v>1-B9701-FA17-65450010004/033-68</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>หุ่นแขนฝึกการเย็บแผล</v>
+        <v>หุ่นฝึกทำแผลและการดูแลแผล</v>
       </c>
       <c r="B80" t="str">
-        <v>EQ-STI-0006</v>
+        <v>EQ-STI-0003</v>
       </c>
       <c r="C80" t="str">
         <v>EQUIPMENT</v>
@@ -3184,7 +3184,7 @@
         <v>1</v>
       </c>
       <c r="G80">
-        <v>25000</v>
+        <v>60000</v>
       </c>
       <c r="H80" t="str">
         <v>2025-08-19</v>
@@ -3193,18 +3193,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J80" t="str">
-        <v>หุ่นแขนฝึกการเย็บแผล (P101)</v>
+        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล (P100)</v>
       </c>
       <c r="K80" t="str">
-        <v>1-B9701-FA17-65450010004/037-68</v>
+        <v>1-B9701-FA17-65450010004/034-68</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>หุ่นแขนฝึกการเย็บแผล</v>
+        <v>หุ่นฝึกทำแผลและการดูแลแผล</v>
       </c>
       <c r="B81" t="str">
-        <v>EQ-STI-0007</v>
+        <v>EQ-STI-0004</v>
       </c>
       <c r="C81" t="str">
         <v>EQUIPMENT</v>
@@ -3219,7 +3219,7 @@
         <v>1</v>
       </c>
       <c r="G81">
-        <v>25000</v>
+        <v>60000</v>
       </c>
       <c r="H81" t="str">
         <v>2025-08-19</v>
@@ -3228,18 +3228,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J81" t="str">
-        <v>หุ่นแขนฝึกการเย็บแผล (P101)</v>
+        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล (P100)</v>
       </c>
       <c r="K81" t="str">
-        <v>1-B9701-FA17-65450010004/038-68</v>
+        <v>1-B9701-FA17-65450010004/035-68</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>หุ่นแขนฝึกการเย็บแผล</v>
+        <v>หุ่นฝึกทำแผลและการดูแลแผล</v>
       </c>
       <c r="B82" t="str">
-        <v>EQ-STI-0008</v>
+        <v>EQ-STI-0005</v>
       </c>
       <c r="C82" t="str">
         <v>EQUIPMENT</v>
@@ -3254,7 +3254,7 @@
         <v>1</v>
       </c>
       <c r="G82">
-        <v>25000</v>
+        <v>60000</v>
       </c>
       <c r="H82" t="str">
         <v>2025-08-19</v>
@@ -3263,10 +3263,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J82" t="str">
-        <v>หุ่นแขนฝึกการเย็บแผล (P101)</v>
+        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล (P100)</v>
       </c>
       <c r="K82" t="str">
-        <v>1-B9701-FA17-65450010004/039-68</v>
+        <v>1-B9701-FA17-65450010004/036-68</v>
       </c>
     </row>
     <row r="83">
@@ -3274,7 +3274,7 @@
         <v>หุ่นแขนฝึกการเย็บแผล</v>
       </c>
       <c r="B83" t="str">
-        <v>EQ-STI-0009</v>
+        <v>EQ-STI-0006</v>
       </c>
       <c r="C83" t="str">
         <v>EQUIPMENT</v>
@@ -3301,15 +3301,15 @@
         <v>หุ่นแขนฝึกการเย็บแผล (P101)</v>
       </c>
       <c r="K83" t="str">
-        <v>1-B9701-FA17-65450010004/040-68</v>
+        <v>1-B9701-FA17-65450010004/037-68</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>หุ่นขาฝึกเย็บแผล</v>
+        <v>หุ่นแขนฝึกการเย็บแผล</v>
       </c>
       <c r="B84" t="str">
-        <v>EQ-STI-0010</v>
+        <v>EQ-STI-0007</v>
       </c>
       <c r="C84" t="str">
         <v>EQUIPMENT</v>
@@ -3324,7 +3324,7 @@
         <v>1</v>
       </c>
       <c r="G84">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="H84" t="str">
         <v>2025-08-19</v>
@@ -3333,18 +3333,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J84" t="str">
-        <v>หุ่นขาฝึกเย็บแผล (LF01034)</v>
+        <v>หุ่นแขนฝึกการเย็บแผล (P101)</v>
       </c>
       <c r="K84" t="str">
-        <v>1-B9701-FA17-65450010004/041-68</v>
+        <v>1-B9701-FA17-65450010004/038-68</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>หุ่นขาฝึกเย็บแผล</v>
+        <v>หุ่นแขนฝึกการเย็บแผล</v>
       </c>
       <c r="B85" t="str">
-        <v>EQ-STI-0011</v>
+        <v>EQ-STI-0008</v>
       </c>
       <c r="C85" t="str">
         <v>EQUIPMENT</v>
@@ -3359,7 +3359,7 @@
         <v>1</v>
       </c>
       <c r="G85">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="H85" t="str">
         <v>2025-08-19</v>
@@ -3368,18 +3368,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J85" t="str">
-        <v>หุ่นขาฝึกเย็บแผล (LF01034)</v>
+        <v>หุ่นแขนฝึกการเย็บแผล (P101)</v>
       </c>
       <c r="K85" t="str">
-        <v>1-B9701-FA17-65450010004/042-68</v>
+        <v>1-B9701-FA17-65450010004/039-68</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>หุ่นขาฝึกเย็บแผล</v>
+        <v>หุ่นแขนฝึกการเย็บแผล</v>
       </c>
       <c r="B86" t="str">
-        <v>EQ-STI-0012</v>
+        <v>EQ-STI-0009</v>
       </c>
       <c r="C86" t="str">
         <v>EQUIPMENT</v>
@@ -3394,7 +3394,7 @@
         <v>1</v>
       </c>
       <c r="G86">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="H86" t="str">
         <v>2025-08-19</v>
@@ -3403,10 +3403,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J86" t="str">
-        <v>หุ่นขาฝึกเย็บแผล (LF01034)</v>
+        <v>หุ่นแขนฝึกการเย็บแผล (P101)</v>
       </c>
       <c r="K86" t="str">
-        <v>1-B9701-FA17-65450010004/043-68</v>
+        <v>1-B9701-FA17-65450010004/040-68</v>
       </c>
     </row>
     <row r="87">
@@ -3414,7 +3414,7 @@
         <v>หุ่นขาฝึกเย็บแผล</v>
       </c>
       <c r="B87" t="str">
-        <v>EQ-STI-0013</v>
+        <v>EQ-STI-0010</v>
       </c>
       <c r="C87" t="str">
         <v>EQUIPMENT</v>
@@ -3441,15 +3441,15 @@
         <v>หุ่นขาฝึกเย็บแผล (LF01034)</v>
       </c>
       <c r="K87" t="str">
-        <v>1-B9701-FA17-65450010004/044-68</v>
+        <v>1-B9701-FA17-65450010004/041-68</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นขาฝึกเย็บแผล</v>
       </c>
       <c r="B88" t="str">
-        <v>EQ-STI-0014</v>
+        <v>EQ-STI-0011</v>
       </c>
       <c r="C88" t="str">
         <v>EQUIPMENT</v>
@@ -3464,27 +3464,27 @@
         <v>1</v>
       </c>
       <c r="G88">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="H88" t="str">
-        <v>2024-06-28</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I88" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J88" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นขาฝึกเย็บแผล (LF01034)</v>
       </c>
       <c r="K88" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (13-1/2)</v>
+        <v>1-B9701-FA17-65450010004/042-68</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นขาฝึกเย็บแผล</v>
       </c>
       <c r="B89" t="str">
-        <v>EQ-STI-0015</v>
+        <v>EQ-STI-0012</v>
       </c>
       <c r="C89" t="str">
         <v>EQUIPMENT</v>
@@ -3499,27 +3499,27 @@
         <v>1</v>
       </c>
       <c r="G89">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="H89" t="str">
-        <v>2024-06-28</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I89" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J89" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นขาฝึกเย็บแผล (LF01034)</v>
       </c>
       <c r="K89" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (13-2/2)</v>
+        <v>1-B9701-FA17-65450010004/043-68</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นขาฝึกเย็บแผล</v>
       </c>
       <c r="B90" t="str">
-        <v>EQ-STI-0016</v>
+        <v>EQ-STI-0013</v>
       </c>
       <c r="C90" t="str">
         <v>EQUIPMENT</v>
@@ -3534,7 +3534,7 @@
         <v>1</v>
       </c>
       <c r="G90">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="H90" t="str">
         <v>2025-08-19</v>
@@ -3543,10 +3543,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J90" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นขาฝึกเย็บแผล (LF01034)</v>
       </c>
       <c r="K90" t="str">
-        <v>1-B9701-FA17-65450010004/045-68</v>
+        <v>1-B9701-FA17-65450010004/044-68</v>
       </c>
     </row>
     <row r="91">
@@ -3554,7 +3554,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B91" t="str">
-        <v>EQ-STI-0017</v>
+        <v>EQ-STI-0014</v>
       </c>
       <c r="C91" t="str">
         <v>EQUIPMENT</v>
@@ -3569,10 +3569,10 @@
         <v>1</v>
       </c>
       <c r="G91">
-        <v>40000</v>
+        <v>25000</v>
       </c>
       <c r="H91" t="str">
-        <v>2025-08-19</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I91" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3581,7 +3581,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K91" t="str">
-        <v>1-B9701-FA17-65450010004/046-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (13-1/2)</v>
       </c>
     </row>
     <row r="92">
@@ -3589,7 +3589,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B92" t="str">
-        <v>EQ-STI-0018</v>
+        <v>EQ-STI-0015</v>
       </c>
       <c r="C92" t="str">
         <v>EQUIPMENT</v>
@@ -3604,10 +3604,10 @@
         <v>1</v>
       </c>
       <c r="G92">
-        <v>40000</v>
+        <v>25000</v>
       </c>
       <c r="H92" t="str">
-        <v>2025-08-19</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I92" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3616,7 +3616,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K92" t="str">
-        <v>1-B9701-FA17-65450010004/047-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (13-2/2)</v>
       </c>
     </row>
     <row r="93">
@@ -3624,7 +3624,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B93" t="str">
-        <v>EQ-STI-0019</v>
+        <v>EQ-STI-0016</v>
       </c>
       <c r="C93" t="str">
         <v>EQUIPMENT</v>
@@ -3651,7 +3651,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K93" t="str">
-        <v>1-B9701-FA17-65450010004/048-68</v>
+        <v>1-B9701-FA17-65450010004/045-68</v>
       </c>
     </row>
     <row r="94">
@@ -3659,7 +3659,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B94" t="str">
-        <v>EQ-STI-0020</v>
+        <v>EQ-STI-0017</v>
       </c>
       <c r="C94" t="str">
         <v>EQUIPMENT</v>
@@ -3686,7 +3686,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K94" t="str">
-        <v>1-B9701-FA17-65450010004/049-68</v>
+        <v>1-B9701-FA17-65450010004/046-68</v>
       </c>
     </row>
     <row r="95">
@@ -3694,7 +3694,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B95" t="str">
-        <v>EQ-STI-0021</v>
+        <v>EQ-STI-0018</v>
       </c>
       <c r="C95" t="str">
         <v>EQUIPMENT</v>
@@ -3721,7 +3721,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K95" t="str">
-        <v>1-B9701-FA17-65450010004/050-68</v>
+        <v>1-B9701-FA17-65450010004/047-68</v>
       </c>
     </row>
     <row r="96">
@@ -3729,7 +3729,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B96" t="str">
-        <v>EQ-STI-0022</v>
+        <v>EQ-STI-0019</v>
       </c>
       <c r="C96" t="str">
         <v>EQUIPMENT</v>
@@ -3756,7 +3756,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K96" t="str">
-        <v>1-B9701-FA17-65450010004/051-68</v>
+        <v>1-B9701-FA17-65450010004/048-68</v>
       </c>
     </row>
     <row r="97">
@@ -3764,7 +3764,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B97" t="str">
-        <v>EQ-STI-0023</v>
+        <v>EQ-STI-0020</v>
       </c>
       <c r="C97" t="str">
         <v>EQUIPMENT</v>
@@ -3791,7 +3791,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K97" t="str">
-        <v>1-B9701-FA17-65450010004/052-68</v>
+        <v>1-B9701-FA17-65450010004/049-68</v>
       </c>
     </row>
     <row r="98">
@@ -3799,7 +3799,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B98" t="str">
-        <v>EQ-STI-0051</v>
+        <v>EQ-STI-0021</v>
       </c>
       <c r="C98" t="str">
         <v>EQUIPMENT</v>
@@ -3826,7 +3826,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K98" t="str">
-        <v>1-B9701-FA17-65450010004/053-68</v>
+        <v>1-B9701-FA17-65450010004/050-68</v>
       </c>
     </row>
     <row r="99">
@@ -3834,7 +3834,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B99" t="str">
-        <v>EQ-STI-0052</v>
+        <v>EQ-STI-0022</v>
       </c>
       <c r="C99" t="str">
         <v>EQUIPMENT</v>
@@ -3861,21 +3861,21 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K99" t="str">
-        <v>1-B9701-FA17-65450010004/054-68</v>
+        <v>1-B9701-FA17-65450010004/051-68</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>SAM</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B100" t="str">
-        <v>EQ-SAM-0001</v>
+        <v>EQ-STI-0023</v>
       </c>
       <c r="C100" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D100" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E100" t="str">
         <v>ชุด</v>
@@ -3884,7 +3884,7 @@
         <v>1</v>
       </c>
       <c r="G100">
-        <v>735000</v>
+        <v>40000</v>
       </c>
       <c r="H100" t="str">
         <v>2025-08-19</v>
@@ -3893,24 +3893,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J100" t="str">
-        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K100" t="str">
-        <v>1-B9701-FA17-65450010004/055-68</v>
+        <v>1-B9701-FA17-65450010004/052-68</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>SAM</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B101" t="str">
-        <v>EQ-SAM-0002</v>
+        <v>EQ-STI-0051</v>
       </c>
       <c r="C101" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D101" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E101" t="str">
         <v>ชุด</v>
@@ -3919,7 +3919,7 @@
         <v>1</v>
       </c>
       <c r="G101">
-        <v>735000</v>
+        <v>40000</v>
       </c>
       <c r="H101" t="str">
         <v>2025-08-19</v>
@@ -3928,24 +3928,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J101" t="str">
-        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K101" t="str">
-        <v>1-B9701-FA17-65450010004/056-68</v>
+        <v>1-B9701-FA17-65450010004/053-68</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>SAM</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B102" t="str">
-        <v>EQ-SAM-0003</v>
+        <v>EQ-STI-0052</v>
       </c>
       <c r="C102" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D102" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E102" t="str">
         <v>ชุด</v>
@@ -3954,7 +3954,7 @@
         <v>1</v>
       </c>
       <c r="G102">
-        <v>735000</v>
+        <v>40000</v>
       </c>
       <c r="H102" t="str">
         <v>2025-08-19</v>
@@ -3963,10 +3963,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J102" t="str">
-        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K102" t="str">
-        <v>1-B9701-FA17-65450010004/057-68</v>
+        <v>1-B9701-FA17-65450010004/054-68</v>
       </c>
     </row>
     <row r="103">
@@ -3974,7 +3974,7 @@
         <v>SAM</v>
       </c>
       <c r="B103" t="str">
-        <v>EQ-SAM-0004</v>
+        <v>EQ-SAM-0001</v>
       </c>
       <c r="C103" t="str">
         <v>EQUIPMENT</v>
@@ -4001,7 +4001,7 @@
         <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
       </c>
       <c r="K103" t="str">
-        <v>1-B9701-FA17-65450010004/058-68</v>
+        <v>1-B9701-FA17-65450010004/055-68</v>
       </c>
     </row>
     <row r="104">
@@ -4009,7 +4009,7 @@
         <v>SAM</v>
       </c>
       <c r="B104" t="str">
-        <v>EQ-SAM-0005</v>
+        <v>EQ-SAM-0002</v>
       </c>
       <c r="C104" t="str">
         <v>EQUIPMENT</v>
@@ -4036,7 +4036,7 @@
         <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
       </c>
       <c r="K104" t="str">
-        <v>1-B9701-FA17-65450010004/059-68</v>
+        <v>1-B9701-FA17-65450010004/056-68</v>
       </c>
     </row>
     <row r="105">
@@ -4044,7 +4044,7 @@
         <v>SAM</v>
       </c>
       <c r="B105" t="str">
-        <v>EQ-SAM-0006</v>
+        <v>EQ-SAM-0003</v>
       </c>
       <c r="C105" t="str">
         <v>EQUIPMENT</v>
@@ -4071,7 +4071,7 @@
         <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
       </c>
       <c r="K105" t="str">
-        <v>1-B9701-FA17-65450010004/060-68</v>
+        <v>1-B9701-FA17-65450010004/057-68</v>
       </c>
     </row>
     <row r="106">
@@ -4079,7 +4079,7 @@
         <v>SAM</v>
       </c>
       <c r="B106" t="str">
-        <v>EQ-SAM-0007</v>
+        <v>EQ-SAM-0004</v>
       </c>
       <c r="C106" t="str">
         <v>EQUIPMENT</v>
@@ -4106,7 +4106,7 @@
         <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
       </c>
       <c r="K106" t="str">
-        <v>1-B9701-FA17-65450010004/061-68</v>
+        <v>1-B9701-FA17-65450010004/058-68</v>
       </c>
     </row>
     <row r="107">
@@ -4114,7 +4114,7 @@
         <v>SAM</v>
       </c>
       <c r="B107" t="str">
-        <v>EQ-SAM-0008</v>
+        <v>EQ-SAM-0005</v>
       </c>
       <c r="C107" t="str">
         <v>EQUIPMENT</v>
@@ -4141,7 +4141,7 @@
         <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
       </c>
       <c r="K107" t="str">
-        <v>1-B9701-FA17-65450010004/062-68</v>
+        <v>1-B9701-FA17-65450010004/059-68</v>
       </c>
     </row>
     <row r="108">
@@ -4149,7 +4149,7 @@
         <v>SAM</v>
       </c>
       <c r="B108" t="str">
-        <v>EQ-SAM-0009</v>
+        <v>EQ-SAM-0006</v>
       </c>
       <c r="C108" t="str">
         <v>EQUIPMENT</v>
@@ -4176,7 +4176,7 @@
         <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
       </c>
       <c r="K108" t="str">
-        <v>1-B9701-FA17-65450010004/063-68</v>
+        <v>1-B9701-FA17-65450010004/060-68</v>
       </c>
     </row>
     <row r="109">
@@ -4184,7 +4184,7 @@
         <v>SAM</v>
       </c>
       <c r="B109" t="str">
-        <v>EQ-SAM-0010</v>
+        <v>EQ-SAM-0007</v>
       </c>
       <c r="C109" t="str">
         <v>EQUIPMENT</v>
@@ -4211,21 +4211,21 @@
         <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
       </c>
       <c r="K109" t="str">
-        <v>1-B9701-FA17-65450010004/064-68</v>
+        <v>1-B9701-FA17-65450010004/061-68</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>SIM MAN</v>
+        <v>SAM</v>
       </c>
       <c r="B110" t="str">
-        <v>EQ-SIM-0006</v>
+        <v>EQ-SAM-0008</v>
       </c>
       <c r="C110" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D110" t="str">
-        <v>(SIM MAN) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E110" t="str">
         <v>ชุด</v>
@@ -4234,7 +4234,7 @@
         <v>1</v>
       </c>
       <c r="G110">
-        <v>4760000</v>
+        <v>735000</v>
       </c>
       <c r="H110" t="str">
         <v>2025-08-19</v>
@@ -4243,18 +4243,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J110" t="str">
-        <v>หุ่นจำลองสถานการณ์ทางการแพทย์และพยาบาลขั้นสูง (LeonardoHF)</v>
+        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
       </c>
       <c r="K110" t="str">
-        <v>1-B9701-FA17-65450010004/065-68</v>
+        <v>1-B9701-FA17-65450010004/062-68</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>SAM IPAD</v>
+        <v>SAM</v>
       </c>
       <c r="B111" t="str">
-        <v>EQ-SAM-0011</v>
+        <v>EQ-SAM-0009</v>
       </c>
       <c r="C111" t="str">
         <v>EQUIPMENT</v>
@@ -4263,13 +4263,13 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E111" t="str">
-        <v>เครื่อง</v>
+        <v>ชุด</v>
       </c>
       <c r="F111">
         <v>1</v>
       </c>
       <c r="G111">
-        <v>15000</v>
+        <v>735000</v>
       </c>
       <c r="H111" t="str">
         <v>2025-08-19</v>
@@ -4278,18 +4278,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J111" t="str">
-        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
+        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
       </c>
       <c r="K111" t="str">
-        <v>1-B9701-FA18-74400010005/001-68</v>
+        <v>1-B9701-FA17-65450010004/063-68</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>SAM IPAD</v>
+        <v>SAM</v>
       </c>
       <c r="B112" t="str">
-        <v>EQ-SAM-0012</v>
+        <v>EQ-SAM-0010</v>
       </c>
       <c r="C112" t="str">
         <v>EQUIPMENT</v>
@@ -4298,13 +4298,13 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E112" t="str">
-        <v>เครื่อง</v>
+        <v>ชุด</v>
       </c>
       <c r="F112">
         <v>1</v>
       </c>
       <c r="G112">
-        <v>15000</v>
+        <v>735000</v>
       </c>
       <c r="H112" t="str">
         <v>2025-08-19</v>
@@ -4313,33 +4313,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J112" t="str">
-        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
+        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
       </c>
       <c r="K112" t="str">
-        <v>1-B9701-FA18-74400010005/002-68</v>
+        <v>1-B9701-FA17-65450010004/064-68</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>SAM IPAD</v>
+        <v>SIM MAN</v>
       </c>
       <c r="B113" t="str">
-        <v>EQ-SAM-0013</v>
+        <v>EQ-SIM-0006</v>
       </c>
       <c r="C113" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D113" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>(SIM MAN) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E113" t="str">
-        <v>เครื่อง</v>
+        <v>ชุด</v>
       </c>
       <c r="F113">
         <v>1</v>
       </c>
       <c r="G113">
-        <v>15000</v>
+        <v>4760000</v>
       </c>
       <c r="H113" t="str">
         <v>2025-08-19</v>
@@ -4348,10 +4348,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J113" t="str">
-        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
+        <v>หุ่นจำลองสถานการณ์ทางการแพทย์และพยาบาลขั้นสูง (LeonardoHF)</v>
       </c>
       <c r="K113" t="str">
-        <v>1-B9701-FA18-74400010005/003-68</v>
+        <v>1-B9701-FA17-65450010004/065-68</v>
       </c>
     </row>
     <row r="114">
@@ -4359,7 +4359,7 @@
         <v>SAM IPAD</v>
       </c>
       <c r="B114" t="str">
-        <v>EQ-SAM-0014</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="C114" t="str">
         <v>EQUIPMENT</v>
@@ -4386,7 +4386,7 @@
         <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
       </c>
       <c r="K114" t="str">
-        <v>1-B9701-FA18-74400010005/004-68</v>
+        <v>1-B9701-FA18-74400010005/001-68</v>
       </c>
     </row>
     <row r="115">
@@ -4394,7 +4394,7 @@
         <v>SAM IPAD</v>
       </c>
       <c r="B115" t="str">
-        <v>EQ-SAM-0015</v>
+        <v>EQ-SAM-0012</v>
       </c>
       <c r="C115" t="str">
         <v>EQUIPMENT</v>
@@ -4421,7 +4421,7 @@
         <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
       </c>
       <c r="K115" t="str">
-        <v>1-B9701-FA18-74400010005/005-68</v>
+        <v>1-B9701-FA18-74400010005/002-68</v>
       </c>
     </row>
     <row r="116">
@@ -4429,7 +4429,7 @@
         <v>SAM IPAD</v>
       </c>
       <c r="B116" t="str">
-        <v>EQ-SAM-0016</v>
+        <v>EQ-SAM-0013</v>
       </c>
       <c r="C116" t="str">
         <v>EQUIPMENT</v>
@@ -4456,7 +4456,7 @@
         <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
       </c>
       <c r="K116" t="str">
-        <v>1-B9701-FA18-74400010005/006-68</v>
+        <v>1-B9701-FA18-74400010005/003-68</v>
       </c>
     </row>
     <row r="117">
@@ -4464,7 +4464,7 @@
         <v>SAM IPAD</v>
       </c>
       <c r="B117" t="str">
-        <v>EQ-SAM-0017</v>
+        <v>EQ-SAM-0014</v>
       </c>
       <c r="C117" t="str">
         <v>EQUIPMENT</v>
@@ -4491,7 +4491,7 @@
         <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
       </c>
       <c r="K117" t="str">
-        <v>1-B9701-FA18-74400010005/007-68</v>
+        <v>1-B9701-FA18-74400010005/004-68</v>
       </c>
     </row>
     <row r="118">
@@ -4499,7 +4499,7 @@
         <v>SAM IPAD</v>
       </c>
       <c r="B118" t="str">
-        <v>EQ-SAM-0018</v>
+        <v>EQ-SAM-0015</v>
       </c>
       <c r="C118" t="str">
         <v>EQUIPMENT</v>
@@ -4526,7 +4526,7 @@
         <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
       </c>
       <c r="K118" t="str">
-        <v>1-B9701-FA18-74400010005/008-68</v>
+        <v>1-B9701-FA18-74400010005/005-68</v>
       </c>
     </row>
     <row r="119">
@@ -4534,7 +4534,7 @@
         <v>SAM IPAD</v>
       </c>
       <c r="B119" t="str">
-        <v>EQ-SAM-0019</v>
+        <v>EQ-SAM-0016</v>
       </c>
       <c r="C119" t="str">
         <v>EQUIPMENT</v>
@@ -4561,7 +4561,7 @@
         <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
       </c>
       <c r="K119" t="str">
-        <v>1-B9701-FA18-74400010005/009-68</v>
+        <v>1-B9701-FA18-74400010005/006-68</v>
       </c>
     </row>
     <row r="120">
@@ -4569,7 +4569,7 @@
         <v>SAM IPAD</v>
       </c>
       <c r="B120" t="str">
-        <v>EQ-SAM-0020</v>
+        <v>EQ-SAM-0017</v>
       </c>
       <c r="C120" t="str">
         <v>EQUIPMENT</v>
@@ -4596,30 +4596,30 @@
         <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
       </c>
       <c r="K120" t="str">
-        <v>1-B9701-FA18-74400010005/010-68</v>
+        <v>1-B9701-FA18-74400010005/007-68</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Body Interact</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="B121" t="str">
-        <v>EQ-BI-0001</v>
+        <v>EQ-SAM-0018</v>
       </c>
       <c r="C121" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D121" t="str">
-        <v>เครื่องจำลองสถานการณ์ (BI)</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E121" t="str">
-        <v>ชุด</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F121">
         <v>1</v>
       </c>
       <c r="G121">
-        <v>4412000</v>
+        <v>15000</v>
       </c>
       <c r="H121" t="str">
         <v>2025-08-19</v>
@@ -4628,103 +4628,103 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J121" t="str">
-        <v>ระบบฝึกปฏิบัติการจำลองสถานการณ์ทางคลินิกแบบหน้าจอสัมผัส 30 สถานการณ์ Body Interact BI-30SW-4Y-TH</v>
+        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
       </c>
       <c r="K121" t="str">
-        <v>1-B9701-FA32-74400200001/001-68</v>
+        <v>1-B9701-FA18-74400010005/008-68</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>เตียงตรวจโรค</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="B122" t="str">
-        <v>EQ-BED-0003</v>
+        <v>EQ-SAM-0019</v>
       </c>
       <c r="C122" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D122" t="str">
-        <v>เตียงและตู้ข้างเตียง</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E122" t="str">
-        <v>หลัง</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F122">
         <v>1</v>
       </c>
       <c r="G122">
-        <v>10152</v>
+        <v>15000</v>
       </c>
       <c r="H122" t="str">
-        <v>2024-08-01</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I122" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 2</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J122" t="str">
-        <v>เตียงตรวจโรค</v>
+        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
       </c>
       <c r="K122" t="str">
-        <v>2-B9701-FD17-71050030001/001-67</v>
+        <v>1-B9701-FA18-74400010005/009-68</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="B123" t="str">
-        <v>EQ-TRS-0001</v>
+        <v>EQ-SAM-0020</v>
       </c>
       <c r="C123" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D123" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E123" t="str">
-        <v>แผ่น</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F123">
         <v>1</v>
       </c>
       <c r="G123">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="H123" t="str">
-        <v>2024-06-28</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I123" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J123" t="str">
-        <v>กระดานรองสำหรับช่วยฟื้นคืนชีพ</v>
+        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
       </c>
       <c r="K123" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (42-1/1)</v>
+        <v>1-B9701-FA18-74400010005/010-68</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
+        <v>Body Interact</v>
       </c>
       <c r="B124" t="str">
-        <v>EQ-TRS-0002</v>
+        <v>EQ-BI-0001</v>
       </c>
       <c r="C124" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D124" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
+        <v>เครื่องจำลองสถานการณ์ (BI)</v>
       </c>
       <c r="E124" t="str">
-        <v>แผ่น</v>
+        <v>ชุด</v>
       </c>
       <c r="F124">
         <v>1</v>
       </c>
       <c r="G124">
-        <v>1000</v>
+        <v>4412000</v>
       </c>
       <c r="H124" t="str">
         <v>2025-08-19</v>
@@ -4733,45 +4733,45 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J124" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR (CPR-B)</v>
+        <v>ระบบฝึกปฏิบัติการจำลองสถานการณ์ทางคลินิกแบบหน้าจอสัมผัส 30 สถานการณ์ Body Interact BI-30SW-4Y-TH</v>
       </c>
       <c r="K124" t="str">
-        <v>1-B9701-FN17-65450010002/001-68</v>
+        <v>1-B9701-FA32-74400200001/001-68</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
+        <v>เตียงตรวจโรค</v>
       </c>
       <c r="B125" t="str">
-        <v>EQ-TRS-0003</v>
+        <v>EQ-BED-0003</v>
       </c>
       <c r="C125" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D125" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
+        <v>เตียงและตู้ข้างเตียง</v>
       </c>
       <c r="E125" t="str">
-        <v>แผ่น</v>
+        <v>หลัง</v>
       </c>
       <c r="F125">
         <v>1</v>
       </c>
       <c r="G125">
-        <v>1000</v>
+        <v>10152</v>
       </c>
       <c r="H125" t="str">
-        <v>2025-08-19</v>
+        <v>2024-08-01</v>
       </c>
       <c r="I125" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 2</v>
       </c>
       <c r="J125" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR (CPR-B)</v>
+        <v>เตียงตรวจโรค</v>
       </c>
       <c r="K125" t="str">
-        <v>1-B9701-FN17-65450010002/002-68</v>
+        <v>2-B9701-FD17-71050030001/001-67</v>
       </c>
     </row>
     <row r="126">
@@ -4779,7 +4779,7 @@
         <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="B126" t="str">
-        <v>EQ-TRS-0004</v>
+        <v>EQ-TRS-0001</v>
       </c>
       <c r="C126" t="str">
         <v>EQUIPMENT</v>
@@ -4794,33 +4794,33 @@
         <v>1</v>
       </c>
       <c r="G126">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="H126" t="str">
-        <v>2025-08-19</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I126" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J126" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR (CPR-B)</v>
+        <v>กระดานรองสำหรับช่วยฟื้นคืนชีพ</v>
       </c>
       <c r="K126" t="str">
-        <v>1-B9701-FN17-65450010002/003-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (42-1/1)</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="B127" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-TRS-0002</v>
       </c>
       <c r="C127" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D127" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="E127" t="str">
         <v>แผ่น</v>
@@ -4829,7 +4829,7 @@
         <v>1</v>
       </c>
       <c r="G127">
-        <v>4700</v>
+        <v>1000</v>
       </c>
       <c r="H127" t="str">
         <v>2025-08-19</v>
@@ -4838,24 +4838,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J127" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR (CPR-B)</v>
       </c>
       <c r="K127" t="str">
-        <v>1-B9701-FN17-65450010002/004-68</v>
+        <v>1-B9701-FN17-65450010002/001-68</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="B128" t="str">
-        <v>EQ-STI-0025</v>
+        <v>EQ-TRS-0003</v>
       </c>
       <c r="C128" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D128" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="E128" t="str">
         <v>แผ่น</v>
@@ -4864,7 +4864,7 @@
         <v>1</v>
       </c>
       <c r="G128">
-        <v>4700</v>
+        <v>1000</v>
       </c>
       <c r="H128" t="str">
         <v>2025-08-19</v>
@@ -4873,24 +4873,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J128" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR (CPR-B)</v>
       </c>
       <c r="K128" t="str">
-        <v>1-B9701-FN17-65450010002/005-68</v>
+        <v>1-B9701-FN17-65450010002/002-68</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="B129" t="str">
-        <v>EQ-STI-0026</v>
+        <v>EQ-TRS-0004</v>
       </c>
       <c r="C129" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D129" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="E129" t="str">
         <v>แผ่น</v>
@@ -4899,7 +4899,7 @@
         <v>1</v>
       </c>
       <c r="G129">
-        <v>4700</v>
+        <v>1000</v>
       </c>
       <c r="H129" t="str">
         <v>2025-08-19</v>
@@ -4908,10 +4908,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J129" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR (CPR-B)</v>
       </c>
       <c r="K129" t="str">
-        <v>1-B9701-FN17-65450010002/006-68</v>
+        <v>1-B9701-FN17-65450010002/003-68</v>
       </c>
     </row>
     <row r="130">
@@ -4919,7 +4919,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B130" t="str">
-        <v>EQ-STI-0027</v>
+        <v>EQ-STI-0024</v>
       </c>
       <c r="C130" t="str">
         <v>EQUIPMENT</v>
@@ -4946,7 +4946,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K130" t="str">
-        <v>1-B9701-FN17-65450010002/007-68</v>
+        <v>1-B9701-FN17-65450010002/004-68</v>
       </c>
     </row>
     <row r="131">
@@ -4954,7 +4954,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B131" t="str">
-        <v>EQ-STI-0028</v>
+        <v>EQ-STI-0025</v>
       </c>
       <c r="C131" t="str">
         <v>EQUIPMENT</v>
@@ -4981,7 +4981,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K131" t="str">
-        <v>1-B9701-FN17-65450010002/008-68</v>
+        <v>1-B9701-FN17-65450010002/005-68</v>
       </c>
     </row>
     <row r="132">
@@ -4989,7 +4989,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B132" t="str">
-        <v>EQ-STI-0029</v>
+        <v>EQ-STI-0026</v>
       </c>
       <c r="C132" t="str">
         <v>EQUIPMENT</v>
@@ -5016,7 +5016,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K132" t="str">
-        <v>1-B9701-FN17-65450010002/009-68</v>
+        <v>1-B9701-FN17-65450010002/006-68</v>
       </c>
     </row>
     <row r="133">
@@ -5024,7 +5024,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B133" t="str">
-        <v>EQ-STI-0030</v>
+        <v>EQ-STI-0027</v>
       </c>
       <c r="C133" t="str">
         <v>EQUIPMENT</v>
@@ -5051,7 +5051,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K133" t="str">
-        <v>1-B9701-FN17-65450010002/010-68</v>
+        <v>1-B9701-FN17-65450010002/007-68</v>
       </c>
     </row>
     <row r="134">
@@ -5059,7 +5059,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B134" t="str">
-        <v>EQ-STI-0031</v>
+        <v>EQ-STI-0028</v>
       </c>
       <c r="C134" t="str">
         <v>EQUIPMENT</v>
@@ -5086,7 +5086,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K134" t="str">
-        <v>1-B9701-FN17-65450010002/011-68</v>
+        <v>1-B9701-FN17-65450010002/008-68</v>
       </c>
     </row>
     <row r="135">
@@ -5094,7 +5094,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B135" t="str">
-        <v>EQ-STI-0032</v>
+        <v>EQ-STI-0029</v>
       </c>
       <c r="C135" t="str">
         <v>EQUIPMENT</v>
@@ -5121,7 +5121,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K135" t="str">
-        <v>1-B9701-FN17-65450010002/012-68</v>
+        <v>1-B9701-FN17-65450010002/009-68</v>
       </c>
     </row>
     <row r="136">
@@ -5129,7 +5129,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B136" t="str">
-        <v>EQ-STI-0033</v>
+        <v>EQ-STI-0030</v>
       </c>
       <c r="C136" t="str">
         <v>EQUIPMENT</v>
@@ -5156,7 +5156,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K136" t="str">
-        <v>1-B9701-FN17-65450010002/013-68</v>
+        <v>1-B9701-FN17-65450010002/010-68</v>
       </c>
     </row>
     <row r="137">
@@ -5164,7 +5164,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B137" t="str">
-        <v>EQ-STI-0034</v>
+        <v>EQ-STI-0031</v>
       </c>
       <c r="C137" t="str">
         <v>EQUIPMENT</v>
@@ -5191,7 +5191,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K137" t="str">
-        <v>1-B9701-FN17-65450010002/014-68</v>
+        <v>1-B9701-FN17-65450010002/011-68</v>
       </c>
     </row>
     <row r="138">
@@ -5199,7 +5199,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B138" t="str">
-        <v>EQ-STI-0035</v>
+        <v>EQ-STI-0032</v>
       </c>
       <c r="C138" t="str">
         <v>EQUIPMENT</v>
@@ -5226,7 +5226,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K138" t="str">
-        <v>1-B9701-FN17-65450010002/015-68</v>
+        <v>1-B9701-FN17-65450010002/012-68</v>
       </c>
     </row>
     <row r="139">
@@ -5234,7 +5234,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B139" t="str">
-        <v>EQ-STI-0036</v>
+        <v>EQ-STI-0033</v>
       </c>
       <c r="C139" t="str">
         <v>EQUIPMENT</v>
@@ -5261,7 +5261,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K139" t="str">
-        <v>1-B9701-FN17-65450010002/016-68</v>
+        <v>1-B9701-FN17-65450010002/013-68</v>
       </c>
     </row>
     <row r="140">
@@ -5269,7 +5269,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B140" t="str">
-        <v>EQ-STI-0037</v>
+        <v>EQ-STI-0034</v>
       </c>
       <c r="C140" t="str">
         <v>EQUIPMENT</v>
@@ -5296,7 +5296,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K140" t="str">
-        <v>1-B9701-FN17-65450010002/017-68</v>
+        <v>1-B9701-FN17-65450010002/014-68</v>
       </c>
     </row>
     <row r="141">
@@ -5304,7 +5304,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B141" t="str">
-        <v>EQ-STI-0038</v>
+        <v>EQ-STI-0035</v>
       </c>
       <c r="C141" t="str">
         <v>EQUIPMENT</v>
@@ -5331,7 +5331,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K141" t="str">
-        <v>1-B9701-FN17-65450010002/018-68</v>
+        <v>1-B9701-FN17-65450010002/015-68</v>
       </c>
     </row>
     <row r="142">
@@ -5339,7 +5339,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B142" t="str">
-        <v>EQ-STI-0039</v>
+        <v>EQ-STI-0036</v>
       </c>
       <c r="C142" t="str">
         <v>EQUIPMENT</v>
@@ -5366,7 +5366,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K142" t="str">
-        <v>1-B9701-FN17-65450010002/019-68</v>
+        <v>1-B9701-FN17-65450010002/016-68</v>
       </c>
     </row>
     <row r="143">
@@ -5374,7 +5374,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B143" t="str">
-        <v>EQ-STI-0040</v>
+        <v>EQ-STI-0037</v>
       </c>
       <c r="C143" t="str">
         <v>EQUIPMENT</v>
@@ -5401,7 +5401,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K143" t="str">
-        <v>1-B9701-FN17-65450010002/020-68</v>
+        <v>1-B9701-FN17-65450010002/017-68</v>
       </c>
     </row>
     <row r="144">
@@ -5409,7 +5409,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B144" t="str">
-        <v>EQ-STI-0041</v>
+        <v>EQ-STI-0038</v>
       </c>
       <c r="C144" t="str">
         <v>EQUIPMENT</v>
@@ -5436,7 +5436,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K144" t="str">
-        <v>1-B9701-FN17-65450010002/021-68</v>
+        <v>1-B9701-FN17-65450010002/018-68</v>
       </c>
     </row>
     <row r="145">
@@ -5444,7 +5444,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B145" t="str">
-        <v>EQ-STI-0042</v>
+        <v>EQ-STI-0039</v>
       </c>
       <c r="C145" t="str">
         <v>EQUIPMENT</v>
@@ -5471,7 +5471,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K145" t="str">
-        <v>1-B9701-FN17-65450010002/022-68</v>
+        <v>1-B9701-FN17-65450010002/019-68</v>
       </c>
     </row>
     <row r="146">
@@ -5479,7 +5479,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B146" t="str">
-        <v>EQ-STI-0043</v>
+        <v>EQ-STI-0040</v>
       </c>
       <c r="C146" t="str">
         <v>EQUIPMENT</v>
@@ -5506,30 +5506,30 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K146" t="str">
-        <v>1-B9701-FN17-65450010002/023-68</v>
+        <v>1-B9701-FN17-65450010002/020-68</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>แทบเล็ตสำหรับหุ่น AI</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B147" t="str">
-        <v>EQ-AI-0003</v>
+        <v>EQ-STI-0041</v>
       </c>
       <c r="C147" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D147" t="str">
-        <v>(หุ่น AI) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E147" t="str">
-        <v>ชุด</v>
+        <v>แผ่น</v>
       </c>
       <c r="F147">
         <v>1</v>
       </c>
       <c r="G147">
-        <v>5000</v>
+        <v>4700</v>
       </c>
       <c r="H147" t="str">
         <v>2025-08-19</v>
@@ -5538,33 +5538,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J147" t="str">
-        <v>แทบเล็ตสำหรับหุ่น AI (i-pad-alex)</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K147" t="str">
-        <v>1-B9701-FN18-74400010005/001-68</v>
+        <v>1-B9701-FN17-65450010002/021-68</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>แทบเล็ตสำหรับหุ่น AI</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B148" t="str">
-        <v>EQ-AI-0004</v>
+        <v>EQ-STI-0042</v>
       </c>
       <c r="C148" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D148" t="str">
-        <v>(หุ่น AI) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E148" t="str">
-        <v>ชุด</v>
+        <v>แผ่น</v>
       </c>
       <c r="F148">
         <v>1</v>
       </c>
       <c r="G148">
-        <v>5000</v>
+        <v>4700</v>
       </c>
       <c r="H148" t="str">
         <v>2025-08-19</v>
@@ -5573,33 +5573,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J148" t="str">
-        <v>แทบเล็ตสำหรับหุ่น AI (i-pad-alex)</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K148" t="str">
-        <v>1-B9701-FN18-74400010005/002-68</v>
+        <v>1-B9701-FN17-65450010002/022-68</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Android tablet</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B149" t="str">
-        <v>EQ-IT-0005</v>
+        <v>EQ-STI-0043</v>
       </c>
       <c r="C149" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D149" t="str">
-        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E149" t="str">
-        <v>เครื่อง</v>
+        <v>แผ่น</v>
       </c>
       <c r="F149">
         <v>1</v>
       </c>
       <c r="G149">
-        <v>4500</v>
+        <v>4700</v>
       </c>
       <c r="H149" t="str">
         <v>2025-08-19</v>
@@ -5608,33 +5608,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J149" t="str">
-        <v>Android tablet (AD-Tablet)</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K149" t="str">
-        <v>1-B9701-FN18-74400010005/003-68</v>
+        <v>1-B9701-FN17-65450010002/023-68</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Android tablet</v>
+        <v>แทบเล็ตสำหรับหุ่น AI</v>
       </c>
       <c r="B150" t="str">
-        <v>EQ-IT-0006</v>
+        <v>EQ-AI-0003</v>
       </c>
       <c r="C150" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D150" t="str">
-        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
+        <v>(หุ่น AI) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E150" t="str">
-        <v>เครื่อง</v>
+        <v>ชุด</v>
       </c>
       <c r="F150">
         <v>1</v>
       </c>
       <c r="G150">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="H150" t="str">
         <v>2025-08-19</v>
@@ -5643,33 +5643,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J150" t="str">
-        <v>Android tablet (AD-Tablet)</v>
+        <v>แทบเล็ตสำหรับหุ่น AI (i-pad-alex)</v>
       </c>
       <c r="K150" t="str">
-        <v>1-B9701-FN18-74400010005/004-68</v>
+        <v>1-B9701-FN18-74400010005/001-68</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Android tablet</v>
+        <v>แทบเล็ตสำหรับหุ่น AI</v>
       </c>
       <c r="B151" t="str">
-        <v>EQ-IT-0007</v>
+        <v>EQ-AI-0004</v>
       </c>
       <c r="C151" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D151" t="str">
-        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
+        <v>(หุ่น AI) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E151" t="str">
-        <v>เครื่อง</v>
+        <v>ชุด</v>
       </c>
       <c r="F151">
         <v>1</v>
       </c>
       <c r="G151">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="H151" t="str">
         <v>2025-08-19</v>
@@ -5678,24 +5678,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J151" t="str">
-        <v>Android tablet (AD-Tablet)</v>
+        <v>แทบเล็ตสำหรับหุ่น AI (i-pad-alex)</v>
       </c>
       <c r="K151" t="str">
-        <v>1-B9701-FN18-74400010005/005-68</v>
+        <v>1-B9701-FN18-74400010005/002-68</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>เครื่องสำรองไฟ (BI)</v>
+        <v>Android tablet</v>
       </c>
       <c r="B152" t="str">
-        <v>EQ-BI-0002</v>
+        <v>EQ-IT-0005</v>
       </c>
       <c r="C152" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D152" t="str">
-        <v>เครื่องจำลองสถานการณ์ (BI)</v>
+        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
       </c>
       <c r="E152" t="str">
         <v>เครื่อง</v>
@@ -5704,7 +5704,7 @@
         <v>1</v>
       </c>
       <c r="G152">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="H152" t="str">
         <v>2025-08-19</v>
@@ -5713,24 +5713,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J152" t="str">
-        <v>เครื่องสำรองไฟที่สามารถรองรับการไฟดับได้อย่างน้อย 15 นาที (UPS 1200W)</v>
+        <v>Android tablet (AD-Tablet)</v>
       </c>
       <c r="K152" t="str">
-        <v>1-B9701-FN18-74400090003/001-68</v>
+        <v>1-B9701-FN18-74400010005/003-68</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>เครื่องสำรองไฟ (BI)</v>
+        <v>Android tablet</v>
       </c>
       <c r="B153" t="str">
-        <v>EQ-BI-0003</v>
+        <v>EQ-IT-0006</v>
       </c>
       <c r="C153" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D153" t="str">
-        <v>เครื่องจำลองสถานการณ์ (BI)</v>
+        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
       </c>
       <c r="E153" t="str">
         <v>เครื่อง</v>
@@ -5739,7 +5739,7 @@
         <v>1</v>
       </c>
       <c r="G153">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="H153" t="str">
         <v>2025-08-19</v>
@@ -5748,18 +5748,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J153" t="str">
-        <v>เครื่องสำรองไฟที่สามารถรองรับการไฟดับได้อย่างน้อย 15 นาที (UPS 1200W)</v>
+        <v>Android tablet (AD-Tablet)</v>
       </c>
       <c r="K153" t="str">
-        <v>1-B9701-FN18-74400090003/002-68</v>
+        <v>1-B9701-FN18-74400010005/004-68</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>เครื่องพิมพ์</v>
+        <v>Android tablet</v>
       </c>
       <c r="B154" t="str">
-        <v>EQ-IT-0008</v>
+        <v>EQ-IT-0007</v>
       </c>
       <c r="C154" t="str">
         <v>EQUIPMENT</v>
@@ -5774,7 +5774,7 @@
         <v>1</v>
       </c>
       <c r="G154">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="H154" t="str">
         <v>2025-08-19</v>
@@ -5783,24 +5783,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J154" t="str">
-        <v>เครื่องพิมพ์ (IM-PT-PERI)</v>
+        <v>Android tablet (AD-Tablet)</v>
       </c>
       <c r="K154" t="str">
-        <v>1-B9701-FN18-74400120002/001-68</v>
+        <v>1-B9701-FN18-74400010005/005-68</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>เครื่องพิมพ์</v>
+        <v>เครื่องสำรองไฟ (BI)</v>
       </c>
       <c r="B155" t="str">
-        <v>EQ-IT-0009</v>
+        <v>EQ-BI-0002</v>
       </c>
       <c r="C155" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D155" t="str">
-        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
+        <v>เครื่องจำลองสถานการณ์ (BI)</v>
       </c>
       <c r="E155" t="str">
         <v>เครื่อง</v>
@@ -5809,7 +5809,7 @@
         <v>1</v>
       </c>
       <c r="G155">
-        <v>1500</v>
+        <v>4000</v>
       </c>
       <c r="H155" t="str">
         <v>2025-08-19</v>
@@ -5818,24 +5818,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J155" t="str">
-        <v>เครื่องพิมพ์ (IM-PT-PERI)</v>
+        <v>เครื่องสำรองไฟที่สามารถรองรับการไฟดับได้อย่างน้อย 15 นาที (UPS 1200W)</v>
       </c>
       <c r="K155" t="str">
-        <v>1-B9701-FN18-74400120002/002-68</v>
+        <v>1-B9701-FN18-74400090003/001-68</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>เครื่องพิมพ์</v>
+        <v>เครื่องสำรองไฟ (BI)</v>
       </c>
       <c r="B156" t="str">
-        <v>EQ-IT-0010</v>
+        <v>EQ-BI-0003</v>
       </c>
       <c r="C156" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D156" t="str">
-        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
+        <v>เครื่องจำลองสถานการณ์ (BI)</v>
       </c>
       <c r="E156" t="str">
         <v>เครื่อง</v>
@@ -5844,7 +5844,7 @@
         <v>1</v>
       </c>
       <c r="G156">
-        <v>1500</v>
+        <v>4000</v>
       </c>
       <c r="H156" t="str">
         <v>2025-08-19</v>
@@ -5853,115 +5853,115 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J156" t="str">
-        <v>เครื่องพิมพ์ (IM-PT-PERI)</v>
+        <v>เครื่องสำรองไฟที่สามารถรองรับการไฟดับได้อย่างน้อย 15 นาที (UPS 1200W)</v>
       </c>
       <c r="K156" t="str">
-        <v>1-B9701-FN18-74400120002/003-68</v>
+        <v>1-B9701-FN18-74400090003/002-68</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>เครื่องพิมพ์</v>
       </c>
       <c r="B157" t="str">
-        <v>EQ-FN-0001</v>
+        <v>EQ-IT-0008</v>
       </c>
       <c r="C157" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D157" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
       </c>
       <c r="E157" t="str">
-        <v>ตู้</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F157">
         <v>1</v>
       </c>
       <c r="G157">
-        <v>4500</v>
+        <v>1500</v>
       </c>
       <c r="H157" t="str">
-        <v>2024-08-01</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I157" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J157" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>เครื่องพิมพ์ (IM-PT-PERI)</v>
       </c>
       <c r="K157" t="str">
-        <v>2-B9701-FP05-71100150007/001-67</v>
+        <v>1-B9701-FN18-74400120002/001-68</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>เครื่องพิมพ์</v>
       </c>
       <c r="B158" t="str">
-        <v>EQ-FN-0002</v>
+        <v>EQ-IT-0009</v>
       </c>
       <c r="C158" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D158" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
       </c>
       <c r="E158" t="str">
-        <v>ตู้</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F158">
         <v>1</v>
       </c>
       <c r="G158">
-        <v>4500</v>
+        <v>1500</v>
       </c>
       <c r="H158" t="str">
-        <v>2024-08-01</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I158" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J158" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>เครื่องพิมพ์ (IM-PT-PERI)</v>
       </c>
       <c r="K158" t="str">
-        <v>2-B9701-FP05-71100150007/002-67</v>
+        <v>1-B9701-FN18-74400120002/002-68</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>เครื่องพิมพ์</v>
       </c>
       <c r="B159" t="str">
-        <v>EQ-FN-0003</v>
+        <v>EQ-IT-0010</v>
       </c>
       <c r="C159" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D159" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
       </c>
       <c r="E159" t="str">
-        <v>ตู้</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F159">
         <v>1</v>
       </c>
       <c r="G159">
-        <v>4500</v>
+        <v>1500</v>
       </c>
       <c r="H159" t="str">
-        <v>2024-08-01</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I159" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J159" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>เครื่องพิมพ์ (IM-PT-PERI)</v>
       </c>
       <c r="K159" t="str">
-        <v>2-B9701-FP05-71100150007/003-67</v>
+        <v>1-B9701-FN18-74400120002/003-68</v>
       </c>
     </row>
     <row r="160">
@@ -5969,7 +5969,7 @@
         <v>ตู้เก็บของ</v>
       </c>
       <c r="B160" t="str">
-        <v>EQ-FN-0004</v>
+        <v>EQ-FN-0001</v>
       </c>
       <c r="C160" t="str">
         <v>EQUIPMENT</v>
@@ -5996,7 +5996,7 @@
         <v>ตู้เก็บของ</v>
       </c>
       <c r="K160" t="str">
-        <v>2-B9701-FP05-71100150007/004-67</v>
+        <v>2-B9701-FP05-71100150007/001-67</v>
       </c>
     </row>
     <row r="161">
@@ -6004,7 +6004,7 @@
         <v>ตู้เก็บของ</v>
       </c>
       <c r="B161" t="str">
-        <v>EQ-FN-0005</v>
+        <v>EQ-FN-0002</v>
       </c>
       <c r="C161" t="str">
         <v>EQUIPMENT</v>
@@ -6025,13 +6025,13 @@
         <v>2024-08-01</v>
       </c>
       <c r="I161" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 2</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
       </c>
       <c r="J161" t="str">
         <v>ตู้เก็บของ</v>
       </c>
       <c r="K161" t="str">
-        <v>2-B9701-FP05-71100150007/005-67</v>
+        <v>2-B9701-FP05-71100150007/002-67</v>
       </c>
     </row>
     <row r="162">
@@ -6039,7 +6039,7 @@
         <v>ตู้เก็บของ</v>
       </c>
       <c r="B162" t="str">
-        <v>EQ-FN-0006</v>
+        <v>EQ-FN-0003</v>
       </c>
       <c r="C162" t="str">
         <v>EQUIPMENT</v>
@@ -6060,13 +6060,13 @@
         <v>2024-08-01</v>
       </c>
       <c r="I162" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
       </c>
       <c r="J162" t="str">
         <v>ตู้เก็บของ</v>
       </c>
       <c r="K162" t="str">
-        <v>2-B9701-FP05-71100150007/006-67</v>
+        <v>2-B9701-FP05-71100150007/003-67</v>
       </c>
     </row>
     <row r="163">
@@ -6074,7 +6074,7 @@
         <v>ตู้เก็บของ</v>
       </c>
       <c r="B163" t="str">
-        <v>EQ-FN-0007</v>
+        <v>EQ-FN-0004</v>
       </c>
       <c r="C163" t="str">
         <v>EQUIPMENT</v>
@@ -6095,118 +6095,118 @@
         <v>2024-08-01</v>
       </c>
       <c r="I163" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
       </c>
       <c r="J163" t="str">
         <v>ตู้เก็บของ</v>
       </c>
       <c r="K163" t="str">
-        <v>2-B9701-FP05-71100150007/007-67</v>
+        <v>2-B9701-FP05-71100150007/004-67</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>ชั้นวางของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="B164" t="str">
-        <v>EQ-FN-0008</v>
+        <v>EQ-FN-0005</v>
       </c>
       <c r="C164" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D164" t="str">
-        <v>ชั้นเก็บของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="E164" t="str">
-        <v>ชั้น</v>
+        <v>ตู้</v>
       </c>
       <c r="F164">
         <v>1</v>
       </c>
       <c r="G164">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="H164" t="str">
         <v>2024-08-01</v>
       </c>
       <c r="I164" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 2</v>
       </c>
       <c r="J164" t="str">
-        <v>ชั้นวางของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="K164" t="str">
-        <v>2-B9701-FP05-73300160001/001-67</v>
+        <v>2-B9701-FP05-71100150007/005-67</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>ชั้นวางของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="B165" t="str">
-        <v>EQ-FN-0009</v>
+        <v>EQ-FN-0006</v>
       </c>
       <c r="C165" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D165" t="str">
-        <v>ชั้นเก็บของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="E165" t="str">
-        <v>ชั้น</v>
+        <v>ตู้</v>
       </c>
       <c r="F165">
         <v>1</v>
       </c>
       <c r="G165">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="H165" t="str">
         <v>2024-08-01</v>
       </c>
       <c r="I165" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
       </c>
       <c r="J165" t="str">
-        <v>ชั้นวางของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="K165" t="str">
-        <v>2-B9701-FP05-73300160001/002-67</v>
+        <v>2-B9701-FP05-71100150007/006-67</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>ชั้นวางของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="B166" t="str">
-        <v>EQ-FN-0010</v>
+        <v>EQ-FN-0007</v>
       </c>
       <c r="C166" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D166" t="str">
-        <v>ชั้นเก็บของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="E166" t="str">
-        <v>ชั้น</v>
+        <v>ตู้</v>
       </c>
       <c r="F166">
         <v>1</v>
       </c>
       <c r="G166">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="H166" t="str">
         <v>2024-08-01</v>
       </c>
       <c r="I166" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
       </c>
       <c r="J166" t="str">
-        <v>ชั้นวางของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="K166" t="str">
-        <v>2-B9701-FP05-73300160001/003-67</v>
+        <v>2-B9701-FP05-71100150007/007-67</v>
       </c>
     </row>
     <row r="167">
@@ -6214,7 +6214,7 @@
         <v>ชั้นวางของ</v>
       </c>
       <c r="B167" t="str">
-        <v>EQ-FN-0011</v>
+        <v>EQ-FN-0008</v>
       </c>
       <c r="C167" t="str">
         <v>EQUIPMENT</v>
@@ -6235,13 +6235,13 @@
         <v>2024-08-01</v>
       </c>
       <c r="I167" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 2</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
       </c>
       <c r="J167" t="str">
         <v>ชั้นวางของ</v>
       </c>
       <c r="K167" t="str">
-        <v>2-B9701-FP05-73300160001/004-67</v>
+        <v>2-B9701-FP05-73300160001/001-67</v>
       </c>
     </row>
     <row r="168">
@@ -6249,7 +6249,7 @@
         <v>ชั้นวางของ</v>
       </c>
       <c r="B168" t="str">
-        <v>EQ-FN-0012</v>
+        <v>EQ-FN-0009</v>
       </c>
       <c r="C168" t="str">
         <v>EQUIPMENT</v>
@@ -6270,13 +6270,13 @@
         <v>2024-08-01</v>
       </c>
       <c r="I168" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
       </c>
       <c r="J168" t="str">
         <v>ชั้นวางของ</v>
       </c>
       <c r="K168" t="str">
-        <v>2-B9701-FP05-73300160001/005-67</v>
+        <v>2-B9701-FP05-73300160001/002-67</v>
       </c>
     </row>
     <row r="169">
@@ -6284,7 +6284,7 @@
         <v>ชั้นวางของ</v>
       </c>
       <c r="B169" t="str">
-        <v>EQ-FN-0013</v>
+        <v>EQ-FN-0010</v>
       </c>
       <c r="C169" t="str">
         <v>EQUIPMENT</v>
@@ -6305,13 +6305,13 @@
         <v>2024-08-01</v>
       </c>
       <c r="I169" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
       </c>
       <c r="J169" t="str">
         <v>ชั้นวางของ</v>
       </c>
       <c r="K169" t="str">
-        <v>2-B9701-FP05-73300160001/006-67</v>
+        <v>2-B9701-FP05-73300160001/003-67</v>
       </c>
     </row>
     <row r="170">
@@ -6319,7 +6319,7 @@
         <v>ชั้นวางของ</v>
       </c>
       <c r="B170" t="str">
-        <v>EQ-FN-0014</v>
+        <v>EQ-FN-0011</v>
       </c>
       <c r="C170" t="str">
         <v>EQUIPMENT</v>
@@ -6340,118 +6340,118 @@
         <v>2024-08-01</v>
       </c>
       <c r="I170" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 5</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 2</v>
       </c>
       <c r="J170" t="str">
         <v>ชั้นวางของ</v>
       </c>
       <c r="K170" t="str">
-        <v>2-B9701-FP05-73300160001/007-67</v>
+        <v>2-B9701-FP05-73300160001/004-67</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="B171" t="str">
-        <v>EQ-BED-0004</v>
+        <v>EQ-FN-0012</v>
       </c>
       <c r="C171" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D171" t="str">
-        <v>เตียงและตู้ข้างเตียง</v>
+        <v>ชั้นเก็บของ</v>
       </c>
       <c r="E171" t="str">
-        <v>หลัง</v>
+        <v>ชั้น</v>
       </c>
       <c r="F171">
         <v>1</v>
       </c>
       <c r="G171">
-        <v>70645</v>
+        <v>2500</v>
       </c>
       <c r="H171" t="str">
-        <v>2025-05-01</v>
+        <v>2024-08-01</v>
       </c>
       <c r="I171" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
       </c>
       <c r="J171" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="K171" t="str">
-        <v>1-B9701-FT17-65300010001/001-68</v>
+        <v>2-B9701-FP05-73300160001/005-67</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="B172" t="str">
-        <v>EQ-BED-0005</v>
+        <v>EQ-FN-0013</v>
       </c>
       <c r="C172" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D172" t="str">
-        <v>เตียงและตู้ข้างเตียง</v>
+        <v>ชั้นเก็บของ</v>
       </c>
       <c r="E172" t="str">
-        <v>หลัง</v>
+        <v>ชั้น</v>
       </c>
       <c r="F172">
         <v>1</v>
       </c>
       <c r="G172">
-        <v>70645</v>
+        <v>2500</v>
       </c>
       <c r="H172" t="str">
-        <v>2025-05-01</v>
+        <v>2024-08-01</v>
       </c>
       <c r="I172" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
       </c>
       <c r="J172" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="K172" t="str">
-        <v>1-B9701-FT17-65300010001/002-68</v>
+        <v>2-B9701-FP05-73300160001/006-67</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="B173" t="str">
-        <v>EQ-BED-0006</v>
+        <v>EQ-FN-0014</v>
       </c>
       <c r="C173" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D173" t="str">
-        <v>เตียงและตู้ข้างเตียง</v>
+        <v>ชั้นเก็บของ</v>
       </c>
       <c r="E173" t="str">
-        <v>หลัง</v>
+        <v>ชั้น</v>
       </c>
       <c r="F173">
         <v>1</v>
       </c>
       <c r="G173">
-        <v>70645</v>
+        <v>2500</v>
       </c>
       <c r="H173" t="str">
-        <v>2025-05-01</v>
+        <v>2024-08-01</v>
       </c>
       <c r="I173" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 5</v>
       </c>
       <c r="J173" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="K173" t="str">
-        <v>1-B9701-FT17-65300010001/003-68</v>
+        <v>2-B9701-FP05-73300160001/007-67</v>
       </c>
     </row>
     <row r="174">
@@ -6459,7 +6459,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B174" t="str">
-        <v>EQ-BED-0007</v>
+        <v>EQ-BED-0004</v>
       </c>
       <c r="C174" t="str">
         <v>EQUIPMENT</v>
@@ -6486,7 +6486,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K174" t="str">
-        <v>1-B9701-FT17-65300010001/004-68</v>
+        <v>1-B9701-FT17-65300010001/001-68</v>
       </c>
     </row>
     <row r="175">
@@ -6494,7 +6494,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B175" t="str">
-        <v>EQ-BED-0008</v>
+        <v>EQ-BED-0005</v>
       </c>
       <c r="C175" t="str">
         <v>EQUIPMENT</v>
@@ -6521,7 +6521,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K175" t="str">
-        <v>1-B9701-FT17-65300010001/005-68</v>
+        <v>1-B9701-FT17-65300010001/002-68</v>
       </c>
     </row>
     <row r="176">
@@ -6529,7 +6529,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B176" t="str">
-        <v>EQ-BED-0009</v>
+        <v>EQ-BED-0006</v>
       </c>
       <c r="C176" t="str">
         <v>EQUIPMENT</v>
@@ -6556,7 +6556,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K176" t="str">
-        <v>1-B9701-FT17-65300010001/006-68</v>
+        <v>1-B9701-FT17-65300010001/003-68</v>
       </c>
     </row>
     <row r="177">
@@ -6564,7 +6564,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B177" t="str">
-        <v>EQ-BED-0010</v>
+        <v>EQ-BED-0007</v>
       </c>
       <c r="C177" t="str">
         <v>EQUIPMENT</v>
@@ -6591,7 +6591,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K177" t="str">
-        <v>1-B9701-FT17-65300010001/007-68</v>
+        <v>1-B9701-FT17-65300010001/004-68</v>
       </c>
     </row>
     <row r="178">
@@ -6599,7 +6599,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B178" t="str">
-        <v>EQ-BED-0011</v>
+        <v>EQ-BED-0008</v>
       </c>
       <c r="C178" t="str">
         <v>EQUIPMENT</v>
@@ -6626,7 +6626,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K178" t="str">
-        <v>1-B9701-FT17-65300010001/008-68</v>
+        <v>1-B9701-FT17-65300010001/005-68</v>
       </c>
     </row>
     <row r="179">
@@ -6634,7 +6634,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B179" t="str">
-        <v>EQ-BED-0012</v>
+        <v>EQ-BED-0009</v>
       </c>
       <c r="C179" t="str">
         <v>EQUIPMENT</v>
@@ -6661,7 +6661,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K179" t="str">
-        <v>1-B9701-FT17-65300010001/009-68</v>
+        <v>1-B9701-FT17-65300010001/006-68</v>
       </c>
     </row>
     <row r="180">
@@ -6669,7 +6669,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B180" t="str">
-        <v>EQ-BED-0013</v>
+        <v>EQ-BED-0010</v>
       </c>
       <c r="C180" t="str">
         <v>EQUIPMENT</v>
@@ -6696,7 +6696,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K180" t="str">
-        <v>1-B9701-FT17-65300010001/010-68</v>
+        <v>1-B9701-FT17-65300010001/007-68</v>
       </c>
     </row>
     <row r="181">
@@ -6704,7 +6704,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B181" t="str">
-        <v>EQ-BED-0014</v>
+        <v>EQ-BED-0011</v>
       </c>
       <c r="C181" t="str">
         <v>EQUIPMENT</v>
@@ -6731,7 +6731,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K181" t="str">
-        <v>1-B9701-FT17-65300010001/011-68</v>
+        <v>1-B9701-FT17-65300010001/008-68</v>
       </c>
     </row>
     <row r="182">
@@ -6739,7 +6739,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B182" t="str">
-        <v>EQ-BED-0015</v>
+        <v>EQ-BED-0012</v>
       </c>
       <c r="C182" t="str">
         <v>EQUIPMENT</v>
@@ -6766,7 +6766,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K182" t="str">
-        <v>1-B9701-FT17-65300010001/012-68</v>
+        <v>1-B9701-FT17-65300010001/009-68</v>
       </c>
     </row>
     <row r="183">
@@ -6774,7 +6774,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B183" t="str">
-        <v>EQ-BED-0016</v>
+        <v>EQ-BED-0013</v>
       </c>
       <c r="C183" t="str">
         <v>EQUIPMENT</v>
@@ -6801,7 +6801,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K183" t="str">
-        <v>1-B9701-FT17-65300010001/013-68</v>
+        <v>1-B9701-FT17-65300010001/010-68</v>
       </c>
     </row>
     <row r="184">
@@ -6809,7 +6809,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B184" t="str">
-        <v>EQ-BED-0017</v>
+        <v>EQ-BED-0014</v>
       </c>
       <c r="C184" t="str">
         <v>EQUIPMENT</v>
@@ -6836,7 +6836,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K184" t="str">
-        <v>1-B9701-FT17-65300010001/014-68</v>
+        <v>1-B9701-FT17-65300010001/011-68</v>
       </c>
     </row>
     <row r="185">
@@ -6844,7 +6844,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B185" t="str">
-        <v>EQ-BED-0018</v>
+        <v>EQ-BED-0015</v>
       </c>
       <c r="C185" t="str">
         <v>EQUIPMENT</v>
@@ -6871,7 +6871,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K185" t="str">
-        <v>1-B9701-FT17-65300010001/015-68</v>
+        <v>1-B9701-FT17-65300010001/012-68</v>
       </c>
     </row>
     <row r="186">
@@ -6879,7 +6879,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B186" t="str">
-        <v>EQ-BED-0019</v>
+        <v>EQ-BED-0016</v>
       </c>
       <c r="C186" t="str">
         <v>EQUIPMENT</v>
@@ -6906,7 +6906,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K186" t="str">
-        <v>1-B9701-FT17-65300010001/016-68</v>
+        <v>1-B9701-FT17-65300010001/013-68</v>
       </c>
     </row>
     <row r="187">
@@ -6914,7 +6914,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B187" t="str">
-        <v>EQ-BED-0020</v>
+        <v>EQ-BED-0017</v>
       </c>
       <c r="C187" t="str">
         <v>EQUIPMENT</v>
@@ -6941,7 +6941,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K187" t="str">
-        <v>1-B9701-FT17-65300010001/017-68</v>
+        <v>1-B9701-FT17-65300010001/014-68</v>
       </c>
     </row>
     <row r="188">
@@ -6949,7 +6949,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B188" t="str">
-        <v>EQ-BED-0021</v>
+        <v>EQ-BED-0018</v>
       </c>
       <c r="C188" t="str">
         <v>EQUIPMENT</v>
@@ -6976,7 +6976,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K188" t="str">
-        <v>1-B9701-FT17-65300010001/018-68</v>
+        <v>1-B9701-FT17-65300010001/015-68</v>
       </c>
     </row>
     <row r="189">
@@ -6984,7 +6984,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B189" t="str">
-        <v>EQ-BED-0022</v>
+        <v>EQ-BED-0019</v>
       </c>
       <c r="C189" t="str">
         <v>EQUIPMENT</v>
@@ -7011,7 +7011,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K189" t="str">
-        <v>1-B9701-FT17-65300010001/019-68</v>
+        <v>1-B9701-FT17-65300010001/016-68</v>
       </c>
     </row>
     <row r="190">
@@ -7019,7 +7019,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B190" t="str">
-        <v>EQ-BED-0023</v>
+        <v>EQ-BED-0020</v>
       </c>
       <c r="C190" t="str">
         <v>EQUIPMENT</v>
@@ -7046,15 +7046,15 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K190" t="str">
-        <v>1-B9701-FT17-65300010001/020-68</v>
+        <v>1-B9701-FT17-65300010001/017-68</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 2 ไกร์ราวสไลด์ (เตียงใหญ่)</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B191" t="str">
-        <v>EQ-BED-0024</v>
+        <v>EQ-BED-0021</v>
       </c>
       <c r="C191" t="str">
         <v>EQUIPMENT</v>
@@ -7069,7 +7069,7 @@
         <v>1</v>
       </c>
       <c r="G191">
-        <v>64900</v>
+        <v>70645</v>
       </c>
       <c r="H191" t="str">
         <v>2025-05-01</v>
@@ -7078,33 +7078,33 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J191" t="str">
-        <v>เตียงเฟาว์เลอร์ 2 ไกร์ แบบดิจิตอล พร้อมที่นอน หมอน</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K191" t="str">
-        <v>1-B9701-FT17-65300010001/021-68</v>
+        <v>1-B9701-FT17-65300010001/018-68</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>เครื่องแสดงสัญญาณชีพ</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B192" t="str">
-        <v>EQ-SIM2-0001</v>
+        <v>EQ-BED-0022</v>
       </c>
       <c r="C192" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D192" t="str">
-        <v>(SIM MAN 2)ครุภัณฑ์การแพทย์และการพยาบาล</v>
+        <v>เตียงและตู้ข้างเตียง</v>
       </c>
       <c r="E192" t="str">
-        <v>เครื่อง</v>
+        <v>หลัง</v>
       </c>
       <c r="F192">
         <v>1</v>
       </c>
       <c r="G192">
-        <v>280000</v>
+        <v>70645</v>
       </c>
       <c r="H192" t="str">
         <v>2025-05-01</v>
@@ -7113,33 +7113,33 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J192" t="str">
-        <v>เครื่องแสดงสัญญาณชีพ</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K192" t="str">
-        <v>1-B9701-FT17-65450010002/001-68</v>
+        <v>1-B9701-FT17-65300010001/019-68</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>ชุดระบบบันทึกสถานการณ์การฝึกแบบเคลื่อนที่</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B193" t="str">
-        <v>EQ-SIM2-0002</v>
+        <v>EQ-BED-0023</v>
       </c>
       <c r="C193" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D193" t="str">
-        <v>(SIM MAN 2)ครุภัณฑ์การแพทย์และการพยาบาล</v>
+        <v>เตียงและตู้ข้างเตียง</v>
       </c>
       <c r="E193" t="str">
-        <v>ชุด</v>
+        <v>หลัง</v>
       </c>
       <c r="F193">
         <v>1</v>
       </c>
       <c r="G193">
-        <v>1200000</v>
+        <v>70645</v>
       </c>
       <c r="H193" t="str">
         <v>2025-05-01</v>
@@ -7148,33 +7148,33 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J193" t="str">
-        <v>ชุดระบบบันทึกสถานการณ์การฝึกแบบเคลื่อนที่</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K193" t="str">
-        <v>1-B9701-FT17-65450010002/002-68</v>
+        <v>1-B9701-FT17-65300010001/020-68</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 2 ไกร์ราวสไลด์ (เตียงใหญ่)</v>
       </c>
       <c r="B194" t="str">
-        <v>EQ-CPR-0004</v>
+        <v>EQ-BED-0024</v>
       </c>
       <c r="C194" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D194" t="str">
-        <v>หุ่นฝึก CPR</v>
+        <v>เตียงและตู้ข้างเตียง</v>
       </c>
       <c r="E194" t="str">
-        <v>ชุด</v>
+        <v>หลัง</v>
       </c>
       <c r="F194">
         <v>1</v>
       </c>
       <c r="G194">
-        <v>12500</v>
+        <v>64900</v>
       </c>
       <c r="H194" t="str">
         <v>2025-05-01</v>
@@ -7183,33 +7183,33 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J194" t="str">
-        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>เตียงเฟาว์เลอร์ 2 ไกร์ แบบดิจิตอล พร้อมที่นอน หมอน</v>
       </c>
       <c r="K194" t="str">
-        <v>1-B9701-FT17-65450010003/001-68</v>
+        <v>1-B9701-FT17-65300010001/021-68</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>เครื่องแสดงสัญญาณชีพ</v>
       </c>
       <c r="B195" t="str">
-        <v>EQ-CPR-0005</v>
+        <v>EQ-SIM2-0001</v>
       </c>
       <c r="C195" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D195" t="str">
-        <v>หุ่นฝึก CPR</v>
+        <v>(SIM MAN 2)ครุภัณฑ์การแพทย์และการพยาบาล</v>
       </c>
       <c r="E195" t="str">
-        <v>ชุด</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F195">
         <v>1</v>
       </c>
       <c r="G195">
-        <v>12500</v>
+        <v>280000</v>
       </c>
       <c r="H195" t="str">
         <v>2025-05-01</v>
@@ -7218,24 +7218,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J195" t="str">
-        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>เครื่องแสดงสัญญาณชีพ</v>
       </c>
       <c r="K195" t="str">
-        <v>1-B9701-FT17-65450010003/002-68</v>
+        <v>1-B9701-FT17-65450010002/001-68</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>ชุดระบบบันทึกสถานการณ์การฝึกแบบเคลื่อนที่</v>
       </c>
       <c r="B196" t="str">
-        <v>EQ-CPR-0006</v>
+        <v>EQ-SIM2-0002</v>
       </c>
       <c r="C196" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D196" t="str">
-        <v>หุ่นฝึก CPR</v>
+        <v>(SIM MAN 2)ครุภัณฑ์การแพทย์และการพยาบาล</v>
       </c>
       <c r="E196" t="str">
         <v>ชุด</v>
@@ -7244,7 +7244,7 @@
         <v>1</v>
       </c>
       <c r="G196">
-        <v>12500</v>
+        <v>1200000</v>
       </c>
       <c r="H196" t="str">
         <v>2025-05-01</v>
@@ -7253,10 +7253,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J196" t="str">
-        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>ชุดระบบบันทึกสถานการณ์การฝึกแบบเคลื่อนที่</v>
       </c>
       <c r="K196" t="str">
-        <v>1-B9701-FT17-65450010003/003-68</v>
+        <v>1-B9701-FT17-65450010002/002-68</v>
       </c>
     </row>
     <row r="197">
@@ -7264,7 +7264,7 @@
         <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B197" t="str">
-        <v>EQ-CPR-0007</v>
+        <v>EQ-CPR-0004</v>
       </c>
       <c r="C197" t="str">
         <v>EQUIPMENT</v>
@@ -7291,7 +7291,7 @@
         <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="K197" t="str">
-        <v>1-B9701-FT17-65450010003/004-68</v>
+        <v>1-B9701-FT17-65450010003/001-68</v>
       </c>
     </row>
     <row r="198">
@@ -7299,7 +7299,7 @@
         <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B198" t="str">
-        <v>EQ-CPR-0008</v>
+        <v>EQ-CPR-0005</v>
       </c>
       <c r="C198" t="str">
         <v>EQUIPMENT</v>
@@ -7326,21 +7326,21 @@
         <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="K198" t="str">
-        <v>1-B9701-FT17-65450010003/005-68</v>
+        <v>1-B9701-FT17-65450010003/002-68</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
+        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B199" t="str">
-        <v>EQ-URC-0011</v>
+        <v>EQ-CPR-0006</v>
       </c>
       <c r="C199" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D199" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>หุ่นฝึก CPR</v>
       </c>
       <c r="E199" t="str">
         <v>ชุด</v>
@@ -7349,7 +7349,7 @@
         <v>1</v>
       </c>
       <c r="G199">
-        <v>111100</v>
+        <v>12500</v>
       </c>
       <c r="H199" t="str">
         <v>2025-05-01</v>
@@ -7358,24 +7358,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J199" t="str">
-        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
+        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="K199" t="str">
-        <v>1-B9701-FT17-65450010004/001-68</v>
+        <v>1-B9701-FT17-65450010003/003-68</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
+        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B200" t="str">
-        <v>EQ-URC-0012</v>
+        <v>EQ-CPR-0007</v>
       </c>
       <c r="C200" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D200" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>หุ่นฝึก CPR</v>
       </c>
       <c r="E200" t="str">
         <v>ชุด</v>
@@ -7384,7 +7384,7 @@
         <v>1</v>
       </c>
       <c r="G200">
-        <v>111100</v>
+        <v>12500</v>
       </c>
       <c r="H200" t="str">
         <v>2025-05-01</v>
@@ -7393,24 +7393,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J200" t="str">
-        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
+        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="K200" t="str">
-        <v>1-B9701-FT17-65450010004/002-68</v>
+        <v>1-B9701-FT17-65450010003/004-68</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
+        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B201" t="str">
-        <v>EQ-URC-0013</v>
+        <v>EQ-CPR-0008</v>
       </c>
       <c r="C201" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D201" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>หุ่นฝึก CPR</v>
       </c>
       <c r="E201" t="str">
         <v>ชุด</v>
@@ -7419,7 +7419,7 @@
         <v>1</v>
       </c>
       <c r="G201">
-        <v>111100</v>
+        <v>12500</v>
       </c>
       <c r="H201" t="str">
         <v>2025-05-01</v>
@@ -7428,10 +7428,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J201" t="str">
-        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
+        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="K201" t="str">
-        <v>1-B9701-FT17-65450010004/003-68</v>
+        <v>1-B9701-FT17-65450010003/005-68</v>
       </c>
     </row>
     <row r="202">
@@ -7439,7 +7439,7 @@
         <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
       </c>
       <c r="B202" t="str">
-        <v>EQ-URC-0014</v>
+        <v>EQ-URC-0011</v>
       </c>
       <c r="C202" t="str">
         <v>EQUIPMENT</v>
@@ -7466,7 +7466,7 @@
         <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
       </c>
       <c r="K202" t="str">
-        <v>1-B9701-FT17-65450010004/004-68</v>
+        <v>1-B9701-FT17-65450010004/001-68</v>
       </c>
     </row>
     <row r="203">
@@ -7474,7 +7474,7 @@
         <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
       </c>
       <c r="B203" t="str">
-        <v>EQ-URC-0015</v>
+        <v>EQ-URC-0012</v>
       </c>
       <c r="C203" t="str">
         <v>EQUIPMENT</v>
@@ -7501,15 +7501,15 @@
         <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
       </c>
       <c r="K203" t="str">
-        <v>1-B9701-FT17-65450010004/005-68</v>
+        <v>1-B9701-FT17-65450010004/002-68</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
+        <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
       </c>
       <c r="B204" t="str">
-        <v>EQ-URC-0016</v>
+        <v>EQ-URC-0013</v>
       </c>
       <c r="C204" t="str">
         <v>EQUIPMENT</v>
@@ -7533,18 +7533,18 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J204" t="str">
-        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
+        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
       </c>
       <c r="K204" t="str">
-        <v>1-B9701-FT17-65450010004/006-68</v>
+        <v>1-B9701-FT17-65450010004/003-68</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
+        <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
       </c>
       <c r="B205" t="str">
-        <v>EQ-URC-0017</v>
+        <v>EQ-URC-0014</v>
       </c>
       <c r="C205" t="str">
         <v>EQUIPMENT</v>
@@ -7568,18 +7568,18 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J205" t="str">
-        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
+        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
       </c>
       <c r="K205" t="str">
-        <v>1-B9701-FT17-65450010004/007-68</v>
+        <v>1-B9701-FT17-65450010004/004-68</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
+        <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
       </c>
       <c r="B206" t="str">
-        <v>EQ-URC-0018</v>
+        <v>EQ-URC-0015</v>
       </c>
       <c r="C206" t="str">
         <v>EQUIPMENT</v>
@@ -7603,10 +7603,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J206" t="str">
-        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
+        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
       </c>
       <c r="K206" t="str">
-        <v>1-B9701-FT17-65450010004/008-68</v>
+        <v>1-B9701-FT17-65450010004/005-68</v>
       </c>
     </row>
     <row r="207">
@@ -7614,7 +7614,7 @@
         <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
       </c>
       <c r="B207" t="str">
-        <v>EQ-URC-0019</v>
+        <v>EQ-URC-0016</v>
       </c>
       <c r="C207" t="str">
         <v>EQUIPMENT</v>
@@ -7641,7 +7641,7 @@
         <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
       </c>
       <c r="K207" t="str">
-        <v>1-B9701-FT17-65450010004/009-68</v>
+        <v>1-B9701-FT17-65450010004/006-68</v>
       </c>
     </row>
     <row r="208">
@@ -7649,7 +7649,7 @@
         <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
       </c>
       <c r="B208" t="str">
-        <v>EQ-URC-0020</v>
+        <v>EQ-URC-0017</v>
       </c>
       <c r="C208" t="str">
         <v>EQUIPMENT</v>
@@ -7676,21 +7676,21 @@
         <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
       </c>
       <c r="K208" t="str">
-        <v>1-B9701-FT17-65450010004/010-68</v>
+        <v>1-B9701-FT17-65450010004/007-68</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
       </c>
       <c r="B209" t="str">
-        <v>EQ-NG-0006</v>
+        <v>EQ-URC-0018</v>
       </c>
       <c r="C209" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D209" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E209" t="str">
         <v>ชุด</v>
@@ -7699,7 +7699,7 @@
         <v>1</v>
       </c>
       <c r="G209">
-        <v>121330</v>
+        <v>111100</v>
       </c>
       <c r="H209" t="str">
         <v>2025-05-01</v>
@@ -7708,24 +7708,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J209" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
       </c>
       <c r="K209" t="str">
-        <v>1-B9701-FT17-65450010004/011-68</v>
+        <v>1-B9701-FT17-65450010004/008-68</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
       </c>
       <c r="B210" t="str">
-        <v>EQ-NG-0007</v>
+        <v>EQ-URC-0019</v>
       </c>
       <c r="C210" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D210" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E210" t="str">
         <v>ชุด</v>
@@ -7734,7 +7734,7 @@
         <v>1</v>
       </c>
       <c r="G210">
-        <v>121330</v>
+        <v>111100</v>
       </c>
       <c r="H210" t="str">
         <v>2025-05-01</v>
@@ -7743,24 +7743,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J210" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
       </c>
       <c r="K210" t="str">
-        <v>1-B9701-FT17-65450010004/012-68</v>
+        <v>1-B9701-FT17-65450010004/009-68</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
       </c>
       <c r="B211" t="str">
-        <v>EQ-NG-0008</v>
+        <v>EQ-URC-0020</v>
       </c>
       <c r="C211" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D211" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E211" t="str">
         <v>ชุด</v>
@@ -7769,7 +7769,7 @@
         <v>1</v>
       </c>
       <c r="G211">
-        <v>121330</v>
+        <v>111100</v>
       </c>
       <c r="H211" t="str">
         <v>2025-05-01</v>
@@ -7778,10 +7778,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J211" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
       </c>
       <c r="K211" t="str">
-        <v>1-B9701-FT17-65450010004/013-68</v>
+        <v>1-B9701-FT17-65450010004/010-68</v>
       </c>
     </row>
     <row r="212">
@@ -7789,7 +7789,7 @@
         <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="B212" t="str">
-        <v>EQ-NG-0009</v>
+        <v>EQ-NG-0006</v>
       </c>
       <c r="C212" t="str">
         <v>EQUIPMENT</v>
@@ -7816,7 +7816,7 @@
         <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="K212" t="str">
-        <v>1-B9701-FT17-65450010004/014-68</v>
+        <v>1-B9701-FT17-65450010004/011-68</v>
       </c>
     </row>
     <row r="213">
@@ -7824,7 +7824,7 @@
         <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="B213" t="str">
-        <v>EQ-NG-0010</v>
+        <v>EQ-NG-0007</v>
       </c>
       <c r="C213" t="str">
         <v>EQUIPMENT</v>
@@ -7851,21 +7851,21 @@
         <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="K213" t="str">
-        <v>1-B9701-FT17-65450010004/015-68</v>
+        <v>1-B9701-FT17-65450010004/012-68</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>หุ่นจำลองผู้ใหญ่</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="B214" t="str">
-        <v>EQ-FMS-0003</v>
+        <v>EQ-NG-0008</v>
       </c>
       <c r="C214" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D214" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="E214" t="str">
         <v>ชุด</v>
@@ -7874,7 +7874,7 @@
         <v>1</v>
       </c>
       <c r="G214">
-        <v>3920000</v>
+        <v>121330</v>
       </c>
       <c r="H214" t="str">
         <v>2025-05-01</v>
@@ -7883,24 +7883,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J214" t="str">
-        <v>หุ่นจำลองผู้ใหญ่</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="K214" t="str">
-        <v>1-B9701-FT17-65450010004/016-68</v>
+        <v>1-B9701-FT17-65450010004/013-68</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="B215" t="str">
-        <v>EQ-IV-0001</v>
+        <v>EQ-NG-0009</v>
       </c>
       <c r="C215" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D215" t="str">
-        <v>หุ่นฝึกฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="E215" t="str">
         <v>ชุด</v>
@@ -7909,33 +7909,33 @@
         <v>1</v>
       </c>
       <c r="G215">
-        <v>40000</v>
+        <v>121330</v>
       </c>
       <c r="H215" t="str">
-        <v>2024-06-28</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I215" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J215" t="str">
-        <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="K215" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (11-1/4)</v>
+        <v>1-B9701-FT17-65450010004/014-68</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="B216" t="str">
-        <v>EQ-IV-0002</v>
+        <v>EQ-NG-0010</v>
       </c>
       <c r="C216" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D216" t="str">
-        <v>หุ่นฝึกฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="E216" t="str">
         <v>ชุด</v>
@@ -7944,33 +7944,33 @@
         <v>1</v>
       </c>
       <c r="G216">
-        <v>40000</v>
+        <v>121330</v>
       </c>
       <c r="H216" t="str">
-        <v>2024-06-28</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I216" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J216" t="str">
-        <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="K216" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (11-2/4)</v>
+        <v>1-B9701-FT17-65450010004/015-68</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
+        <v>หุ่นจำลองผู้ใหญ่</v>
       </c>
       <c r="B217" t="str">
-        <v>EQ-IV-0003</v>
+        <v>EQ-FMS-0003</v>
       </c>
       <c r="C217" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D217" t="str">
-        <v>หุ่นฝึกฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E217" t="str">
         <v>ชุด</v>
@@ -7979,19 +7979,19 @@
         <v>1</v>
       </c>
       <c r="G217">
-        <v>40000</v>
+        <v>3920000</v>
       </c>
       <c r="H217" t="str">
-        <v>2024-06-28</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I217" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J217" t="str">
-        <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
+        <v>หุ่นจำลองผู้ใหญ่</v>
       </c>
       <c r="K217" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (11-3/4)</v>
+        <v>1-B9701-FT17-65450010004/016-68</v>
       </c>
     </row>
     <row r="218">
@@ -7999,7 +7999,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B218" t="str">
-        <v>EQ-IV-0004</v>
+        <v>EQ-IV-0001</v>
       </c>
       <c r="C218" t="str">
         <v>EQUIPMENT</v>
@@ -8026,7 +8026,7 @@
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K218" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (11-4/4)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (11-1/4)</v>
       </c>
     </row>
     <row r="219">
@@ -8034,7 +8034,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B219" t="str">
-        <v>EQ-IV-0005</v>
+        <v>EQ-IV-0002</v>
       </c>
       <c r="C219" t="str">
         <v>EQUIPMENT</v>
@@ -8049,19 +8049,19 @@
         <v>1</v>
       </c>
       <c r="G219">
-        <v>60100</v>
+        <v>40000</v>
       </c>
       <c r="H219" t="str">
-        <v>2025-05-01</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I219" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J219" t="str">
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K219" t="str">
-        <v>1-B9701-FT17-65450010004/017-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (11-2/4)</v>
       </c>
     </row>
     <row r="220">
@@ -8069,7 +8069,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B220" t="str">
-        <v>EQ-IV-0006</v>
+        <v>EQ-IV-0003</v>
       </c>
       <c r="C220" t="str">
         <v>EQUIPMENT</v>
@@ -8084,19 +8084,19 @@
         <v>1</v>
       </c>
       <c r="G220">
-        <v>60100</v>
+        <v>40000</v>
       </c>
       <c r="H220" t="str">
-        <v>2025-05-01</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I220" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J220" t="str">
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K220" t="str">
-        <v>1-B9701-FT17-65450010004/018-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (11-3/4)</v>
       </c>
     </row>
     <row r="221">
@@ -8104,7 +8104,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B221" t="str">
-        <v>EQ-IV-0007</v>
+        <v>EQ-IV-0004</v>
       </c>
       <c r="C221" t="str">
         <v>EQUIPMENT</v>
@@ -8119,19 +8119,19 @@
         <v>1</v>
       </c>
       <c r="G221">
-        <v>60100</v>
+        <v>40000</v>
       </c>
       <c r="H221" t="str">
-        <v>2025-05-01</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I221" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J221" t="str">
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K221" t="str">
-        <v>1-B9701-FT17-65450010004/019-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (11-4/4)</v>
       </c>
     </row>
     <row r="222">
@@ -8139,7 +8139,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B222" t="str">
-        <v>EQ-IV-0008</v>
+        <v>EQ-IV-0005</v>
       </c>
       <c r="C222" t="str">
         <v>EQUIPMENT</v>
@@ -8166,7 +8166,7 @@
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K222" t="str">
-        <v>1-B9701-FT17-65450010004/020-68</v>
+        <v>1-B9701-FT17-65450010004/017-68</v>
       </c>
     </row>
     <row r="223">
@@ -8174,7 +8174,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B223" t="str">
-        <v>EQ-IV-0009</v>
+        <v>EQ-IV-0006</v>
       </c>
       <c r="C223" t="str">
         <v>EQUIPMENT</v>
@@ -8201,7 +8201,7 @@
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K223" t="str">
-        <v>1-B9701-FT17-65450010004/021-68</v>
+        <v>1-B9701-FT17-65450010004/018-68</v>
       </c>
     </row>
     <row r="224">
@@ -8209,7 +8209,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B224" t="str">
-        <v>EQ-IV-0010</v>
+        <v>EQ-IV-0007</v>
       </c>
       <c r="C224" t="str">
         <v>EQUIPMENT</v>
@@ -8236,7 +8236,7 @@
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K224" t="str">
-        <v>1-B9701-FT17-65450010004/022-68</v>
+        <v>1-B9701-FT17-65450010004/019-68</v>
       </c>
     </row>
     <row r="225">
@@ -8244,7 +8244,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B225" t="str">
-        <v>EQ-IV-0011</v>
+        <v>EQ-IV-0008</v>
       </c>
       <c r="C225" t="str">
         <v>EQUIPMENT</v>
@@ -8271,21 +8271,21 @@
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K225" t="str">
-        <v>1-B9701-FT17-65450010004/023-68</v>
+        <v>1-B9701-FT17-65450010004/020-68</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
+        <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B226" t="str">
-        <v>EQ-STI-0044</v>
+        <v>EQ-IV-0009</v>
       </c>
       <c r="C226" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D226" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="E226" t="str">
         <v>ชุด</v>
@@ -8294,7 +8294,7 @@
         <v>1</v>
       </c>
       <c r="G226">
-        <v>54800</v>
+        <v>60100</v>
       </c>
       <c r="H226" t="str">
         <v>2025-05-01</v>
@@ -8303,24 +8303,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J226" t="str">
-        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
+        <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K226" t="str">
-        <v>1-B9701-FT17-65450010004/024-68</v>
+        <v>1-B9701-FT17-65450010004/021-68</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
+        <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B227" t="str">
-        <v>EQ-STI-0045</v>
+        <v>EQ-IV-0010</v>
       </c>
       <c r="C227" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D227" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="E227" t="str">
         <v>ชุด</v>
@@ -8329,7 +8329,7 @@
         <v>1</v>
       </c>
       <c r="G227">
-        <v>54800</v>
+        <v>60100</v>
       </c>
       <c r="H227" t="str">
         <v>2025-05-01</v>
@@ -8338,24 +8338,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J227" t="str">
-        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
+        <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K227" t="str">
-        <v>1-B9701-FT17-65450010004/025-68</v>
+        <v>1-B9701-FT17-65450010004/022-68</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
+        <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B228" t="str">
-        <v>EQ-STI-0046</v>
+        <v>EQ-IV-0011</v>
       </c>
       <c r="C228" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D228" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="E228" t="str">
         <v>ชุด</v>
@@ -8364,7 +8364,7 @@
         <v>1</v>
       </c>
       <c r="G228">
-        <v>54800</v>
+        <v>60100</v>
       </c>
       <c r="H228" t="str">
         <v>2025-05-01</v>
@@ -8373,10 +8373,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J228" t="str">
-        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
+        <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K228" t="str">
-        <v>1-B9701-FT17-65450010004/026-68</v>
+        <v>1-B9701-FT17-65450010004/023-68</v>
       </c>
     </row>
     <row r="229">
@@ -8384,7 +8384,7 @@
         <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="B229" t="str">
-        <v>EQ-STI-0047</v>
+        <v>EQ-STI-0044</v>
       </c>
       <c r="C229" t="str">
         <v>EQUIPMENT</v>
@@ -8411,7 +8411,7 @@
         <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="K229" t="str">
-        <v>1-B9701-FT17-65450010004/027-68</v>
+        <v>1-B9701-FT17-65450010004/024-68</v>
       </c>
     </row>
     <row r="230">
@@ -8419,7 +8419,7 @@
         <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="B230" t="str">
-        <v>EQ-STI-0048</v>
+        <v>EQ-STI-0045</v>
       </c>
       <c r="C230" t="str">
         <v>EQUIPMENT</v>
@@ -8446,21 +8446,21 @@
         <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="K230" t="str">
-        <v>1-B9701-FT17-65450010004/028-68</v>
+        <v>1-B9701-FT17-65450010004/025-68</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
+        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="B231" t="str">
-        <v>EQ-IM-0010</v>
+        <v>EQ-STI-0046</v>
       </c>
       <c r="C231" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D231" t="str">
-        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E231" t="str">
         <v>ชุด</v>
@@ -8469,7 +8469,7 @@
         <v>1</v>
       </c>
       <c r="G231">
-        <v>17900</v>
+        <v>54800</v>
       </c>
       <c r="H231" t="str">
         <v>2025-05-01</v>
@@ -8478,24 +8478,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J231" t="str">
-        <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
+        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="K231" t="str">
-        <v>1-B9701-FT17-65450010004/029-68</v>
+        <v>1-B9701-FT17-65450010004/026-68</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
+        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="B232" t="str">
-        <v>EQ-IM-0011</v>
+        <v>EQ-STI-0047</v>
       </c>
       <c r="C232" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D232" t="str">
-        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E232" t="str">
         <v>ชุด</v>
@@ -8504,7 +8504,7 @@
         <v>1</v>
       </c>
       <c r="G232">
-        <v>17900</v>
+        <v>54800</v>
       </c>
       <c r="H232" t="str">
         <v>2025-05-01</v>
@@ -8513,24 +8513,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J232" t="str">
-        <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
+        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="K232" t="str">
-        <v>1-B9701-FT17-65450010004/030-68</v>
+        <v>1-B9701-FT17-65450010004/027-68</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
+        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="B233" t="str">
-        <v>EQ-IM-0012</v>
+        <v>EQ-STI-0048</v>
       </c>
       <c r="C233" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D233" t="str">
-        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E233" t="str">
         <v>ชุด</v>
@@ -8539,7 +8539,7 @@
         <v>1</v>
       </c>
       <c r="G233">
-        <v>17900</v>
+        <v>54800</v>
       </c>
       <c r="H233" t="str">
         <v>2025-05-01</v>
@@ -8548,10 +8548,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J233" t="str">
-        <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
+        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="K233" t="str">
-        <v>1-B9701-FT17-65450010004/031-68</v>
+        <v>1-B9701-FT17-65450010004/028-68</v>
       </c>
     </row>
     <row r="234">
@@ -8559,7 +8559,7 @@
         <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
       </c>
       <c r="B234" t="str">
-        <v>EQ-IM-0013</v>
+        <v>EQ-IM-0010</v>
       </c>
       <c r="C234" t="str">
         <v>EQUIPMENT</v>
@@ -8586,7 +8586,7 @@
         <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
       </c>
       <c r="K234" t="str">
-        <v>1-B9701-FT17-65450010004/032-68</v>
+        <v>1-B9701-FT17-65450010004/029-68</v>
       </c>
     </row>
     <row r="235">
@@ -8594,7 +8594,7 @@
         <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
       </c>
       <c r="B235" t="str">
-        <v>EQ-IM-0014</v>
+        <v>EQ-IM-0011</v>
       </c>
       <c r="C235" t="str">
         <v>EQUIPMENT</v>
@@ -8621,21 +8621,21 @@
         <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
       </c>
       <c r="K235" t="str">
-        <v>1-B9701-FT17-65450010004/033-68</v>
+        <v>1-B9701-FT17-65450010004/030-68</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
+        <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
       </c>
       <c r="B236" t="str">
-        <v>EQ-FMS-0004</v>
+        <v>EQ-IM-0012</v>
       </c>
       <c r="C236" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D236" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
       </c>
       <c r="E236" t="str">
         <v>ชุด</v>
@@ -8644,7 +8644,7 @@
         <v>1</v>
       </c>
       <c r="G236">
-        <v>246500</v>
+        <v>17900</v>
       </c>
       <c r="H236" t="str">
         <v>2025-05-01</v>
@@ -8653,24 +8653,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J236" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
+        <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
       </c>
       <c r="K236" t="str">
-        <v>1-B9701-FT17-65450010004/034-68</v>
+        <v>1-B9701-FT17-65450010004/031-68</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
+        <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
       </c>
       <c r="B237" t="str">
-        <v>EQ-FMS-0005</v>
+        <v>EQ-IM-0013</v>
       </c>
       <c r="C237" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D237" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
       </c>
       <c r="E237" t="str">
         <v>ชุด</v>
@@ -8679,7 +8679,7 @@
         <v>1</v>
       </c>
       <c r="G237">
-        <v>246500</v>
+        <v>17900</v>
       </c>
       <c r="H237" t="str">
         <v>2025-05-01</v>
@@ -8688,24 +8688,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J237" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
+        <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
       </c>
       <c r="K237" t="str">
-        <v>1-B9701-FT17-65450010004/035-68</v>
+        <v>1-B9701-FT17-65450010004/032-68</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
+        <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
       </c>
       <c r="B238" t="str">
-        <v>EQ-FMS-0006</v>
+        <v>EQ-IM-0014</v>
       </c>
       <c r="C238" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D238" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
       </c>
       <c r="E238" t="str">
         <v>ชุด</v>
@@ -8714,7 +8714,7 @@
         <v>1</v>
       </c>
       <c r="G238">
-        <v>246500</v>
+        <v>17900</v>
       </c>
       <c r="H238" t="str">
         <v>2025-05-01</v>
@@ -8723,10 +8723,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J238" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
+        <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
       </c>
       <c r="K238" t="str">
-        <v>1-B9701-FT17-65450010004/036-68</v>
+        <v>1-B9701-FT17-65450010004/033-68</v>
       </c>
     </row>
     <row r="239">
@@ -8734,7 +8734,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
       </c>
       <c r="B239" t="str">
-        <v>EQ-FMS-0007</v>
+        <v>EQ-FMS-0004</v>
       </c>
       <c r="C239" t="str">
         <v>EQUIPMENT</v>
@@ -8761,7 +8761,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
       </c>
       <c r="K239" t="str">
-        <v>1-B9701-FT17-65450010004/037-68</v>
+        <v>1-B9701-FT17-65450010004/034-68</v>
       </c>
     </row>
     <row r="240">
@@ -8769,7 +8769,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
       </c>
       <c r="B240" t="str">
-        <v>EQ-FMS-0008</v>
+        <v>EQ-FMS-0005</v>
       </c>
       <c r="C240" t="str">
         <v>EQUIPMENT</v>
@@ -8796,15 +8796,15 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
       </c>
       <c r="K240" t="str">
-        <v>1-B9701-FT17-65450010004/038-68</v>
+        <v>1-B9701-FT17-65450010004/035-68</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
       </c>
       <c r="B241" t="str">
-        <v>EQ-FMS-0009</v>
+        <v>EQ-FMS-0006</v>
       </c>
       <c r="C241" t="str">
         <v>EQUIPMENT</v>
@@ -8828,18 +8828,18 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J241" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
       </c>
       <c r="K241" t="str">
-        <v>1-B9701-FT17-65450010004/039-68</v>
+        <v>1-B9701-FT17-65450010004/036-68</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
       </c>
       <c r="B242" t="str">
-        <v>EQ-FMS-0010</v>
+        <v>EQ-FMS-0007</v>
       </c>
       <c r="C242" t="str">
         <v>EQUIPMENT</v>
@@ -8863,18 +8863,18 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J242" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
       </c>
       <c r="K242" t="str">
-        <v>1-B9701-FT17-65450010004/040-68</v>
+        <v>1-B9701-FT17-65450010004/037-68</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
       </c>
       <c r="B243" t="str">
-        <v>EQ-FMS-0011</v>
+        <v>EQ-FMS-0008</v>
       </c>
       <c r="C243" t="str">
         <v>EQUIPMENT</v>
@@ -8898,10 +8898,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J243" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
       </c>
       <c r="K243" t="str">
-        <v>1-B9701-FT17-65450010004/041-68</v>
+        <v>1-B9701-FT17-65450010004/038-68</v>
       </c>
     </row>
     <row r="244">
@@ -8909,7 +8909,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
       </c>
       <c r="B244" t="str">
-        <v>EQ-FMS-0012</v>
+        <v>EQ-FMS-0009</v>
       </c>
       <c r="C244" t="str">
         <v>EQUIPMENT</v>
@@ -8936,7 +8936,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
       </c>
       <c r="K244" t="str">
-        <v>1-B9701-FT17-65450010004/042-68</v>
+        <v>1-B9701-FT17-65450010004/039-68</v>
       </c>
     </row>
     <row r="245">
@@ -8944,7 +8944,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
       </c>
       <c r="B245" t="str">
-        <v>EQ-FMS-0013</v>
+        <v>EQ-FMS-0010</v>
       </c>
       <c r="C245" t="str">
         <v>EQUIPMENT</v>
@@ -8971,21 +8971,21 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
       </c>
       <c r="K245" t="str">
-        <v>1-B9701-FT17-65450010004/043-68</v>
+        <v>1-B9701-FT17-65450010004/040-68</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>หุ่นจำลองกะโหลกศีรษะ</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
       </c>
       <c r="B246" t="str">
-        <v>EQ-ANA-0001</v>
+        <v>EQ-FMS-0011</v>
       </c>
       <c r="C246" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D246" t="str">
-        <v>หุ่นจำลองกายวิภาคศาสตร์</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E246" t="str">
         <v>ชุด</v>
@@ -8994,33 +8994,33 @@
         <v>1</v>
       </c>
       <c r="G246">
-        <v>7600</v>
+        <v>246500</v>
       </c>
       <c r="H246" t="str">
-        <v>2024-06-28</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I246" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J246" t="str">
-        <v>หุ่นจำลองกะโหลกศีรษะ แยกชิ้นส่วนได้</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
       </c>
       <c r="K246" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (1-1/1)</v>
+        <v>1-B9701-FT17-65450010004/041-68</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>หุ่นจำลองสมองและเส้นเลือดแดง</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
       </c>
       <c r="B247" t="str">
-        <v>EQ-ANA-0002</v>
+        <v>EQ-FMS-0012</v>
       </c>
       <c r="C247" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D247" t="str">
-        <v>หุ่นจำลองกายวิภาคศาสตร์</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E247" t="str">
         <v>ชุด</v>
@@ -9029,33 +9029,33 @@
         <v>1</v>
       </c>
       <c r="G247">
-        <v>18000</v>
+        <v>246500</v>
       </c>
       <c r="H247" t="str">
-        <v>2024-06-28</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I247" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J247" t="str">
-        <v>หุ่นจำลองสมองและเส้นเลือดแดง</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
       </c>
       <c r="K247" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (2-1/1)</v>
+        <v>1-B9701-FT17-65450010004/042-68</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>หุ่นจำลองโครงกระดูกเต็มตัวขนาดเท่าจริง</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
       </c>
       <c r="B248" t="str">
-        <v>EQ-ANA-0003</v>
+        <v>EQ-FMS-0013</v>
       </c>
       <c r="C248" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D248" t="str">
-        <v>หุ่นจำลองกายวิภาคศาสตร์</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E248" t="str">
         <v>ชุด</v>
@@ -9064,27 +9064,27 @@
         <v>1</v>
       </c>
       <c r="G248">
-        <v>18000</v>
+        <v>246500</v>
       </c>
       <c r="H248" t="str">
-        <v>2024-06-28</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I248" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J248" t="str">
-        <v>หุ่นจำลองโครงกระดูกเต็มตัวขนาดเท่าจริง</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
       </c>
       <c r="K248" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (3-1/1)</v>
+        <v>1-B9701-FT17-65450010004/043-68</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>โมเดลหัวใจ</v>
+        <v>หุ่นจำลองกะโหลกศีรษะ</v>
       </c>
       <c r="B249" t="str">
-        <v>EQ-ANA-0004</v>
+        <v>EQ-ANA-0001</v>
       </c>
       <c r="C249" t="str">
         <v>EQUIPMENT</v>
@@ -9099,7 +9099,7 @@
         <v>1</v>
       </c>
       <c r="G249">
-        <v>4100</v>
+        <v>7600</v>
       </c>
       <c r="H249" t="str">
         <v>2024-06-28</v>
@@ -9108,24 +9108,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J249" t="str">
-        <v>โมเดลหัวใจ</v>
+        <v>หุ่นจำลองกะโหลกศีรษะ แยกชิ้นส่วนได้</v>
       </c>
       <c r="K249" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (4-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (1-1/1)</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
+        <v>หุ่นจำลองสมองและเส้นเลือดแดง</v>
       </c>
       <c r="B250" t="str">
-        <v>EQ-FMS-0014</v>
+        <v>EQ-ANA-0002</v>
       </c>
       <c r="C250" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D250" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นจำลองกายวิภาคศาสตร์</v>
       </c>
       <c r="E250" t="str">
         <v>ชุด</v>
@@ -9134,7 +9134,7 @@
         <v>1</v>
       </c>
       <c r="G250">
-        <v>140000</v>
+        <v>18000</v>
       </c>
       <c r="H250" t="str">
         <v>2024-06-28</v>
@@ -9143,24 +9143,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J250" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
+        <v>หุ่นจำลองสมองและเส้นเลือดแดง</v>
       </c>
       <c r="K250" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (5-1/6)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (2-1/1)</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
+        <v>หุ่นจำลองโครงกระดูกเต็มตัวขนาดเท่าจริง</v>
       </c>
       <c r="B251" t="str">
-        <v>EQ-FMS-0015</v>
+        <v>EQ-ANA-0003</v>
       </c>
       <c r="C251" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D251" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นจำลองกายวิภาคศาสตร์</v>
       </c>
       <c r="E251" t="str">
         <v>ชุด</v>
@@ -9169,7 +9169,7 @@
         <v>1</v>
       </c>
       <c r="G251">
-        <v>140000</v>
+        <v>18000</v>
       </c>
       <c r="H251" t="str">
         <v>2024-06-28</v>
@@ -9178,24 +9178,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J251" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
+        <v>หุ่นจำลองโครงกระดูกเต็มตัวขนาดเท่าจริง</v>
       </c>
       <c r="K251" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (5-2/6)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (3-1/1)</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
+        <v>โมเดลหัวใจ</v>
       </c>
       <c r="B252" t="str">
-        <v>EQ-FMS-0016</v>
+        <v>EQ-ANA-0004</v>
       </c>
       <c r="C252" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D252" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นจำลองกายวิภาคศาสตร์</v>
       </c>
       <c r="E252" t="str">
         <v>ชุด</v>
@@ -9204,7 +9204,7 @@
         <v>1</v>
       </c>
       <c r="G252">
-        <v>140000</v>
+        <v>4100</v>
       </c>
       <c r="H252" t="str">
         <v>2024-06-28</v>
@@ -9213,10 +9213,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J252" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
+        <v>โมเดลหัวใจ</v>
       </c>
       <c r="K252" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (5-3/6)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (4-1/1)</v>
       </c>
     </row>
     <row r="253">
@@ -9224,7 +9224,7 @@
         <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="B253" t="str">
-        <v>EQ-FMS-0017</v>
+        <v>EQ-FMS-0014</v>
       </c>
       <c r="C253" t="str">
         <v>EQUIPMENT</v>
@@ -9251,7 +9251,7 @@
         <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="K253" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (5-4/6)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (5-1/6)</v>
       </c>
     </row>
     <row r="254">
@@ -9259,7 +9259,7 @@
         <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="B254" t="str">
-        <v>EQ-FMS-0018</v>
+        <v>EQ-FMS-0015</v>
       </c>
       <c r="C254" t="str">
         <v>EQUIPMENT</v>
@@ -9286,7 +9286,7 @@
         <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="K254" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (5-5/6)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (5-2/6)</v>
       </c>
     </row>
     <row r="255">
@@ -9294,7 +9294,7 @@
         <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="B255" t="str">
-        <v>EQ-FMS-0019</v>
+        <v>EQ-FMS-0016</v>
       </c>
       <c r="C255" t="str">
         <v>EQUIPMENT</v>
@@ -9321,21 +9321,21 @@
         <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="K255" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (5-6/6)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (5-3/6)</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>หุ่นฝึก CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="B256" t="str">
-        <v>EQ-CPR-0009</v>
+        <v>EQ-FMS-0017</v>
       </c>
       <c r="C256" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D256" t="str">
-        <v>หุ่นฝึก CPR</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E256" t="str">
         <v>ชุด</v>
@@ -9344,7 +9344,7 @@
         <v>1</v>
       </c>
       <c r="G256">
-        <v>20000</v>
+        <v>140000</v>
       </c>
       <c r="H256" t="str">
         <v>2024-06-28</v>
@@ -9353,24 +9353,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J256" t="str">
-        <v>หุ่นฝึกช่วยพื้นคืนชีพผู้ใหญ่ขั้นพื้นฐานแบบครึ่งตัว</v>
+        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="K256" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (6-1/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (5-4/6)</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>หุ่นฝึก CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="B257" t="str">
-        <v>EQ-CPR-0010</v>
+        <v>EQ-FMS-0018</v>
       </c>
       <c r="C257" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D257" t="str">
-        <v>หุ่นฝึก CPR</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E257" t="str">
         <v>ชุด</v>
@@ -9379,7 +9379,7 @@
         <v>1</v>
       </c>
       <c r="G257">
-        <v>20000</v>
+        <v>140000</v>
       </c>
       <c r="H257" t="str">
         <v>2024-06-28</v>
@@ -9388,24 +9388,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J257" t="str">
-        <v>หุ่นฝึกช่วยพื้นคืนชีพผู้ใหญ่ขั้นพื้นฐานแบบครึ่งตัว</v>
+        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="K257" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (6-2/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (5-5/6)</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหารทางจมูก</v>
+        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="B258" t="str">
-        <v>EQ-NG-0011</v>
+        <v>EQ-FMS-0019</v>
       </c>
       <c r="C258" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D258" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E258" t="str">
         <v>ชุด</v>
@@ -9414,7 +9414,7 @@
         <v>1</v>
       </c>
       <c r="G258">
-        <v>60000</v>
+        <v>140000</v>
       </c>
       <c r="H258" t="str">
         <v>2024-06-28</v>
@@ -9423,24 +9423,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J258" t="str">
-        <v>หุ่นฝึกการใส่สายให้อาหารทางจมูก</v>
+        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="K258" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (8-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (5-6/6)</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
+        <v>หุ่นฝึก CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B259" t="str">
-        <v>EQ-URC-0021</v>
+        <v>EQ-CPR-0009</v>
       </c>
       <c r="C259" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D259" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>หุ่นฝึก CPR</v>
       </c>
       <c r="E259" t="str">
         <v>ชุด</v>
@@ -9449,7 +9449,7 @@
         <v>1</v>
       </c>
       <c r="G259">
-        <v>65000</v>
+        <v>20000</v>
       </c>
       <c r="H259" t="str">
         <v>2024-06-28</v>
@@ -9458,24 +9458,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J259" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
+        <v>หุ่นฝึกช่วยพื้นคืนชีพผู้ใหญ่ขั้นพื้นฐานแบบครึ่งตัว</v>
       </c>
       <c r="K259" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (9-1/3)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (6-1/2)</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
+        <v>หุ่นฝึก CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B260" t="str">
-        <v>EQ-URC-0022</v>
+        <v>EQ-CPR-0010</v>
       </c>
       <c r="C260" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D260" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>หุ่นฝึก CPR</v>
       </c>
       <c r="E260" t="str">
         <v>ชุด</v>
@@ -9484,7 +9484,7 @@
         <v>1</v>
       </c>
       <c r="G260">
-        <v>65000</v>
+        <v>20000</v>
       </c>
       <c r="H260" t="str">
         <v>2024-06-28</v>
@@ -9493,24 +9493,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J260" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
+        <v>หุ่นฝึกช่วยพื้นคืนชีพผู้ใหญ่ขั้นพื้นฐานแบบครึ่งตัว</v>
       </c>
       <c r="K260" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (9-2/3)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (6-2/2)</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
+        <v>หุ่นฝึกใส่สายให้อาหารทางจมูก</v>
       </c>
       <c r="B261" t="str">
-        <v>EQ-URC-0023</v>
+        <v>EQ-NG-0011</v>
       </c>
       <c r="C261" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D261" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="E261" t="str">
         <v>ชุด</v>
@@ -9519,7 +9519,7 @@
         <v>1</v>
       </c>
       <c r="G261">
-        <v>65000</v>
+        <v>60000</v>
       </c>
       <c r="H261" t="str">
         <v>2024-06-28</v>
@@ -9528,10 +9528,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J261" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
+        <v>หุ่นฝึกการใส่สายให้อาหารทางจมูก</v>
       </c>
       <c r="K261" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (9-3/3)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (8-1/1)</v>
       </c>
     </row>
     <row r="262">

--- a/ข้อมูลครุภัณฑ์/Template_Items_and_Assets_v3.xlsx
+++ b/ข้อมูลครุภัณฑ์/Template_Items_and_Assets_v3.xlsx
@@ -1731,7 +1731,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>หุ่นฝึกช่วยพื้นคืนชีพผู้ใหญ่ขั้นพื้นฐานแบบครึ่งตัว มีสัญญาณไฟพร้อมรองรับการประเมินผล/Amoul Man Pro</v>
+        <v>CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B39" t="str">
         <v>EQ-CPR-0001</v>
@@ -1743,30 +1743,30 @@
         <v>หุ่นฝึก CPR</v>
       </c>
       <c r="E39" t="str">
-        <v>ตัว</v>
+        <v>ชุด</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="H39" t="str">
-        <v>2025-08-19</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I39" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J39" t="str">
-        <v>หุ่นฝึกช่วยพื้นคืนชีพผู้ใหญ่ขั้นพื้นฐานแบบครึ่งตัว มีสัญญาณไฟพร้อมรองรับการประเมินผล/Amoul Man Pro (AMM-P)</v>
+        <v>รุ่นมาตรฐาน (ปีงบ 67)</v>
       </c>
       <c r="K39" t="str">
-        <v>1-B9701-FA17-65450010003/001-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (6-1/2)</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>หุ่นฝึกช่วยพื้นคืนชีพผู้ใหญ่ขั้นพื้นฐานแบบครึ่งตัว มีสัญญาณไฟพร้อมรองรับการประเมินผล/Amoul Man Pro</v>
+        <v>CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B40" t="str">
         <v>EQ-CPR-0002</v>
@@ -1778,30 +1778,30 @@
         <v>หุ่นฝึก CPR</v>
       </c>
       <c r="E40" t="str">
-        <v>ตัว</v>
+        <v>ชุด</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="G40">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="H40" t="str">
-        <v>2025-08-19</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I40" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J40" t="str">
-        <v>หุ่นฝึกช่วยพื้นคืนชีพผู้ใหญ่ขั้นพื้นฐานแบบครึ่งตัว มีสัญญาณไฟพร้อมรองรับการประเมินผล/Amoul Man Pro (AMM-P)</v>
+        <v>รุ่นมาตรฐาน (ปีงบ 67)</v>
       </c>
       <c r="K40" t="str">
-        <v>1-B9701-FA17-65450010003/002-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (6-2/2)</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>หุ่นฝึกช่วยพื้นคืนชีพผู้ใหญ่ขั้นพื้นฐานแบบครึ่งตัว มีสัญญาณไฟพร้อมรองรับการประเมินผล/Amoul Man Pro</v>
+        <v>CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B41" t="str">
         <v>EQ-CPR-0003</v>
@@ -1813,109 +1813,109 @@
         <v>หุ่นฝึก CPR</v>
       </c>
       <c r="E41" t="str">
-        <v>ตัว</v>
+        <v>ชุด</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="G41">
-        <v>18000</v>
+        <v>12500</v>
       </c>
       <c r="H41" t="str">
-        <v>2025-08-19</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I41" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J41" t="str">
-        <v>หุ่นฝึกช่วยพื้นคืนชีพผู้ใหญ่ขั้นพื้นฐานแบบครึ่งตัว มีสัญญาณไฟพร้อมรองรับการประเมินผล/Amoul Man Pro (AMM-P)</v>
+        <v>รุ่นมาตรฐาน (ปีงบ 68)</v>
       </c>
       <c r="K41" t="str">
-        <v>1-B9701-FA17-65450010003/003-68</v>
+        <v>1-B9701-FT17-65450010003/001-68</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลขั้นสูง</v>
+        <v>CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B42" t="str">
-        <v>EQ-FMS-0001</v>
+        <v>EQ-CPR-0004</v>
       </c>
       <c r="C42" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D42" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นฝึก CPR</v>
       </c>
       <c r="E42" t="str">
-        <v>ตัว</v>
+        <v>ชุด</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="G42">
-        <v>2765000</v>
+        <v>12500</v>
       </c>
       <c r="H42" t="str">
-        <v>2025-08-19</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I42" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J42" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลขั้นสูง (101-7140-8Y)</v>
+        <v>รุ่นมาตรฐาน (ปีงบ 68)</v>
       </c>
       <c r="K42" t="str">
-        <v>1-B9701-FA17-65450010004/001-68</v>
+        <v>1-B9701-FT17-65450010003/002-68</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลขั้นสูง</v>
+        <v>CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B43" t="str">
-        <v>EQ-FMS-0002</v>
+        <v>EQ-CPR-0005</v>
       </c>
       <c r="C43" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D43" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นฝึก CPR</v>
       </c>
       <c r="E43" t="str">
-        <v>ตัว</v>
+        <v>ชุด</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43">
-        <v>2765000</v>
+        <v>12500</v>
       </c>
       <c r="H43" t="str">
-        <v>2025-08-19</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I43" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J43" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลขั้นสูง (101-7140-8Y)</v>
+        <v>รุ่นมาตรฐาน (ปีงบ 68)</v>
       </c>
       <c r="K43" t="str">
-        <v>1-B9701-FA17-65450010004/002-68</v>
+        <v>1-B9701-FT17-65450010003/003-68</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>หุ่นฝึกฉีดยาหัวไหล่ แบบมีสัญญาณไฟ</v>
+        <v>CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B44" t="str">
-        <v>EQ-IM-0001</v>
+        <v>EQ-CPR-0006</v>
       </c>
       <c r="C44" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D44" t="str">
-        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
+        <v>หุ่นฝึก CPR</v>
       </c>
       <c r="E44" t="str">
         <v>ชุด</v>
@@ -1924,77 +1924,77 @@
         <v>1</v>
       </c>
       <c r="G44">
-        <v>200000</v>
+        <v>12500</v>
       </c>
       <c r="H44" t="str">
-        <v>2024-06-28</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I44" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J44" t="str">
-        <v>หุ่นฝึกการฉีดยากล้ามเนื้อหัวไหล่ แบบโปร่งใส</v>
+        <v>รุ่นมาตรฐาน (ปีงบ 68)</v>
       </c>
       <c r="K44" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (7-1/1)</v>
+        <v>1-B9701-FT17-65450010003/004-68</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>หุ่นฝึกฉีดยาหัวไหล่ แบบมีสัญญาณไฟ</v>
+        <v>CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B45" t="str">
-        <v>EQ-IM-0002</v>
+        <v>EQ-CPR-0007</v>
       </c>
       <c r="C45" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D45" t="str">
-        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
+        <v>หุ่นฝึก CPR</v>
       </c>
       <c r="E45" t="str">
-        <v>ตัว</v>
+        <v>ชุด</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="G45">
-        <v>275000</v>
+        <v>12500</v>
       </c>
       <c r="H45" t="str">
-        <v>2025-08-19</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I45" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J45" t="str">
-        <v>หุ่นฝึกการฉีดยากล้ามเนื้อหัวไหล่ แบบโปร่งใส (M155)</v>
+        <v>รุ่นมาตรฐาน (ปีงบ 68)</v>
       </c>
       <c r="K45" t="str">
-        <v>1-B9701-FA17-65450010004/003-68</v>
+        <v>1-B9701-FT17-65450010003/005-68</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>หุ่นฝึกฉีดยาหัวไหล่ แบบมีสัญญาณไฟ</v>
+        <v>CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B46" t="str">
-        <v>EQ-IM-0003</v>
+        <v>EQ-CPR-0008</v>
       </c>
       <c r="C46" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D46" t="str">
-        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
+        <v>หุ่นฝึก CPR</v>
       </c>
       <c r="E46" t="str">
-        <v>ตัว</v>
+        <v>ชุด</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="G46">
-        <v>275000</v>
+        <v>18000</v>
       </c>
       <c r="H46" t="str">
         <v>2025-08-19</v>
@@ -2003,33 +2003,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J46" t="str">
-        <v>หุ่นฝึกการฉีดยากล้ามเนื้อหัวไหล่ แบบโปร่งใส (M155)</v>
+        <v>รุ่น Amoul Man Pro (AMM-P) มีสัญญาณไฟพร้อมรองรับการประเมินผล</v>
       </c>
       <c r="K46" t="str">
-        <v>1-B9701-FA17-65450010004/004-68</v>
+        <v>1-B9701-FA17-65450010003/001-68</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>หุ่นฝึกฉีดยาหัวไหล่ แบบมีสัญญาณไฟ</v>
+        <v>CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B47" t="str">
-        <v>EQ-IM-0004</v>
+        <v>EQ-CPR-0009</v>
       </c>
       <c r="C47" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D47" t="str">
-        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
+        <v>หุ่นฝึก CPR</v>
       </c>
       <c r="E47" t="str">
-        <v>ตัว</v>
+        <v>ชุด</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="G47">
-        <v>275000</v>
+        <v>18000</v>
       </c>
       <c r="H47" t="str">
         <v>2025-08-19</v>
@@ -2038,33 +2038,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J47" t="str">
-        <v>หุ่นฝึกการฉีดยากล้ามเนื้อหัวไหล่ แบบโปร่งใส (M155)</v>
+        <v>รุ่น Amoul Man Pro (AMM-P) มีสัญญาณไฟพร้อมรองรับการประเมินผล</v>
       </c>
       <c r="K47" t="str">
-        <v>1-B9701-FA17-65450010004/005-68</v>
+        <v>1-B9701-FA17-65450010003/002-68</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>หุ่นฝึกฉีดยาหัวไหล่ แบบมีสัญญาณไฟ</v>
+        <v>CPR ผู้ใหญ่ครึ่งตัว</v>
       </c>
       <c r="B48" t="str">
-        <v>EQ-IM-0015</v>
+        <v>EQ-CPR-0010</v>
       </c>
       <c r="C48" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D48" t="str">
-        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
+        <v>หุ่นฝึก CPR</v>
       </c>
       <c r="E48" t="str">
-        <v>ตัว</v>
+        <v>ชุด</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="G48">
-        <v>275000</v>
+        <v>18000</v>
       </c>
       <c r="H48" t="str">
         <v>2025-08-19</v>
@@ -2073,94 +2073,94 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J48" t="str">
-        <v>หุ่นฝึกการฉีดยากล้ามเนื้อหัวไหล่ แบบโปร่งใส (M155)</v>
+        <v>รุ่น Amoul Man Pro (AMM-P) มีสัญญาณไฟพร้อมรองรับการประเมินผล</v>
       </c>
       <c r="K48" t="str">
-        <v>1-B9701-FA17-65450010004/006-68</v>
+        <v>1-B9701-FA17-65450010003/003-68</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>หุ่นฝึกฉีดยาสะโพก แบบมีสัญญาณไฟ</v>
+        <v>หุ่นฝึก CPR ทารก แบบมีสัญญาณไฟ</v>
       </c>
       <c r="B49" t="str">
-        <v>EQ-IM-0005</v>
+        <v>EQ-CPR-0011</v>
       </c>
       <c r="C49" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D49" t="str">
-        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
+        <v>หุ่นฝึก CPR</v>
       </c>
       <c r="E49" t="str">
-        <v>ตัว</v>
+        <v>ชุด</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="G49">
-        <v>245000</v>
+        <v>10000</v>
       </c>
       <c r="H49" t="str">
-        <v>2025-08-19</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I49" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J49" t="str">
-        <v>หุ่นฝึกการฉีดยากล้ามเนื้อสะโพก แบบโปร่งใส (M152)</v>
+        <v>หุ่นจำลองช่วยฟื้นคืนชีพ ทารก แบบมีสัญญาณไฟ</v>
       </c>
       <c r="K49" t="str">
-        <v>1-B9701-FA17-65450010004/007-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (20-1/2)</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>หุ่นฝึกฉีดยาสะโพก แบบมีสัญญาณไฟ</v>
+        <v>หุ่นฝึก CPR ทารก แบบมีสัญญาณไฟ</v>
       </c>
       <c r="B50" t="str">
-        <v>EQ-IM-0006</v>
+        <v>EQ-CPR-0012</v>
       </c>
       <c r="C50" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D50" t="str">
-        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
+        <v>หุ่นฝึก CPR</v>
       </c>
       <c r="E50" t="str">
-        <v>ตัว</v>
+        <v>ชุด</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="G50">
-        <v>245000</v>
+        <v>10000</v>
       </c>
       <c r="H50" t="str">
-        <v>2025-08-19</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I50" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J50" t="str">
-        <v>หุ่นฝึกการฉีดยากล้ามเนื้อสะโพก แบบโปร่งใส (M152)</v>
+        <v>หุ่นจำลองช่วยฟื้นคืนชีพ ทารก แบบมีสัญญาณไฟ</v>
       </c>
       <c r="K50" t="str">
-        <v>1-B9701-FA17-65450010004/008-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (20-2/2)</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>หุ่นฝึกฉีดยาสะโพก แบบมีสัญญาณไฟ</v>
+        <v>หุ่นฝึกทักษะการพยาบาลขั้นสูง</v>
       </c>
       <c r="B51" t="str">
-        <v>EQ-IM-0007</v>
+        <v>EQ-FMS-0001</v>
       </c>
       <c r="C51" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D51" t="str">
-        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E51" t="str">
         <v>ตัว</v>
@@ -2169,7 +2169,7 @@
         <v>1</v>
       </c>
       <c r="G51">
-        <v>245000</v>
+        <v>2765000</v>
       </c>
       <c r="H51" t="str">
         <v>2025-08-19</v>
@@ -2178,24 +2178,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J51" t="str">
-        <v>หุ่นฝึกการฉีดยากล้ามเนื้อสะโพก แบบโปร่งใส (M152)</v>
+        <v>หุ่นฝึกทักษะการพยาบาลขั้นสูง (101-7140-8Y)</v>
       </c>
       <c r="K51" t="str">
-        <v>1-B9701-FA17-65450010004/009-68</v>
+        <v>1-B9701-FA17-65450010004/001-68</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>หุ่นฝึกฉีดยาสะโพก แบบมีสัญญาณไฟ</v>
+        <v>หุ่นฝึกทักษะการพยาบาลขั้นสูง</v>
       </c>
       <c r="B52" t="str">
-        <v>EQ-IM-0008</v>
+        <v>EQ-FMS-0002</v>
       </c>
       <c r="C52" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D52" t="str">
-        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E52" t="str">
         <v>ตัว</v>
@@ -2204,7 +2204,7 @@
         <v>1</v>
       </c>
       <c r="G52">
-        <v>245000</v>
+        <v>2765000</v>
       </c>
       <c r="H52" t="str">
         <v>2025-08-19</v>
@@ -2213,18 +2213,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J52" t="str">
-        <v>หุ่นฝึกการฉีดยากล้ามเนื้อสะโพก แบบโปร่งใส (M152)</v>
+        <v>หุ่นฝึกทักษะการพยาบาลขั้นสูง (101-7140-8Y)</v>
       </c>
       <c r="K52" t="str">
-        <v>1-B9701-FA17-65450010004/010-68</v>
+        <v>1-B9701-FA17-65450010004/002-68</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>หุ่นฝึกฉีดยาสะโพก แบบมีสัญญาณไฟ</v>
+        <v>หุ่นฝึกฉีดยาหัวไหล่ แบบมีสัญญาณไฟ</v>
       </c>
       <c r="B53" t="str">
-        <v>EQ-IM-0009</v>
+        <v>EQ-IM-0001</v>
       </c>
       <c r="C53" t="str">
         <v>EQUIPMENT</v>
@@ -2233,39 +2233,39 @@
         <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
       </c>
       <c r="E53" t="str">
-        <v>ตัว</v>
+        <v>ชุด</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="G53">
-        <v>245000</v>
+        <v>200000</v>
       </c>
       <c r="H53" t="str">
-        <v>2025-08-19</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I53" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J53" t="str">
-        <v>หุ่นฝึกการฉีดยากล้ามเนื้อสะโพก แบบโปร่งใส (M152)</v>
+        <v>หุ่นฝึกการฉีดยากล้ามเนื้อหัวไหล่ แบบโปร่งใส</v>
       </c>
       <c r="K53" t="str">
-        <v>1-B9701-FA17-65450010004/011-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (7-1/1)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>หุ่นฝึกการใส่สายให้อาหาร</v>
+        <v>หุ่นฝึกฉีดยาหัวไหล่ แบบมีสัญญาณไฟ</v>
       </c>
       <c r="B54" t="str">
-        <v>EQ-NG-0001</v>
+        <v>EQ-IM-0002</v>
       </c>
       <c r="C54" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D54" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
       </c>
       <c r="E54" t="str">
         <v>ตัว</v>
@@ -2274,7 +2274,7 @@
         <v>1</v>
       </c>
       <c r="G54">
-        <v>90000</v>
+        <v>275000</v>
       </c>
       <c r="H54" t="str">
         <v>2025-08-19</v>
@@ -2283,24 +2283,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J54" t="str">
-        <v>หุ่นฝึกการใส่สายให้อาหาร (LF01174)</v>
+        <v>หุ่นฝึกการฉีดยากล้ามเนื้อหัวไหล่ แบบโปร่งใส (M155)</v>
       </c>
       <c r="K54" t="str">
-        <v>1-B9701-FA17-65450010004/012-68</v>
+        <v>1-B9701-FA17-65450010004/003-68</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>หุ่นฝึกการใส่สายให้อาหาร</v>
+        <v>หุ่นฝึกฉีดยาหัวไหล่ แบบมีสัญญาณไฟ</v>
       </c>
       <c r="B55" t="str">
-        <v>EQ-NG-0002</v>
+        <v>EQ-IM-0003</v>
       </c>
       <c r="C55" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D55" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
       </c>
       <c r="E55" t="str">
         <v>ตัว</v>
@@ -2309,7 +2309,7 @@
         <v>1</v>
       </c>
       <c r="G55">
-        <v>90000</v>
+        <v>275000</v>
       </c>
       <c r="H55" t="str">
         <v>2025-08-19</v>
@@ -2318,24 +2318,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J55" t="str">
-        <v>หุ่นฝึกการใส่สายให้อาหาร (LF01174)</v>
+        <v>หุ่นฝึกการฉีดยากล้ามเนื้อหัวไหล่ แบบโปร่งใส (M155)</v>
       </c>
       <c r="K55" t="str">
-        <v>1-B9701-FA17-65450010004/013-68</v>
+        <v>1-B9701-FA17-65450010004/004-68</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>หุ่นฝึกการใส่สายให้อาหาร</v>
+        <v>หุ่นฝึกฉีดยาหัวไหล่ แบบมีสัญญาณไฟ</v>
       </c>
       <c r="B56" t="str">
-        <v>EQ-NG-0003</v>
+        <v>EQ-IM-0004</v>
       </c>
       <c r="C56" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D56" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
       </c>
       <c r="E56" t="str">
         <v>ตัว</v>
@@ -2344,7 +2344,7 @@
         <v>1</v>
       </c>
       <c r="G56">
-        <v>90000</v>
+        <v>275000</v>
       </c>
       <c r="H56" t="str">
         <v>2025-08-19</v>
@@ -2353,24 +2353,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J56" t="str">
-        <v>หุ่นฝึกการใส่สายให้อาหาร (LF01174)</v>
+        <v>หุ่นฝึกการฉีดยากล้ามเนื้อหัวไหล่ แบบโปร่งใส (M155)</v>
       </c>
       <c r="K56" t="str">
-        <v>1-B9701-FA17-65450010004/014-68</v>
+        <v>1-B9701-FA17-65450010004/005-68</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>หุ่นฝึกการใส่สายให้อาหาร</v>
+        <v>หุ่นฝึกฉีดยาหัวไหล่ แบบมีสัญญาณไฟ</v>
       </c>
       <c r="B57" t="str">
-        <v>EQ-NG-0004</v>
+        <v>EQ-IM-0015</v>
       </c>
       <c r="C57" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D57" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
       </c>
       <c r="E57" t="str">
         <v>ตัว</v>
@@ -2379,7 +2379,7 @@
         <v>1</v>
       </c>
       <c r="G57">
-        <v>90000</v>
+        <v>275000</v>
       </c>
       <c r="H57" t="str">
         <v>2025-08-19</v>
@@ -2388,24 +2388,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J57" t="str">
-        <v>หุ่นฝึกการใส่สายให้อาหาร (LF01174)</v>
+        <v>หุ่นฝึกการฉีดยากล้ามเนื้อหัวไหล่ แบบโปร่งใส (M155)</v>
       </c>
       <c r="K57" t="str">
-        <v>1-B9701-FA17-65450010004/015-68</v>
+        <v>1-B9701-FA17-65450010004/006-68</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>หุ่นฝึกการใส่สายให้อาหาร</v>
+        <v>หุ่นฝึกฉีดยาสะโพก แบบมีสัญญาณไฟ</v>
       </c>
       <c r="B58" t="str">
-        <v>EQ-NG-0005</v>
+        <v>EQ-IM-0005</v>
       </c>
       <c r="C58" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D58" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
       </c>
       <c r="E58" t="str">
         <v>ตัว</v>
@@ -2414,7 +2414,7 @@
         <v>1</v>
       </c>
       <c r="G58">
-        <v>90000</v>
+        <v>245000</v>
       </c>
       <c r="H58" t="str">
         <v>2025-08-19</v>
@@ -2423,24 +2423,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J58" t="str">
-        <v>หุ่นฝึกการใส่สายให้อาหาร (LF01174)</v>
+        <v>หุ่นฝึกการฉีดยากล้ามเนื้อสะโพก แบบโปร่งใส (M152)</v>
       </c>
       <c r="K58" t="str">
-        <v>1-B9701-FA17-65450010004/016-68</v>
+        <v>1-B9701-FA17-65450010004/007-68</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
+        <v>หุ่นฝึกฉีดยาสะโพก แบบมีสัญญาณไฟ</v>
       </c>
       <c r="B59" t="str">
-        <v>EQ-URC-0001</v>
+        <v>EQ-IM-0006</v>
       </c>
       <c r="C59" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D59" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
       </c>
       <c r="E59" t="str">
         <v>ตัว</v>
@@ -2449,33 +2449,33 @@
         <v>1</v>
       </c>
       <c r="G59">
-        <v>65000</v>
+        <v>245000</v>
       </c>
       <c r="H59" t="str">
-        <v>2024-06-28</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I59" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J59" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
+        <v>หุ่นฝึกการฉีดยากล้ามเนื้อสะโพก แบบโปร่งใส (M152)</v>
       </c>
       <c r="K59" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (9-1/3)</v>
+        <v>1-B9701-FA17-65450010004/008-68</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
+        <v>หุ่นฝึกฉีดยาสะโพก แบบมีสัญญาณไฟ</v>
       </c>
       <c r="B60" t="str">
-        <v>EQ-URC-0002</v>
+        <v>EQ-IM-0007</v>
       </c>
       <c r="C60" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D60" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
       </c>
       <c r="E60" t="str">
         <v>ตัว</v>
@@ -2484,33 +2484,33 @@
         <v>1</v>
       </c>
       <c r="G60">
-        <v>65000</v>
+        <v>245000</v>
       </c>
       <c r="H60" t="str">
-        <v>2024-06-28</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I60" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J60" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
+        <v>หุ่นฝึกการฉีดยากล้ามเนื้อสะโพก แบบโปร่งใส (M152)</v>
       </c>
       <c r="K60" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (9-2/3)</v>
+        <v>1-B9701-FA17-65450010004/009-68</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
+        <v>หุ่นฝึกฉีดยาสะโพก แบบมีสัญญาณไฟ</v>
       </c>
       <c r="B61" t="str">
-        <v>EQ-URC-0003</v>
+        <v>EQ-IM-0008</v>
       </c>
       <c r="C61" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D61" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
       </c>
       <c r="E61" t="str">
         <v>ตัว</v>
@@ -2519,33 +2519,33 @@
         <v>1</v>
       </c>
       <c r="G61">
-        <v>65000</v>
+        <v>245000</v>
       </c>
       <c r="H61" t="str">
-        <v>2024-06-28</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I61" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J61" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
+        <v>หุ่นฝึกการฉีดยากล้ามเนื้อสะโพก แบบโปร่งใส (M152)</v>
       </c>
       <c r="K61" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (9-3/3)</v>
+        <v>1-B9701-FA17-65450010004/010-68</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
+        <v>หุ่นฝึกฉีดยาสะโพก แบบมีสัญญาณไฟ</v>
       </c>
       <c r="B62" t="str">
-        <v>EQ-URC-0004</v>
+        <v>EQ-IM-0009</v>
       </c>
       <c r="C62" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D62" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
       </c>
       <c r="E62" t="str">
         <v>ตัว</v>
@@ -2554,7 +2554,7 @@
         <v>1</v>
       </c>
       <c r="G62">
-        <v>79200</v>
+        <v>245000</v>
       </c>
       <c r="H62" t="str">
         <v>2025-08-19</v>
@@ -2563,24 +2563,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J62" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
+        <v>หุ่นฝึกการฉีดยากล้ามเนื้อสะโพก แบบโปร่งใส (M152)</v>
       </c>
       <c r="K62" t="str">
-        <v>1-B9701-FA17-65450010004/017-68</v>
+        <v>1-B9701-FA17-65450010004/011-68</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
+        <v>หุ่นฝึกการใส่สายให้อาหาร</v>
       </c>
       <c r="B63" t="str">
-        <v>EQ-URC-0005</v>
+        <v>EQ-NG-0001</v>
       </c>
       <c r="C63" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D63" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="E63" t="str">
         <v>ตัว</v>
@@ -2589,7 +2589,7 @@
         <v>1</v>
       </c>
       <c r="G63">
-        <v>79200</v>
+        <v>90000</v>
       </c>
       <c r="H63" t="str">
         <v>2025-08-19</v>
@@ -2598,24 +2598,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J63" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
+        <v>หุ่นฝึกการใส่สายให้อาหาร (LF01174)</v>
       </c>
       <c r="K63" t="str">
-        <v>1-B9701-FA17-65450010004/018-68</v>
+        <v>1-B9701-FA17-65450010004/012-68</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
+        <v>หุ่นฝึกการใส่สายให้อาหาร</v>
       </c>
       <c r="B64" t="str">
-        <v>EQ-URC-0006</v>
+        <v>EQ-NG-0002</v>
       </c>
       <c r="C64" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D64" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="E64" t="str">
         <v>ตัว</v>
@@ -2624,7 +2624,7 @@
         <v>1</v>
       </c>
       <c r="G64">
-        <v>79200</v>
+        <v>90000</v>
       </c>
       <c r="H64" t="str">
         <v>2025-08-19</v>
@@ -2633,24 +2633,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J64" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
+        <v>หุ่นฝึกการใส่สายให้อาหาร (LF01174)</v>
       </c>
       <c r="K64" t="str">
-        <v>1-B9701-FA17-65450010004/019-68</v>
+        <v>1-B9701-FA17-65450010004/013-68</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
+        <v>หุ่นฝึกการใส่สายให้อาหาร</v>
       </c>
       <c r="B65" t="str">
-        <v>EQ-URC-0007</v>
+        <v>EQ-NG-0003</v>
       </c>
       <c r="C65" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D65" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="E65" t="str">
         <v>ตัว</v>
@@ -2659,7 +2659,7 @@
         <v>1</v>
       </c>
       <c r="G65">
-        <v>79200</v>
+        <v>90000</v>
       </c>
       <c r="H65" t="str">
         <v>2025-08-19</v>
@@ -2668,24 +2668,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J65" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
+        <v>หุ่นฝึกการใส่สายให้อาหาร (LF01174)</v>
       </c>
       <c r="K65" t="str">
-        <v>1-B9701-FA17-65450010004/020-68</v>
+        <v>1-B9701-FA17-65450010004/014-68</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
+        <v>หุ่นฝึกการใส่สายให้อาหาร</v>
       </c>
       <c r="B66" t="str">
-        <v>EQ-URC-0008</v>
+        <v>EQ-NG-0004</v>
       </c>
       <c r="C66" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D66" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="E66" t="str">
         <v>ตัว</v>
@@ -2694,7 +2694,7 @@
         <v>1</v>
       </c>
       <c r="G66">
-        <v>79200</v>
+        <v>90000</v>
       </c>
       <c r="H66" t="str">
         <v>2025-08-19</v>
@@ -2703,24 +2703,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J66" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
+        <v>หุ่นฝึกการใส่สายให้อาหาร (LF01174)</v>
       </c>
       <c r="K66" t="str">
-        <v>1-B9701-FA17-65450010004/021-68</v>
+        <v>1-B9701-FA17-65450010004/015-68</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
+        <v>หุ่นฝึกการใส่สายให้อาหาร</v>
       </c>
       <c r="B67" t="str">
-        <v>EQ-URC-0009</v>
+        <v>EQ-NG-0005</v>
       </c>
       <c r="C67" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D67" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="E67" t="str">
         <v>ตัว</v>
@@ -2729,7 +2729,7 @@
         <v>1</v>
       </c>
       <c r="G67">
-        <v>79200</v>
+        <v>90000</v>
       </c>
       <c r="H67" t="str">
         <v>2025-08-19</v>
@@ -2738,10 +2738,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J67" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
+        <v>หุ่นฝึกการใส่สายให้อาหาร (LF01174)</v>
       </c>
       <c r="K67" t="str">
-        <v>1-B9701-FA17-65450010004/022-68</v>
+        <v>1-B9701-FA17-65450010004/016-68</v>
       </c>
     </row>
     <row r="68">
@@ -2749,7 +2749,7 @@
         <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
       </c>
       <c r="B68" t="str">
-        <v>EQ-URC-0010</v>
+        <v>EQ-URC-0001</v>
       </c>
       <c r="C68" t="str">
         <v>EQUIPMENT</v>
@@ -2764,19 +2764,19 @@
         <v>1</v>
       </c>
       <c r="G68">
-        <v>79200</v>
+        <v>65000</v>
       </c>
       <c r="H68" t="str">
-        <v>2025-08-19</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I68" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J68" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
       </c>
       <c r="K68" t="str">
-        <v>1-B9701-FA17-65450010004/023-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (9-1/3)</v>
       </c>
     </row>
     <row r="69">
@@ -2784,7 +2784,7 @@
         <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
       </c>
       <c r="B69" t="str">
-        <v>EQ-URC-0021</v>
+        <v>EQ-URC-0002</v>
       </c>
       <c r="C69" t="str">
         <v>EQUIPMENT</v>
@@ -2799,19 +2799,19 @@
         <v>1</v>
       </c>
       <c r="G69">
-        <v>79200</v>
+        <v>65000</v>
       </c>
       <c r="H69" t="str">
-        <v>2025-08-19</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I69" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J69" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
       </c>
       <c r="K69" t="str">
-        <v>1-B9701-FA17-65450010004/024-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (9-2/3)</v>
       </c>
     </row>
     <row r="70">
@@ -2819,7 +2819,7 @@
         <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
       </c>
       <c r="B70" t="str">
-        <v>EQ-URC-0022</v>
+        <v>EQ-URC-0003</v>
       </c>
       <c r="C70" t="str">
         <v>EQUIPMENT</v>
@@ -2834,19 +2834,19 @@
         <v>1</v>
       </c>
       <c r="G70">
-        <v>79200</v>
+        <v>65000</v>
       </c>
       <c r="H70" t="str">
-        <v>2025-08-19</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I70" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J70" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ)</v>
       </c>
       <c r="K70" t="str">
-        <v>1-B9701-FA17-65450010004/025-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (9-3/3)</v>
       </c>
     </row>
     <row r="71">
@@ -2854,7 +2854,7 @@
         <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
       </c>
       <c r="B71" t="str">
-        <v>EQ-URC-0023</v>
+        <v>EQ-URC-0004</v>
       </c>
       <c r="C71" t="str">
         <v>EQUIPMENT</v>
@@ -2881,56 +2881,56 @@
         <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
       </c>
       <c r="K71" t="str">
-        <v>1-B9701-FA17-65450010004/026-68</v>
+        <v>1-B9701-FA17-65450010004/017-68</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
       </c>
       <c r="B72" t="str">
-        <v>EQ-BRE-0001</v>
+        <v>EQ-URC-0005</v>
       </c>
       <c r="C72" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D72" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E72" t="str">
-        <v>ชุด</v>
+        <v>ตัว</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
       <c r="G72">
-        <v>60000</v>
+        <v>79200</v>
       </c>
       <c r="H72" t="str">
-        <v>2024-06-28</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I72" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J72" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
       </c>
       <c r="K72" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (10-1/1)</v>
+        <v>1-B9701-FA17-65450010004/018-68</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
       </c>
       <c r="B73" t="str">
-        <v>EQ-BRE-0002</v>
+        <v>EQ-URC-0006</v>
       </c>
       <c r="C73" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D73" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E73" t="str">
         <v>ตัว</v>
@@ -2939,7 +2939,7 @@
         <v>1</v>
       </c>
       <c r="G73">
-        <v>64000</v>
+        <v>79200</v>
       </c>
       <c r="H73" t="str">
         <v>2025-08-19</v>
@@ -2948,24 +2948,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J73" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม (40201)</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
       </c>
       <c r="K73" t="str">
-        <v>1-B9701-FA17-65450010004/027-68</v>
+        <v>1-B9701-FA17-65450010004/019-68</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
       </c>
       <c r="B74" t="str">
-        <v>EQ-BRE-0003</v>
+        <v>EQ-URC-0007</v>
       </c>
       <c r="C74" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D74" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E74" t="str">
         <v>ตัว</v>
@@ -2974,7 +2974,7 @@
         <v>1</v>
       </c>
       <c r="G74">
-        <v>64000</v>
+        <v>79200</v>
       </c>
       <c r="H74" t="str">
         <v>2025-08-19</v>
@@ -2983,24 +2983,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J74" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม (40201)</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
       </c>
       <c r="K74" t="str">
-        <v>1-B9701-FA17-65450010004/028-68</v>
+        <v>1-B9701-FA17-65450010004/020-68</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
       </c>
       <c r="B75" t="str">
-        <v>EQ-BRE-0004</v>
+        <v>EQ-URC-0008</v>
       </c>
       <c r="C75" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D75" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E75" t="str">
         <v>ตัว</v>
@@ -3009,7 +3009,7 @@
         <v>1</v>
       </c>
       <c r="G75">
-        <v>64000</v>
+        <v>79200</v>
       </c>
       <c r="H75" t="str">
         <v>2025-08-19</v>
@@ -3018,24 +3018,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J75" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม (40201)</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
       </c>
       <c r="K75" t="str">
-        <v>1-B9701-FA17-65450010004/029-68</v>
+        <v>1-B9701-FA17-65450010004/021-68</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
       </c>
       <c r="B76" t="str">
-        <v>EQ-BRE-0005</v>
+        <v>EQ-URC-0009</v>
       </c>
       <c r="C76" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D76" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E76" t="str">
         <v>ตัว</v>
@@ -3044,7 +3044,7 @@
         <v>1</v>
       </c>
       <c r="G76">
-        <v>64000</v>
+        <v>79200</v>
       </c>
       <c r="H76" t="str">
         <v>2025-08-19</v>
@@ -3053,24 +3053,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J76" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม (40201)</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
       </c>
       <c r="K76" t="str">
-        <v>1-B9701-FA17-65450010004/030-68</v>
+        <v>1-B9701-FA17-65450010004/022-68</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
       </c>
       <c r="B77" t="str">
-        <v>EQ-BRE-0006</v>
+        <v>EQ-URC-0010</v>
       </c>
       <c r="C77" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D77" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E77" t="str">
         <v>ตัว</v>
@@ -3079,7 +3079,7 @@
         <v>1</v>
       </c>
       <c r="G77">
-        <v>64000</v>
+        <v>79200</v>
       </c>
       <c r="H77" t="str">
         <v>2025-08-19</v>
@@ -3088,33 +3088,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J77" t="str">
-        <v>หุ่นฝึกการตรวจเต้านม (40201)</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
       </c>
       <c r="K77" t="str">
-        <v>1-B9701-FA17-65450010004/031-68</v>
+        <v>1-B9701-FA17-65450010004/023-68</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>หุ่นฝึกทำแผลและการดูแลแผล</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
       </c>
       <c r="B78" t="str">
-        <v>EQ-STI-0001</v>
+        <v>EQ-URC-0021</v>
       </c>
       <c r="C78" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D78" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E78" t="str">
-        <v>ชุด</v>
+        <v>ตัว</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="G78">
-        <v>60000</v>
+        <v>79200</v>
       </c>
       <c r="H78" t="str">
         <v>2025-08-19</v>
@@ -3123,33 +3123,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J78" t="str">
-        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล (P100)</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
       </c>
       <c r="K78" t="str">
-        <v>1-B9701-FA17-65450010004/032-68</v>
+        <v>1-B9701-FA17-65450010004/024-68</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>หุ่นฝึกทำแผลและการดูแลแผล</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
       </c>
       <c r="B79" t="str">
-        <v>EQ-STI-0002</v>
+        <v>EQ-URC-0022</v>
       </c>
       <c r="C79" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D79" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E79" t="str">
-        <v>ชุด</v>
+        <v>ตัว</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
       <c r="G79">
-        <v>60000</v>
+        <v>79200</v>
       </c>
       <c r="H79" t="str">
         <v>2025-08-19</v>
@@ -3158,33 +3158,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J79" t="str">
-        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล (P100)</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
       </c>
       <c r="K79" t="str">
-        <v>1-B9701-FA17-65450010004/033-68</v>
+        <v>1-B9701-FA17-65450010004/025-68</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>หุ่นฝึกทำแผลและการดูแลแผล</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ (สลับเพศ)</v>
       </c>
       <c r="B80" t="str">
-        <v>EQ-STI-0003</v>
+        <v>EQ-URC-0023</v>
       </c>
       <c r="C80" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D80" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E80" t="str">
-        <v>ชุด</v>
+        <v>ตัว</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="G80">
-        <v>60000</v>
+        <v>79200</v>
       </c>
       <c r="H80" t="str">
         <v>2025-08-19</v>
@@ -3193,24 +3193,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J80" t="str">
-        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล (P100)</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะเพศชายและเพศหญิง (สลับเพศ) (P93SPC-S)</v>
       </c>
       <c r="K80" t="str">
-        <v>1-B9701-FA17-65450010004/034-68</v>
+        <v>1-B9701-FA17-65450010004/026-68</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>หุ่นฝึกทำแผลและการดูแลแผล</v>
+        <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="B81" t="str">
-        <v>EQ-STI-0004</v>
+        <v>EQ-BRE-0001</v>
       </c>
       <c r="C81" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D81" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="E81" t="str">
         <v>ชุด</v>
@@ -3222,39 +3222,39 @@
         <v>60000</v>
       </c>
       <c r="H81" t="str">
-        <v>2025-08-19</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I81" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J81" t="str">
-        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล (P100)</v>
+        <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="K81" t="str">
-        <v>1-B9701-FA17-65450010004/035-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (10-1/1)</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>หุ่นฝึกทำแผลและการดูแลแผล</v>
+        <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="B82" t="str">
-        <v>EQ-STI-0005</v>
+        <v>EQ-BRE-0002</v>
       </c>
       <c r="C82" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D82" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="E82" t="str">
-        <v>ชุด</v>
+        <v>ตัว</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="G82">
-        <v>60000</v>
+        <v>64000</v>
       </c>
       <c r="H82" t="str">
         <v>2025-08-19</v>
@@ -3263,33 +3263,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J82" t="str">
-        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล (P100)</v>
+        <v>หุ่นฝึกการตรวจเต้านม (40201)</v>
       </c>
       <c r="K82" t="str">
-        <v>1-B9701-FA17-65450010004/036-68</v>
+        <v>1-B9701-FA17-65450010004/027-68</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>หุ่นแขนฝึกการเย็บแผล</v>
+        <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="B83" t="str">
-        <v>EQ-STI-0006</v>
+        <v>EQ-BRE-0003</v>
       </c>
       <c r="C83" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D83" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="E83" t="str">
-        <v>ชุด</v>
+        <v>ตัว</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="G83">
-        <v>25000</v>
+        <v>64000</v>
       </c>
       <c r="H83" t="str">
         <v>2025-08-19</v>
@@ -3298,33 +3298,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J83" t="str">
-        <v>หุ่นแขนฝึกการเย็บแผล (P101)</v>
+        <v>หุ่นฝึกการตรวจเต้านม (40201)</v>
       </c>
       <c r="K83" t="str">
-        <v>1-B9701-FA17-65450010004/037-68</v>
+        <v>1-B9701-FA17-65450010004/028-68</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>หุ่นแขนฝึกการเย็บแผล</v>
+        <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="B84" t="str">
-        <v>EQ-STI-0007</v>
+        <v>EQ-BRE-0004</v>
       </c>
       <c r="C84" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D84" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="E84" t="str">
-        <v>ชุด</v>
+        <v>ตัว</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="G84">
-        <v>25000</v>
+        <v>64000</v>
       </c>
       <c r="H84" t="str">
         <v>2025-08-19</v>
@@ -3333,33 +3333,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J84" t="str">
-        <v>หุ่นแขนฝึกการเย็บแผล (P101)</v>
+        <v>หุ่นฝึกการตรวจเต้านม (40201)</v>
       </c>
       <c r="K84" t="str">
-        <v>1-B9701-FA17-65450010004/038-68</v>
+        <v>1-B9701-FA17-65450010004/029-68</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>หุ่นแขนฝึกการเย็บแผล</v>
+        <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="B85" t="str">
-        <v>EQ-STI-0008</v>
+        <v>EQ-BRE-0005</v>
       </c>
       <c r="C85" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D85" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="E85" t="str">
-        <v>ชุด</v>
+        <v>ตัว</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="G85">
-        <v>25000</v>
+        <v>64000</v>
       </c>
       <c r="H85" t="str">
         <v>2025-08-19</v>
@@ -3368,33 +3368,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J85" t="str">
-        <v>หุ่นแขนฝึกการเย็บแผล (P101)</v>
+        <v>หุ่นฝึกการตรวจเต้านม (40201)</v>
       </c>
       <c r="K85" t="str">
-        <v>1-B9701-FA17-65450010004/039-68</v>
+        <v>1-B9701-FA17-65450010004/030-68</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>หุ่นแขนฝึกการเย็บแผล</v>
+        <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="B86" t="str">
-        <v>EQ-STI-0009</v>
+        <v>EQ-BRE-0006</v>
       </c>
       <c r="C86" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D86" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกการตรวจเต้านม</v>
       </c>
       <c r="E86" t="str">
-        <v>ชุด</v>
+        <v>ตัว</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
       <c r="G86">
-        <v>25000</v>
+        <v>64000</v>
       </c>
       <c r="H86" t="str">
         <v>2025-08-19</v>
@@ -3403,18 +3403,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J86" t="str">
-        <v>หุ่นแขนฝึกการเย็บแผล (P101)</v>
+        <v>หุ่นฝึกการตรวจเต้านม (40201)</v>
       </c>
       <c r="K86" t="str">
-        <v>1-B9701-FA17-65450010004/040-68</v>
+        <v>1-B9701-FA17-65450010004/031-68</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>หุ่นขาฝึกเย็บแผล</v>
+        <v>หุ่นฝึกทำแผลและการดูแลแผล</v>
       </c>
       <c r="B87" t="str">
-        <v>EQ-STI-0010</v>
+        <v>EQ-STI-0001</v>
       </c>
       <c r="C87" t="str">
         <v>EQUIPMENT</v>
@@ -3429,7 +3429,7 @@
         <v>1</v>
       </c>
       <c r="G87">
-        <v>30000</v>
+        <v>60000</v>
       </c>
       <c r="H87" t="str">
         <v>2025-08-19</v>
@@ -3438,18 +3438,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J87" t="str">
-        <v>หุ่นขาฝึกเย็บแผล (LF01034)</v>
+        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล (P100)</v>
       </c>
       <c r="K87" t="str">
-        <v>1-B9701-FA17-65450010004/041-68</v>
+        <v>1-B9701-FA17-65450010004/032-68</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>หุ่นขาฝึกเย็บแผล</v>
+        <v>หุ่นฝึกทำแผลและการดูแลแผล</v>
       </c>
       <c r="B88" t="str">
-        <v>EQ-STI-0011</v>
+        <v>EQ-STI-0002</v>
       </c>
       <c r="C88" t="str">
         <v>EQUIPMENT</v>
@@ -3464,7 +3464,7 @@
         <v>1</v>
       </c>
       <c r="G88">
-        <v>30000</v>
+        <v>60000</v>
       </c>
       <c r="H88" t="str">
         <v>2025-08-19</v>
@@ -3473,18 +3473,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J88" t="str">
-        <v>หุ่นขาฝึกเย็บแผล (LF01034)</v>
+        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล (P100)</v>
       </c>
       <c r="K88" t="str">
-        <v>1-B9701-FA17-65450010004/042-68</v>
+        <v>1-B9701-FA17-65450010004/033-68</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>หุ่นขาฝึกเย็บแผล</v>
+        <v>หุ่นฝึกทำแผลและการดูแลแผล</v>
       </c>
       <c r="B89" t="str">
-        <v>EQ-STI-0012</v>
+        <v>EQ-STI-0003</v>
       </c>
       <c r="C89" t="str">
         <v>EQUIPMENT</v>
@@ -3499,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="G89">
-        <v>30000</v>
+        <v>60000</v>
       </c>
       <c r="H89" t="str">
         <v>2025-08-19</v>
@@ -3508,18 +3508,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J89" t="str">
-        <v>หุ่นขาฝึกเย็บแผล (LF01034)</v>
+        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล (P100)</v>
       </c>
       <c r="K89" t="str">
-        <v>1-B9701-FA17-65450010004/043-68</v>
+        <v>1-B9701-FA17-65450010004/034-68</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>หุ่นขาฝึกเย็บแผล</v>
+        <v>หุ่นฝึกทำแผลและการดูแลแผล</v>
       </c>
       <c r="B90" t="str">
-        <v>EQ-STI-0013</v>
+        <v>EQ-STI-0004</v>
       </c>
       <c r="C90" t="str">
         <v>EQUIPMENT</v>
@@ -3534,7 +3534,7 @@
         <v>1</v>
       </c>
       <c r="G90">
-        <v>30000</v>
+        <v>60000</v>
       </c>
       <c r="H90" t="str">
         <v>2025-08-19</v>
@@ -3543,18 +3543,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J90" t="str">
-        <v>หุ่นขาฝึกเย็บแผล (LF01034)</v>
+        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล (P100)</v>
       </c>
       <c r="K90" t="str">
-        <v>1-B9701-FA17-65450010004/044-68</v>
+        <v>1-B9701-FA17-65450010004/035-68</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นฝึกทำแผลและการดูแลแผล</v>
       </c>
       <c r="B91" t="str">
-        <v>EQ-STI-0014</v>
+        <v>EQ-STI-0005</v>
       </c>
       <c r="C91" t="str">
         <v>EQUIPMENT</v>
@@ -3569,27 +3569,27 @@
         <v>1</v>
       </c>
       <c r="G91">
-        <v>25000</v>
+        <v>60000</v>
       </c>
       <c r="H91" t="str">
-        <v>2024-06-28</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I91" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J91" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล (P100)</v>
       </c>
       <c r="K91" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (13-1/2)</v>
+        <v>1-B9701-FA17-65450010004/036-68</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นแขนฝึกการเย็บแผล</v>
       </c>
       <c r="B92" t="str">
-        <v>EQ-STI-0015</v>
+        <v>EQ-STI-0006</v>
       </c>
       <c r="C92" t="str">
         <v>EQUIPMENT</v>
@@ -3607,24 +3607,24 @@
         <v>25000</v>
       </c>
       <c r="H92" t="str">
-        <v>2024-06-28</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I92" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J92" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นแขนฝึกการเย็บแผล (P101)</v>
       </c>
       <c r="K92" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (13-2/2)</v>
+        <v>1-B9701-FA17-65450010004/037-68</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นแขนฝึกการเย็บแผล</v>
       </c>
       <c r="B93" t="str">
-        <v>EQ-STI-0016</v>
+        <v>EQ-STI-0007</v>
       </c>
       <c r="C93" t="str">
         <v>EQUIPMENT</v>
@@ -3639,7 +3639,7 @@
         <v>1</v>
       </c>
       <c r="G93">
-        <v>40000</v>
+        <v>25000</v>
       </c>
       <c r="H93" t="str">
         <v>2025-08-19</v>
@@ -3648,18 +3648,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J93" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นแขนฝึกการเย็บแผล (P101)</v>
       </c>
       <c r="K93" t="str">
-        <v>1-B9701-FA17-65450010004/045-68</v>
+        <v>1-B9701-FA17-65450010004/038-68</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นแขนฝึกการเย็บแผล</v>
       </c>
       <c r="B94" t="str">
-        <v>EQ-STI-0017</v>
+        <v>EQ-STI-0008</v>
       </c>
       <c r="C94" t="str">
         <v>EQUIPMENT</v>
@@ -3674,7 +3674,7 @@
         <v>1</v>
       </c>
       <c r="G94">
-        <v>40000</v>
+        <v>25000</v>
       </c>
       <c r="H94" t="str">
         <v>2025-08-19</v>
@@ -3683,18 +3683,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J94" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นแขนฝึกการเย็บแผล (P101)</v>
       </c>
       <c r="K94" t="str">
-        <v>1-B9701-FA17-65450010004/046-68</v>
+        <v>1-B9701-FA17-65450010004/039-68</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นแขนฝึกการเย็บแผล</v>
       </c>
       <c r="B95" t="str">
-        <v>EQ-STI-0018</v>
+        <v>EQ-STI-0009</v>
       </c>
       <c r="C95" t="str">
         <v>EQUIPMENT</v>
@@ -3709,7 +3709,7 @@
         <v>1</v>
       </c>
       <c r="G95">
-        <v>40000</v>
+        <v>25000</v>
       </c>
       <c r="H95" t="str">
         <v>2025-08-19</v>
@@ -3718,18 +3718,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J95" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นแขนฝึกการเย็บแผล (P101)</v>
       </c>
       <c r="K95" t="str">
-        <v>1-B9701-FA17-65450010004/047-68</v>
+        <v>1-B9701-FA17-65450010004/040-68</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นขาฝึกเย็บแผล</v>
       </c>
       <c r="B96" t="str">
-        <v>EQ-STI-0019</v>
+        <v>EQ-STI-0010</v>
       </c>
       <c r="C96" t="str">
         <v>EQUIPMENT</v>
@@ -3744,7 +3744,7 @@
         <v>1</v>
       </c>
       <c r="G96">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="H96" t="str">
         <v>2025-08-19</v>
@@ -3753,18 +3753,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J96" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นขาฝึกเย็บแผล (LF01034)</v>
       </c>
       <c r="K96" t="str">
-        <v>1-B9701-FA17-65450010004/048-68</v>
+        <v>1-B9701-FA17-65450010004/041-68</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นขาฝึกเย็บแผล</v>
       </c>
       <c r="B97" t="str">
-        <v>EQ-STI-0020</v>
+        <v>EQ-STI-0011</v>
       </c>
       <c r="C97" t="str">
         <v>EQUIPMENT</v>
@@ -3779,7 +3779,7 @@
         <v>1</v>
       </c>
       <c r="G97">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="H97" t="str">
         <v>2025-08-19</v>
@@ -3788,18 +3788,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J97" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นขาฝึกเย็บแผล (LF01034)</v>
       </c>
       <c r="K97" t="str">
-        <v>1-B9701-FA17-65450010004/049-68</v>
+        <v>1-B9701-FA17-65450010004/042-68</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นขาฝึกเย็บแผล</v>
       </c>
       <c r="B98" t="str">
-        <v>EQ-STI-0021</v>
+        <v>EQ-STI-0012</v>
       </c>
       <c r="C98" t="str">
         <v>EQUIPMENT</v>
@@ -3814,7 +3814,7 @@
         <v>1</v>
       </c>
       <c r="G98">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="H98" t="str">
         <v>2025-08-19</v>
@@ -3823,18 +3823,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J98" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นขาฝึกเย็บแผล (LF01034)</v>
       </c>
       <c r="K98" t="str">
-        <v>1-B9701-FA17-65450010004/050-68</v>
+        <v>1-B9701-FA17-65450010004/043-68</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นขาฝึกเย็บแผล</v>
       </c>
       <c r="B99" t="str">
-        <v>EQ-STI-0022</v>
+        <v>EQ-STI-0013</v>
       </c>
       <c r="C99" t="str">
         <v>EQUIPMENT</v>
@@ -3849,7 +3849,7 @@
         <v>1</v>
       </c>
       <c r="G99">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="H99" t="str">
         <v>2025-08-19</v>
@@ -3858,10 +3858,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J99" t="str">
-        <v>โมเดลบาดแผลจำลอง</v>
+        <v>หุ่นขาฝึกเย็บแผล (LF01034)</v>
       </c>
       <c r="K99" t="str">
-        <v>1-B9701-FA17-65450010004/051-68</v>
+        <v>1-B9701-FA17-65450010004/044-68</v>
       </c>
     </row>
     <row r="100">
@@ -3869,7 +3869,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B100" t="str">
-        <v>EQ-STI-0023</v>
+        <v>EQ-STI-0014</v>
       </c>
       <c r="C100" t="str">
         <v>EQUIPMENT</v>
@@ -3884,10 +3884,10 @@
         <v>1</v>
       </c>
       <c r="G100">
-        <v>40000</v>
+        <v>25000</v>
       </c>
       <c r="H100" t="str">
-        <v>2025-08-19</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I100" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3896,7 +3896,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K100" t="str">
-        <v>1-B9701-FA17-65450010004/052-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (13-1/2)</v>
       </c>
     </row>
     <row r="101">
@@ -3904,7 +3904,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B101" t="str">
-        <v>EQ-STI-0051</v>
+        <v>EQ-STI-0015</v>
       </c>
       <c r="C101" t="str">
         <v>EQUIPMENT</v>
@@ -3919,10 +3919,10 @@
         <v>1</v>
       </c>
       <c r="G101">
-        <v>40000</v>
+        <v>25000</v>
       </c>
       <c r="H101" t="str">
-        <v>2025-08-19</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I101" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3931,7 +3931,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K101" t="str">
-        <v>1-B9701-FA17-65450010004/053-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (13-2/2)</v>
       </c>
     </row>
     <row r="102">
@@ -3939,7 +3939,7 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B102" t="str">
-        <v>EQ-STI-0052</v>
+        <v>EQ-STI-0016</v>
       </c>
       <c r="C102" t="str">
         <v>EQUIPMENT</v>
@@ -3966,21 +3966,21 @@
         <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K102" t="str">
-        <v>1-B9701-FA17-65450010004/054-68</v>
+        <v>1-B9701-FA17-65450010004/045-68</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>SAM</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B103" t="str">
-        <v>EQ-SAM-0001</v>
+        <v>EQ-STI-0017</v>
       </c>
       <c r="C103" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D103" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E103" t="str">
         <v>ชุด</v>
@@ -3989,7 +3989,7 @@
         <v>1</v>
       </c>
       <c r="G103">
-        <v>735000</v>
+        <v>40000</v>
       </c>
       <c r="H103" t="str">
         <v>2025-08-19</v>
@@ -3998,24 +3998,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J103" t="str">
-        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K103" t="str">
-        <v>1-B9701-FA17-65450010004/055-68</v>
+        <v>1-B9701-FA17-65450010004/046-68</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>SAM</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B104" t="str">
-        <v>EQ-SAM-0002</v>
+        <v>EQ-STI-0018</v>
       </c>
       <c r="C104" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D104" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E104" t="str">
         <v>ชุด</v>
@@ -4024,7 +4024,7 @@
         <v>1</v>
       </c>
       <c r="G104">
-        <v>735000</v>
+        <v>40000</v>
       </c>
       <c r="H104" t="str">
         <v>2025-08-19</v>
@@ -4033,24 +4033,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J104" t="str">
-        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K104" t="str">
-        <v>1-B9701-FA17-65450010004/056-68</v>
+        <v>1-B9701-FA17-65450010004/047-68</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>SAM</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B105" t="str">
-        <v>EQ-SAM-0003</v>
+        <v>EQ-STI-0019</v>
       </c>
       <c r="C105" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D105" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E105" t="str">
         <v>ชุด</v>
@@ -4059,7 +4059,7 @@
         <v>1</v>
       </c>
       <c r="G105">
-        <v>735000</v>
+        <v>40000</v>
       </c>
       <c r="H105" t="str">
         <v>2025-08-19</v>
@@ -4068,24 +4068,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J105" t="str">
-        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K105" t="str">
-        <v>1-B9701-FA17-65450010004/057-68</v>
+        <v>1-B9701-FA17-65450010004/048-68</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>SAM</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B106" t="str">
-        <v>EQ-SAM-0004</v>
+        <v>EQ-STI-0020</v>
       </c>
       <c r="C106" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D106" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E106" t="str">
         <v>ชุด</v>
@@ -4094,7 +4094,7 @@
         <v>1</v>
       </c>
       <c r="G106">
-        <v>735000</v>
+        <v>40000</v>
       </c>
       <c r="H106" t="str">
         <v>2025-08-19</v>
@@ -4103,24 +4103,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J106" t="str">
-        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K106" t="str">
-        <v>1-B9701-FA17-65450010004/058-68</v>
+        <v>1-B9701-FA17-65450010004/049-68</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>SAM</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B107" t="str">
-        <v>EQ-SAM-0005</v>
+        <v>EQ-STI-0021</v>
       </c>
       <c r="C107" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D107" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E107" t="str">
         <v>ชุด</v>
@@ -4129,7 +4129,7 @@
         <v>1</v>
       </c>
       <c r="G107">
-        <v>735000</v>
+        <v>40000</v>
       </c>
       <c r="H107" t="str">
         <v>2025-08-19</v>
@@ -4138,24 +4138,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J107" t="str">
-        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K107" t="str">
-        <v>1-B9701-FA17-65450010004/059-68</v>
+        <v>1-B9701-FA17-65450010004/050-68</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>SAM</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B108" t="str">
-        <v>EQ-SAM-0006</v>
+        <v>EQ-STI-0022</v>
       </c>
       <c r="C108" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D108" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E108" t="str">
         <v>ชุด</v>
@@ -4164,7 +4164,7 @@
         <v>1</v>
       </c>
       <c r="G108">
-        <v>735000</v>
+        <v>40000</v>
       </c>
       <c r="H108" t="str">
         <v>2025-08-19</v>
@@ -4173,24 +4173,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J108" t="str">
-        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K108" t="str">
-        <v>1-B9701-FA17-65450010004/060-68</v>
+        <v>1-B9701-FA17-65450010004/051-68</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>SAM</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B109" t="str">
-        <v>EQ-SAM-0007</v>
+        <v>EQ-STI-0023</v>
       </c>
       <c r="C109" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D109" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E109" t="str">
         <v>ชุด</v>
@@ -4199,7 +4199,7 @@
         <v>1</v>
       </c>
       <c r="G109">
-        <v>735000</v>
+        <v>40000</v>
       </c>
       <c r="H109" t="str">
         <v>2025-08-19</v>
@@ -4208,24 +4208,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J109" t="str">
-        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K109" t="str">
-        <v>1-B9701-FA17-65450010004/061-68</v>
+        <v>1-B9701-FA17-65450010004/052-68</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>SAM</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B110" t="str">
-        <v>EQ-SAM-0008</v>
+        <v>EQ-STI-0051</v>
       </c>
       <c r="C110" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D110" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E110" t="str">
         <v>ชุด</v>
@@ -4234,7 +4234,7 @@
         <v>1</v>
       </c>
       <c r="G110">
-        <v>735000</v>
+        <v>40000</v>
       </c>
       <c r="H110" t="str">
         <v>2025-08-19</v>
@@ -4243,24 +4243,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J110" t="str">
-        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K110" t="str">
-        <v>1-B9701-FA17-65450010004/062-68</v>
+        <v>1-B9701-FA17-65450010004/053-68</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>SAM</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="B111" t="str">
-        <v>EQ-SAM-0009</v>
+        <v>EQ-STI-0052</v>
       </c>
       <c r="C111" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D111" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E111" t="str">
         <v>ชุด</v>
@@ -4269,7 +4269,7 @@
         <v>1</v>
       </c>
       <c r="G111">
-        <v>735000</v>
+        <v>40000</v>
       </c>
       <c r="H111" t="str">
         <v>2025-08-19</v>
@@ -4278,10 +4278,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J111" t="str">
-        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
+        <v>โมเดลบาดแผลจำลอง</v>
       </c>
       <c r="K111" t="str">
-        <v>1-B9701-FA17-65450010004/063-68</v>
+        <v>1-B9701-FA17-65450010004/054-68</v>
       </c>
     </row>
     <row r="112">
@@ -4289,7 +4289,7 @@
         <v>SAM</v>
       </c>
       <c r="B112" t="str">
-        <v>EQ-SAM-0010</v>
+        <v>EQ-SAM-0001</v>
       </c>
       <c r="C112" t="str">
         <v>EQUIPMENT</v>
@@ -4316,21 +4316,21 @@
         <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
       </c>
       <c r="K112" t="str">
-        <v>1-B9701-FA17-65450010004/064-68</v>
+        <v>1-B9701-FA17-65450010004/055-68</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>SIM MAN</v>
+        <v>SAM</v>
       </c>
       <c r="B113" t="str">
-        <v>EQ-SIM-0006</v>
+        <v>EQ-SAM-0002</v>
       </c>
       <c r="C113" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D113" t="str">
-        <v>(SIM MAN) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E113" t="str">
         <v>ชุด</v>
@@ -4339,7 +4339,7 @@
         <v>1</v>
       </c>
       <c r="G113">
-        <v>4760000</v>
+        <v>735000</v>
       </c>
       <c r="H113" t="str">
         <v>2025-08-19</v>
@@ -4348,18 +4348,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J113" t="str">
-        <v>หุ่นจำลองสถานการณ์ทางการแพทย์และพยาบาลขั้นสูง (LeonardoHF)</v>
+        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
       </c>
       <c r="K113" t="str">
-        <v>1-B9701-FA17-65450010004/065-68</v>
+        <v>1-B9701-FA17-65450010004/056-68</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>SAM IPAD</v>
+        <v>SAM</v>
       </c>
       <c r="B114" t="str">
-        <v>EQ-SAM-0011</v>
+        <v>EQ-SAM-0003</v>
       </c>
       <c r="C114" t="str">
         <v>EQUIPMENT</v>
@@ -4368,13 +4368,13 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E114" t="str">
-        <v>เครื่อง</v>
+        <v>ชุด</v>
       </c>
       <c r="F114">
         <v>1</v>
       </c>
       <c r="G114">
-        <v>15000</v>
+        <v>735000</v>
       </c>
       <c r="H114" t="str">
         <v>2025-08-19</v>
@@ -4383,18 +4383,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J114" t="str">
-        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
+        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
       </c>
       <c r="K114" t="str">
-        <v>1-B9701-FA18-74400010005/001-68</v>
+        <v>1-B9701-FA17-65450010004/057-68</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>SAM IPAD</v>
+        <v>SAM</v>
       </c>
       <c r="B115" t="str">
-        <v>EQ-SAM-0012</v>
+        <v>EQ-SAM-0004</v>
       </c>
       <c r="C115" t="str">
         <v>EQUIPMENT</v>
@@ -4403,13 +4403,13 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E115" t="str">
-        <v>เครื่อง</v>
+        <v>ชุด</v>
       </c>
       <c r="F115">
         <v>1</v>
       </c>
       <c r="G115">
-        <v>15000</v>
+        <v>735000</v>
       </c>
       <c r="H115" t="str">
         <v>2025-08-19</v>
@@ -4418,18 +4418,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J115" t="str">
-        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
+        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
       </c>
       <c r="K115" t="str">
-        <v>1-B9701-FA18-74400010005/002-68</v>
+        <v>1-B9701-FA17-65450010004/058-68</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>SAM IPAD</v>
+        <v>SAM</v>
       </c>
       <c r="B116" t="str">
-        <v>EQ-SAM-0013</v>
+        <v>EQ-SAM-0005</v>
       </c>
       <c r="C116" t="str">
         <v>EQUIPMENT</v>
@@ -4438,13 +4438,13 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E116" t="str">
-        <v>เครื่อง</v>
+        <v>ชุด</v>
       </c>
       <c r="F116">
         <v>1</v>
       </c>
       <c r="G116">
-        <v>15000</v>
+        <v>735000</v>
       </c>
       <c r="H116" t="str">
         <v>2025-08-19</v>
@@ -4453,18 +4453,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J116" t="str">
-        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
+        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
       </c>
       <c r="K116" t="str">
-        <v>1-B9701-FA18-74400010005/003-68</v>
+        <v>1-B9701-FA17-65450010004/059-68</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>SAM IPAD</v>
+        <v>SAM</v>
       </c>
       <c r="B117" t="str">
-        <v>EQ-SAM-0014</v>
+        <v>EQ-SAM-0006</v>
       </c>
       <c r="C117" t="str">
         <v>EQUIPMENT</v>
@@ -4473,13 +4473,13 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E117" t="str">
-        <v>เครื่อง</v>
+        <v>ชุด</v>
       </c>
       <c r="F117">
         <v>1</v>
       </c>
       <c r="G117">
-        <v>15000</v>
+        <v>735000</v>
       </c>
       <c r="H117" t="str">
         <v>2025-08-19</v>
@@ -4488,18 +4488,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J117" t="str">
-        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
+        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
       </c>
       <c r="K117" t="str">
-        <v>1-B9701-FA18-74400010005/004-68</v>
+        <v>1-B9701-FA17-65450010004/060-68</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>SAM IPAD</v>
+        <v>SAM</v>
       </c>
       <c r="B118" t="str">
-        <v>EQ-SAM-0015</v>
+        <v>EQ-SAM-0007</v>
       </c>
       <c r="C118" t="str">
         <v>EQUIPMENT</v>
@@ -4508,13 +4508,13 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E118" t="str">
-        <v>เครื่อง</v>
+        <v>ชุด</v>
       </c>
       <c r="F118">
         <v>1</v>
       </c>
       <c r="G118">
-        <v>15000</v>
+        <v>735000</v>
       </c>
       <c r="H118" t="str">
         <v>2025-08-19</v>
@@ -4523,18 +4523,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J118" t="str">
-        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
+        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
       </c>
       <c r="K118" t="str">
-        <v>1-B9701-FA18-74400010005/005-68</v>
+        <v>1-B9701-FA17-65450010004/061-68</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>SAM IPAD</v>
+        <v>SAM</v>
       </c>
       <c r="B119" t="str">
-        <v>EQ-SAM-0016</v>
+        <v>EQ-SAM-0008</v>
       </c>
       <c r="C119" t="str">
         <v>EQUIPMENT</v>
@@ -4543,13 +4543,13 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E119" t="str">
-        <v>เครื่อง</v>
+        <v>ชุด</v>
       </c>
       <c r="F119">
         <v>1</v>
       </c>
       <c r="G119">
-        <v>15000</v>
+        <v>735000</v>
       </c>
       <c r="H119" t="str">
         <v>2025-08-19</v>
@@ -4558,18 +4558,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J119" t="str">
-        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
+        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
       </c>
       <c r="K119" t="str">
-        <v>1-B9701-FA18-74400010005/006-68</v>
+        <v>1-B9701-FA17-65450010004/062-68</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>SAM IPAD</v>
+        <v>SAM</v>
       </c>
       <c r="B120" t="str">
-        <v>EQ-SAM-0017</v>
+        <v>EQ-SAM-0009</v>
       </c>
       <c r="C120" t="str">
         <v>EQUIPMENT</v>
@@ -4578,13 +4578,13 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E120" t="str">
-        <v>เครื่อง</v>
+        <v>ชุด</v>
       </c>
       <c r="F120">
         <v>1</v>
       </c>
       <c r="G120">
-        <v>15000</v>
+        <v>735000</v>
       </c>
       <c r="H120" t="str">
         <v>2025-08-19</v>
@@ -4593,18 +4593,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J120" t="str">
-        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
+        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
       </c>
       <c r="K120" t="str">
-        <v>1-B9701-FA18-74400010005/007-68</v>
+        <v>1-B9701-FA17-65450010004/063-68</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>SAM IPAD</v>
+        <v>SAM</v>
       </c>
       <c r="B121" t="str">
-        <v>EQ-SAM-0018</v>
+        <v>EQ-SAM-0010</v>
       </c>
       <c r="C121" t="str">
         <v>EQUIPMENT</v>
@@ -4613,13 +4613,13 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E121" t="str">
-        <v>เครื่อง</v>
+        <v>ชุด</v>
       </c>
       <c r="F121">
         <v>1</v>
       </c>
       <c r="G121">
-        <v>15000</v>
+        <v>735000</v>
       </c>
       <c r="H121" t="str">
         <v>2025-08-19</v>
@@ -4628,33 +4628,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J121" t="str">
-        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
+        <v>หุ่นตรวจร่างกายครึ่งตัว (หุ่นฝึกการฟังเสียงในร่างกาย (ผู้ใหญ่) Brand:Cardionics (SAM 4 )) (718-8804)</v>
       </c>
       <c r="K121" t="str">
-        <v>1-B9701-FA18-74400010005/008-68</v>
+        <v>1-B9701-FA17-65450010004/064-68</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>SAM IPAD</v>
+        <v>SIM MAN</v>
       </c>
       <c r="B122" t="str">
-        <v>EQ-SAM-0019</v>
+        <v>EQ-SIM-0006</v>
       </c>
       <c r="C122" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D122" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>(SIM MAN) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E122" t="str">
-        <v>เครื่อง</v>
+        <v>ชุด</v>
       </c>
       <c r="F122">
         <v>1</v>
       </c>
       <c r="G122">
-        <v>15000</v>
+        <v>4760000</v>
       </c>
       <c r="H122" t="str">
         <v>2025-08-19</v>
@@ -4663,10 +4663,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J122" t="str">
-        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
+        <v>หุ่นจำลองสถานการณ์ทางการแพทย์และพยาบาลขั้นสูง (LeonardoHF)</v>
       </c>
       <c r="K122" t="str">
-        <v>1-B9701-FA18-74400010005/009-68</v>
+        <v>1-B9701-FA17-65450010004/065-68</v>
       </c>
     </row>
     <row r="123">
@@ -4674,7 +4674,7 @@
         <v>SAM IPAD</v>
       </c>
       <c r="B123" t="str">
-        <v>EQ-SAM-0020</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="C123" t="str">
         <v>EQUIPMENT</v>
@@ -4701,30 +4701,30 @@
         <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
       </c>
       <c r="K123" t="str">
-        <v>1-B9701-FA18-74400010005/010-68</v>
+        <v>1-B9701-FA18-74400010005/001-68</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Body Interact</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="B124" t="str">
-        <v>EQ-BI-0001</v>
+        <v>EQ-SAM-0012</v>
       </c>
       <c r="C124" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D124" t="str">
-        <v>เครื่องจำลองสถานการณ์ (BI)</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E124" t="str">
-        <v>ชุด</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F124">
         <v>1</v>
       </c>
       <c r="G124">
-        <v>4412000</v>
+        <v>15000</v>
       </c>
       <c r="H124" t="str">
         <v>2025-08-19</v>
@@ -4733,103 +4733,103 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J124" t="str">
-        <v>ระบบฝึกปฏิบัติการจำลองสถานการณ์ทางคลินิกแบบหน้าจอสัมผัส 30 สถานการณ์ Body Interact BI-30SW-4Y-TH</v>
+        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
       </c>
       <c r="K124" t="str">
-        <v>1-B9701-FA32-74400200001/001-68</v>
+        <v>1-B9701-FA18-74400010005/002-68</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>เตียงตรวจโรค</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="B125" t="str">
-        <v>EQ-BED-0003</v>
+        <v>EQ-SAM-0013</v>
       </c>
       <c r="C125" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D125" t="str">
-        <v>เตียงและตู้ข้างเตียง</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E125" t="str">
-        <v>หลัง</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F125">
         <v>1</v>
       </c>
       <c r="G125">
-        <v>10152</v>
+        <v>15000</v>
       </c>
       <c r="H125" t="str">
-        <v>2024-08-01</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I125" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 2</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J125" t="str">
-        <v>เตียงตรวจโรค</v>
+        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
       </c>
       <c r="K125" t="str">
-        <v>2-B9701-FD17-71050030001/001-67</v>
+        <v>1-B9701-FA18-74400010005/003-68</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="B126" t="str">
-        <v>EQ-TRS-0001</v>
+        <v>EQ-SAM-0014</v>
       </c>
       <c r="C126" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D126" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E126" t="str">
-        <v>แผ่น</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F126">
         <v>1</v>
       </c>
       <c r="G126">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="H126" t="str">
-        <v>2024-06-28</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I126" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J126" t="str">
-        <v>กระดานรองสำหรับช่วยฟื้นคืนชีพ</v>
+        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
       </c>
       <c r="K126" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (42-1/1)</v>
+        <v>1-B9701-FA18-74400010005/004-68</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="B127" t="str">
-        <v>EQ-TRS-0002</v>
+        <v>EQ-SAM-0015</v>
       </c>
       <c r="C127" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D127" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E127" t="str">
-        <v>แผ่น</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F127">
         <v>1</v>
       </c>
       <c r="G127">
-        <v>1000</v>
+        <v>15000</v>
       </c>
       <c r="H127" t="str">
         <v>2025-08-19</v>
@@ -4838,33 +4838,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J127" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR (CPR-B)</v>
+        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
       </c>
       <c r="K127" t="str">
-        <v>1-B9701-FN17-65450010002/001-68</v>
+        <v>1-B9701-FA18-74400010005/005-68</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="B128" t="str">
-        <v>EQ-TRS-0003</v>
+        <v>EQ-SAM-0016</v>
       </c>
       <c r="C128" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D128" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E128" t="str">
-        <v>แผ่น</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F128">
         <v>1</v>
       </c>
       <c r="G128">
-        <v>1000</v>
+        <v>15000</v>
       </c>
       <c r="H128" t="str">
         <v>2025-08-19</v>
@@ -4873,33 +4873,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J128" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR (CPR-B)</v>
+        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
       </c>
       <c r="K128" t="str">
-        <v>1-B9701-FN17-65450010002/002-68</v>
+        <v>1-B9701-FA18-74400010005/006-68</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="B129" t="str">
-        <v>EQ-TRS-0004</v>
+        <v>EQ-SAM-0017</v>
       </c>
       <c r="C129" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D129" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E129" t="str">
-        <v>แผ่น</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F129">
         <v>1</v>
       </c>
       <c r="G129">
-        <v>1000</v>
+        <v>15000</v>
       </c>
       <c r="H129" t="str">
         <v>2025-08-19</v>
@@ -4908,33 +4908,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J129" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR (CPR-B)</v>
+        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
       </c>
       <c r="K129" t="str">
-        <v>1-B9701-FN17-65450010002/003-68</v>
+        <v>1-B9701-FA18-74400010005/007-68</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="B130" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-SAM-0018</v>
       </c>
       <c r="C130" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D130" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E130" t="str">
-        <v>แผ่น</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F130">
         <v>1</v>
       </c>
       <c r="G130">
-        <v>4700</v>
+        <v>15000</v>
       </c>
       <c r="H130" t="str">
         <v>2025-08-19</v>
@@ -4943,33 +4943,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J130" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
+        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
       </c>
       <c r="K130" t="str">
-        <v>1-B9701-FN17-65450010002/004-68</v>
+        <v>1-B9701-FA18-74400010005/008-68</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="B131" t="str">
-        <v>EQ-STI-0025</v>
+        <v>EQ-SAM-0019</v>
       </c>
       <c r="C131" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D131" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E131" t="str">
-        <v>แผ่น</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F131">
         <v>1</v>
       </c>
       <c r="G131">
-        <v>4700</v>
+        <v>15000</v>
       </c>
       <c r="H131" t="str">
         <v>2025-08-19</v>
@@ -4978,33 +4978,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J131" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
+        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
       </c>
       <c r="K131" t="str">
-        <v>1-B9701-FN17-65450010002/005-68</v>
+        <v>1-B9701-FA18-74400010005/009-68</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="B132" t="str">
-        <v>EQ-STI-0026</v>
+        <v>EQ-SAM-0020</v>
       </c>
       <c r="C132" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D132" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="E132" t="str">
-        <v>แผ่น</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F132">
         <v>1</v>
       </c>
       <c r="G132">
-        <v>4700</v>
+        <v>15000</v>
       </c>
       <c r="H132" t="str">
         <v>2025-08-19</v>
@@ -5013,33 +5013,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J132" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
+        <v>Apple IPAD 10.2 Wi-Fi (Apple IPAD)</v>
       </c>
       <c r="K132" t="str">
-        <v>1-B9701-FN17-65450010002/006-68</v>
+        <v>1-B9701-FA18-74400010005/010-68</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>Body Interact</v>
       </c>
       <c r="B133" t="str">
-        <v>EQ-STI-0027</v>
+        <v>EQ-BI-0001</v>
       </c>
       <c r="C133" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D133" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>เครื่องจำลองสถานการณ์ (BI)</v>
       </c>
       <c r="E133" t="str">
-        <v>แผ่น</v>
+        <v>ชุด</v>
       </c>
       <c r="F133">
         <v>1</v>
       </c>
       <c r="G133">
-        <v>4700</v>
+        <v>4412000</v>
       </c>
       <c r="H133" t="str">
         <v>2025-08-19</v>
@@ -5048,59 +5048,59 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J133" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
+        <v>ระบบฝึกปฏิบัติการจำลองสถานการณ์ทางคลินิกแบบหน้าจอสัมผัส 30 สถานการณ์ Body Interact BI-30SW-4Y-TH</v>
       </c>
       <c r="K133" t="str">
-        <v>1-B9701-FN17-65450010002/007-68</v>
+        <v>1-B9701-FA32-74400200001/001-68</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>เตียงตรวจโรค</v>
       </c>
       <c r="B134" t="str">
-        <v>EQ-STI-0028</v>
+        <v>EQ-BED-0003</v>
       </c>
       <c r="C134" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D134" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>เตียงและตู้ข้างเตียง</v>
       </c>
       <c r="E134" t="str">
-        <v>แผ่น</v>
+        <v>หลัง</v>
       </c>
       <c r="F134">
         <v>1</v>
       </c>
       <c r="G134">
-        <v>4700</v>
+        <v>10152</v>
       </c>
       <c r="H134" t="str">
-        <v>2025-08-19</v>
+        <v>2024-08-01</v>
       </c>
       <c r="I134" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 2</v>
       </c>
       <c r="J134" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
+        <v>เตียงตรวจโรค</v>
       </c>
       <c r="K134" t="str">
-        <v>1-B9701-FN17-65450010002/008-68</v>
+        <v>2-B9701-FD17-71050030001/001-67</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="B135" t="str">
-        <v>EQ-STI-0029</v>
+        <v>EQ-TRS-0001</v>
       </c>
       <c r="C135" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D135" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="E135" t="str">
         <v>แผ่น</v>
@@ -5109,33 +5109,33 @@
         <v>1</v>
       </c>
       <c r="G135">
-        <v>4700</v>
+        <v>7000</v>
       </c>
       <c r="H135" t="str">
-        <v>2025-08-19</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I135" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J135" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
+        <v>กระดานรองสำหรับช่วยฟื้นคืนชีพ</v>
       </c>
       <c r="K135" t="str">
-        <v>1-B9701-FN17-65450010002/009-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (42-1/1)</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="B136" t="str">
-        <v>EQ-STI-0030</v>
+        <v>EQ-TRS-0002</v>
       </c>
       <c r="C136" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D136" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="E136" t="str">
         <v>แผ่น</v>
@@ -5144,7 +5144,7 @@
         <v>1</v>
       </c>
       <c r="G136">
-        <v>4700</v>
+        <v>1000</v>
       </c>
       <c r="H136" t="str">
         <v>2025-08-19</v>
@@ -5153,24 +5153,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J136" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR (CPR-B)</v>
       </c>
       <c r="K136" t="str">
-        <v>1-B9701-FN17-65450010002/010-68</v>
+        <v>1-B9701-FN17-65450010002/001-68</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="B137" t="str">
-        <v>EQ-STI-0031</v>
+        <v>EQ-TRS-0003</v>
       </c>
       <c r="C137" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D137" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="E137" t="str">
         <v>แผ่น</v>
@@ -5179,7 +5179,7 @@
         <v>1</v>
       </c>
       <c r="G137">
-        <v>4700</v>
+        <v>1000</v>
       </c>
       <c r="H137" t="str">
         <v>2025-08-19</v>
@@ -5188,24 +5188,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J137" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR (CPR-B)</v>
       </c>
       <c r="K137" t="str">
-        <v>1-B9701-FN17-65450010002/011-68</v>
+        <v>1-B9701-FN17-65450010002/002-68</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="B138" t="str">
-        <v>EQ-STI-0032</v>
+        <v>EQ-TRS-0004</v>
       </c>
       <c r="C138" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D138" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="E138" t="str">
         <v>แผ่น</v>
@@ -5214,7 +5214,7 @@
         <v>1</v>
       </c>
       <c r="G138">
-        <v>4700</v>
+        <v>1000</v>
       </c>
       <c r="H138" t="str">
         <v>2025-08-19</v>
@@ -5223,10 +5223,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J138" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR (CPR-B)</v>
       </c>
       <c r="K138" t="str">
-        <v>1-B9701-FN17-65450010002/012-68</v>
+        <v>1-B9701-FN17-65450010002/003-68</v>
       </c>
     </row>
     <row r="139">
@@ -5234,7 +5234,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B139" t="str">
-        <v>EQ-STI-0033</v>
+        <v>EQ-STI-0024</v>
       </c>
       <c r="C139" t="str">
         <v>EQUIPMENT</v>
@@ -5261,7 +5261,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K139" t="str">
-        <v>1-B9701-FN17-65450010002/013-68</v>
+        <v>1-B9701-FN17-65450010002/004-68</v>
       </c>
     </row>
     <row r="140">
@@ -5269,7 +5269,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B140" t="str">
-        <v>EQ-STI-0034</v>
+        <v>EQ-STI-0025</v>
       </c>
       <c r="C140" t="str">
         <v>EQUIPMENT</v>
@@ -5296,7 +5296,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K140" t="str">
-        <v>1-B9701-FN17-65450010002/014-68</v>
+        <v>1-B9701-FN17-65450010002/005-68</v>
       </c>
     </row>
     <row r="141">
@@ -5304,7 +5304,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B141" t="str">
-        <v>EQ-STI-0035</v>
+        <v>EQ-STI-0026</v>
       </c>
       <c r="C141" t="str">
         <v>EQUIPMENT</v>
@@ -5331,7 +5331,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K141" t="str">
-        <v>1-B9701-FN17-65450010002/015-68</v>
+        <v>1-B9701-FN17-65450010002/006-68</v>
       </c>
     </row>
     <row r="142">
@@ -5339,7 +5339,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B142" t="str">
-        <v>EQ-STI-0036</v>
+        <v>EQ-STI-0027</v>
       </c>
       <c r="C142" t="str">
         <v>EQUIPMENT</v>
@@ -5366,7 +5366,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K142" t="str">
-        <v>1-B9701-FN17-65450010002/016-68</v>
+        <v>1-B9701-FN17-65450010002/007-68</v>
       </c>
     </row>
     <row r="143">
@@ -5374,7 +5374,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B143" t="str">
-        <v>EQ-STI-0037</v>
+        <v>EQ-STI-0028</v>
       </c>
       <c r="C143" t="str">
         <v>EQUIPMENT</v>
@@ -5401,7 +5401,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K143" t="str">
-        <v>1-B9701-FN17-65450010002/017-68</v>
+        <v>1-B9701-FN17-65450010002/008-68</v>
       </c>
     </row>
     <row r="144">
@@ -5409,7 +5409,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B144" t="str">
-        <v>EQ-STI-0038</v>
+        <v>EQ-STI-0029</v>
       </c>
       <c r="C144" t="str">
         <v>EQUIPMENT</v>
@@ -5436,7 +5436,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K144" t="str">
-        <v>1-B9701-FN17-65450010002/018-68</v>
+        <v>1-B9701-FN17-65450010002/009-68</v>
       </c>
     </row>
     <row r="145">
@@ -5444,7 +5444,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B145" t="str">
-        <v>EQ-STI-0039</v>
+        <v>EQ-STI-0030</v>
       </c>
       <c r="C145" t="str">
         <v>EQUIPMENT</v>
@@ -5471,7 +5471,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K145" t="str">
-        <v>1-B9701-FN17-65450010002/019-68</v>
+        <v>1-B9701-FN17-65450010002/010-68</v>
       </c>
     </row>
     <row r="146">
@@ -5479,7 +5479,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B146" t="str">
-        <v>EQ-STI-0040</v>
+        <v>EQ-STI-0031</v>
       </c>
       <c r="C146" t="str">
         <v>EQUIPMENT</v>
@@ -5506,7 +5506,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K146" t="str">
-        <v>1-B9701-FN17-65450010002/020-68</v>
+        <v>1-B9701-FN17-65450010002/011-68</v>
       </c>
     </row>
     <row r="147">
@@ -5514,7 +5514,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B147" t="str">
-        <v>EQ-STI-0041</v>
+        <v>EQ-STI-0032</v>
       </c>
       <c r="C147" t="str">
         <v>EQUIPMENT</v>
@@ -5541,7 +5541,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K147" t="str">
-        <v>1-B9701-FN17-65450010002/021-68</v>
+        <v>1-B9701-FN17-65450010002/012-68</v>
       </c>
     </row>
     <row r="148">
@@ -5549,7 +5549,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B148" t="str">
-        <v>EQ-STI-0042</v>
+        <v>EQ-STI-0033</v>
       </c>
       <c r="C148" t="str">
         <v>EQUIPMENT</v>
@@ -5576,7 +5576,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K148" t="str">
-        <v>1-B9701-FN17-65450010002/022-68</v>
+        <v>1-B9701-FN17-65450010002/013-68</v>
       </c>
     </row>
     <row r="149">
@@ -5584,7 +5584,7 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B149" t="str">
-        <v>EQ-STI-0043</v>
+        <v>EQ-STI-0034</v>
       </c>
       <c r="C149" t="str">
         <v>EQUIPMENT</v>
@@ -5611,30 +5611,30 @@
         <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K149" t="str">
-        <v>1-B9701-FN17-65450010002/023-68</v>
+        <v>1-B9701-FN17-65450010002/014-68</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>แทบเล็ตสำหรับหุ่น AI</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B150" t="str">
-        <v>EQ-AI-0003</v>
+        <v>EQ-STI-0035</v>
       </c>
       <c r="C150" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D150" t="str">
-        <v>(หุ่น AI) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E150" t="str">
-        <v>ชุด</v>
+        <v>แผ่น</v>
       </c>
       <c r="F150">
         <v>1</v>
       </c>
       <c r="G150">
-        <v>5000</v>
+        <v>4700</v>
       </c>
       <c r="H150" t="str">
         <v>2025-08-19</v>
@@ -5643,33 +5643,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J150" t="str">
-        <v>แทบเล็ตสำหรับหุ่น AI (i-pad-alex)</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K150" t="str">
-        <v>1-B9701-FN18-74400010005/001-68</v>
+        <v>1-B9701-FN17-65450010002/015-68</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>แทบเล็ตสำหรับหุ่น AI</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B151" t="str">
-        <v>EQ-AI-0004</v>
+        <v>EQ-STI-0036</v>
       </c>
       <c r="C151" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D151" t="str">
-        <v>(หุ่น AI) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E151" t="str">
-        <v>ชุด</v>
+        <v>แผ่น</v>
       </c>
       <c r="F151">
         <v>1</v>
       </c>
       <c r="G151">
-        <v>5000</v>
+        <v>4700</v>
       </c>
       <c r="H151" t="str">
         <v>2025-08-19</v>
@@ -5678,33 +5678,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J151" t="str">
-        <v>แทบเล็ตสำหรับหุ่น AI (i-pad-alex)</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K151" t="str">
-        <v>1-B9701-FN18-74400010005/002-68</v>
+        <v>1-B9701-FN17-65450010002/016-68</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Android tablet</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B152" t="str">
-        <v>EQ-IT-0005</v>
+        <v>EQ-STI-0037</v>
       </c>
       <c r="C152" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D152" t="str">
-        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E152" t="str">
-        <v>เครื่อง</v>
+        <v>แผ่น</v>
       </c>
       <c r="F152">
         <v>1</v>
       </c>
       <c r="G152">
-        <v>4500</v>
+        <v>4700</v>
       </c>
       <c r="H152" t="str">
         <v>2025-08-19</v>
@@ -5713,33 +5713,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J152" t="str">
-        <v>Android tablet (AD-Tablet)</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K152" t="str">
-        <v>1-B9701-FN18-74400010005/003-68</v>
+        <v>1-B9701-FN17-65450010002/017-68</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Android tablet</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B153" t="str">
-        <v>EQ-IT-0006</v>
+        <v>EQ-STI-0038</v>
       </c>
       <c r="C153" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D153" t="str">
-        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E153" t="str">
-        <v>เครื่อง</v>
+        <v>แผ่น</v>
       </c>
       <c r="F153">
         <v>1</v>
       </c>
       <c r="G153">
-        <v>4500</v>
+        <v>4700</v>
       </c>
       <c r="H153" t="str">
         <v>2025-08-19</v>
@@ -5748,33 +5748,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J153" t="str">
-        <v>Android tablet (AD-Tablet)</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K153" t="str">
-        <v>1-B9701-FN18-74400010005/004-68</v>
+        <v>1-B9701-FN17-65450010002/018-68</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Android tablet</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B154" t="str">
-        <v>EQ-IT-0007</v>
+        <v>EQ-STI-0039</v>
       </c>
       <c r="C154" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D154" t="str">
-        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E154" t="str">
-        <v>เครื่อง</v>
+        <v>แผ่น</v>
       </c>
       <c r="F154">
         <v>1</v>
       </c>
       <c r="G154">
-        <v>4500</v>
+        <v>4700</v>
       </c>
       <c r="H154" t="str">
         <v>2025-08-19</v>
@@ -5783,33 +5783,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J154" t="str">
-        <v>Android tablet (AD-Tablet)</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K154" t="str">
-        <v>1-B9701-FN18-74400010005/005-68</v>
+        <v>1-B9701-FN17-65450010002/019-68</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>เครื่องสำรองไฟ (BI)</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B155" t="str">
-        <v>EQ-BI-0002</v>
+        <v>EQ-STI-0040</v>
       </c>
       <c r="C155" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D155" t="str">
-        <v>เครื่องจำลองสถานการณ์ (BI)</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E155" t="str">
-        <v>เครื่อง</v>
+        <v>แผ่น</v>
       </c>
       <c r="F155">
         <v>1</v>
       </c>
       <c r="G155">
-        <v>4000</v>
+        <v>4700</v>
       </c>
       <c r="H155" t="str">
         <v>2025-08-19</v>
@@ -5818,33 +5818,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J155" t="str">
-        <v>เครื่องสำรองไฟที่สามารถรองรับการไฟดับได้อย่างน้อย 15 นาที (UPS 1200W)</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K155" t="str">
-        <v>1-B9701-FN18-74400090003/001-68</v>
+        <v>1-B9701-FN17-65450010002/020-68</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>เครื่องสำรองไฟ (BI)</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B156" t="str">
-        <v>EQ-BI-0003</v>
+        <v>EQ-STI-0041</v>
       </c>
       <c r="C156" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D156" t="str">
-        <v>เครื่องจำลองสถานการณ์ (BI)</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E156" t="str">
-        <v>เครื่อง</v>
+        <v>แผ่น</v>
       </c>
       <c r="F156">
         <v>1</v>
       </c>
       <c r="G156">
-        <v>4000</v>
+        <v>4700</v>
       </c>
       <c r="H156" t="str">
         <v>2025-08-19</v>
@@ -5853,33 +5853,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J156" t="str">
-        <v>เครื่องสำรองไฟที่สามารถรองรับการไฟดับได้อย่างน้อย 15 นาที (UPS 1200W)</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K156" t="str">
-        <v>1-B9701-FN18-74400090003/002-68</v>
+        <v>1-B9701-FN17-65450010002/021-68</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>เครื่องพิมพ์</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B157" t="str">
-        <v>EQ-IT-0008</v>
+        <v>EQ-STI-0042</v>
       </c>
       <c r="C157" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D157" t="str">
-        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E157" t="str">
-        <v>เครื่อง</v>
+        <v>แผ่น</v>
       </c>
       <c r="F157">
         <v>1</v>
       </c>
       <c r="G157">
-        <v>1500</v>
+        <v>4700</v>
       </c>
       <c r="H157" t="str">
         <v>2025-08-19</v>
@@ -5888,33 +5888,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J157" t="str">
-        <v>เครื่องพิมพ์ (IM-PT-PERI)</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K157" t="str">
-        <v>1-B9701-FN18-74400120002/001-68</v>
+        <v>1-B9701-FN17-65450010002/022-68</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>เครื่องพิมพ์</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
       </c>
       <c r="B158" t="str">
-        <v>EQ-IT-0009</v>
+        <v>EQ-STI-0043</v>
       </c>
       <c r="C158" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D158" t="str">
-        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E158" t="str">
-        <v>เครื่อง</v>
+        <v>แผ่น</v>
       </c>
       <c r="F158">
         <v>1</v>
       </c>
       <c r="G158">
-        <v>1500</v>
+        <v>4700</v>
       </c>
       <c r="H158" t="str">
         <v>2025-08-19</v>
@@ -5923,33 +5923,33 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J158" t="str">
-        <v>เครื่องพิมพ์ (IM-PT-PERI)</v>
+        <v>แผ่นผิวหนังฝึกเย็บแผล (LF01043)</v>
       </c>
       <c r="K158" t="str">
-        <v>1-B9701-FN18-74400120002/002-68</v>
+        <v>1-B9701-FN17-65450010002/023-68</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>เครื่องพิมพ์</v>
+        <v>แทบเล็ตสำหรับหุ่น AI</v>
       </c>
       <c r="B159" t="str">
-        <v>EQ-IT-0010</v>
+        <v>EQ-AI-0003</v>
       </c>
       <c r="C159" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D159" t="str">
-        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
+        <v>(หุ่น AI) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E159" t="str">
-        <v>เครื่อง</v>
+        <v>ชุด</v>
       </c>
       <c r="F159">
         <v>1</v>
       </c>
       <c r="G159">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="H159" t="str">
         <v>2025-08-19</v>
@@ -5958,62 +5958,62 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J159" t="str">
-        <v>เครื่องพิมพ์ (IM-PT-PERI)</v>
+        <v>แทบเล็ตสำหรับหุ่น AI (i-pad-alex)</v>
       </c>
       <c r="K159" t="str">
-        <v>1-B9701-FN18-74400120002/003-68</v>
+        <v>1-B9701-FN18-74400010005/001-68</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>แทบเล็ตสำหรับหุ่น AI</v>
       </c>
       <c r="B160" t="str">
-        <v>EQ-FN-0001</v>
+        <v>EQ-AI-0004</v>
       </c>
       <c r="C160" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D160" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>(หุ่น AI) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E160" t="str">
-        <v>ตู้</v>
+        <v>ชุด</v>
       </c>
       <c r="F160">
         <v>1</v>
       </c>
       <c r="G160">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="H160" t="str">
-        <v>2024-08-01</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I160" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J160" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>แทบเล็ตสำหรับหุ่น AI (i-pad-alex)</v>
       </c>
       <c r="K160" t="str">
-        <v>2-B9701-FP05-71100150007/001-67</v>
+        <v>1-B9701-FN18-74400010005/002-68</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>Android tablet</v>
       </c>
       <c r="B161" t="str">
-        <v>EQ-FN-0002</v>
+        <v>EQ-IT-0005</v>
       </c>
       <c r="C161" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D161" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
       </c>
       <c r="E161" t="str">
-        <v>ตู้</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F161">
         <v>1</v>
@@ -6022,33 +6022,33 @@
         <v>4500</v>
       </c>
       <c r="H161" t="str">
-        <v>2024-08-01</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I161" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J161" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>Android tablet (AD-Tablet)</v>
       </c>
       <c r="K161" t="str">
-        <v>2-B9701-FP05-71100150007/002-67</v>
+        <v>1-B9701-FN18-74400010005/003-68</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>Android tablet</v>
       </c>
       <c r="B162" t="str">
-        <v>EQ-FN-0003</v>
+        <v>EQ-IT-0006</v>
       </c>
       <c r="C162" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D162" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
       </c>
       <c r="E162" t="str">
-        <v>ตู้</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F162">
         <v>1</v>
@@ -6057,33 +6057,33 @@
         <v>4500</v>
       </c>
       <c r="H162" t="str">
-        <v>2024-08-01</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I162" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J162" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>Android tablet (AD-Tablet)</v>
       </c>
       <c r="K162" t="str">
-        <v>2-B9701-FP05-71100150007/003-67</v>
+        <v>1-B9701-FN18-74400010005/004-68</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>Android tablet</v>
       </c>
       <c r="B163" t="str">
-        <v>EQ-FN-0004</v>
+        <v>EQ-IT-0007</v>
       </c>
       <c r="C163" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D163" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
       </c>
       <c r="E163" t="str">
-        <v>ตู้</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -6092,214 +6092,214 @@
         <v>4500</v>
       </c>
       <c r="H163" t="str">
-        <v>2024-08-01</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I163" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J163" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>Android tablet (AD-Tablet)</v>
       </c>
       <c r="K163" t="str">
-        <v>2-B9701-FP05-71100150007/004-67</v>
+        <v>1-B9701-FN18-74400010005/005-68</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>เครื่องสำรองไฟ (BI)</v>
       </c>
       <c r="B164" t="str">
-        <v>EQ-FN-0005</v>
+        <v>EQ-BI-0002</v>
       </c>
       <c r="C164" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D164" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>เครื่องจำลองสถานการณ์ (BI)</v>
       </c>
       <c r="E164" t="str">
-        <v>ตู้</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F164">
         <v>1</v>
       </c>
       <c r="G164">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="H164" t="str">
-        <v>2024-08-01</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I164" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 2</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J164" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>เครื่องสำรองไฟที่สามารถรองรับการไฟดับได้อย่างน้อย 15 นาที (UPS 1200W)</v>
       </c>
       <c r="K164" t="str">
-        <v>2-B9701-FP05-71100150007/005-67</v>
+        <v>1-B9701-FN18-74400090003/001-68</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>เครื่องสำรองไฟ (BI)</v>
       </c>
       <c r="B165" t="str">
-        <v>EQ-FN-0006</v>
+        <v>EQ-BI-0003</v>
       </c>
       <c r="C165" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D165" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>เครื่องจำลองสถานการณ์ (BI)</v>
       </c>
       <c r="E165" t="str">
-        <v>ตู้</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F165">
         <v>1</v>
       </c>
       <c r="G165">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="H165" t="str">
-        <v>2024-08-01</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I165" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J165" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>เครื่องสำรองไฟที่สามารถรองรับการไฟดับได้อย่างน้อย 15 นาที (UPS 1200W)</v>
       </c>
       <c r="K165" t="str">
-        <v>2-B9701-FP05-71100150007/006-67</v>
+        <v>1-B9701-FN18-74400090003/002-68</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>เครื่องพิมพ์</v>
       </c>
       <c r="B166" t="str">
-        <v>EQ-FN-0007</v>
+        <v>EQ-IT-0008</v>
       </c>
       <c r="C166" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D166" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
       </c>
       <c r="E166" t="str">
-        <v>ตู้</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F166">
         <v>1</v>
       </c>
       <c r="G166">
-        <v>4500</v>
+        <v>1500</v>
       </c>
       <c r="H166" t="str">
-        <v>2024-08-01</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I166" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J166" t="str">
-        <v>ตู้เก็บของ</v>
+        <v>เครื่องพิมพ์ (IM-PT-PERI)</v>
       </c>
       <c r="K166" t="str">
-        <v>2-B9701-FP05-71100150007/007-67</v>
+        <v>1-B9701-FN18-74400120002/001-68</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>ชั้นวางของ</v>
+        <v>เครื่องพิมพ์</v>
       </c>
       <c r="B167" t="str">
-        <v>EQ-FN-0008</v>
+        <v>EQ-IT-0009</v>
       </c>
       <c r="C167" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D167" t="str">
-        <v>ชั้นเก็บของ</v>
+        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
       </c>
       <c r="E167" t="str">
-        <v>ชั้น</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F167">
         <v>1</v>
       </c>
       <c r="G167">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="H167" t="str">
-        <v>2024-08-01</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I167" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J167" t="str">
-        <v>ชั้นวางของ</v>
+        <v>เครื่องพิมพ์ (IM-PT-PERI)</v>
       </c>
       <c r="K167" t="str">
-        <v>2-B9701-FP05-73300160001/001-67</v>
+        <v>1-B9701-FN18-74400120002/002-68</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>ชั้นวางของ</v>
+        <v>เครื่องพิมพ์</v>
       </c>
       <c r="B168" t="str">
-        <v>EQ-FN-0009</v>
+        <v>EQ-IT-0010</v>
       </c>
       <c r="C168" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D168" t="str">
-        <v>ชั้นเก็บของ</v>
+        <v>ครุภัณฑ์คอมพิวเตอร์และโสตทัศนูปกรณ์</v>
       </c>
       <c r="E168" t="str">
-        <v>ชั้น</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F168">
         <v>1</v>
       </c>
       <c r="G168">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="H168" t="str">
-        <v>2024-08-01</v>
+        <v>2025-08-19</v>
       </c>
       <c r="I168" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J168" t="str">
-        <v>ชั้นวางของ</v>
+        <v>เครื่องพิมพ์ (IM-PT-PERI)</v>
       </c>
       <c r="K168" t="str">
-        <v>2-B9701-FP05-73300160001/002-67</v>
+        <v>1-B9701-FN18-74400120002/003-68</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>ชั้นวางของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="B169" t="str">
-        <v>EQ-FN-0010</v>
+        <v>EQ-FN-0001</v>
       </c>
       <c r="C169" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D169" t="str">
-        <v>ชั้นเก็บของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="E169" t="str">
-        <v>ชั้น</v>
+        <v>ตู้</v>
       </c>
       <c r="F169">
         <v>1</v>
       </c>
       <c r="G169">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="H169" t="str">
         <v>2024-08-01</v>
@@ -6308,465 +6308,465 @@
         <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
       </c>
       <c r="J169" t="str">
-        <v>ชั้นวางของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="K169" t="str">
-        <v>2-B9701-FP05-73300160001/003-67</v>
+        <v>2-B9701-FP05-71100150007/001-67</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>ชั้นวางของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="B170" t="str">
-        <v>EQ-FN-0011</v>
+        <v>EQ-FN-0002</v>
       </c>
       <c r="C170" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D170" t="str">
-        <v>ชั้นเก็บของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="E170" t="str">
-        <v>ชั้น</v>
+        <v>ตู้</v>
       </c>
       <c r="F170">
         <v>1</v>
       </c>
       <c r="G170">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="H170" t="str">
         <v>2024-08-01</v>
       </c>
       <c r="I170" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 2</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
       </c>
       <c r="J170" t="str">
-        <v>ชั้นวางของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="K170" t="str">
-        <v>2-B9701-FP05-73300160001/004-67</v>
+        <v>2-B9701-FP05-71100150007/002-67</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>ชั้นวางของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="B171" t="str">
-        <v>EQ-FN-0012</v>
+        <v>EQ-FN-0003</v>
       </c>
       <c r="C171" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D171" t="str">
-        <v>ชั้นเก็บของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="E171" t="str">
-        <v>ชั้น</v>
+        <v>ตู้</v>
       </c>
       <c r="F171">
         <v>1</v>
       </c>
       <c r="G171">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="H171" t="str">
         <v>2024-08-01</v>
       </c>
       <c r="I171" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
       </c>
       <c r="J171" t="str">
-        <v>ชั้นวางของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="K171" t="str">
-        <v>2-B9701-FP05-73300160001/005-67</v>
+        <v>2-B9701-FP05-71100150007/003-67</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>ชั้นวางของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="B172" t="str">
-        <v>EQ-FN-0013</v>
+        <v>EQ-FN-0004</v>
       </c>
       <c r="C172" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D172" t="str">
-        <v>ชั้นเก็บของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="E172" t="str">
-        <v>ชั้น</v>
+        <v>ตู้</v>
       </c>
       <c r="F172">
         <v>1</v>
       </c>
       <c r="G172">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="H172" t="str">
         <v>2024-08-01</v>
       </c>
       <c r="I172" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
       </c>
       <c r="J172" t="str">
-        <v>ชั้นวางของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="K172" t="str">
-        <v>2-B9701-FP05-73300160001/006-67</v>
+        <v>2-B9701-FP05-71100150007/004-67</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>ชั้นวางของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="B173" t="str">
-        <v>EQ-FN-0014</v>
+        <v>EQ-FN-0005</v>
       </c>
       <c r="C173" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D173" t="str">
-        <v>ชั้นเก็บของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="E173" t="str">
-        <v>ชั้น</v>
+        <v>ตู้</v>
       </c>
       <c r="F173">
         <v>1</v>
       </c>
       <c r="G173">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="H173" t="str">
         <v>2024-08-01</v>
       </c>
       <c r="I173" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 5</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 2</v>
       </c>
       <c r="J173" t="str">
-        <v>ชั้นวางของ</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="K173" t="str">
-        <v>2-B9701-FP05-73300160001/007-67</v>
+        <v>2-B9701-FP05-71100150007/005-67</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="B174" t="str">
-        <v>EQ-BED-0004</v>
+        <v>EQ-FN-0006</v>
       </c>
       <c r="C174" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D174" t="str">
-        <v>เตียงและตู้ข้างเตียง</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="E174" t="str">
-        <v>หลัง</v>
+        <v>ตู้</v>
       </c>
       <c r="F174">
         <v>1</v>
       </c>
       <c r="G174">
-        <v>70645</v>
+        <v>4500</v>
       </c>
       <c r="H174" t="str">
-        <v>2025-05-01</v>
+        <v>2024-08-01</v>
       </c>
       <c r="I174" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
       </c>
       <c r="J174" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="K174" t="str">
-        <v>1-B9701-FT17-65300010001/001-68</v>
+        <v>2-B9701-FP05-71100150007/006-67</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="B175" t="str">
-        <v>EQ-BED-0005</v>
+        <v>EQ-FN-0007</v>
       </c>
       <c r="C175" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D175" t="str">
-        <v>เตียงและตู้ข้างเตียง</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="E175" t="str">
-        <v>หลัง</v>
+        <v>ตู้</v>
       </c>
       <c r="F175">
         <v>1</v>
       </c>
       <c r="G175">
-        <v>70645</v>
+        <v>4500</v>
       </c>
       <c r="H175" t="str">
-        <v>2025-05-01</v>
+        <v>2024-08-01</v>
       </c>
       <c r="I175" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
       </c>
       <c r="J175" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ตู้เก็บของ</v>
       </c>
       <c r="K175" t="str">
-        <v>1-B9701-FT17-65300010001/002-68</v>
+        <v>2-B9701-FP05-71100150007/007-67</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="B176" t="str">
-        <v>EQ-BED-0006</v>
+        <v>EQ-FN-0008</v>
       </c>
       <c r="C176" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D176" t="str">
-        <v>เตียงและตู้ข้างเตียง</v>
+        <v>ชั้นเก็บของ</v>
       </c>
       <c r="E176" t="str">
-        <v>หลัง</v>
+        <v>ชั้น</v>
       </c>
       <c r="F176">
         <v>1</v>
       </c>
       <c r="G176">
-        <v>70645</v>
+        <v>2500</v>
       </c>
       <c r="H176" t="str">
-        <v>2025-05-01</v>
+        <v>2024-08-01</v>
       </c>
       <c r="I176" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
       </c>
       <c r="J176" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="K176" t="str">
-        <v>1-B9701-FT17-65300010001/003-68</v>
+        <v>2-B9701-FP05-73300160001/001-67</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="B177" t="str">
-        <v>EQ-BED-0007</v>
+        <v>EQ-FN-0009</v>
       </c>
       <c r="C177" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D177" t="str">
-        <v>เตียงและตู้ข้างเตียง</v>
+        <v>ชั้นเก็บของ</v>
       </c>
       <c r="E177" t="str">
-        <v>หลัง</v>
+        <v>ชั้น</v>
       </c>
       <c r="F177">
         <v>1</v>
       </c>
       <c r="G177">
-        <v>70645</v>
+        <v>2500</v>
       </c>
       <c r="H177" t="str">
-        <v>2025-05-01</v>
+        <v>2024-08-01</v>
       </c>
       <c r="I177" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
       </c>
       <c r="J177" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="K177" t="str">
-        <v>1-B9701-FT17-65300010001/004-68</v>
+        <v>2-B9701-FP05-73300160001/002-67</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="B178" t="str">
-        <v>EQ-BED-0008</v>
+        <v>EQ-FN-0010</v>
       </c>
       <c r="C178" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D178" t="str">
-        <v>เตียงและตู้ข้างเตียง</v>
+        <v>ชั้นเก็บของ</v>
       </c>
       <c r="E178" t="str">
-        <v>หลัง</v>
+        <v>ชั้น</v>
       </c>
       <c r="F178">
         <v>1</v>
       </c>
       <c r="G178">
-        <v>70645</v>
+        <v>2500</v>
       </c>
       <c r="H178" t="str">
-        <v>2025-05-01</v>
+        <v>2024-08-01</v>
       </c>
       <c r="I178" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
       </c>
       <c r="J178" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="K178" t="str">
-        <v>1-B9701-FT17-65300010001/005-68</v>
+        <v>2-B9701-FP05-73300160001/003-67</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="B179" t="str">
-        <v>EQ-BED-0009</v>
+        <v>EQ-FN-0011</v>
       </c>
       <c r="C179" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D179" t="str">
-        <v>เตียงและตู้ข้างเตียง</v>
+        <v>ชั้นเก็บของ</v>
       </c>
       <c r="E179" t="str">
-        <v>หลัง</v>
+        <v>ชั้น</v>
       </c>
       <c r="F179">
         <v>1</v>
       </c>
       <c r="G179">
-        <v>70645</v>
+        <v>2500</v>
       </c>
       <c r="H179" t="str">
-        <v>2025-05-01</v>
+        <v>2024-08-01</v>
       </c>
       <c r="I179" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 2</v>
       </c>
       <c r="J179" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="K179" t="str">
-        <v>1-B9701-FT17-65300010001/006-68</v>
+        <v>2-B9701-FP05-73300160001/004-67</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="B180" t="str">
-        <v>EQ-BED-0010</v>
+        <v>EQ-FN-0012</v>
       </c>
       <c r="C180" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D180" t="str">
-        <v>เตียงและตู้ข้างเตียง</v>
+        <v>ชั้นเก็บของ</v>
       </c>
       <c r="E180" t="str">
-        <v>หลัง</v>
+        <v>ชั้น</v>
       </c>
       <c r="F180">
         <v>1</v>
       </c>
       <c r="G180">
-        <v>70645</v>
+        <v>2500</v>
       </c>
       <c r="H180" t="str">
-        <v>2025-05-01</v>
+        <v>2024-08-01</v>
       </c>
       <c r="I180" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
       </c>
       <c r="J180" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="K180" t="str">
-        <v>1-B9701-FT17-65300010001/007-68</v>
+        <v>2-B9701-FP05-73300160001/005-67</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="B181" t="str">
-        <v>EQ-BED-0011</v>
+        <v>EQ-FN-0013</v>
       </c>
       <c r="C181" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D181" t="str">
-        <v>เตียงและตู้ข้างเตียง</v>
+        <v>ชั้นเก็บของ</v>
       </c>
       <c r="E181" t="str">
-        <v>หลัง</v>
+        <v>ชั้น</v>
       </c>
       <c r="F181">
         <v>1</v>
       </c>
       <c r="G181">
-        <v>70645</v>
+        <v>2500</v>
       </c>
       <c r="H181" t="str">
-        <v>2025-05-01</v>
+        <v>2024-08-01</v>
       </c>
       <c r="I181" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
       </c>
       <c r="J181" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="K181" t="str">
-        <v>1-B9701-FT17-65300010001/008-68</v>
+        <v>2-B9701-FP05-73300160001/006-67</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="B182" t="str">
-        <v>EQ-BED-0012</v>
+        <v>EQ-FN-0014</v>
       </c>
       <c r="C182" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D182" t="str">
-        <v>เตียงและตู้ข้างเตียง</v>
+        <v>ชั้นเก็บของ</v>
       </c>
       <c r="E182" t="str">
-        <v>หลัง</v>
+        <v>ชั้น</v>
       </c>
       <c r="F182">
         <v>1</v>
       </c>
       <c r="G182">
-        <v>70645</v>
+        <v>2500</v>
       </c>
       <c r="H182" t="str">
-        <v>2025-05-01</v>
+        <v>2024-08-01</v>
       </c>
       <c r="I182" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 5</v>
       </c>
       <c r="J182" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
+        <v>ชั้นวางของ</v>
       </c>
       <c r="K182" t="str">
-        <v>1-B9701-FT17-65300010001/009-68</v>
+        <v>2-B9701-FP05-73300160001/007-67</v>
       </c>
     </row>
     <row r="183">
@@ -6774,7 +6774,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B183" t="str">
-        <v>EQ-BED-0013</v>
+        <v>EQ-BED-0004</v>
       </c>
       <c r="C183" t="str">
         <v>EQUIPMENT</v>
@@ -6801,7 +6801,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K183" t="str">
-        <v>1-B9701-FT17-65300010001/010-68</v>
+        <v>1-B9701-FT17-65300010001/001-68</v>
       </c>
     </row>
     <row r="184">
@@ -6809,7 +6809,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B184" t="str">
-        <v>EQ-BED-0014</v>
+        <v>EQ-BED-0005</v>
       </c>
       <c r="C184" t="str">
         <v>EQUIPMENT</v>
@@ -6836,7 +6836,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K184" t="str">
-        <v>1-B9701-FT17-65300010001/011-68</v>
+        <v>1-B9701-FT17-65300010001/002-68</v>
       </c>
     </row>
     <row r="185">
@@ -6844,7 +6844,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B185" t="str">
-        <v>EQ-BED-0015</v>
+        <v>EQ-BED-0006</v>
       </c>
       <c r="C185" t="str">
         <v>EQUIPMENT</v>
@@ -6871,7 +6871,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K185" t="str">
-        <v>1-B9701-FT17-65300010001/012-68</v>
+        <v>1-B9701-FT17-65300010001/003-68</v>
       </c>
     </row>
     <row r="186">
@@ -6879,7 +6879,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B186" t="str">
-        <v>EQ-BED-0016</v>
+        <v>EQ-BED-0007</v>
       </c>
       <c r="C186" t="str">
         <v>EQUIPMENT</v>
@@ -6906,7 +6906,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K186" t="str">
-        <v>1-B9701-FT17-65300010001/013-68</v>
+        <v>1-B9701-FT17-65300010001/004-68</v>
       </c>
     </row>
     <row r="187">
@@ -6914,7 +6914,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B187" t="str">
-        <v>EQ-BED-0017</v>
+        <v>EQ-BED-0008</v>
       </c>
       <c r="C187" t="str">
         <v>EQUIPMENT</v>
@@ -6941,7 +6941,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K187" t="str">
-        <v>1-B9701-FT17-65300010001/014-68</v>
+        <v>1-B9701-FT17-65300010001/005-68</v>
       </c>
     </row>
     <row r="188">
@@ -6949,7 +6949,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B188" t="str">
-        <v>EQ-BED-0018</v>
+        <v>EQ-BED-0009</v>
       </c>
       <c r="C188" t="str">
         <v>EQUIPMENT</v>
@@ -6976,7 +6976,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K188" t="str">
-        <v>1-B9701-FT17-65300010001/015-68</v>
+        <v>1-B9701-FT17-65300010001/006-68</v>
       </c>
     </row>
     <row r="189">
@@ -6984,7 +6984,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B189" t="str">
-        <v>EQ-BED-0019</v>
+        <v>EQ-BED-0010</v>
       </c>
       <c r="C189" t="str">
         <v>EQUIPMENT</v>
@@ -7011,7 +7011,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K189" t="str">
-        <v>1-B9701-FT17-65300010001/016-68</v>
+        <v>1-B9701-FT17-65300010001/007-68</v>
       </c>
     </row>
     <row r="190">
@@ -7019,7 +7019,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B190" t="str">
-        <v>EQ-BED-0020</v>
+        <v>EQ-BED-0011</v>
       </c>
       <c r="C190" t="str">
         <v>EQUIPMENT</v>
@@ -7046,7 +7046,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K190" t="str">
-        <v>1-B9701-FT17-65300010001/017-68</v>
+        <v>1-B9701-FT17-65300010001/008-68</v>
       </c>
     </row>
     <row r="191">
@@ -7054,7 +7054,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B191" t="str">
-        <v>EQ-BED-0021</v>
+        <v>EQ-BED-0012</v>
       </c>
       <c r="C191" t="str">
         <v>EQUIPMENT</v>
@@ -7081,7 +7081,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K191" t="str">
-        <v>1-B9701-FT17-65300010001/018-68</v>
+        <v>1-B9701-FT17-65300010001/009-68</v>
       </c>
     </row>
     <row r="192">
@@ -7089,7 +7089,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B192" t="str">
-        <v>EQ-BED-0022</v>
+        <v>EQ-BED-0013</v>
       </c>
       <c r="C192" t="str">
         <v>EQUIPMENT</v>
@@ -7116,7 +7116,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K192" t="str">
-        <v>1-B9701-FT17-65300010001/019-68</v>
+        <v>1-B9701-FT17-65300010001/010-68</v>
       </c>
     </row>
     <row r="193">
@@ -7124,7 +7124,7 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B193" t="str">
-        <v>EQ-BED-0023</v>
+        <v>EQ-BED-0014</v>
       </c>
       <c r="C193" t="str">
         <v>EQUIPMENT</v>
@@ -7151,15 +7151,15 @@
         <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K193" t="str">
-        <v>1-B9701-FT17-65300010001/020-68</v>
+        <v>1-B9701-FT17-65300010001/011-68</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>เตียงคนไข้ระบบไฟฟ้า 2 ไกร์ราวสไลด์ (เตียงใหญ่)</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B194" t="str">
-        <v>EQ-BED-0024</v>
+        <v>EQ-BED-0015</v>
       </c>
       <c r="C194" t="str">
         <v>EQUIPMENT</v>
@@ -7174,7 +7174,7 @@
         <v>1</v>
       </c>
       <c r="G194">
-        <v>64900</v>
+        <v>70645</v>
       </c>
       <c r="H194" t="str">
         <v>2025-05-01</v>
@@ -7183,33 +7183,33 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J194" t="str">
-        <v>เตียงเฟาว์เลอร์ 2 ไกร์ แบบดิจิตอล พร้อมที่นอน หมอน</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K194" t="str">
-        <v>1-B9701-FT17-65300010001/021-68</v>
+        <v>1-B9701-FT17-65300010001/012-68</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>เครื่องแสดงสัญญาณชีพ</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B195" t="str">
-        <v>EQ-SIM2-0001</v>
+        <v>EQ-BED-0016</v>
       </c>
       <c r="C195" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D195" t="str">
-        <v>(SIM MAN 2)ครุภัณฑ์การแพทย์และการพยาบาล</v>
+        <v>เตียงและตู้ข้างเตียง</v>
       </c>
       <c r="E195" t="str">
-        <v>เครื่อง</v>
+        <v>หลัง</v>
       </c>
       <c r="F195">
         <v>1</v>
       </c>
       <c r="G195">
-        <v>280000</v>
+        <v>70645</v>
       </c>
       <c r="H195" t="str">
         <v>2025-05-01</v>
@@ -7218,33 +7218,33 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J195" t="str">
-        <v>เครื่องแสดงสัญญาณชีพ</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K195" t="str">
-        <v>1-B9701-FT17-65450010002/001-68</v>
+        <v>1-B9701-FT17-65300010001/013-68</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>ชุดระบบบันทึกสถานการณ์การฝึกแบบเคลื่อนที่</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B196" t="str">
-        <v>EQ-SIM2-0002</v>
+        <v>EQ-BED-0017</v>
       </c>
       <c r="C196" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D196" t="str">
-        <v>(SIM MAN 2)ครุภัณฑ์การแพทย์และการพยาบาล</v>
+        <v>เตียงและตู้ข้างเตียง</v>
       </c>
       <c r="E196" t="str">
-        <v>ชุด</v>
+        <v>หลัง</v>
       </c>
       <c r="F196">
         <v>1</v>
       </c>
       <c r="G196">
-        <v>1200000</v>
+        <v>70645</v>
       </c>
       <c r="H196" t="str">
         <v>2025-05-01</v>
@@ -7253,33 +7253,33 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J196" t="str">
-        <v>ชุดระบบบันทึกสถานการณ์การฝึกแบบเคลื่อนที่</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K196" t="str">
-        <v>1-B9701-FT17-65450010002/002-68</v>
+        <v>1-B9701-FT17-65300010001/014-68</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B197" t="str">
-        <v>EQ-CPR-0004</v>
+        <v>EQ-BED-0018</v>
       </c>
       <c r="C197" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D197" t="str">
-        <v>หุ่นฝึก CPR</v>
+        <v>เตียงและตู้ข้างเตียง</v>
       </c>
       <c r="E197" t="str">
-        <v>ชุด</v>
+        <v>หลัง</v>
       </c>
       <c r="F197">
         <v>1</v>
       </c>
       <c r="G197">
-        <v>12500</v>
+        <v>70645</v>
       </c>
       <c r="H197" t="str">
         <v>2025-05-01</v>
@@ -7288,33 +7288,33 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J197" t="str">
-        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K197" t="str">
-        <v>1-B9701-FT17-65450010003/001-68</v>
+        <v>1-B9701-FT17-65300010001/015-68</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B198" t="str">
-        <v>EQ-CPR-0005</v>
+        <v>EQ-BED-0019</v>
       </c>
       <c r="C198" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D198" t="str">
-        <v>หุ่นฝึก CPR</v>
+        <v>เตียงและตู้ข้างเตียง</v>
       </c>
       <c r="E198" t="str">
-        <v>ชุด</v>
+        <v>หลัง</v>
       </c>
       <c r="F198">
         <v>1</v>
       </c>
       <c r="G198">
-        <v>12500</v>
+        <v>70645</v>
       </c>
       <c r="H198" t="str">
         <v>2025-05-01</v>
@@ -7323,33 +7323,33 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J198" t="str">
-        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K198" t="str">
-        <v>1-B9701-FT17-65450010003/002-68</v>
+        <v>1-B9701-FT17-65300010001/016-68</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B199" t="str">
-        <v>EQ-CPR-0006</v>
+        <v>EQ-BED-0020</v>
       </c>
       <c r="C199" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D199" t="str">
-        <v>หุ่นฝึก CPR</v>
+        <v>เตียงและตู้ข้างเตียง</v>
       </c>
       <c r="E199" t="str">
-        <v>ชุด</v>
+        <v>หลัง</v>
       </c>
       <c r="F199">
         <v>1</v>
       </c>
       <c r="G199">
-        <v>12500</v>
+        <v>70645</v>
       </c>
       <c r="H199" t="str">
         <v>2025-05-01</v>
@@ -7358,33 +7358,33 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J199" t="str">
-        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K199" t="str">
-        <v>1-B9701-FT17-65450010003/003-68</v>
+        <v>1-B9701-FT17-65300010001/017-68</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B200" t="str">
-        <v>EQ-CPR-0007</v>
+        <v>EQ-BED-0021</v>
       </c>
       <c r="C200" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D200" t="str">
-        <v>หุ่นฝึก CPR</v>
+        <v>เตียงและตู้ข้างเตียง</v>
       </c>
       <c r="E200" t="str">
-        <v>ชุด</v>
+        <v>หลัง</v>
       </c>
       <c r="F200">
         <v>1</v>
       </c>
       <c r="G200">
-        <v>12500</v>
+        <v>70645</v>
       </c>
       <c r="H200" t="str">
         <v>2025-05-01</v>
@@ -7393,33 +7393,33 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J200" t="str">
-        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K200" t="str">
-        <v>1-B9701-FT17-65450010003/004-68</v>
+        <v>1-B9701-FT17-65300010001/018-68</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B201" t="str">
-        <v>EQ-CPR-0008</v>
+        <v>EQ-BED-0022</v>
       </c>
       <c r="C201" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D201" t="str">
-        <v>หุ่นฝึก CPR</v>
+        <v>เตียงและตู้ข้างเตียง</v>
       </c>
       <c r="E201" t="str">
-        <v>ชุด</v>
+        <v>หลัง</v>
       </c>
       <c r="F201">
         <v>1</v>
       </c>
       <c r="G201">
-        <v>12500</v>
+        <v>70645</v>
       </c>
       <c r="H201" t="str">
         <v>2025-05-01</v>
@@ -7428,33 +7428,33 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J201" t="str">
-        <v>หุ่น CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K201" t="str">
-        <v>1-B9701-FT17-65450010003/005-68</v>
+        <v>1-B9701-FT17-65300010001/019-68</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="B202" t="str">
-        <v>EQ-URC-0011</v>
+        <v>EQ-BED-0023</v>
       </c>
       <c r="C202" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D202" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>เตียงและตู้ข้างเตียง</v>
       </c>
       <c r="E202" t="str">
-        <v>ชุด</v>
+        <v>หลัง</v>
       </c>
       <c r="F202">
         <v>1</v>
       </c>
       <c r="G202">
-        <v>111100</v>
+        <v>70645</v>
       </c>
       <c r="H202" t="str">
         <v>2025-05-01</v>
@@ -7463,33 +7463,33 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J202" t="str">
-        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 3 ไกร์ราวสไลด์</v>
       </c>
       <c r="K202" t="str">
-        <v>1-B9701-FT17-65450010004/001-68</v>
+        <v>1-B9701-FT17-65300010001/020-68</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
+        <v>เตียงคนไข้ระบบไฟฟ้า 2 ไกร์ราวสไลด์ (เตียงใหญ่)</v>
       </c>
       <c r="B203" t="str">
-        <v>EQ-URC-0012</v>
+        <v>EQ-BED-0024</v>
       </c>
       <c r="C203" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D203" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>เตียงและตู้ข้างเตียง</v>
       </c>
       <c r="E203" t="str">
-        <v>ชุด</v>
+        <v>หลัง</v>
       </c>
       <c r="F203">
         <v>1</v>
       </c>
       <c r="G203">
-        <v>111100</v>
+        <v>64900</v>
       </c>
       <c r="H203" t="str">
         <v>2025-05-01</v>
@@ -7498,33 +7498,33 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J203" t="str">
-        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
+        <v>เตียงเฟาว์เลอร์ 2 ไกร์ แบบดิจิตอล พร้อมที่นอน หมอน</v>
       </c>
       <c r="K203" t="str">
-        <v>1-B9701-FT17-65450010004/002-68</v>
+        <v>1-B9701-FT17-65300010001/021-68</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
+        <v>เครื่องแสดงสัญญาณชีพ</v>
       </c>
       <c r="B204" t="str">
-        <v>EQ-URC-0013</v>
+        <v>EQ-SIM2-0001</v>
       </c>
       <c r="C204" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D204" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>(SIM MAN 2)ครุภัณฑ์การแพทย์และการพยาบาล</v>
       </c>
       <c r="E204" t="str">
-        <v>ชุด</v>
+        <v>เครื่อง</v>
       </c>
       <c r="F204">
         <v>1</v>
       </c>
       <c r="G204">
-        <v>111100</v>
+        <v>280000</v>
       </c>
       <c r="H204" t="str">
         <v>2025-05-01</v>
@@ -7533,24 +7533,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J204" t="str">
-        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
+        <v>เครื่องแสดงสัญญาณชีพ</v>
       </c>
       <c r="K204" t="str">
-        <v>1-B9701-FT17-65450010004/003-68</v>
+        <v>1-B9701-FT17-65450010002/001-68</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
+        <v>ชุดระบบบันทึกสถานการณ์การฝึกแบบเคลื่อนที่</v>
       </c>
       <c r="B205" t="str">
-        <v>EQ-URC-0014</v>
+        <v>EQ-SIM2-0002</v>
       </c>
       <c r="C205" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D205" t="str">
-        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
+        <v>(SIM MAN 2)ครุภัณฑ์การแพทย์และการพยาบาล</v>
       </c>
       <c r="E205" t="str">
         <v>ชุด</v>
@@ -7559,7 +7559,7 @@
         <v>1</v>
       </c>
       <c r="G205">
-        <v>111100</v>
+        <v>1200000</v>
       </c>
       <c r="H205" t="str">
         <v>2025-05-01</v>
@@ -7568,10 +7568,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J205" t="str">
-        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
+        <v>ชุดระบบบันทึกสถานการณ์การฝึกแบบเคลื่อนที่</v>
       </c>
       <c r="K205" t="str">
-        <v>1-B9701-FT17-65450010004/004-68</v>
+        <v>1-B9701-FT17-65450010002/002-68</v>
       </c>
     </row>
     <row r="206">
@@ -7579,7 +7579,7 @@
         <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
       </c>
       <c r="B206" t="str">
-        <v>EQ-URC-0015</v>
+        <v>EQ-URC-0011</v>
       </c>
       <c r="C206" t="str">
         <v>EQUIPMENT</v>
@@ -7606,15 +7606,15 @@
         <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
       </c>
       <c r="K206" t="str">
-        <v>1-B9701-FT17-65450010004/005-68</v>
+        <v>1-B9701-FT17-65450010004/001-68</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
+        <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
       </c>
       <c r="B207" t="str">
-        <v>EQ-URC-0016</v>
+        <v>EQ-URC-0012</v>
       </c>
       <c r="C207" t="str">
         <v>EQUIPMENT</v>
@@ -7638,18 +7638,18 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J207" t="str">
-        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
+        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
       </c>
       <c r="K207" t="str">
-        <v>1-B9701-FT17-65450010004/006-68</v>
+        <v>1-B9701-FT17-65450010004/002-68</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
+        <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
       </c>
       <c r="B208" t="str">
-        <v>EQ-URC-0017</v>
+        <v>EQ-URC-0013</v>
       </c>
       <c r="C208" t="str">
         <v>EQUIPMENT</v>
@@ -7673,18 +7673,18 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J208" t="str">
-        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
+        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
       </c>
       <c r="K208" t="str">
-        <v>1-B9701-FT17-65450010004/007-68</v>
+        <v>1-B9701-FT17-65450010004/003-68</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
+        <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
       </c>
       <c r="B209" t="str">
-        <v>EQ-URC-0018</v>
+        <v>EQ-URC-0014</v>
       </c>
       <c r="C209" t="str">
         <v>EQUIPMENT</v>
@@ -7708,18 +7708,18 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J209" t="str">
-        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
+        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
       </c>
       <c r="K209" t="str">
-        <v>1-B9701-FT17-65450010004/008-68</v>
+        <v>1-B9701-FT17-65450010004/004-68</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
+        <v>หุ่นจำลองฝึกสวนปัสสาวะ (ชาย)</v>
       </c>
       <c r="B210" t="str">
-        <v>EQ-URC-0019</v>
+        <v>EQ-URC-0015</v>
       </c>
       <c r="C210" t="str">
         <v>EQUIPMENT</v>
@@ -7743,10 +7743,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J210" t="str">
-        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
+        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศชาย</v>
       </c>
       <c r="K210" t="str">
-        <v>1-B9701-FT17-65450010004/009-68</v>
+        <v>1-B9701-FT17-65450010004/005-68</v>
       </c>
     </row>
     <row r="211">
@@ -7754,7 +7754,7 @@
         <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
       </c>
       <c r="B211" t="str">
-        <v>EQ-URC-0020</v>
+        <v>EQ-URC-0016</v>
       </c>
       <c r="C211" t="str">
         <v>EQUIPMENT</v>
@@ -7781,21 +7781,21 @@
         <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
       </c>
       <c r="K211" t="str">
-        <v>1-B9701-FT17-65450010004/010-68</v>
+        <v>1-B9701-FT17-65450010004/006-68</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
       </c>
       <c r="B212" t="str">
-        <v>EQ-NG-0006</v>
+        <v>EQ-URC-0017</v>
       </c>
       <c r="C212" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D212" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E212" t="str">
         <v>ชุด</v>
@@ -7804,7 +7804,7 @@
         <v>1</v>
       </c>
       <c r="G212">
-        <v>121330</v>
+        <v>111100</v>
       </c>
       <c r="H212" t="str">
         <v>2025-05-01</v>
@@ -7813,24 +7813,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J212" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
       </c>
       <c r="K212" t="str">
-        <v>1-B9701-FT17-65450010004/011-68</v>
+        <v>1-B9701-FT17-65450010004/007-68</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
       </c>
       <c r="B213" t="str">
-        <v>EQ-NG-0007</v>
+        <v>EQ-URC-0018</v>
       </c>
       <c r="C213" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D213" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E213" t="str">
         <v>ชุด</v>
@@ -7839,7 +7839,7 @@
         <v>1</v>
       </c>
       <c r="G213">
-        <v>121330</v>
+        <v>111100</v>
       </c>
       <c r="H213" t="str">
         <v>2025-05-01</v>
@@ -7848,24 +7848,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J213" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
       </c>
       <c r="K213" t="str">
-        <v>1-B9701-FT17-65450010004/012-68</v>
+        <v>1-B9701-FT17-65450010004/008-68</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
       </c>
       <c r="B214" t="str">
-        <v>EQ-NG-0008</v>
+        <v>EQ-URC-0019</v>
       </c>
       <c r="C214" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D214" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E214" t="str">
         <v>ชุด</v>
@@ -7874,7 +7874,7 @@
         <v>1</v>
       </c>
       <c r="G214">
-        <v>121330</v>
+        <v>111100</v>
       </c>
       <c r="H214" t="str">
         <v>2025-05-01</v>
@@ -7883,24 +7883,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J214" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
       </c>
       <c r="K214" t="str">
-        <v>1-B9701-FT17-65450010004/013-68</v>
+        <v>1-B9701-FT17-65450010004/009-68</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นจำลองฝึกสวนปัสสาวะ (หญิง)</v>
       </c>
       <c r="B215" t="str">
-        <v>EQ-NG-0009</v>
+        <v>EQ-URC-0020</v>
       </c>
       <c r="C215" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D215" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นฝึกการใส่สายสวนปัสสาวะ</v>
       </c>
       <c r="E215" t="str">
         <v>ชุด</v>
@@ -7909,7 +7909,7 @@
         <v>1</v>
       </c>
       <c r="G215">
-        <v>121330</v>
+        <v>111100</v>
       </c>
       <c r="H215" t="str">
         <v>2025-05-01</v>
@@ -7918,10 +7918,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J215" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นจำลองสำหรับฝึกสวนปัสสาวะเพศหญิง</v>
       </c>
       <c r="K215" t="str">
-        <v>1-B9701-FT17-65450010004/014-68</v>
+        <v>1-B9701-FT17-65450010004/010-68</v>
       </c>
     </row>
     <row r="216">
@@ -7929,7 +7929,7 @@
         <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="B216" t="str">
-        <v>EQ-NG-0010</v>
+        <v>EQ-NG-0006</v>
       </c>
       <c r="C216" t="str">
         <v>EQUIPMENT</v>
@@ -7956,21 +7956,21 @@
         <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="K216" t="str">
-        <v>1-B9701-FT17-65450010004/015-68</v>
+        <v>1-B9701-FT17-65450010004/011-68</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>หุ่นจำลองผู้ใหญ่</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="B217" t="str">
-        <v>EQ-FMS-0003</v>
+        <v>EQ-NG-0007</v>
       </c>
       <c r="C217" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D217" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="E217" t="str">
         <v>ชุด</v>
@@ -7979,7 +7979,7 @@
         <v>1</v>
       </c>
       <c r="G217">
-        <v>3920000</v>
+        <v>121330</v>
       </c>
       <c r="H217" t="str">
         <v>2025-05-01</v>
@@ -7988,24 +7988,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J217" t="str">
-        <v>หุ่นจำลองผู้ใหญ่</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="K217" t="str">
-        <v>1-B9701-FT17-65450010004/016-68</v>
+        <v>1-B9701-FT17-65450010004/012-68</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="B218" t="str">
-        <v>EQ-IV-0001</v>
+        <v>EQ-NG-0008</v>
       </c>
       <c r="C218" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D218" t="str">
-        <v>หุ่นฝึกฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="E218" t="str">
         <v>ชุด</v>
@@ -8014,33 +8014,33 @@
         <v>1</v>
       </c>
       <c r="G218">
-        <v>40000</v>
+        <v>121330</v>
       </c>
       <c r="H218" t="str">
-        <v>2024-06-28</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I218" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J218" t="str">
-        <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="K218" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (11-1/4)</v>
+        <v>1-B9701-FT17-65450010004/013-68</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="B219" t="str">
-        <v>EQ-IV-0002</v>
+        <v>EQ-NG-0009</v>
       </c>
       <c r="C219" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D219" t="str">
-        <v>หุ่นฝึกฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="E219" t="str">
         <v>ชุด</v>
@@ -8049,33 +8049,33 @@
         <v>1</v>
       </c>
       <c r="G219">
-        <v>40000</v>
+        <v>121330</v>
       </c>
       <c r="H219" t="str">
-        <v>2024-06-28</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I219" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J219" t="str">
-        <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="K219" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (11-2/4)</v>
+        <v>1-B9701-FT17-65450010004/014-68</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="B220" t="str">
-        <v>EQ-IV-0003</v>
+        <v>EQ-NG-0010</v>
       </c>
       <c r="C220" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D220" t="str">
-        <v>หุ่นฝึกฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="E220" t="str">
         <v>ชุด</v>
@@ -8084,33 +8084,33 @@
         <v>1</v>
       </c>
       <c r="G220">
-        <v>40000</v>
+        <v>121330</v>
       </c>
       <c r="H220" t="str">
-        <v>2024-06-28</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I220" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J220" t="str">
-        <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="K220" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (11-3/4)</v>
+        <v>1-B9701-FT17-65450010004/015-68</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
+        <v>หุ่นจำลองผู้ใหญ่</v>
       </c>
       <c r="B221" t="str">
-        <v>EQ-IV-0004</v>
+        <v>EQ-FMS-0003</v>
       </c>
       <c r="C221" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D221" t="str">
-        <v>หุ่นฝึกฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E221" t="str">
         <v>ชุด</v>
@@ -8119,19 +8119,19 @@
         <v>1</v>
       </c>
       <c r="G221">
-        <v>40000</v>
+        <v>3920000</v>
       </c>
       <c r="H221" t="str">
-        <v>2024-06-28</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I221" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J221" t="str">
-        <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
+        <v>หุ่นจำลองผู้ใหญ่</v>
       </c>
       <c r="K221" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (11-4/4)</v>
+        <v>1-B9701-FT17-65450010004/016-68</v>
       </c>
     </row>
     <row r="222">
@@ -8139,7 +8139,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B222" t="str">
-        <v>EQ-IV-0005</v>
+        <v>EQ-IV-0001</v>
       </c>
       <c r="C222" t="str">
         <v>EQUIPMENT</v>
@@ -8154,19 +8154,19 @@
         <v>1</v>
       </c>
       <c r="G222">
-        <v>60100</v>
+        <v>40000</v>
       </c>
       <c r="H222" t="str">
-        <v>2025-05-01</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I222" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J222" t="str">
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K222" t="str">
-        <v>1-B9701-FT17-65450010004/017-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (11-1/4)</v>
       </c>
     </row>
     <row r="223">
@@ -8174,7 +8174,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B223" t="str">
-        <v>EQ-IV-0006</v>
+        <v>EQ-IV-0002</v>
       </c>
       <c r="C223" t="str">
         <v>EQUIPMENT</v>
@@ -8189,19 +8189,19 @@
         <v>1</v>
       </c>
       <c r="G223">
-        <v>60100</v>
+        <v>40000</v>
       </c>
       <c r="H223" t="str">
-        <v>2025-05-01</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I223" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J223" t="str">
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K223" t="str">
-        <v>1-B9701-FT17-65450010004/018-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (11-2/4)</v>
       </c>
     </row>
     <row r="224">
@@ -8209,7 +8209,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B224" t="str">
-        <v>EQ-IV-0007</v>
+        <v>EQ-IV-0003</v>
       </c>
       <c r="C224" t="str">
         <v>EQUIPMENT</v>
@@ -8224,19 +8224,19 @@
         <v>1</v>
       </c>
       <c r="G224">
-        <v>60100</v>
+        <v>40000</v>
       </c>
       <c r="H224" t="str">
-        <v>2025-05-01</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I224" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J224" t="str">
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K224" t="str">
-        <v>1-B9701-FT17-65450010004/019-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (11-3/4)</v>
       </c>
     </row>
     <row r="225">
@@ -8244,7 +8244,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B225" t="str">
-        <v>EQ-IV-0008</v>
+        <v>EQ-IV-0004</v>
       </c>
       <c r="C225" t="str">
         <v>EQUIPMENT</v>
@@ -8259,19 +8259,19 @@
         <v>1</v>
       </c>
       <c r="G225">
-        <v>60100</v>
+        <v>40000</v>
       </c>
       <c r="H225" t="str">
-        <v>2025-05-01</v>
+        <v>2024-06-28</v>
       </c>
       <c r="I225" t="str">
-        <v>อาคารวิทยบริการ ชั้น 3</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J225" t="str">
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K225" t="str">
-        <v>1-B9701-FT17-65450010004/020-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (11-4/4)</v>
       </c>
     </row>
     <row r="226">
@@ -8279,7 +8279,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B226" t="str">
-        <v>EQ-IV-0009</v>
+        <v>EQ-IV-0005</v>
       </c>
       <c r="C226" t="str">
         <v>EQUIPMENT</v>
@@ -8306,7 +8306,7 @@
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K226" t="str">
-        <v>1-B9701-FT17-65450010004/021-68</v>
+        <v>1-B9701-FT17-65450010004/017-68</v>
       </c>
     </row>
     <row r="227">
@@ -8314,7 +8314,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B227" t="str">
-        <v>EQ-IV-0010</v>
+        <v>EQ-IV-0006</v>
       </c>
       <c r="C227" t="str">
         <v>EQUIPMENT</v>
@@ -8341,7 +8341,7 @@
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K227" t="str">
-        <v>1-B9701-FT17-65450010004/022-68</v>
+        <v>1-B9701-FT17-65450010004/018-68</v>
       </c>
     </row>
     <row r="228">
@@ -8349,7 +8349,7 @@
         <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B228" t="str">
-        <v>EQ-IV-0011</v>
+        <v>EQ-IV-0007</v>
       </c>
       <c r="C228" t="str">
         <v>EQUIPMENT</v>
@@ -8376,21 +8376,21 @@
         <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K228" t="str">
-        <v>1-B9701-FT17-65450010004/023-68</v>
+        <v>1-B9701-FT17-65450010004/019-68</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
+        <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B229" t="str">
-        <v>EQ-STI-0044</v>
+        <v>EQ-IV-0008</v>
       </c>
       <c r="C229" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D229" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="E229" t="str">
         <v>ชุด</v>
@@ -8399,7 +8399,7 @@
         <v>1</v>
       </c>
       <c r="G229">
-        <v>54800</v>
+        <v>60100</v>
       </c>
       <c r="H229" t="str">
         <v>2025-05-01</v>
@@ -8408,24 +8408,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J229" t="str">
-        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
+        <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K229" t="str">
-        <v>1-B9701-FT17-65450010004/024-68</v>
+        <v>1-B9701-FT17-65450010004/020-68</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
+        <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B230" t="str">
-        <v>EQ-STI-0045</v>
+        <v>EQ-IV-0009</v>
       </c>
       <c r="C230" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D230" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="E230" t="str">
         <v>ชุด</v>
@@ -8434,7 +8434,7 @@
         <v>1</v>
       </c>
       <c r="G230">
-        <v>54800</v>
+        <v>60100</v>
       </c>
       <c r="H230" t="str">
         <v>2025-05-01</v>
@@ -8443,24 +8443,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J230" t="str">
-        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
+        <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K230" t="str">
-        <v>1-B9701-FT17-65450010004/025-68</v>
+        <v>1-B9701-FT17-65450010004/021-68</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
+        <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B231" t="str">
-        <v>EQ-STI-0046</v>
+        <v>EQ-IV-0010</v>
       </c>
       <c r="C231" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D231" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="E231" t="str">
         <v>ชุด</v>
@@ -8469,7 +8469,7 @@
         <v>1</v>
       </c>
       <c r="G231">
-        <v>54800</v>
+        <v>60100</v>
       </c>
       <c r="H231" t="str">
         <v>2025-05-01</v>
@@ -8478,24 +8478,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J231" t="str">
-        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
+        <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K231" t="str">
-        <v>1-B9701-FT17-65450010004/026-68</v>
+        <v>1-B9701-FT17-65450010004/022-68</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
+        <v>หุ่นแขนฝึกฉีดยาและให้สารน้ำ</v>
       </c>
       <c r="B232" t="str">
-        <v>EQ-STI-0047</v>
+        <v>EQ-IV-0011</v>
       </c>
       <c r="C232" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D232" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="E232" t="str">
         <v>ชุด</v>
@@ -8504,7 +8504,7 @@
         <v>1</v>
       </c>
       <c r="G232">
-        <v>54800</v>
+        <v>60100</v>
       </c>
       <c r="H232" t="str">
         <v>2025-05-01</v>
@@ -8513,10 +8513,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J232" t="str">
-        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
+        <v>หุ่นแขนฝึกการฉีดยาและให้สารน้ำทางหลอดเลือดดำ</v>
       </c>
       <c r="K232" t="str">
-        <v>1-B9701-FT17-65450010004/027-68</v>
+        <v>1-B9701-FT17-65450010004/023-68</v>
       </c>
     </row>
     <row r="233">
@@ -8524,7 +8524,7 @@
         <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="B233" t="str">
-        <v>EQ-STI-0048</v>
+        <v>EQ-STI-0044</v>
       </c>
       <c r="C233" t="str">
         <v>EQUIPMENT</v>
@@ -8551,21 +8551,21 @@
         <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="K233" t="str">
-        <v>1-B9701-FT17-65450010004/028-68</v>
+        <v>1-B9701-FT17-65450010004/024-68</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
+        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="B234" t="str">
-        <v>EQ-IM-0010</v>
+        <v>EQ-STI-0045</v>
       </c>
       <c r="C234" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D234" t="str">
-        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E234" t="str">
         <v>ชุด</v>
@@ -8574,7 +8574,7 @@
         <v>1</v>
       </c>
       <c r="G234">
-        <v>17900</v>
+        <v>54800</v>
       </c>
       <c r="H234" t="str">
         <v>2025-05-01</v>
@@ -8583,24 +8583,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J234" t="str">
-        <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
+        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="K234" t="str">
-        <v>1-B9701-FT17-65450010004/029-68</v>
+        <v>1-B9701-FT17-65450010004/025-68</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
+        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="B235" t="str">
-        <v>EQ-IM-0011</v>
+        <v>EQ-STI-0046</v>
       </c>
       <c r="C235" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D235" t="str">
-        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E235" t="str">
         <v>ชุด</v>
@@ -8609,7 +8609,7 @@
         <v>1</v>
       </c>
       <c r="G235">
-        <v>17900</v>
+        <v>54800</v>
       </c>
       <c r="H235" t="str">
         <v>2025-05-01</v>
@@ -8618,24 +8618,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J235" t="str">
-        <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
+        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="K235" t="str">
-        <v>1-B9701-FT17-65450010004/030-68</v>
+        <v>1-B9701-FT17-65450010004/026-68</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
+        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="B236" t="str">
-        <v>EQ-IM-0012</v>
+        <v>EQ-STI-0047</v>
       </c>
       <c r="C236" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D236" t="str">
-        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E236" t="str">
         <v>ชุด</v>
@@ -8644,7 +8644,7 @@
         <v>1</v>
       </c>
       <c r="G236">
-        <v>17900</v>
+        <v>54800</v>
       </c>
       <c r="H236" t="str">
         <v>2025-05-01</v>
@@ -8653,24 +8653,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J236" t="str">
-        <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
+        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="K236" t="str">
-        <v>1-B9701-FT17-65450010004/031-68</v>
+        <v>1-B9701-FT17-65450010004/027-68</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
+        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="B237" t="str">
-        <v>EQ-IM-0013</v>
+        <v>EQ-STI-0048</v>
       </c>
       <c r="C237" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D237" t="str">
-        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E237" t="str">
         <v>ชุด</v>
@@ -8679,7 +8679,7 @@
         <v>1</v>
       </c>
       <c r="G237">
-        <v>17900</v>
+        <v>54800</v>
       </c>
       <c r="H237" t="str">
         <v>2025-05-01</v>
@@ -8688,10 +8688,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J237" t="str">
-        <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
+        <v>หุ่นทำแผลผ่าตัดชนิดต่างๆ</v>
       </c>
       <c r="K237" t="str">
-        <v>1-B9701-FT17-65450010004/032-68</v>
+        <v>1-B9701-FT17-65450010004/028-68</v>
       </c>
     </row>
     <row r="238">
@@ -8699,7 +8699,7 @@
         <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
       </c>
       <c r="B238" t="str">
-        <v>EQ-IM-0014</v>
+        <v>EQ-IM-0010</v>
       </c>
       <c r="C238" t="str">
         <v>EQUIPMENT</v>
@@ -8726,21 +8726,21 @@
         <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
       </c>
       <c r="K238" t="str">
-        <v>1-B9701-FT17-65450010004/033-68</v>
+        <v>1-B9701-FT17-65450010004/029-68</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
+        <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
       </c>
       <c r="B239" t="str">
-        <v>EQ-FMS-0004</v>
+        <v>EQ-IM-0011</v>
       </c>
       <c r="C239" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D239" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
       </c>
       <c r="E239" t="str">
         <v>ชุด</v>
@@ -8749,7 +8749,7 @@
         <v>1</v>
       </c>
       <c r="G239">
-        <v>246500</v>
+        <v>17900</v>
       </c>
       <c r="H239" t="str">
         <v>2025-05-01</v>
@@ -8758,24 +8758,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J239" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
+        <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
       </c>
       <c r="K239" t="str">
-        <v>1-B9701-FT17-65450010004/034-68</v>
+        <v>1-B9701-FT17-65450010004/030-68</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
+        <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
       </c>
       <c r="B240" t="str">
-        <v>EQ-FMS-0005</v>
+        <v>EQ-IM-0012</v>
       </c>
       <c r="C240" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D240" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
       </c>
       <c r="E240" t="str">
         <v>ชุด</v>
@@ -8784,7 +8784,7 @@
         <v>1</v>
       </c>
       <c r="G240">
-        <v>246500</v>
+        <v>17900</v>
       </c>
       <c r="H240" t="str">
         <v>2025-05-01</v>
@@ -8793,24 +8793,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J240" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
+        <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
       </c>
       <c r="K240" t="str">
-        <v>1-B9701-FT17-65450010004/035-68</v>
+        <v>1-B9701-FT17-65450010004/031-68</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
+        <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
       </c>
       <c r="B241" t="str">
-        <v>EQ-FMS-0006</v>
+        <v>EQ-IM-0013</v>
       </c>
       <c r="C241" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D241" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
       </c>
       <c r="E241" t="str">
         <v>ชุด</v>
@@ -8819,7 +8819,7 @@
         <v>1</v>
       </c>
       <c r="G241">
-        <v>246500</v>
+        <v>17900</v>
       </c>
       <c r="H241" t="str">
         <v>2025-05-01</v>
@@ -8828,24 +8828,24 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J241" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
+        <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
       </c>
       <c r="K241" t="str">
-        <v>1-B9701-FT17-65450010004/036-68</v>
+        <v>1-B9701-FT17-65450010004/032-68</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
+        <v>หุ่นฝึกฉีดยาหัวไหล่ (แบบสวม)</v>
       </c>
       <c r="B242" t="str">
-        <v>EQ-FMS-0007</v>
+        <v>EQ-IM-0014</v>
       </c>
       <c r="C242" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D242" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นฝึกฉีดยาเข้ากล้ามเนื้อ</v>
       </c>
       <c r="E242" t="str">
         <v>ชุด</v>
@@ -8854,7 +8854,7 @@
         <v>1</v>
       </c>
       <c r="G242">
-        <v>246500</v>
+        <v>17900</v>
       </c>
       <c r="H242" t="str">
         <v>2025-05-01</v>
@@ -8863,10 +8863,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J242" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
+        <v>หุ่นฝึกการฉีดยาเข้ากล้ามเนื้อหัวไหล่ แบบสวม</v>
       </c>
       <c r="K242" t="str">
-        <v>1-B9701-FT17-65450010004/037-68</v>
+        <v>1-B9701-FT17-65450010004/033-68</v>
       </c>
     </row>
     <row r="243">
@@ -8874,7 +8874,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
       </c>
       <c r="B243" t="str">
-        <v>EQ-FMS-0008</v>
+        <v>EQ-FMS-0004</v>
       </c>
       <c r="C243" t="str">
         <v>EQUIPMENT</v>
@@ -8901,15 +8901,15 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
       </c>
       <c r="K243" t="str">
-        <v>1-B9701-FT17-65450010004/038-68</v>
+        <v>1-B9701-FT17-65450010004/034-68</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
       </c>
       <c r="B244" t="str">
-        <v>EQ-FMS-0009</v>
+        <v>EQ-FMS-0005</v>
       </c>
       <c r="C244" t="str">
         <v>EQUIPMENT</v>
@@ -8933,18 +8933,18 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J244" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
       </c>
       <c r="K244" t="str">
-        <v>1-B9701-FT17-65450010004/039-68</v>
+        <v>1-B9701-FT17-65450010004/035-68</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
       </c>
       <c r="B245" t="str">
-        <v>EQ-FMS-0010</v>
+        <v>EQ-FMS-0006</v>
       </c>
       <c r="C245" t="str">
         <v>EQUIPMENT</v>
@@ -8968,18 +8968,18 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J245" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
       </c>
       <c r="K245" t="str">
-        <v>1-B9701-FT17-65450010004/040-68</v>
+        <v>1-B9701-FT17-65450010004/036-68</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
       </c>
       <c r="B246" t="str">
-        <v>EQ-FMS-0011</v>
+        <v>EQ-FMS-0007</v>
       </c>
       <c r="C246" t="str">
         <v>EQUIPMENT</v>
@@ -9003,18 +9003,18 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J246" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
       </c>
       <c r="K246" t="str">
-        <v>1-B9701-FT17-65450010004/041-68</v>
+        <v>1-B9701-FT17-65450010004/037-68</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (ชาย)</v>
       </c>
       <c r="B247" t="str">
-        <v>EQ-FMS-0012</v>
+        <v>EQ-FMS-0008</v>
       </c>
       <c r="C247" t="str">
         <v>EQUIPMENT</v>
@@ -9038,10 +9038,10 @@
         <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J247" t="str">
-        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศชาย</v>
       </c>
       <c r="K247" t="str">
-        <v>1-B9701-FT17-65450010004/042-68</v>
+        <v>1-B9701-FT17-65450010004/038-68</v>
       </c>
     </row>
     <row r="248">
@@ -9049,7 +9049,7 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
       </c>
       <c r="B248" t="str">
-        <v>EQ-FMS-0013</v>
+        <v>EQ-FMS-0009</v>
       </c>
       <c r="C248" t="str">
         <v>EQUIPMENT</v>
@@ -9076,21 +9076,21 @@
         <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
       </c>
       <c r="K248" t="str">
-        <v>1-B9701-FT17-65450010004/043-68</v>
+        <v>1-B9701-FT17-65450010004/039-68</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>หุ่นจำลองกะโหลกศีรษะ</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
       </c>
       <c r="B249" t="str">
-        <v>EQ-ANA-0001</v>
+        <v>EQ-FMS-0010</v>
       </c>
       <c r="C249" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D249" t="str">
-        <v>หุ่นจำลองกายวิภาคศาสตร์</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E249" t="str">
         <v>ชุด</v>
@@ -9099,33 +9099,33 @@
         <v>1</v>
       </c>
       <c r="G249">
-        <v>7600</v>
+        <v>246500</v>
       </c>
       <c r="H249" t="str">
-        <v>2024-06-28</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I249" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J249" t="str">
-        <v>หุ่นจำลองกะโหลกศีรษะ แยกชิ้นส่วนได้</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
       </c>
       <c r="K249" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (1-1/1)</v>
+        <v>1-B9701-FT17-65450010004/040-68</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>หุ่นจำลองสมองและเส้นเลือดแดง</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
       </c>
       <c r="B250" t="str">
-        <v>EQ-ANA-0002</v>
+        <v>EQ-FMS-0011</v>
       </c>
       <c r="C250" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D250" t="str">
-        <v>หุ่นจำลองกายวิภาคศาสตร์</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E250" t="str">
         <v>ชุด</v>
@@ -9134,33 +9134,33 @@
         <v>1</v>
       </c>
       <c r="G250">
-        <v>18000</v>
+        <v>246500</v>
       </c>
       <c r="H250" t="str">
-        <v>2024-06-28</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I250" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J250" t="str">
-        <v>หุ่นจำลองสมองและเส้นเลือดแดง</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
       </c>
       <c r="K250" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (2-1/1)</v>
+        <v>1-B9701-FT17-65450010004/041-68</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>หุ่นจำลองโครงกระดูกเต็มตัวขนาดเท่าจริง</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
       </c>
       <c r="B251" t="str">
-        <v>EQ-ANA-0003</v>
+        <v>EQ-FMS-0012</v>
       </c>
       <c r="C251" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D251" t="str">
-        <v>หุ่นจำลองกายวิภาคศาสตร์</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E251" t="str">
         <v>ชุด</v>
@@ -9169,33 +9169,33 @@
         <v>1</v>
       </c>
       <c r="G251">
-        <v>18000</v>
+        <v>246500</v>
       </c>
       <c r="H251" t="str">
-        <v>2024-06-28</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I251" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J251" t="str">
-        <v>หุ่นจำลองโครงกระดูกเต็มตัวขนาดเท่าจริง</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
       </c>
       <c r="K251" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (3-1/1)</v>
+        <v>1-B9701-FT17-65450010004/042-68</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>โมเดลหัวใจ</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลพื้นฐาน (หญิง)</v>
       </c>
       <c r="B252" t="str">
-        <v>EQ-ANA-0004</v>
+        <v>EQ-FMS-0013</v>
       </c>
       <c r="C252" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D252" t="str">
-        <v>หุ่นจำลองกายวิภาคศาสตร์</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E252" t="str">
         <v>ชุด</v>
@@ -9204,33 +9204,33 @@
         <v>1</v>
       </c>
       <c r="G252">
-        <v>4100</v>
+        <v>246500</v>
       </c>
       <c r="H252" t="str">
-        <v>2024-06-28</v>
+        <v>2025-05-01</v>
       </c>
       <c r="I252" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>อาคารวิทยบริการ ชั้น 3</v>
       </c>
       <c r="J252" t="str">
-        <v>โมเดลหัวใจ</v>
+        <v>หุ่นฝึกปฏิบัติการพยาบาลขั้นพื้นฐานเพศหญิง</v>
       </c>
       <c r="K252" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (4-1/1)</v>
+        <v>1-B9701-FT17-65450010004/043-68</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
+        <v>หุ่นจำลองกะโหลกศีรษะ</v>
       </c>
       <c r="B253" t="str">
-        <v>EQ-FMS-0014</v>
+        <v>EQ-ANA-0001</v>
       </c>
       <c r="C253" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D253" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นจำลองกายวิภาคศาสตร์</v>
       </c>
       <c r="E253" t="str">
         <v>ชุด</v>
@@ -9239,7 +9239,7 @@
         <v>1</v>
       </c>
       <c r="G253">
-        <v>140000</v>
+        <v>7600</v>
       </c>
       <c r="H253" t="str">
         <v>2024-06-28</v>
@@ -9248,24 +9248,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J253" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
+        <v>หุ่นจำลองกะโหลกศีรษะ แยกชิ้นส่วนได้</v>
       </c>
       <c r="K253" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (5-1/6)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (1-1/1)</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
+        <v>หุ่นจำลองสมองและเส้นเลือดแดง</v>
       </c>
       <c r="B254" t="str">
-        <v>EQ-FMS-0015</v>
+        <v>EQ-ANA-0002</v>
       </c>
       <c r="C254" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D254" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นจำลองกายวิภาคศาสตร์</v>
       </c>
       <c r="E254" t="str">
         <v>ชุด</v>
@@ -9274,7 +9274,7 @@
         <v>1</v>
       </c>
       <c r="G254">
-        <v>140000</v>
+        <v>18000</v>
       </c>
       <c r="H254" t="str">
         <v>2024-06-28</v>
@@ -9283,24 +9283,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J254" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
+        <v>หุ่นจำลองสมองและเส้นเลือดแดง</v>
       </c>
       <c r="K254" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (5-2/6)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (2-1/1)</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
+        <v>หุ่นจำลองโครงกระดูกเต็มตัวขนาดเท่าจริง</v>
       </c>
       <c r="B255" t="str">
-        <v>EQ-FMS-0016</v>
+        <v>EQ-ANA-0003</v>
       </c>
       <c r="C255" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D255" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นจำลองกายวิภาคศาสตร์</v>
       </c>
       <c r="E255" t="str">
         <v>ชุด</v>
@@ -9309,7 +9309,7 @@
         <v>1</v>
       </c>
       <c r="G255">
-        <v>140000</v>
+        <v>18000</v>
       </c>
       <c r="H255" t="str">
         <v>2024-06-28</v>
@@ -9318,24 +9318,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J255" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
+        <v>หุ่นจำลองโครงกระดูกเต็มตัวขนาดเท่าจริง</v>
       </c>
       <c r="K255" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (5-3/6)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (3-1/1)</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
+        <v>โมเดลหัวใจ</v>
       </c>
       <c r="B256" t="str">
-        <v>EQ-FMS-0017</v>
+        <v>EQ-ANA-0004</v>
       </c>
       <c r="C256" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D256" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>หุ่นจำลองกายวิภาคศาสตร์</v>
       </c>
       <c r="E256" t="str">
         <v>ชุด</v>
@@ -9344,7 +9344,7 @@
         <v>1</v>
       </c>
       <c r="G256">
-        <v>140000</v>
+        <v>4100</v>
       </c>
       <c r="H256" t="str">
         <v>2024-06-28</v>
@@ -9353,10 +9353,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J256" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
+        <v>โมเดลหัวใจ</v>
       </c>
       <c r="K256" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (5-4/6)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (4-1/1)</v>
       </c>
     </row>
     <row r="257">
@@ -9364,7 +9364,7 @@
         <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="B257" t="str">
-        <v>EQ-FMS-0018</v>
+        <v>EQ-FMS-0014</v>
       </c>
       <c r="C257" t="str">
         <v>EQUIPMENT</v>
@@ -9391,7 +9391,7 @@
         <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="K257" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (5-5/6)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (5-1/6)</v>
       </c>
     </row>
     <row r="258">
@@ -9399,7 +9399,7 @@
         <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="B258" t="str">
-        <v>EQ-FMS-0019</v>
+        <v>EQ-FMS-0015</v>
       </c>
       <c r="C258" t="str">
         <v>EQUIPMENT</v>
@@ -9426,21 +9426,21 @@
         <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="K258" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (5-6/6)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (5-2/6)</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>หุ่นฝึก CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="B259" t="str">
-        <v>EQ-CPR-0009</v>
+        <v>EQ-FMS-0016</v>
       </c>
       <c r="C259" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D259" t="str">
-        <v>หุ่นฝึก CPR</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E259" t="str">
         <v>ชุด</v>
@@ -9449,7 +9449,7 @@
         <v>1</v>
       </c>
       <c r="G259">
-        <v>20000</v>
+        <v>140000</v>
       </c>
       <c r="H259" t="str">
         <v>2024-06-28</v>
@@ -9458,24 +9458,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J259" t="str">
-        <v>หุ่นฝึกช่วยพื้นคืนชีพผู้ใหญ่ขั้นพื้นฐานแบบครึ่งตัว</v>
+        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="K259" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (6-1/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (5-3/6)</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>หุ่นฝึก CPR ผู้ใหญ่ครึ่งตัว</v>
+        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="B260" t="str">
-        <v>EQ-CPR-0010</v>
+        <v>EQ-FMS-0017</v>
       </c>
       <c r="C260" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D260" t="str">
-        <v>หุ่นฝึก CPR</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E260" t="str">
         <v>ชุด</v>
@@ -9484,7 +9484,7 @@
         <v>1</v>
       </c>
       <c r="G260">
-        <v>20000</v>
+        <v>140000</v>
       </c>
       <c r="H260" t="str">
         <v>2024-06-28</v>
@@ -9493,24 +9493,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J260" t="str">
-        <v>หุ่นฝึกช่วยพื้นคืนชีพผู้ใหญ่ขั้นพื้นฐานแบบครึ่งตัว</v>
+        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="K260" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (6-2/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (5-4/6)</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหารทางจมูก</v>
+        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="B261" t="str">
-        <v>EQ-NG-0011</v>
+        <v>EQ-FMS-0018</v>
       </c>
       <c r="C261" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D261" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E261" t="str">
         <v>ชุด</v>
@@ -9519,7 +9519,7 @@
         <v>1</v>
       </c>
       <c r="G261">
-        <v>60000</v>
+        <v>140000</v>
       </c>
       <c r="H261" t="str">
         <v>2024-06-28</v>
@@ -9528,24 +9528,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J261" t="str">
-        <v>หุ่นฝึกการใส่สายให้อาหารทางจมูก</v>
+        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="K261" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (8-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (5-5/6)</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล</v>
+        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="B262" t="str">
-        <v>EQ-STI-0049</v>
+        <v>EQ-FMS-0019</v>
       </c>
       <c r="C262" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D262" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="E262" t="str">
         <v>ชุด</v>
@@ -9554,7 +9554,7 @@
         <v>1</v>
       </c>
       <c r="G262">
-        <v>40000</v>
+        <v>140000</v>
       </c>
       <c r="H262" t="str">
         <v>2024-06-28</v>
@@ -9563,24 +9563,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J262" t="str">
-        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล</v>
+        <v>หุ่นฝึกทักษะการพยาบาลผู้ใหญ่</v>
       </c>
       <c r="K262" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (12-1/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (5-6/6)</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล</v>
+        <v>หุ่นฝึกใส่สายให้อาหารทางจมูก</v>
       </c>
       <c r="B263" t="str">
-        <v>EQ-STI-0050</v>
+        <v>EQ-NG-0011</v>
       </c>
       <c r="C263" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D263" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกใส่สายให้อาหาร</v>
       </c>
       <c r="E263" t="str">
         <v>ชุด</v>
@@ -9589,7 +9589,7 @@
         <v>1</v>
       </c>
       <c r="G263">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="H263" t="str">
         <v>2024-06-28</v>
@@ -9598,24 +9598,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J263" t="str">
-        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล</v>
+        <v>หุ่นฝึกการใส่สายให้อาหารทางจมูก</v>
       </c>
       <c r="K263" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (12-2/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (8-1/1)</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
+        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล</v>
       </c>
       <c r="B264" t="str">
-        <v>EQ-OB-0001</v>
+        <v>EQ-STI-0049</v>
       </c>
       <c r="C264" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D264" t="str">
-        <v>หุ่นฝึกสูติศาสตร์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E264" t="str">
         <v>ชุด</v>
@@ -9624,7 +9624,7 @@
         <v>1</v>
       </c>
       <c r="G264">
-        <v>300000</v>
+        <v>40000</v>
       </c>
       <c r="H264" t="str">
         <v>2024-06-28</v>
@@ -9633,24 +9633,24 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J264" t="str">
-        <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
+        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล</v>
       </c>
       <c r="K264" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (14-1/5)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (12-1/2)</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
+        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล</v>
       </c>
       <c r="B265" t="str">
-        <v>EQ-OB-0002</v>
+        <v>EQ-STI-0050</v>
       </c>
       <c r="C265" t="str">
         <v>EQUIPMENT</v>
       </c>
       <c r="D265" t="str">
-        <v>หุ่นฝึกสูติศาสตร์</v>
+        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="E265" t="str">
         <v>ชุด</v>
@@ -9659,7 +9659,7 @@
         <v>1</v>
       </c>
       <c r="G265">
-        <v>300000</v>
+        <v>40000</v>
       </c>
       <c r="H265" t="str">
         <v>2024-06-28</v>
@@ -9668,10 +9668,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J265" t="str">
-        <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
+        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล</v>
       </c>
       <c r="K265" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (14-2/5)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (12-2/2)</v>
       </c>
     </row>
     <row r="266">
@@ -9679,7 +9679,7 @@
         <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
       </c>
       <c r="B266" t="str">
-        <v>EQ-OB-0003</v>
+        <v>EQ-OB-0001</v>
       </c>
       <c r="C266" t="str">
         <v>EQUIPMENT</v>
@@ -9706,7 +9706,7 @@
         <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
       </c>
       <c r="K266" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (14-3/5)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (14-1/5)</v>
       </c>
     </row>
     <row r="267">
@@ -9714,7 +9714,7 @@
         <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
       </c>
       <c r="B267" t="str">
-        <v>EQ-OB-0004</v>
+        <v>EQ-OB-0002</v>
       </c>
       <c r="C267" t="str">
         <v>EQUIPMENT</v>
@@ -9741,7 +9741,7 @@
         <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
       </c>
       <c r="K267" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (14-4/5)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (14-2/5)</v>
       </c>
     </row>
     <row r="268">
@@ -9749,7 +9749,7 @@
         <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
       </c>
       <c r="B268" t="str">
-        <v>EQ-OB-0005</v>
+        <v>EQ-OB-0003</v>
       </c>
       <c r="C268" t="str">
         <v>EQUIPMENT</v>
@@ -9776,15 +9776,15 @@
         <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
       </c>
       <c r="K268" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (14-5/5)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (14-3/5)</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>ชุดฝึกการตรวจความกว้างและความบางของปากมดลูกก่อนคลอด</v>
+        <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
       </c>
       <c r="B269" t="str">
-        <v>EQ-OB-0006</v>
+        <v>EQ-OB-0004</v>
       </c>
       <c r="C269" t="str">
         <v>EQUIPMENT</v>
@@ -9799,7 +9799,7 @@
         <v>1</v>
       </c>
       <c r="G269">
-        <v>50000</v>
+        <v>300000</v>
       </c>
       <c r="H269" t="str">
         <v>2024-06-28</v>
@@ -9808,18 +9808,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J269" t="str">
-        <v>ชุดฝึกการตรวจความกว้างและความบางของปากมดลูกก่อนคลอด</v>
+        <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
       </c>
       <c r="K269" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (15-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (14-4/5)</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>หุ่นฝึกตรวจครรภ์</v>
+        <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
       </c>
       <c r="B270" t="str">
-        <v>EQ-OB-0007</v>
+        <v>EQ-OB-0005</v>
       </c>
       <c r="C270" t="str">
         <v>EQUIPMENT</v>
@@ -9834,7 +9834,7 @@
         <v>1</v>
       </c>
       <c r="G270">
-        <v>45000</v>
+        <v>300000</v>
       </c>
       <c r="H270" t="str">
         <v>2024-06-28</v>
@@ -9843,18 +9843,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J270" t="str">
-        <v>หุ่นฝึกตรวจครรภ์</v>
+        <v>หุ่นฝึกทำคลอด (เด็กมีสายสะดือ)</v>
       </c>
       <c r="K270" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (16-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (14-5/5)</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>หุ่นฝึกอาบน้ำทารก เพศชาย</v>
+        <v>ชุดฝึกการตรวจความกว้างและความบางของปากมดลูกก่อนคลอด</v>
       </c>
       <c r="B271" t="str">
-        <v>EQ-OB-0008</v>
+        <v>EQ-OB-0006</v>
       </c>
       <c r="C271" t="str">
         <v>EQUIPMENT</v>
@@ -9869,7 +9869,7 @@
         <v>1</v>
       </c>
       <c r="G271">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="H271" t="str">
         <v>2024-06-28</v>
@@ -9878,18 +9878,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J271" t="str">
-        <v>หุ่นฝึกอาบน้ำทารก เพศชาย</v>
+        <v>ชุดฝึกการตรวจความกว้างและความบางของปากมดลูกก่อนคลอด</v>
       </c>
       <c r="K271" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (17-1/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (15-1/1)</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>หุ่นฝึกอาบน้ำทารก เพศชาย</v>
+        <v>หุ่นฝึกตรวจครรภ์</v>
       </c>
       <c r="B272" t="str">
-        <v>EQ-OB-0009</v>
+        <v>EQ-OB-0007</v>
       </c>
       <c r="C272" t="str">
         <v>EQUIPMENT</v>
@@ -9904,7 +9904,7 @@
         <v>1</v>
       </c>
       <c r="G272">
-        <v>40000</v>
+        <v>45000</v>
       </c>
       <c r="H272" t="str">
         <v>2024-06-28</v>
@@ -9913,18 +9913,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J272" t="str">
-        <v>หุ่นฝึกอาบน้ำทารก เพศชาย</v>
+        <v>หุ่นฝึกตรวจครรภ์</v>
       </c>
       <c r="K272" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (17-2/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (16-1/1)</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>หุ่นฝึกอาบน้ำทารก เพศหญิง</v>
+        <v>หุ่นฝึกอาบน้ำทารก เพศชาย</v>
       </c>
       <c r="B273" t="str">
-        <v>EQ-OB-0010</v>
+        <v>EQ-OB-0008</v>
       </c>
       <c r="C273" t="str">
         <v>EQUIPMENT</v>
@@ -9948,18 +9948,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J273" t="str">
-        <v>หุ่นฝึกอาบน้ำทารก เพศหญิง</v>
+        <v>หุ่นฝึกอาบน้ำทารก เพศชาย</v>
       </c>
       <c r="K273" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (18-1/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (17-1/2)</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>หุ่นฝึกอาบน้ำทารก เพศหญิง</v>
+        <v>หุ่นฝึกอาบน้ำทารก เพศชาย</v>
       </c>
       <c r="B274" t="str">
-        <v>EQ-OB-0011</v>
+        <v>EQ-OB-0009</v>
       </c>
       <c r="C274" t="str">
         <v>EQUIPMENT</v>
@@ -9983,18 +9983,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J274" t="str">
-        <v>หุ่นฝึกอาบน้ำทารก เพศหญิง</v>
+        <v>หุ่นฝึกอาบน้ำทารก เพศชาย</v>
       </c>
       <c r="K274" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (18-2/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (17-2/2)</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>หุ่นจำลองฝึกตรวจสัญญาณชีพทารก</v>
+        <v>หุ่นฝึกอาบน้ำทารก เพศหญิง</v>
       </c>
       <c r="B275" t="str">
-        <v>EQ-OB-0012</v>
+        <v>EQ-OB-0010</v>
       </c>
       <c r="C275" t="str">
         <v>EQUIPMENT</v>
@@ -10009,7 +10009,7 @@
         <v>1</v>
       </c>
       <c r="G275">
-        <v>170000</v>
+        <v>40000</v>
       </c>
       <c r="H275" t="str">
         <v>2024-06-28</v>
@@ -10018,18 +10018,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J275" t="str">
-        <v>หุ่นจำลองฝึกตรวจสัญญาณชีพทารก</v>
+        <v>หุ่นฝึกอาบน้ำทารก เพศหญิง</v>
       </c>
       <c r="K275" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (19-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (18-1/2)</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>หุ่นจำลองช่วยฟื้นคืนชีพ ทารก แบบมีสัญญาณไฟ</v>
+        <v>หุ่นฝึกอาบน้ำทารก เพศหญิง</v>
       </c>
       <c r="B276" t="str">
-        <v>EQ-OB-0013</v>
+        <v>EQ-OB-0011</v>
       </c>
       <c r="C276" t="str">
         <v>EQUIPMENT</v>
@@ -10044,7 +10044,7 @@
         <v>1</v>
       </c>
       <c r="G276">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="H276" t="str">
         <v>2024-06-28</v>
@@ -10053,18 +10053,18 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J276" t="str">
-        <v>หุ่นจำลองช่วยฟื้นคืนชีพ ทารก แบบมีสัญญาณไฟ</v>
+        <v>หุ่นฝึกอาบน้ำทารก เพศหญิง</v>
       </c>
       <c r="K276" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (20-1/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (18-2/2)</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>หุ่นจำลองช่วยฟื้นคืนชีพ ทารก แบบมีสัญญาณไฟ</v>
+        <v>หุ่นจำลองฝึกตรวจสัญญาณชีพทารก</v>
       </c>
       <c r="B277" t="str">
-        <v>EQ-OB-0014</v>
+        <v>EQ-OB-0012</v>
       </c>
       <c r="C277" t="str">
         <v>EQUIPMENT</v>
@@ -10079,7 +10079,7 @@
         <v>1</v>
       </c>
       <c r="G277">
-        <v>10000</v>
+        <v>170000</v>
       </c>
       <c r="H277" t="str">
         <v>2024-06-28</v>
@@ -10088,10 +10088,10 @@
         <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="J277" t="str">
-        <v>หุ่นจำลองช่วยฟื้นคืนชีพ ทารก แบบมีสัญญาณไฟ</v>
+        <v>หุ่นจำลองฝึกตรวจสัญญาณชีพทารก</v>
       </c>
       <c r="K277" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (20-2/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (19-1/1)</v>
       </c>
     </row>
     <row r="278">

--- a/ข้อมูลครุภัณฑ์/Template_Items_and_Assets_v3.xlsx
+++ b/ข้อมูลครุภัณฑ์/Template_Items_and_Assets_v3.xlsx
@@ -475,13 +475,13 @@
         <v>Laerdal</v>
       </c>
       <c r="J2" t="str">
-        <v>SimMan</v>
+        <v>TOUCH32-MiniPC</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M2" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -522,13 +522,13 @@
         <v>Laerdal</v>
       </c>
       <c r="J3" t="str">
-        <v>SimMan</v>
+        <v>TOUCH32-MiniPC</v>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M3" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -566,16 +566,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>TV-LED-43</v>
       </c>
       <c r="K4" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M4" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -613,16 +613,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>TV-LED-43</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M5" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -663,13 +663,13 @@
         <v>Laerdal</v>
       </c>
       <c r="J6" t="str">
-        <v>SimMan</v>
+        <v>TOUCH32</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M6" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -710,13 +710,13 @@
         <v>Laerdal</v>
       </c>
       <c r="J7" t="str">
-        <v>SimMan</v>
+        <v>TOUCH32</v>
       </c>
       <c r="K7" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M7" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -754,16 +754,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>touchscreen-65 NC</v>
       </c>
       <c r="K8" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M8" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -801,16 +801,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J9" t="str">
-        <v/>
+        <v>touchscreen-65 NC</v>
       </c>
       <c r="K9" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L9" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M9" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -848,16 +848,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>touchscreen-65 NC</v>
       </c>
       <c r="K10" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M10" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -895,16 +895,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>touchscreen-65 NC</v>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M11" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -942,16 +942,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>KaWe</v>
       </c>
       <c r="J12" t="str">
-        <v/>
+        <v>04.4510.08</v>
       </c>
       <c r="K12" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L12" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M12" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -989,16 +989,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>KaWe</v>
       </c>
       <c r="J13" t="str">
-        <v/>
+        <v>04.4510.08</v>
       </c>
       <c r="K13" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L13" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M13" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1036,16 +1036,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>KaWe</v>
       </c>
       <c r="J14" t="str">
-        <v/>
+        <v>04.4510.08</v>
       </c>
       <c r="K14" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L14" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M14" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1083,16 +1083,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>KaWe</v>
       </c>
       <c r="J15" t="str">
-        <v/>
+        <v>04.4510.08</v>
       </c>
       <c r="K15" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L15" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M15" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1130,16 +1130,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>KaWe</v>
       </c>
       <c r="J16" t="str">
-        <v/>
+        <v>04.4510.08</v>
       </c>
       <c r="K16" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L16" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M16" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1177,16 +1177,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J17" t="str">
-        <v/>
+        <v>DT-R2050</v>
       </c>
       <c r="K17" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L17" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M17" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1224,16 +1224,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J18" t="str">
-        <v/>
+        <v>DT-R2050</v>
       </c>
       <c r="K18" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L18" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M18" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1271,16 +1271,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J19" t="str">
-        <v/>
+        <v>DT-R2050</v>
       </c>
       <c r="K19" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L19" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M19" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1318,16 +1318,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J20" t="str">
-        <v/>
+        <v>DT-R2050</v>
       </c>
       <c r="K20" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L20" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M20" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1365,16 +1365,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J21" t="str">
-        <v/>
+        <v>DT-R2050</v>
       </c>
       <c r="K21" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L21" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M21" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1412,16 +1412,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J22" t="str">
-        <v/>
+        <v>DT-R2050</v>
       </c>
       <c r="K22" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L22" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M22" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1459,16 +1459,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J23" t="str">
-        <v/>
+        <v>DT-R2050</v>
       </c>
       <c r="K23" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L23" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M23" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1506,16 +1506,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J24" t="str">
-        <v/>
+        <v>DT-R2050</v>
       </c>
       <c r="K24" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L24" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M24" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1553,16 +1553,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J25" t="str">
-        <v/>
+        <v>DT-R2050</v>
       </c>
       <c r="K25" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L25" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M25" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1600,16 +1600,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J26" t="str">
-        <v/>
+        <v>DT-R2050</v>
       </c>
       <c r="K26" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L26" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M26" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1647,16 +1647,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>Philips</v>
       </c>
       <c r="J27" t="str">
-        <v/>
+        <v>Efficia DFM100</v>
       </c>
       <c r="K27" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L27" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M27" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1694,16 +1694,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>Philips</v>
       </c>
       <c r="J28" t="str">
-        <v/>
+        <v>Efficia DFM100</v>
       </c>
       <c r="K28" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L28" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M28" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1741,16 +1741,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>ZOLL</v>
       </c>
       <c r="J29" t="str">
-        <v/>
+        <v>AED 3 Trainer</v>
       </c>
       <c r="K29" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L29" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M29" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1788,16 +1788,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>ZOLL</v>
       </c>
       <c r="J30" t="str">
-        <v/>
+        <v>AED 3 Trainer</v>
       </c>
       <c r="K30" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L30" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M30" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1835,16 +1835,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>ZOLL</v>
       </c>
       <c r="J31" t="str">
-        <v/>
+        <v>AED 3 Trainer</v>
       </c>
       <c r="K31" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L31" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M31" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1882,16 +1882,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>ZOLL</v>
       </c>
       <c r="J32" t="str">
-        <v/>
+        <v>AED 3 Trainer</v>
       </c>
       <c r="K32" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L32" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M32" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1929,16 +1929,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I33" t="str">
-        <v/>
+        <v>ZOLL</v>
       </c>
       <c r="J33" t="str">
-        <v/>
+        <v>AED 3 Trainer</v>
       </c>
       <c r="K33" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L33" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M33" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -1976,16 +1976,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>ZOLL</v>
       </c>
       <c r="J34" t="str">
-        <v/>
+        <v>AED 3 Trainer</v>
       </c>
       <c r="K34" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L34" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M34" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -2023,16 +2023,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I35" t="str">
-        <v/>
+        <v>ZOLL</v>
       </c>
       <c r="J35" t="str">
-        <v/>
+        <v>AED 3 Trainer</v>
       </c>
       <c r="K35" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L35" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M35" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -2070,16 +2070,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I36" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J36" t="str">
-        <v/>
+        <v>DT-FB202H</v>
       </c>
       <c r="K36" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L36" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M36" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -2117,16 +2117,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I37" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J37" t="str">
-        <v/>
+        <v>DT-FB202H</v>
       </c>
       <c r="K37" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L37" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M37" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -2167,13 +2167,13 @@
         <v>Laerdal</v>
       </c>
       <c r="J38" t="str">
-        <v>SimMan</v>
+        <v>LeonardoHF-Bed</v>
       </c>
       <c r="K38" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L38" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M38" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -2211,16 +2211,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I39" t="str">
-        <v/>
+        <v>Amoul</v>
       </c>
       <c r="J39" t="str">
-        <v/>
+        <v>Amoul Man Pro (AMM-P)</v>
       </c>
       <c r="K39" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L39" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M39" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -2258,16 +2258,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I40" t="str">
-        <v/>
+        <v>Amoul</v>
       </c>
       <c r="J40" t="str">
-        <v/>
+        <v>Amoul Man Pro (AMM-P)</v>
       </c>
       <c r="K40" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L40" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M40" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -2305,16 +2305,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>Amoul</v>
       </c>
       <c r="J41" t="str">
-        <v/>
+        <v>รุ่นมาตรฐาน (ปีงบ 68)</v>
       </c>
       <c r="K41" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L41" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M41" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -2352,16 +2352,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I42" t="str">
-        <v/>
+        <v>Amoul</v>
       </c>
       <c r="J42" t="str">
-        <v/>
+        <v>รุ่นมาตรฐาน (ปีงบ 68)</v>
       </c>
       <c r="K42" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L42" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M42" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -2399,16 +2399,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I43" t="str">
-        <v/>
+        <v>Amoul</v>
       </c>
       <c r="J43" t="str">
-        <v/>
+        <v>รุ่นมาตรฐาน (ปีงบ 68)</v>
       </c>
       <c r="K43" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L43" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M43" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -2446,16 +2446,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I44" t="str">
-        <v/>
+        <v>Amoul</v>
       </c>
       <c r="J44" t="str">
-        <v/>
+        <v>รุ่นมาตรฐาน (ปีงบ 68)</v>
       </c>
       <c r="K44" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L44" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M44" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -2493,16 +2493,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I45" t="str">
-        <v/>
+        <v>Amoul</v>
       </c>
       <c r="J45" t="str">
-        <v/>
+        <v>รุ่นมาตรฐาน (ปีงบ 68)</v>
       </c>
       <c r="K45" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L45" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M45" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -2546,10 +2546,10 @@
         <v>Amoul Man Pro (AMM-P)</v>
       </c>
       <c r="K46" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L46" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M46" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -2593,10 +2593,10 @@
         <v>Amoul Man Pro (AMM-P)</v>
       </c>
       <c r="K47" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L47" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M47" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -2640,10 +2640,10 @@
         <v>Amoul Man Pro (AMM-P)</v>
       </c>
       <c r="K48" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L48" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M48" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -2681,16 +2681,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I49" t="str">
-        <v/>
+        <v>Amoul</v>
       </c>
       <c r="J49" t="str">
-        <v/>
+        <v>Baby CPR Light-indicator</v>
       </c>
       <c r="K49" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L49" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M49" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -2728,16 +2728,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I50" t="str">
-        <v/>
+        <v>Amoul</v>
       </c>
       <c r="J50" t="str">
-        <v/>
+        <v>Baby CPR Light-indicator</v>
       </c>
       <c r="K50" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L50" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M50" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -2775,16 +2775,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I51" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J51" t="str">
-        <v/>
+        <v>101-7140-8Y (KERi)</v>
       </c>
       <c r="K51" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L51" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M51" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -2822,16 +2822,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I52" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J52" t="str">
-        <v/>
+        <v>101-7140-8Y (KERi)</v>
       </c>
       <c r="K52" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L52" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M52" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -2869,16 +2869,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I53" t="str">
-        <v/>
+        <v>Koken</v>
       </c>
       <c r="J53" t="str">
-        <v/>
+        <v>M155</v>
       </c>
       <c r="K53" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L53" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M53" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -2916,16 +2916,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I54" t="str">
-        <v/>
+        <v>Koken</v>
       </c>
       <c r="J54" t="str">
-        <v/>
+        <v>M155</v>
       </c>
       <c r="K54" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L54" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M54" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -2963,16 +2963,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I55" t="str">
-        <v/>
+        <v>Koken</v>
       </c>
       <c r="J55" t="str">
-        <v/>
+        <v>M155</v>
       </c>
       <c r="K55" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L55" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M55" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3010,16 +3010,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>Koken</v>
       </c>
       <c r="J56" t="str">
-        <v/>
+        <v>M155</v>
       </c>
       <c r="K56" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L56" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M56" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3057,16 +3057,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>Koken</v>
       </c>
       <c r="J57" t="str">
-        <v/>
+        <v>M155</v>
       </c>
       <c r="K57" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L57" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M57" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3104,16 +3104,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>Koken</v>
       </c>
       <c r="J58" t="str">
-        <v/>
+        <v>M152</v>
       </c>
       <c r="K58" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L58" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M58" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3151,16 +3151,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I59" t="str">
-        <v/>
+        <v>Koken</v>
       </c>
       <c r="J59" t="str">
-        <v/>
+        <v>M152</v>
       </c>
       <c r="K59" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L59" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M59" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3198,16 +3198,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>Koken</v>
       </c>
       <c r="J60" t="str">
-        <v/>
+        <v>M152</v>
       </c>
       <c r="K60" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L60" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M60" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3245,16 +3245,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I61" t="str">
-        <v/>
+        <v>Koken</v>
       </c>
       <c r="J61" t="str">
-        <v/>
+        <v>M152</v>
       </c>
       <c r="K61" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L61" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M61" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3292,16 +3292,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I62" t="str">
-        <v/>
+        <v>Koken</v>
       </c>
       <c r="J62" t="str">
-        <v/>
+        <v>M152</v>
       </c>
       <c r="K62" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L62" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M62" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3339,16 +3339,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I63" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J63" t="str">
-        <v/>
+        <v>LF01174</v>
       </c>
       <c r="K63" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L63" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M63" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3386,16 +3386,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I64" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J64" t="str">
-        <v/>
+        <v>LF01174</v>
       </c>
       <c r="K64" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L64" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M64" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3433,16 +3433,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I65" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J65" t="str">
-        <v/>
+        <v>LF01174</v>
       </c>
       <c r="K65" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L65" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M65" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3480,16 +3480,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I66" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J66" t="str">
-        <v/>
+        <v>LF01174</v>
       </c>
       <c r="K66" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L66" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M66" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3527,16 +3527,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I67" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J67" t="str">
-        <v/>
+        <v>LF01174</v>
       </c>
       <c r="K67" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L67" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M67" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3574,16 +3574,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I68" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J68" t="str">
-        <v/>
+        <v>P93SPC-S</v>
       </c>
       <c r="K68" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L68" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M68" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3621,16 +3621,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I69" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J69" t="str">
-        <v/>
+        <v>P93SPC-S</v>
       </c>
       <c r="K69" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L69" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M69" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3668,16 +3668,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I70" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J70" t="str">
-        <v/>
+        <v>P93SPC-S</v>
       </c>
       <c r="K70" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L70" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M70" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3715,16 +3715,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J71" t="str">
-        <v/>
+        <v>P93SPC-S</v>
       </c>
       <c r="K71" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L71" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M71" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3762,16 +3762,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I72" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J72" t="str">
-        <v/>
+        <v>P93SPC-S</v>
       </c>
       <c r="K72" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L72" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M72" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3809,16 +3809,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I73" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J73" t="str">
-        <v/>
+        <v>P93SPC-S</v>
       </c>
       <c r="K73" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L73" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M73" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3856,16 +3856,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I74" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J74" t="str">
-        <v/>
+        <v>P93SPC-S</v>
       </c>
       <c r="K74" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L74" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M74" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3903,16 +3903,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I75" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J75" t="str">
-        <v/>
+        <v>P93SPC-S</v>
       </c>
       <c r="K75" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L75" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M75" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3950,16 +3950,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I76" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J76" t="str">
-        <v/>
+        <v>P93SPC-S</v>
       </c>
       <c r="K76" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L76" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M76" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3997,16 +3997,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J77" t="str">
-        <v/>
+        <v>P93SPC-S</v>
       </c>
       <c r="K77" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L77" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M77" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4044,16 +4044,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I78" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J78" t="str">
-        <v/>
+        <v>P93SPC-S</v>
       </c>
       <c r="K78" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L78" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M78" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4091,16 +4091,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I79" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J79" t="str">
-        <v/>
+        <v>P93SPC-S</v>
       </c>
       <c r="K79" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L79" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M79" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4138,16 +4138,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I80" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J80" t="str">
-        <v/>
+        <v>P93SPC-S</v>
       </c>
       <c r="K80" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L80" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M80" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4185,16 +4185,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I81" t="str">
-        <v/>
+        <v>Limbs &amp; Things</v>
       </c>
       <c r="J81" t="str">
-        <v/>
+        <v>40201</v>
       </c>
       <c r="K81" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L81" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M81" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4232,16 +4232,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I82" t="str">
-        <v/>
+        <v>Limbs &amp; Things</v>
       </c>
       <c r="J82" t="str">
-        <v/>
+        <v>40201</v>
       </c>
       <c r="K82" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L82" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M82" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4279,16 +4279,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I83" t="str">
-        <v/>
+        <v>Limbs &amp; Things</v>
       </c>
       <c r="J83" t="str">
-        <v/>
+        <v>40201</v>
       </c>
       <c r="K83" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L83" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M83" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4326,16 +4326,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I84" t="str">
-        <v/>
+        <v>Limbs &amp; Things</v>
       </c>
       <c r="J84" t="str">
-        <v/>
+        <v>40201</v>
       </c>
       <c r="K84" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L84" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M84" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4373,16 +4373,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I85" t="str">
-        <v/>
+        <v>Limbs &amp; Things</v>
       </c>
       <c r="J85" t="str">
-        <v/>
+        <v>40201</v>
       </c>
       <c r="K85" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L85" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M85" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4420,16 +4420,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I86" t="str">
-        <v/>
+        <v>Limbs &amp; Things</v>
       </c>
       <c r="J86" t="str">
-        <v/>
+        <v>40201</v>
       </c>
       <c r="K86" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L86" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M86" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4467,16 +4467,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I87" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J87" t="str">
-        <v/>
+        <v>P100</v>
       </c>
       <c r="K87" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L87" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M87" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4514,16 +4514,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I88" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J88" t="str">
-        <v/>
+        <v>P100</v>
       </c>
       <c r="K88" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L88" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M88" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4561,16 +4561,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I89" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J89" t="str">
-        <v/>
+        <v>P100</v>
       </c>
       <c r="K89" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L89" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M89" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4608,16 +4608,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I90" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J90" t="str">
-        <v/>
+        <v>P100</v>
       </c>
       <c r="K90" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L90" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M90" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4655,16 +4655,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I91" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J91" t="str">
-        <v/>
+        <v>P100</v>
       </c>
       <c r="K91" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L91" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M91" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4702,16 +4702,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I92" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J92" t="str">
-        <v/>
+        <v>P101</v>
       </c>
       <c r="K92" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L92" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M92" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4749,16 +4749,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I93" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J93" t="str">
-        <v/>
+        <v>P101</v>
       </c>
       <c r="K93" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L93" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M93" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4796,16 +4796,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I94" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J94" t="str">
-        <v/>
+        <v>P101</v>
       </c>
       <c r="K94" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L94" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M94" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4843,16 +4843,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I95" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J95" t="str">
-        <v/>
+        <v>P101</v>
       </c>
       <c r="K95" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L95" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M95" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4890,16 +4890,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I96" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J96" t="str">
-        <v/>
+        <v>LF01034</v>
       </c>
       <c r="K96" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L96" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M96" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4937,16 +4937,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I97" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J97" t="str">
-        <v/>
+        <v>LF01034</v>
       </c>
       <c r="K97" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L97" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M97" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -4984,16 +4984,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I98" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J98" t="str">
-        <v/>
+        <v>LF01034</v>
       </c>
       <c r="K98" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L98" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M98" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5031,16 +5031,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I99" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J99" t="str">
-        <v/>
+        <v>LF01034</v>
       </c>
       <c r="K99" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L99" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M99" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5078,16 +5078,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I100" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J100" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K100" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L100" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M100" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5125,16 +5125,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I101" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J101" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K101" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L101" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M101" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5172,16 +5172,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I102" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L102" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M102" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5219,16 +5219,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I103" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L103" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M103" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5266,16 +5266,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I104" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L104" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M104" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5313,16 +5313,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I105" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L105" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M105" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5360,16 +5360,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I106" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L106" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M106" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5407,16 +5407,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I107" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L107" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M107" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5454,16 +5454,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I108" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L108" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M108" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5501,16 +5501,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I109" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L109" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M109" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5548,16 +5548,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I110" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L110" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M110" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5595,16 +5595,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I111" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L111" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M111" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5642,16 +5642,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I112" t="str">
-        <v/>
+        <v>Cardionics</v>
       </c>
       <c r="J112" t="str">
-        <v/>
+        <v>718-8804 SAM</v>
       </c>
       <c r="K112" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L112" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M112" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5689,16 +5689,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I113" t="str">
-        <v/>
+        <v>Cardionics</v>
       </c>
       <c r="J113" t="str">
-        <v/>
+        <v>718-8804 SAM</v>
       </c>
       <c r="K113" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L113" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M113" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5736,16 +5736,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I114" t="str">
-        <v/>
+        <v>Cardionics</v>
       </c>
       <c r="J114" t="str">
-        <v/>
+        <v>718-8804 SAM</v>
       </c>
       <c r="K114" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L114" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M114" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5783,16 +5783,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I115" t="str">
-        <v/>
+        <v>Cardionics</v>
       </c>
       <c r="J115" t="str">
-        <v/>
+        <v>718-8804 SAM</v>
       </c>
       <c r="K115" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L115" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M115" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5830,16 +5830,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I116" t="str">
-        <v/>
+        <v>Cardionics</v>
       </c>
       <c r="J116" t="str">
-        <v/>
+        <v>718-8804 SAM</v>
       </c>
       <c r="K116" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L116" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M116" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5877,16 +5877,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I117" t="str">
-        <v/>
+        <v>Cardionics</v>
       </c>
       <c r="J117" t="str">
-        <v/>
+        <v>718-8804 SAM</v>
       </c>
       <c r="K117" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L117" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M117" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5924,16 +5924,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I118" t="str">
-        <v/>
+        <v>Cardionics</v>
       </c>
       <c r="J118" t="str">
-        <v/>
+        <v>718-8804 SAM</v>
       </c>
       <c r="K118" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L118" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M118" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -5971,16 +5971,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I119" t="str">
-        <v/>
+        <v>Cardionics</v>
       </c>
       <c r="J119" t="str">
-        <v/>
+        <v>718-8804 SAM</v>
       </c>
       <c r="K119" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L119" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M119" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -6018,16 +6018,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I120" t="str">
-        <v/>
+        <v>Cardionics</v>
       </c>
       <c r="J120" t="str">
-        <v/>
+        <v>718-8804 SAM</v>
       </c>
       <c r="K120" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L120" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M120" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -6065,16 +6065,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I121" t="str">
-        <v/>
+        <v>Cardionics</v>
       </c>
       <c r="J121" t="str">
-        <v/>
+        <v>718-8804 SAM</v>
       </c>
       <c r="K121" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L121" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M121" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -6115,13 +6115,13 @@
         <v>Laerdal</v>
       </c>
       <c r="J122" t="str">
-        <v>SimMan</v>
+        <v>LeonardoHF</v>
       </c>
       <c r="K122" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L122" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M122" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -6159,16 +6159,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I123" t="str">
-        <v/>
+        <v>Apple</v>
       </c>
       <c r="J123" t="str">
-        <v/>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="K123" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L123" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M123" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -6206,16 +6206,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I124" t="str">
-        <v/>
+        <v>Apple</v>
       </c>
       <c r="J124" t="str">
-        <v/>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="K124" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L124" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M124" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -6253,16 +6253,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I125" t="str">
-        <v/>
+        <v>Apple</v>
       </c>
       <c r="J125" t="str">
-        <v/>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="K125" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L125" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M125" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -6300,16 +6300,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I126" t="str">
-        <v/>
+        <v>Apple</v>
       </c>
       <c r="J126" t="str">
-        <v/>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="K126" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L126" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M126" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -6347,16 +6347,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I127" t="str">
-        <v/>
+        <v>Apple</v>
       </c>
       <c r="J127" t="str">
-        <v/>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="K127" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L127" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M127" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -6394,16 +6394,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I128" t="str">
-        <v/>
+        <v>Apple</v>
       </c>
       <c r="J128" t="str">
-        <v/>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="K128" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L128" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M128" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -6441,16 +6441,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I129" t="str">
-        <v/>
+        <v>Apple</v>
       </c>
       <c r="J129" t="str">
-        <v/>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="K129" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L129" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M129" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -6488,16 +6488,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I130" t="str">
-        <v/>
+        <v>Apple</v>
       </c>
       <c r="J130" t="str">
-        <v/>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="K130" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L130" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M130" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -6535,16 +6535,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I131" t="str">
-        <v/>
+        <v>Apple</v>
       </c>
       <c r="J131" t="str">
-        <v/>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="K131" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L131" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M131" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -6582,16 +6582,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I132" t="str">
-        <v/>
+        <v>Apple</v>
       </c>
       <c r="J132" t="str">
-        <v/>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="K132" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L132" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M132" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -6629,16 +6629,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I133" t="str">
-        <v/>
+        <v>Body Interact</v>
       </c>
       <c r="J133" t="str">
-        <v/>
+        <v>BI-30SW-4Y-TH</v>
       </c>
       <c r="K133" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L133" t="str">
-        <v/>
+        <v>2029-08-19</v>
       </c>
       <c r="M133" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -6676,16 +6676,16 @@
         <v>2024-08-01</v>
       </c>
       <c r="I134" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J134" t="str">
-        <v/>
+        <v>เตียงตรวจโรคมาตรฐาน</v>
       </c>
       <c r="K134" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L134" t="str">
-        <v/>
+        <v>2025-08-01</v>
       </c>
       <c r="M134" t="str">
         <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 2</v>
@@ -6723,16 +6723,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I135" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J135" t="str">
-        <v/>
+        <v>CPR Board (CPR-B)</v>
       </c>
       <c r="K135" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L135" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M135" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -6770,16 +6770,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I136" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J136" t="str">
-        <v/>
+        <v>CPR Board (CPR-B)</v>
       </c>
       <c r="K136" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L136" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M136" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -6817,16 +6817,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I137" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J137" t="str">
-        <v/>
+        <v>CPR Board (CPR-B)</v>
       </c>
       <c r="K137" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L137" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M137" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -6864,16 +6864,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I138" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J138" t="str">
-        <v/>
+        <v>CPR Board (CPR-B)</v>
       </c>
       <c r="K138" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L138" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M138" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -6911,16 +6911,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I139" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J139" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K139" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L139" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M139" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -6958,16 +6958,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I140" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J140" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K140" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L140" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M140" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7005,16 +7005,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I141" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J141" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K141" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L141" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M141" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7052,16 +7052,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I142" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J142" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K142" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L142" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M142" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7099,16 +7099,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I143" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J143" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K143" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L143" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M143" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7146,16 +7146,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I144" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J144" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K144" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L144" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M144" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7193,16 +7193,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I145" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J145" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K145" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L145" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M145" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7240,16 +7240,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I146" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J146" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K146" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L146" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M146" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7287,16 +7287,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I147" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J147" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K147" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L147" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M147" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7334,16 +7334,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I148" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J148" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K148" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L148" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M148" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7381,16 +7381,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I149" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J149" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K149" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L149" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M149" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7428,16 +7428,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I150" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J150" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K150" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L150" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M150" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7475,16 +7475,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I151" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J151" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K151" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L151" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M151" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7522,16 +7522,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I152" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J152" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K152" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L152" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M152" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7569,16 +7569,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I153" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J153" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K153" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L153" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M153" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7616,16 +7616,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I154" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J154" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K154" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L154" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M154" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7663,16 +7663,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I155" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J155" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K155" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L155" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M155" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7710,16 +7710,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I156" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J156" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K156" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L156" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M156" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7757,16 +7757,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I157" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J157" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K157" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L157" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M157" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7804,16 +7804,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I158" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J158" t="str">
-        <v/>
+        <v>LF01043</v>
       </c>
       <c r="K158" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L158" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M158" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7851,16 +7851,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I159" t="str">
-        <v/>
+        <v>Apple</v>
       </c>
       <c r="J159" t="str">
-        <v/>
+        <v>iPad (Alex AI)</v>
       </c>
       <c r="K159" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L159" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M159" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7898,16 +7898,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I160" t="str">
-        <v/>
+        <v>Apple</v>
       </c>
       <c r="J160" t="str">
-        <v/>
+        <v>iPad (Alex AI)</v>
       </c>
       <c r="K160" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L160" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M160" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7945,16 +7945,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I161" t="str">
-        <v/>
+        <v>Android</v>
       </c>
       <c r="J161" t="str">
-        <v/>
+        <v>AD-Tablet 10"</v>
       </c>
       <c r="K161" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L161" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M161" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -7992,16 +7992,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I162" t="str">
-        <v/>
+        <v>Android</v>
       </c>
       <c r="J162" t="str">
-        <v/>
+        <v>AD-Tablet 10"</v>
       </c>
       <c r="K162" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L162" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M162" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -8039,16 +8039,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I163" t="str">
-        <v/>
+        <v>Android</v>
       </c>
       <c r="J163" t="str">
-        <v/>
+        <v>AD-Tablet 10"</v>
       </c>
       <c r="K163" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L163" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M163" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -8086,16 +8086,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I164" t="str">
-        <v/>
+        <v>Cleanline</v>
       </c>
       <c r="J164" t="str">
-        <v/>
+        <v>UPS 1200W</v>
       </c>
       <c r="K164" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L164" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M164" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -8133,16 +8133,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I165" t="str">
-        <v/>
+        <v>Cleanline</v>
       </c>
       <c r="J165" t="str">
-        <v/>
+        <v>UPS 1200W</v>
       </c>
       <c r="K165" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L165" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M165" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -8180,16 +8180,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I166" t="str">
-        <v/>
+        <v>PeriPage</v>
       </c>
       <c r="J166" t="str">
-        <v/>
+        <v>IM-PT-PERI</v>
       </c>
       <c r="K166" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L166" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M166" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -8227,16 +8227,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I167" t="str">
-        <v/>
+        <v>PeriPage</v>
       </c>
       <c r="J167" t="str">
-        <v/>
+        <v>IM-PT-PERI</v>
       </c>
       <c r="K167" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L167" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M167" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -8274,16 +8274,16 @@
         <v>2025-08-19</v>
       </c>
       <c r="I168" t="str">
-        <v/>
+        <v>PeriPage</v>
       </c>
       <c r="J168" t="str">
-        <v/>
+        <v>IM-PT-PERI</v>
       </c>
       <c r="K168" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L168" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
       <c r="M168" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -8321,16 +8321,16 @@
         <v>2024-08-01</v>
       </c>
       <c r="I169" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J169" t="str">
-        <v/>
+        <v>Lab Furniture Standard</v>
       </c>
       <c r="K169" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L169" t="str">
-        <v/>
+        <v>2025-08-01</v>
       </c>
       <c r="M169" t="str">
         <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
@@ -8368,16 +8368,16 @@
         <v>2024-08-01</v>
       </c>
       <c r="I170" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J170" t="str">
-        <v/>
+        <v>Lab Furniture Standard</v>
       </c>
       <c r="K170" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L170" t="str">
-        <v/>
+        <v>2025-08-01</v>
       </c>
       <c r="M170" t="str">
         <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
@@ -8415,16 +8415,16 @@
         <v>2024-08-01</v>
       </c>
       <c r="I171" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J171" t="str">
-        <v/>
+        <v>Lab Furniture Standard</v>
       </c>
       <c r="K171" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L171" t="str">
-        <v/>
+        <v>2025-08-01</v>
       </c>
       <c r="M171" t="str">
         <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
@@ -8462,16 +8462,16 @@
         <v>2024-08-01</v>
       </c>
       <c r="I172" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J172" t="str">
-        <v/>
+        <v>Lab Furniture Standard</v>
       </c>
       <c r="K172" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L172" t="str">
-        <v/>
+        <v>2025-08-01</v>
       </c>
       <c r="M172" t="str">
         <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
@@ -8509,16 +8509,16 @@
         <v>2024-08-01</v>
       </c>
       <c r="I173" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J173" t="str">
-        <v/>
+        <v>Lab Furniture Standard</v>
       </c>
       <c r="K173" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L173" t="str">
-        <v/>
+        <v>2025-08-01</v>
       </c>
       <c r="M173" t="str">
         <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 2</v>
@@ -8556,16 +8556,16 @@
         <v>2024-08-01</v>
       </c>
       <c r="I174" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J174" t="str">
-        <v/>
+        <v>Lab Furniture Standard</v>
       </c>
       <c r="K174" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L174" t="str">
-        <v/>
+        <v>2025-08-01</v>
       </c>
       <c r="M174" t="str">
         <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
@@ -8603,16 +8603,16 @@
         <v>2024-08-01</v>
       </c>
       <c r="I175" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J175" t="str">
-        <v/>
+        <v>Lab Furniture Standard</v>
       </c>
       <c r="K175" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L175" t="str">
-        <v/>
+        <v>2025-08-01</v>
       </c>
       <c r="M175" t="str">
         <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
@@ -8650,16 +8650,16 @@
         <v>2024-08-01</v>
       </c>
       <c r="I176" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J176" t="str">
-        <v/>
+        <v>Lab Furniture Standard</v>
       </c>
       <c r="K176" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L176" t="str">
-        <v/>
+        <v>2025-08-01</v>
       </c>
       <c r="M176" t="str">
         <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
@@ -8697,16 +8697,16 @@
         <v>2024-08-01</v>
       </c>
       <c r="I177" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J177" t="str">
-        <v/>
+        <v>Lab Furniture Standard</v>
       </c>
       <c r="K177" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L177" t="str">
-        <v/>
+        <v>2025-08-01</v>
       </c>
       <c r="M177" t="str">
         <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
@@ -8744,16 +8744,16 @@
         <v>2024-08-01</v>
       </c>
       <c r="I178" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J178" t="str">
-        <v/>
+        <v>Lab Furniture Standard</v>
       </c>
       <c r="K178" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L178" t="str">
-        <v/>
+        <v>2025-08-01</v>
       </c>
       <c r="M178" t="str">
         <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 1</v>
@@ -8791,16 +8791,16 @@
         <v>2024-08-01</v>
       </c>
       <c r="I179" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J179" t="str">
-        <v/>
+        <v>Lab Furniture Standard</v>
       </c>
       <c r="K179" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L179" t="str">
-        <v/>
+        <v>2025-08-01</v>
       </c>
       <c r="M179" t="str">
         <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 2</v>
@@ -8838,16 +8838,16 @@
         <v>2024-08-01</v>
       </c>
       <c r="I180" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J180" t="str">
-        <v/>
+        <v>Lab Furniture Standard</v>
       </c>
       <c r="K180" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L180" t="str">
-        <v/>
+        <v>2025-08-01</v>
       </c>
       <c r="M180" t="str">
         <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
@@ -8885,16 +8885,16 @@
         <v>2024-08-01</v>
       </c>
       <c r="I181" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J181" t="str">
-        <v/>
+        <v>Lab Furniture Standard</v>
       </c>
       <c r="K181" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L181" t="str">
-        <v/>
+        <v>2025-08-01</v>
       </c>
       <c r="M181" t="str">
         <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 3</v>
@@ -8932,16 +8932,16 @@
         <v>2024-08-01</v>
       </c>
       <c r="I182" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J182" t="str">
-        <v/>
+        <v>Lab Furniture Standard</v>
       </c>
       <c r="K182" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L182" t="str">
-        <v/>
+        <v>2025-08-01</v>
       </c>
       <c r="M182" t="str">
         <v>อาคารวิทยบริการ ชั้น 3 ห้องปฏิบัติการ 5</v>
@@ -8979,16 +8979,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I183" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J183" t="str">
-        <v/>
+        <v>ไฟฟ้า 3 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K183" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L183" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M183" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9026,16 +9026,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I184" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J184" t="str">
-        <v/>
+        <v>ไฟฟ้า 3 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K184" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L184" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M184" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9073,16 +9073,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I185" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J185" t="str">
-        <v/>
+        <v>ไฟฟ้า 3 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K185" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L185" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M185" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9120,16 +9120,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I186" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J186" t="str">
-        <v/>
+        <v>ไฟฟ้า 3 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K186" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L186" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M186" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9167,16 +9167,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I187" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J187" t="str">
-        <v/>
+        <v>ไฟฟ้า 3 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K187" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L187" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M187" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9214,16 +9214,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I188" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J188" t="str">
-        <v/>
+        <v>ไฟฟ้า 3 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K188" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L188" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M188" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9261,16 +9261,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I189" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J189" t="str">
-        <v/>
+        <v>ไฟฟ้า 3 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K189" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L189" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M189" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9308,16 +9308,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I190" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J190" t="str">
-        <v/>
+        <v>ไฟฟ้า 3 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K190" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L190" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M190" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9355,16 +9355,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I191" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J191" t="str">
-        <v/>
+        <v>ไฟฟ้า 3 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K191" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L191" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M191" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9402,16 +9402,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I192" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J192" t="str">
-        <v/>
+        <v>ไฟฟ้า 3 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K192" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L192" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M192" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9449,16 +9449,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I193" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J193" t="str">
-        <v/>
+        <v>ไฟฟ้า 3 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K193" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L193" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M193" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9496,16 +9496,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I194" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J194" t="str">
-        <v/>
+        <v>ไฟฟ้า 3 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K194" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L194" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M194" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9543,16 +9543,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I195" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J195" t="str">
-        <v/>
+        <v>ไฟฟ้า 3 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K195" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L195" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M195" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9590,16 +9590,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I196" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J196" t="str">
-        <v/>
+        <v>ไฟฟ้า 3 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K196" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L196" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M196" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9637,16 +9637,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I197" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J197" t="str">
-        <v/>
+        <v>ไฟฟ้า 3 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K197" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L197" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M197" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9684,16 +9684,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I198" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J198" t="str">
-        <v/>
+        <v>ไฟฟ้า 3 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K198" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L198" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M198" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9731,16 +9731,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I199" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J199" t="str">
-        <v/>
+        <v>ไฟฟ้า 3 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K199" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L199" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M199" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9778,16 +9778,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I200" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J200" t="str">
-        <v/>
+        <v>ไฟฟ้า 3 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K200" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L200" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M200" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9825,16 +9825,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I201" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J201" t="str">
-        <v/>
+        <v>ไฟฟ้า 3 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K201" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L201" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M201" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9872,16 +9872,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I202" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J202" t="str">
-        <v/>
+        <v>ไฟฟ้า 3 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K202" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L202" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M202" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9919,16 +9919,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I203" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J203" t="str">
-        <v/>
+        <v>ไฟฟ้า 2 ไกร์ ราวสไลด์</v>
       </c>
       <c r="K203" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L203" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M203" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -9966,16 +9966,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I204" t="str">
-        <v>Laerdal</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="J204" t="str">
-        <v>SimMan</v>
+        <v>รุ่นมาตรฐาน</v>
       </c>
       <c r="K204" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L204" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M204" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -10013,16 +10013,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I205" t="str">
-        <v>Laerdal</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="J205" t="str">
-        <v>SimMan</v>
+        <v>รุ่นมาตรฐาน</v>
       </c>
       <c r="K205" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L205" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M205" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -10060,16 +10060,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I206" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J206" t="str">
-        <v/>
+        <v>P93-Male</v>
       </c>
       <c r="K206" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L206" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M206" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -10107,16 +10107,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I207" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J207" t="str">
-        <v/>
+        <v>P93-Male</v>
       </c>
       <c r="K207" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L207" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M207" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -10154,16 +10154,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I208" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J208" t="str">
-        <v/>
+        <v>P93-Male</v>
       </c>
       <c r="K208" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L208" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M208" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -10201,16 +10201,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I209" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J209" t="str">
-        <v/>
+        <v>P93-Male</v>
       </c>
       <c r="K209" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L209" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M209" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -10248,16 +10248,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I210" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J210" t="str">
-        <v/>
+        <v>P93-Male</v>
       </c>
       <c r="K210" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L210" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M210" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -10295,16 +10295,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I211" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J211" t="str">
-        <v/>
+        <v>P93-Female</v>
       </c>
       <c r="K211" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L211" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M211" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -10342,16 +10342,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I212" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J212" t="str">
-        <v/>
+        <v>P93-Female</v>
       </c>
       <c r="K212" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L212" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M212" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -10389,16 +10389,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I213" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J213" t="str">
-        <v/>
+        <v>P93-Female</v>
       </c>
       <c r="K213" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L213" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M213" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -10436,16 +10436,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I214" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J214" t="str">
-        <v/>
+        <v>P93-Female</v>
       </c>
       <c r="K214" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L214" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M214" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -10483,16 +10483,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I215" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J215" t="str">
-        <v/>
+        <v>P93-Female</v>
       </c>
       <c r="K215" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L215" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M215" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -10530,16 +10530,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I216" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J216" t="str">
-        <v/>
+        <v>รุ่นมาตรฐาน</v>
       </c>
       <c r="K216" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L216" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M216" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -10577,16 +10577,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I217" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J217" t="str">
-        <v/>
+        <v>รุ่นมาตรฐาน</v>
       </c>
       <c r="K217" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L217" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M217" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -10624,16 +10624,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I218" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J218" t="str">
-        <v/>
+        <v>รุ่นมาตรฐาน</v>
       </c>
       <c r="K218" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L218" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M218" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -10671,16 +10671,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I219" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J219" t="str">
-        <v/>
+        <v>รุ่นมาตรฐาน</v>
       </c>
       <c r="K219" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L219" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M219" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -10718,16 +10718,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I220" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J220" t="str">
-        <v/>
+        <v>รุ่นมาตรฐาน</v>
       </c>
       <c r="K220" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L220" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M220" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -10765,16 +10765,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I221" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J221" t="str">
-        <v/>
+        <v>Nursing Manikin Standard</v>
       </c>
       <c r="K221" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L221" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M221" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -10812,16 +10812,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I222" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J222" t="str">
-        <v/>
+        <v>LF00698 Venipuncture Arm</v>
       </c>
       <c r="K222" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L222" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M222" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -10859,16 +10859,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I223" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J223" t="str">
-        <v/>
+        <v>LF00698 Venipuncture Arm</v>
       </c>
       <c r="K223" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L223" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M223" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -10906,16 +10906,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I224" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J224" t="str">
-        <v/>
+        <v>LF00698 Venipuncture Arm</v>
       </c>
       <c r="K224" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L224" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M224" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -10953,16 +10953,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I225" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J225" t="str">
-        <v/>
+        <v>LF00698 Venipuncture Arm</v>
       </c>
       <c r="K225" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L225" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M225" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -11000,16 +11000,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I226" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J226" t="str">
-        <v/>
+        <v>LF00698 Venipuncture Arm</v>
       </c>
       <c r="K226" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L226" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M226" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11047,16 +11047,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I227" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J227" t="str">
-        <v/>
+        <v>LF00698 Venipuncture Arm</v>
       </c>
       <c r="K227" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L227" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M227" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11094,16 +11094,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I228" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J228" t="str">
-        <v/>
+        <v>LF00698 Venipuncture Arm</v>
       </c>
       <c r="K228" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L228" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M228" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11141,16 +11141,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I229" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J229" t="str">
-        <v/>
+        <v>LF00698 Venipuncture Arm</v>
       </c>
       <c r="K229" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L229" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M229" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11188,16 +11188,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I230" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J230" t="str">
-        <v/>
+        <v>LF00698 Venipuncture Arm</v>
       </c>
       <c r="K230" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L230" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M230" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11235,16 +11235,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I231" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J231" t="str">
-        <v/>
+        <v>LF00698 Venipuncture Arm</v>
       </c>
       <c r="K231" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L231" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M231" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11282,16 +11282,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I232" t="str">
-        <v/>
+        <v>Nasco Life/form</v>
       </c>
       <c r="J232" t="str">
-        <v/>
+        <v>LF00698 Venipuncture Arm</v>
       </c>
       <c r="K232" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L232" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M232" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11329,16 +11329,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I233" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J233" t="str">
-        <v/>
+        <v>P100 Wound Care</v>
       </c>
       <c r="K233" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L233" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M233" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11376,16 +11376,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I234" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J234" t="str">
-        <v/>
+        <v>P100 Wound Care</v>
       </c>
       <c r="K234" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L234" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M234" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11423,16 +11423,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I235" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J235" t="str">
-        <v/>
+        <v>P100 Wound Care</v>
       </c>
       <c r="K235" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L235" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M235" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11470,16 +11470,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I236" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J236" t="str">
-        <v/>
+        <v>P100 Wound Care</v>
       </c>
       <c r="K236" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L236" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M236" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11517,16 +11517,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I237" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J237" t="str">
-        <v/>
+        <v>P100 Wound Care</v>
       </c>
       <c r="K237" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L237" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M237" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11564,16 +11564,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I238" t="str">
-        <v/>
+        <v>Koken</v>
       </c>
       <c r="J238" t="str">
-        <v/>
+        <v>M155-Wearable</v>
       </c>
       <c r="K238" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L238" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M238" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11611,16 +11611,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I239" t="str">
-        <v/>
+        <v>Koken</v>
       </c>
       <c r="J239" t="str">
-        <v/>
+        <v>M155-Wearable</v>
       </c>
       <c r="K239" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L239" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M239" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11658,16 +11658,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I240" t="str">
-        <v/>
+        <v>Koken</v>
       </c>
       <c r="J240" t="str">
-        <v/>
+        <v>M155-Wearable</v>
       </c>
       <c r="K240" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L240" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M240" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11705,16 +11705,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I241" t="str">
-        <v/>
+        <v>Koken</v>
       </c>
       <c r="J241" t="str">
-        <v/>
+        <v>M155-Wearable</v>
       </c>
       <c r="K241" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L241" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M241" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11752,16 +11752,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I242" t="str">
-        <v/>
+        <v>Koken</v>
       </c>
       <c r="J242" t="str">
-        <v/>
+        <v>M155-Wearable</v>
       </c>
       <c r="K242" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L242" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M242" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11799,16 +11799,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I243" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J243" t="str">
-        <v/>
+        <v>Nursing Manikin Standard</v>
       </c>
       <c r="K243" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L243" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M243" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11846,16 +11846,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I244" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J244" t="str">
-        <v/>
+        <v>Nursing Manikin Standard</v>
       </c>
       <c r="K244" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L244" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M244" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11893,16 +11893,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I245" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J245" t="str">
-        <v/>
+        <v>Nursing Manikin Standard</v>
       </c>
       <c r="K245" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L245" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M245" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11940,16 +11940,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I246" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J246" t="str">
-        <v/>
+        <v>Nursing Manikin Standard</v>
       </c>
       <c r="K246" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L246" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M246" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -11987,16 +11987,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I247" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J247" t="str">
-        <v/>
+        <v>Nursing Manikin Standard</v>
       </c>
       <c r="K247" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L247" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M247" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -12034,16 +12034,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I248" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J248" t="str">
-        <v/>
+        <v>Nursing Manikin Standard</v>
       </c>
       <c r="K248" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L248" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M248" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -12081,16 +12081,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I249" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J249" t="str">
-        <v/>
+        <v>Nursing Manikin Standard</v>
       </c>
       <c r="K249" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L249" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M249" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -12128,16 +12128,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I250" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J250" t="str">
-        <v/>
+        <v>Nursing Manikin Standard</v>
       </c>
       <c r="K250" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L250" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M250" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -12175,16 +12175,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I251" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J251" t="str">
-        <v/>
+        <v>Nursing Manikin Standard</v>
       </c>
       <c r="K251" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L251" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M251" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -12222,16 +12222,16 @@
         <v>2025-05-01</v>
       </c>
       <c r="I252" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J252" t="str">
-        <v/>
+        <v>Nursing Manikin Standard</v>
       </c>
       <c r="K252" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L252" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="M252" t="str">
         <v>อาคารวิทยบริการ ชั้น 3</v>
@@ -12269,16 +12269,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I253" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J253" t="str">
-        <v/>
+        <v>Anatomical Model Standard</v>
       </c>
       <c r="K253" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L253" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M253" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -12316,16 +12316,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I254" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J254" t="str">
-        <v/>
+        <v>Anatomical Model Standard</v>
       </c>
       <c r="K254" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L254" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M254" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -12363,16 +12363,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I255" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J255" t="str">
-        <v/>
+        <v>Anatomical Model Standard</v>
       </c>
       <c r="K255" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L255" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M255" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -12410,16 +12410,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I256" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J256" t="str">
-        <v/>
+        <v>Anatomical Model Standard</v>
       </c>
       <c r="K256" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L256" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M256" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -12457,16 +12457,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I257" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J257" t="str">
-        <v/>
+        <v>Nursing Manikin Standard</v>
       </c>
       <c r="K257" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L257" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M257" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -12504,16 +12504,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I258" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J258" t="str">
-        <v/>
+        <v>Nursing Manikin Standard</v>
       </c>
       <c r="K258" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L258" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M258" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -12551,16 +12551,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I259" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J259" t="str">
-        <v/>
+        <v>Nursing Manikin Standard</v>
       </c>
       <c r="K259" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L259" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M259" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -12598,16 +12598,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I260" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J260" t="str">
-        <v/>
+        <v>Nursing Manikin Standard</v>
       </c>
       <c r="K260" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L260" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M260" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -12645,16 +12645,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I261" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J261" t="str">
-        <v/>
+        <v>Nursing Manikin Standard</v>
       </c>
       <c r="K261" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L261" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M261" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -12692,16 +12692,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I262" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J262" t="str">
-        <v/>
+        <v>Nursing Manikin Standard</v>
       </c>
       <c r="K262" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L262" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M262" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -12739,16 +12739,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I263" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J263" t="str">
-        <v/>
+        <v>หุ่น ครุภัณฑ์และอุปกรณ์ในห้องปฏิบัติการพยาบาลการเรียนรู้แบบเสมือนจริง</v>
       </c>
       <c r="K263" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L263" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M263" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -12786,16 +12786,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I264" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J264" t="str">
-        <v/>
+        <v>P100 Wound Care</v>
       </c>
       <c r="K264" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L264" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M264" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -12833,16 +12833,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I265" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J265" t="str">
-        <v/>
+        <v>P100 Wound Care</v>
       </c>
       <c r="K265" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L265" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M265" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -12880,16 +12880,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I266" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J266" t="str">
-        <v/>
+        <v>Birthing Simulator</v>
       </c>
       <c r="K266" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L266" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M266" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -12927,16 +12927,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I267" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J267" t="str">
-        <v/>
+        <v>Birthing Simulator</v>
       </c>
       <c r="K267" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L267" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M267" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -12974,16 +12974,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I268" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J268" t="str">
-        <v/>
+        <v>Birthing Simulator</v>
       </c>
       <c r="K268" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L268" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M268" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13021,16 +13021,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I269" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J269" t="str">
-        <v/>
+        <v>Birthing Simulator</v>
       </c>
       <c r="K269" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L269" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M269" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13068,16 +13068,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I270" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J270" t="str">
-        <v/>
+        <v>Birthing Simulator</v>
       </c>
       <c r="K270" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L270" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M270" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13115,16 +13115,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I271" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J271" t="str">
-        <v/>
+        <v>Obstetric Examination Simulator</v>
       </c>
       <c r="K271" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L271" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M271" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13162,16 +13162,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I272" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J272" t="str">
-        <v/>
+        <v>Obstetric Examination Simulator</v>
       </c>
       <c r="K272" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L272" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M272" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13209,16 +13209,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I273" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J273" t="str">
-        <v/>
+        <v>Baby Care Simulator</v>
       </c>
       <c r="K273" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L273" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M273" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13256,16 +13256,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I274" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J274" t="str">
-        <v/>
+        <v>Baby Care Simulator</v>
       </c>
       <c r="K274" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L274" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M274" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13303,16 +13303,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I275" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J275" t="str">
-        <v/>
+        <v>Baby Care Simulator</v>
       </c>
       <c r="K275" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L275" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M275" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13350,16 +13350,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I276" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J276" t="str">
-        <v/>
+        <v>Baby Care Simulator</v>
       </c>
       <c r="K276" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L276" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M276" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13397,16 +13397,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I277" t="str">
-        <v/>
+        <v>3B Scientific</v>
       </c>
       <c r="J277" t="str">
-        <v/>
+        <v>Baby Care Simulator</v>
       </c>
       <c r="K277" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L277" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M277" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13444,16 +13444,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I278" t="str">
-        <v/>
+        <v>Cardionics</v>
       </c>
       <c r="J278" t="str">
-        <v/>
+        <v>718-8804 SAM</v>
       </c>
       <c r="K278" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L278" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M278" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13491,16 +13491,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I279" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J279" t="str">
-        <v/>
+        <v>Home Visit Bag Set</v>
       </c>
       <c r="K279" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L279" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M279" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13538,16 +13538,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I280" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J280" t="str">
-        <v/>
+        <v>Home Visit Bag Set</v>
       </c>
       <c r="K280" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L280" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M280" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13585,16 +13585,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I281" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J281" t="str">
-        <v/>
+        <v>Home Visit Bag Set</v>
       </c>
       <c r="K281" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L281" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M281" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13632,16 +13632,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I282" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J282" t="str">
-        <v/>
+        <v>Hospital Bed Standard</v>
       </c>
       <c r="K282" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L282" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M282" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13679,16 +13679,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I283" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J283" t="str">
-        <v/>
+        <v>มือหมุน 3 ไกร์</v>
       </c>
       <c r="K283" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L283" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M283" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13726,16 +13726,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I284" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J284" t="str">
-        <v/>
+        <v>มือหมุน 3 ไกร์</v>
       </c>
       <c r="K284" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L284" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M284" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13773,16 +13773,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I285" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J285" t="str">
-        <v/>
+        <v>มือหมุน 3 ไกร์</v>
       </c>
       <c r="K285" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L285" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M285" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13820,16 +13820,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I286" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J286" t="str">
-        <v/>
+        <v>มือหมุน 3 ไกร์</v>
       </c>
       <c r="K286" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L286" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M286" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13867,16 +13867,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I287" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J287" t="str">
-        <v/>
+        <v>มือหมุน 3 ไกร์</v>
       </c>
       <c r="K287" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L287" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M287" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13914,16 +13914,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I288" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J288" t="str">
-        <v/>
+        <v>มือหมุน 3 ไกร์</v>
       </c>
       <c r="K288" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L288" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M288" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -13961,16 +13961,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I289" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J289" t="str">
-        <v/>
+        <v>มือหมุน 3 ไกร์</v>
       </c>
       <c r="K289" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L289" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M289" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14008,16 +14008,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I290" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J290" t="str">
-        <v/>
+        <v>มือหมุน 3 ไกร์</v>
       </c>
       <c r="K290" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L290" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M290" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14055,16 +14055,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I291" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J291" t="str">
-        <v/>
+        <v>มือหมุน 3 ไกร์</v>
       </c>
       <c r="K291" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L291" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M291" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14102,16 +14102,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I292" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J292" t="str">
-        <v/>
+        <v>เตียงทำคลอด 2 ตอนปรับระดับ</v>
       </c>
       <c r="K292" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L292" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M292" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14149,16 +14149,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I293" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J293" t="str">
-        <v/>
+        <v>เตียงเด็กอ่อนพร้อมเบาะ</v>
       </c>
       <c r="K293" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L293" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M293" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14196,16 +14196,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I294" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J294" t="str">
-        <v/>
+        <v>เตียงเด็กอ่อนพร้อมเบาะ</v>
       </c>
       <c r="K294" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L294" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M294" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14243,16 +14243,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I295" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J295" t="str">
-        <v/>
+        <v>Bedside Cabinet</v>
       </c>
       <c r="K295" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L295" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M295" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14290,16 +14290,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I296" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J296" t="str">
-        <v/>
+        <v>Bedside Cabinet</v>
       </c>
       <c r="K296" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L296" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M296" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14337,16 +14337,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I297" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J297" t="str">
-        <v/>
+        <v>Bedside Cabinet</v>
       </c>
       <c r="K297" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L297" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M297" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14384,16 +14384,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I298" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J298" t="str">
-        <v/>
+        <v>Bedside Cabinet</v>
       </c>
       <c r="K298" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L298" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M298" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14431,16 +14431,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I299" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J299" t="str">
-        <v/>
+        <v>Bedside Cabinet</v>
       </c>
       <c r="K299" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L299" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M299" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14478,16 +14478,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I300" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J300" t="str">
-        <v/>
+        <v>Bedside Cabinet</v>
       </c>
       <c r="K300" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L300" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M300" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14525,16 +14525,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I301" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J301" t="str">
-        <v/>
+        <v>Bedside Cabinet</v>
       </c>
       <c r="K301" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L301" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M301" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14572,16 +14572,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I302" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J302" t="str">
-        <v/>
+        <v>Bedside Cabinet</v>
       </c>
       <c r="K302" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L302" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M302" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14619,16 +14619,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I303" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J303" t="str">
-        <v/>
+        <v>Overbed Table</v>
       </c>
       <c r="K303" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L303" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M303" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14666,16 +14666,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I304" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J304" t="str">
-        <v/>
+        <v>Overbed Table</v>
       </c>
       <c r="K304" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L304" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M304" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14713,16 +14713,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I305" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J305" t="str">
-        <v/>
+        <v>Overbed Table</v>
       </c>
       <c r="K305" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L305" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M305" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14760,16 +14760,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I306" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J306" t="str">
-        <v/>
+        <v>Overbed Table</v>
       </c>
       <c r="K306" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L306" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M306" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14807,16 +14807,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I307" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J307" t="str">
-        <v/>
+        <v>Overbed Table</v>
       </c>
       <c r="K307" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L307" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M307" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14854,16 +14854,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I308" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J308" t="str">
-        <v/>
+        <v>Overbed Table</v>
       </c>
       <c r="K308" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L308" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M308" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14901,16 +14901,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I309" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J309" t="str">
-        <v/>
+        <v>Overbed Table</v>
       </c>
       <c r="K309" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L309" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M309" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14948,16 +14948,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I310" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J310" t="str">
-        <v/>
+        <v>Overbed Table</v>
       </c>
       <c r="K310" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L310" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M310" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -14995,16 +14995,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I311" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J311" t="str">
-        <v/>
+        <v>Medical Cart Standard</v>
       </c>
       <c r="K311" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L311" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M311" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15042,16 +15042,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I312" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J312" t="str">
-        <v/>
+        <v>Medical Cart Standard</v>
       </c>
       <c r="K312" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L312" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M312" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15089,16 +15089,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I313" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J313" t="str">
-        <v/>
+        <v>Medical Cart Standard</v>
       </c>
       <c r="K313" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L313" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M313" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15136,16 +15136,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I314" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J314" t="str">
-        <v/>
+        <v>Medical Cart Standard</v>
       </c>
       <c r="K314" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L314" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M314" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15183,16 +15183,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I315" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J315" t="str">
-        <v/>
+        <v>Medical Cart Standard</v>
       </c>
       <c r="K315" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L315" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M315" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15230,16 +15230,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I316" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J316" t="str">
-        <v/>
+        <v>Medical Cart Standard</v>
       </c>
       <c r="K316" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L316" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M316" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15277,16 +15277,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I317" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J317" t="str">
-        <v/>
+        <v>Medical Cart Standard</v>
       </c>
       <c r="K317" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L317" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M317" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15324,16 +15324,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I318" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J318" t="str">
-        <v/>
+        <v>Medical Cart Standard</v>
       </c>
       <c r="K318" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L318" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M318" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15371,16 +15371,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I319" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J319" t="str">
-        <v/>
+        <v>Medical Device Standard</v>
       </c>
       <c r="K319" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L319" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M319" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15418,16 +15418,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I320" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J320" t="str">
-        <v/>
+        <v>Stainless Waste Bin</v>
       </c>
       <c r="K320" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L320" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M320" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15465,16 +15465,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I321" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J321" t="str">
-        <v/>
+        <v>Stainless Waste Bin</v>
       </c>
       <c r="K321" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L321" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M321" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15512,16 +15512,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I322" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J322" t="str">
-        <v/>
+        <v>Stainless Waste Bin</v>
       </c>
       <c r="K322" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L322" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M322" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15559,16 +15559,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I323" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J323" t="str">
-        <v/>
+        <v>Stainless Waste Bin</v>
       </c>
       <c r="K323" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L323" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M323" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15606,16 +15606,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I324" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J324" t="str">
-        <v/>
+        <v>Stainless Waste Bin</v>
       </c>
       <c r="K324" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L324" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M324" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15653,16 +15653,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I325" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J325" t="str">
-        <v/>
+        <v>Stainless Waste Bin</v>
       </c>
       <c r="K325" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L325" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M325" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15700,16 +15700,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I326" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J326" t="str">
-        <v/>
+        <v>Stainless Waste Bin</v>
       </c>
       <c r="K326" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L326" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M326" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15747,16 +15747,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I327" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J327" t="str">
-        <v/>
+        <v>Stainless Waste Bin</v>
       </c>
       <c r="K327" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L327" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M327" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15794,16 +15794,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I328" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J328" t="str">
-        <v/>
+        <v>Medical Device Standard</v>
       </c>
       <c r="K328" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L328" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M328" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15841,16 +15841,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I329" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J329" t="str">
-        <v/>
+        <v>Medical Device Standard</v>
       </c>
       <c r="K329" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L329" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M329" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15888,16 +15888,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I330" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J330" t="str">
-        <v/>
+        <v>Mercurial Sphygmomanometer</v>
       </c>
       <c r="K330" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L330" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M330" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15935,16 +15935,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I331" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J331" t="str">
-        <v/>
+        <v>Mercurial Sphygmomanometer</v>
       </c>
       <c r="K331" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L331" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M331" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -15982,16 +15982,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I332" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J332" t="str">
-        <v/>
+        <v>Mercurial Sphygmomanometer</v>
       </c>
       <c r="K332" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L332" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M332" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16029,16 +16029,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I333" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J333" t="str">
-        <v/>
+        <v>Mercurial Sphygmomanometer</v>
       </c>
       <c r="K333" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L333" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M333" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16076,16 +16076,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I334" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J334" t="str">
-        <v/>
+        <v>Mercurial Sphygmomanometer</v>
       </c>
       <c r="K334" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L334" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M334" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16123,16 +16123,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I335" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J335" t="str">
-        <v/>
+        <v>Digital BP Monitor</v>
       </c>
       <c r="K335" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L335" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M335" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16170,16 +16170,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I336" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J336" t="str">
-        <v/>
+        <v>Digital BP Monitor</v>
       </c>
       <c r="K336" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L336" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M336" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16217,16 +16217,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I337" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J337" t="str">
-        <v/>
+        <v>Digital BP Monitor</v>
       </c>
       <c r="K337" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L337" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M337" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16264,16 +16264,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I338" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J338" t="str">
-        <v/>
+        <v>Digital BP Monitor</v>
       </c>
       <c r="K338" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L338" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M338" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16311,16 +16311,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I339" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J339" t="str">
-        <v/>
+        <v>Digital BP Monitor</v>
       </c>
       <c r="K339" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L339" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M339" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16358,16 +16358,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I340" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J340" t="str">
-        <v/>
+        <v>Digital BP Monitor</v>
       </c>
       <c r="K340" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L340" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M340" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16405,16 +16405,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I341" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J341" t="str">
-        <v/>
+        <v>Digital BP Monitor</v>
       </c>
       <c r="K341" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L341" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M341" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16452,16 +16452,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I342" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J342" t="str">
-        <v/>
+        <v>Digital BP Monitor</v>
       </c>
       <c r="K342" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L342" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M342" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16499,16 +16499,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I343" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J343" t="str">
-        <v/>
+        <v>Digital BP Monitor</v>
       </c>
       <c r="K343" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L343" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M343" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16546,16 +16546,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I344" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J344" t="str">
-        <v/>
+        <v>Digital BP Monitor</v>
       </c>
       <c r="K344" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L344" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M344" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16593,16 +16593,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I345" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J345" t="str">
-        <v/>
+        <v>Medical Device Standard</v>
       </c>
       <c r="K345" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L345" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M345" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16640,16 +16640,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I346" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J346" t="str">
-        <v/>
+        <v>Medical Device Standard</v>
       </c>
       <c r="K346" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L346" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M346" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16687,16 +16687,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I347" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J347" t="str">
-        <v/>
+        <v>Medical Device Standard</v>
       </c>
       <c r="K347" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L347" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M347" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16734,16 +16734,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I348" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J348" t="str">
-        <v/>
+        <v>DT-Otoscope</v>
       </c>
       <c r="K348" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L348" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M348" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16781,16 +16781,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I349" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J349" t="str">
-        <v/>
+        <v>DT-Ophthalmoscope</v>
       </c>
       <c r="K349" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L349" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M349" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16828,16 +16828,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I350" t="str">
-        <v/>
+        <v>KaWe</v>
       </c>
       <c r="J350" t="str">
-        <v/>
+        <v>Laryngoscope Set</v>
       </c>
       <c r="K350" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L350" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M350" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16875,16 +16875,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I351" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J351" t="str">
-        <v/>
+        <v>Patient Transfer Slide</v>
       </c>
       <c r="K351" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L351" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M351" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16922,16 +16922,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I352" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J352" t="str">
-        <v/>
+        <v>Patient Transfer Slide</v>
       </c>
       <c r="K352" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L352" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M352" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -16969,16 +16969,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I353" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J353" t="str">
-        <v/>
+        <v>Medical Device Standard</v>
       </c>
       <c r="K353" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L353" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M353" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17016,16 +17016,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I354" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J354" t="str">
-        <v/>
+        <v>Medical Device Standard</v>
       </c>
       <c r="K354" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L354" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M354" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17063,16 +17063,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I355" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J355" t="str">
-        <v/>
+        <v>Medical Device Standard</v>
       </c>
       <c r="K355" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L355" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M355" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17110,16 +17110,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I356" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J356" t="str">
-        <v/>
+        <v>Medical Device Standard</v>
       </c>
       <c r="K356" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L356" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M356" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17157,16 +17157,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I357" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J357" t="str">
-        <v/>
+        <v>Medical Device Standard</v>
       </c>
       <c r="K357" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L357" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M357" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17204,16 +17204,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I358" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J358" t="str">
-        <v/>
+        <v>Medical Device Standard</v>
       </c>
       <c r="K358" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L358" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M358" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17251,16 +17251,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I359" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J359" t="str">
-        <v/>
+        <v>Medical Device Standard</v>
       </c>
       <c r="K359" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L359" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M359" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17298,16 +17298,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I360" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J360" t="str">
-        <v/>
+        <v>Medical Device Standard</v>
       </c>
       <c r="K360" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L360" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M360" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17345,16 +17345,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I361" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J361" t="str">
-        <v/>
+        <v>Medical Device Standard</v>
       </c>
       <c r="K361" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L361" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M361" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17392,16 +17392,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I362" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J362" t="str">
-        <v/>
+        <v>Medical Device Standard</v>
       </c>
       <c r="K362" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L362" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M362" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17439,16 +17439,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I363" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J363" t="str">
-        <v/>
+        <v>Massage Chair</v>
       </c>
       <c r="K363" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L363" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M363" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17486,16 +17486,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I364" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J364" t="str">
-        <v/>
+        <v>Massage Chair</v>
       </c>
       <c r="K364" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L364" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M364" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17533,16 +17533,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I365" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J365" t="str">
-        <v/>
+        <v>Medical Device Standard</v>
       </c>
       <c r="K365" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L365" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M365" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17580,16 +17580,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I366" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J366" t="str">
-        <v/>
+        <v>Medical Device Standard</v>
       </c>
       <c r="K366" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L366" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M366" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17627,16 +17627,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I367" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J367" t="str">
-        <v/>
+        <v>IV Stand Stainless</v>
       </c>
       <c r="K367" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L367" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M367" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17674,16 +17674,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I368" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J368" t="str">
-        <v/>
+        <v>IV Stand Stainless</v>
       </c>
       <c r="K368" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L368" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M368" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17721,16 +17721,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I369" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J369" t="str">
-        <v/>
+        <v>IV Stand Stainless</v>
       </c>
       <c r="K369" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L369" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M369" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17768,16 +17768,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I370" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J370" t="str">
-        <v/>
+        <v>IV Stand Stainless</v>
       </c>
       <c r="K370" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L370" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M370" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17815,16 +17815,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I371" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J371" t="str">
-        <v/>
+        <v>IV Stand Stainless</v>
       </c>
       <c r="K371" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L371" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M371" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17862,16 +17862,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I372" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J372" t="str">
-        <v/>
+        <v>IV Stand Stainless</v>
       </c>
       <c r="K372" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L372" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M372" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17909,16 +17909,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I373" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J373" t="str">
-        <v/>
+        <v>IV Stand Stainless</v>
       </c>
       <c r="K373" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L373" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M373" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -17956,16 +17956,16 @@
         <v>2024-06-28</v>
       </c>
       <c r="I374" t="str">
-        <v/>
+        <v>Upright Simulation</v>
       </c>
       <c r="J374" t="str">
-        <v/>
+        <v>IV Stand Stainless</v>
       </c>
       <c r="K374" t="str">
-        <v/>
+        <v>บริษัท อัพไรท์ ซิมมูเลชั่น  จำกัด</v>
       </c>
       <c r="L374" t="str">
-        <v/>
+        <v>2025-06-28</v>
       </c>
       <c r="M374" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
